--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -9,13 +9,14 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng quan" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 07-10-2026" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục tối ưu" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đối chiếu 18 mẫu" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 08-10-2026" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục tối ưu" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đối chiếu 18 mẫu" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -2100,13 +2101,13 @@
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
-    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="B53:G53"/>
     <mergeCell ref="B48:G48"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
@@ -3170,6 +3171,1183 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G62"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" customWidth="1" style="27" min="1" max="1"/>
+    <col width="66" customWidth="1" style="27" min="2" max="2"/>
+    <col width="24" customWidth="1" style="27" min="3" max="3"/>
+    <col width="8" customWidth="1" style="27" min="4" max="4"/>
+    <col width="11" customWidth="1" style="27" min="5" max="5"/>
+    <col width="16" customWidth="1" style="27" min="6" max="6"/>
+    <col width="34" customWidth="1" style="27" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="57" t="inlineStr">
+        <is>
+          <t>TIẾN ĐỘ ĐỢT TỐI ƯU TÁC TỬ — chốt ngày 08/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="58" t="inlineStr">
+        <is>
+          <t>Mỗi dòng 'Xong' đều có: mục DEV-LOG tra lại được · số ca kiểm trước→sau · một con số đo trên dữ liệu thật · phần còn nợ. Cột chi tiết nằm ở sheet “Danh mục tối ưu”, cột T–Y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="59" t="inlineStr">
+        <is>
+          <t>Tổng quan</t>
+        </is>
+      </c>
+      <c r="B4" s="59" t="inlineStr">
+        <is>
+          <t>Số việc</t>
+        </is>
+      </c>
+      <c r="C4" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>Xong (đã gộp vào main, đã đẩy)</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="n">
+        <v>16</v>
+      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>16 việc đầu của Giai đoạn 1, theo đúng thứ tự # của kế hoạch</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="60" t="inlineStr">
+        <is>
+          <t>Đang làm (chưa commit)</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="61" t="inlineStr">
+        <is>
+          <t>không việc nào đang dở — M3-13 đã chốt và gộp main sáng 08/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="60" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="n">
+        <v>90</v>
+      </c>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>90 việc còn lại trong 106</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="62" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B8" s="62" t="n">
+        <v>106</v>
+      </c>
+      <c r="C8" s="61" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>Phép đo của cả đợt</t>
+        </is>
+      </c>
+      <c r="B10" s="59" t="inlineStr">
+        <is>
+          <t>Trước (06/10)</t>
+        </is>
+      </c>
+      <c r="C10" s="59" t="inlineStr">
+        <is>
+          <t>Sau (08/10)</t>
+        </is>
+      </c>
+      <c r="D10" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị Python (pytest -q)</t>
+        </is>
+      </c>
+      <c r="B11" s="63" t="inlineStr">
+        <is>
+          <t>1 610</t>
+        </is>
+      </c>
+      <c r="C11" s="63" t="inlineStr">
+        <is>
+          <t>1 773</t>
+        </is>
+      </c>
+      <c r="D11" s="63" t="inlineStr">
+        <is>
+          <t>+163 ca so với 06/10; không ca cũ nào đỏ ở bất kỳ bước nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị giao diện (swift test)</t>
+        </is>
+      </c>
+      <c r="B12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="inlineStr">
+        <is>
+          <t>không nhiệm vụ nào đụng ui/ — kiểu khối A2.2 dùng “table”, Swift đã dựng được</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>kiem_tai_lieu.py</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="C13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ LỆCH CHẮC CHẮN cả hai lượt. Hôm nay nó bắt đúng chuyện cần bắt: hai công cụ mới làm README lệch số công cụ 127 → 129, và số 'cần đọc lại' nhảy 11 → 15 → về 11 sau khi sửa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>thu_sch.py (cờ schematic bật)</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="C14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="D14" s="63" t="inlineStr">
+        <is>
+          <t>chạy ở M3-03 và M3-04, không tụt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t>Mục DEV-LOG mới</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330 → DEV-345</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="inlineStr">
+        <is>
+          <t>16 mục, mỗi việc một mục</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="63" t="inlineStr">
+        <is>
+          <t>Cờ tính năng mới</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>1 (schematic)</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="63" t="inlineStr">
+        <is>
+          <t>6 cờ mới, TẤT CẢ mặc định TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="63" t="inlineStr">
+        <is>
+          <t>Mã lỗi mới</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>E4031 · E4032 · E6012 · E4033</t>
+        </is>
+      </c>
+      <c r="D17" s="63" t="inlineStr">
+        <is>
+          <t>E4033 của M3-18 KHÔNG lấy theo kế hoạch: tôi chọn E4031 trước, rồi grep thấy loop.py:1085 đã dùng E4031 cho 'chưa chạy, vì chờ cổng'</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="59" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="C19" s="59" t="inlineStr">
+        <is>
+          <t>Mảng</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="E19" s="59" t="inlineStr">
+        <is>
+          <t>DEV-LOG</t>
+        </is>
+      </c>
+      <c r="F19" s="59" t="inlineStr">
+        <is>
+          <t>Ca kiểm</t>
+        </is>
+      </c>
+      <c r="G19" s="59" t="inlineStr">
+        <is>
+          <t>Cờ mặc định</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="63" t="inlineStr">
+        <is>
+          <t>M1-01</t>
+        </is>
+      </c>
+      <c r="C20" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D20" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E20" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330</t>
+        </is>
+      </c>
+      <c r="F20" s="63" t="inlineStr">
+        <is>
+          <t>105/309 phiên thật có lịch sử tự mâu thuẫn — 255 chỗ (156 kết quả thứ hai cùng id, 74 message chen giữa, 24 kết quả lạc lượt, 1 lời gọi không kết quả)</t>
+        </is>
+      </c>
+      <c r="G20" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="63" t="inlineStr">
+        <is>
+          <t>M1-02</t>
+        </is>
+      </c>
+      <c r="C21" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D21" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E21" s="63" t="inlineStr">
+        <is>
+          <t>DEV-331</t>
+        </is>
+      </c>
+      <c r="F21" s="63" t="inlineStr">
+        <is>
+          <t>lược đồ công cụ thật: 25 869 token/lời gọi (trần tool_schema=4000 chưa dòng mã nào đọc). Cờ bật: 4 475 token, giảm 82,7 %; 73 → 18 công cụ</t>
+        </is>
+      </c>
+      <c r="G21" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="63" t="inlineStr">
+        <is>
+          <t>M1-03</t>
+        </is>
+      </c>
+      <c r="C22" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D22" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E22" s="63" t="inlineStr">
+        <is>
+          <t>DEV-332</t>
+        </is>
+      </c>
+      <c r="F22" s="63" t="inlineStr">
+        <is>
+          <t>1 822 lời gọi của tác tử con trong 26 phiên thật, 0 lần qua lớp luật. Toàn công cụ đọc trừ một build.compile — lỗ hổng chưa bị bước vào, không phải được canh</t>
+        </is>
+      </c>
+      <c r="G22" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="63" t="inlineStr">
+        <is>
+          <t>M2-01</t>
+        </is>
+      </c>
+      <c r="C23" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D23" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E23" s="63" t="inlineStr">
+        <is>
+          <t>DEV-333</t>
+        </is>
+      </c>
+      <c r="F23" s="63" t="inlineStr">
+        <is>
+          <t>kịch bản 3 REQ + 3 phương án + 3 tiêu chí + 3 tệp: sửa MỘT REQ làm 9 hiện vật STALE → còn 3. Phép đo đầu ra 6→2 vì bị hàng rào E4020 chặn, đã sửa kịch bản đo</t>
+        </is>
+      </c>
+      <c r="G23" s="63" t="inlineStr">
+        <is>
+          <t>TRUY_VET — TẮT (phần nền chạy cả khi tắt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>M2-02</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D24" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E24" s="63" t="inlineStr">
+        <is>
+          <t>DEV-334</t>
+        </is>
+      </c>
+      <c r="F24" s="63" t="inlineStr">
+        <is>
+          <t>63 kho thật: 5/37 REQ có ít nhất một phép đo; 27 chưa có phương án nào nhận; 0 REQ đi hết chuỗi. Cột 'Mã nguồn' trống ở MỌI dự án vì hien_thuc_req vừa mới tồn tại</t>
+        </is>
+      </c>
+      <c r="G24" s="63" t="inlineStr">
+        <is>
+          <t>REQ_PHU — TẮT (khối A2.2 trên tab không phụ thuộc cờ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="63" t="inlineStr">
+        <is>
+          <t>M2-03</t>
+        </is>
+      </c>
+      <c r="C25" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D25" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E25" s="63" t="inlineStr">
+        <is>
+          <t>DEV-335</t>
+        </is>
+      </c>
+      <c r="F25" s="63" t="inlineStr">
+        <is>
+          <t>37 REQ thật: 25 sạch (67 %), 11 thiếu tiêu chí đo được, 2 có từ mơ hồ. Lần đo đầu ra 3 từ mơ hồ, một là kêu oan ('ít nhất 2 lần' là mức đo được) — đã vá</t>
+        </is>
+      </c>
+      <c r="G25" s="63" t="inlineStr">
+        <is>
+          <t>REQ_CHAT_LUONG — TẮT (module yeu_cau.py luôn có)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="63" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="63" t="inlineStr">
+        <is>
+          <t>M2-06</t>
+        </is>
+      </c>
+      <c r="C26" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D26" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E26" s="63" t="inlineStr">
+        <is>
+          <t>DEV-336</t>
+        </is>
+      </c>
+      <c r="F26" s="63" t="inlineStr">
+        <is>
+          <t>sổ cái thật: 26 lần đánh dấu 'xong' ngay sau một lần ghi mã, 19 lần (73 %) không có phép kiểm nào đạt ở giữa. Phép đo đầu ở mức dự án ra 0 — đúng nhưng đo sai câu hỏi</t>
+        </is>
+      </c>
+      <c r="G26" s="63" t="inlineStr">
+        <is>
+          <t>KE_HOACH_CONG_KIEM — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="63" t="inlineStr">
+        <is>
+          <t>M2-08</t>
+        </is>
+      </c>
+      <c r="C27" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D27" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E27" s="63" t="inlineStr">
+        <is>
+          <t>DEV-337</t>
+        </is>
+      </c>
+      <c r="F27" s="63" t="inlineStr">
+        <is>
+          <t>185 tệp .c thật: 1 758 → 1 786 hàm thấy được (+28 hàm trước đây VÔ HÌNH: 8 ngắt + 20 bị regex tham lam nuốt). 78 hàm nay gắn nhãn 'isr', 70 trong đó vốn đã có trong danh sách</t>
+        </is>
+      </c>
+      <c r="G27" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="63" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="63" t="inlineStr">
+        <is>
+          <t>M3-01</t>
+        </is>
+      </c>
+      <c r="C28" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D28" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E28" s="63" t="inlineStr">
+        <is>
+          <t>DEV-338</t>
+        </is>
+      </c>
+      <c r="F28" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mô hình mạch thật — và lý do đáng hơn con số: 3 kho CÓ Fact v_max thì KHÔNG có mô hình mạch, 5 kho có mạch thì không có Fact ấy; thêm nữa Fact dùng chủ thể chip:X mà ERC không tra tiền tố đó</t>
+        </is>
+      </c>
+      <c r="G28" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="63" t="inlineStr">
+        <is>
+          <t>M3-03</t>
+        </is>
+      </c>
+      <c r="C29" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D29" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E29" s="63" t="inlineStr">
+        <is>
+          <t>DEV-339</t>
+        </is>
+      </c>
+      <c r="F29" s="63" t="inlineStr">
+        <is>
+          <t>8 phát hiện trên 5 mạch thật (6 nguon_khong_cap + 2 net_mot_chan), trong đó net clock I2C nối đúng một chân. SÁU trong tám là 'mô hình chưa khai' chứ không phải 'mạch sai'. robot-canbang: 107 Port lá, KHÔNG Port nào là power_out</t>
+        </is>
+      </c>
+      <c r="G29" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="63" t="n">
+        <v>11</v>
+      </c>
+      <c r="B30" s="63" t="inlineStr">
+        <is>
+          <t>M3-04</t>
+        </is>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D30" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E30" s="63" t="inlineStr">
+        <is>
+          <t>DEV-340</t>
+        </is>
+      </c>
+      <c r="F30" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mạch thật — và đây là con số ĐÚNG (hai lỗi này catastrophic, không bo nào sống tới lúc lưu kho). Đã CẤY hai bộ cấp vào bản sao kho robot-canbang để chứng minh luật sống: nổ đúng 1 blocker trên net +5V thật</t>
+        </is>
+      </c>
+      <c r="G30" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="B31" s="63" t="inlineStr">
+        <is>
+          <t>M3-07</t>
+        </is>
+      </c>
+      <c r="C31" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D31" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E31" s="63" t="inlineStr">
+        <is>
+          <t>DEV-341</t>
+        </is>
+      </c>
+      <c r="F31" s="63" t="inlineStr">
+        <is>
+          <t>Fact tới được ERC: 5 → 17 (+12). Ba kho có Fact datasheet thì TOÀN BỘ mang chủ thể chip:, tức trước đó không một Fact nào tới được ERC. Độ phủ 5 mạch thật nay đọc được</t>
+        </is>
+      </c>
+      <c r="G31" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="63" t="n">
+        <v>13</v>
+      </c>
+      <c r="B32" s="63" t="inlineStr">
+        <is>
+          <t>M3-10</t>
+        </is>
+      </c>
+      <c r="C32" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D32" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E32" s="63" t="inlineStr">
+        <is>
+          <t>DEV-342</t>
+        </is>
+      </c>
+      <c r="F32" s="63" t="inlineStr">
+        <is>
+          <t>chi phí đo thật: mạch lớn nhất trong kho 187 nút → ERC 7,6 ms mỗi lần ghi. Trần 2000 nút, vượt thì NÓI RA chứ không im lặng bỏ qua</t>
+        </is>
+      </c>
+      <c r="G32" s="63" t="inlineStr">
+        <is>
+          <t>ERC_TU_DONG — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="B33" s="63" t="inlineStr">
+        <is>
+          <t>M3-12</t>
+        </is>
+      </c>
+      <c r="C33" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D33" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E33" s="63" t="inlineStr">
+        <is>
+          <t>DEV-343</t>
+        </is>
+      </c>
+      <c r="F33" s="63" t="inlineStr">
+        <is>
+          <t>846 bản ghi mô phỏng thật: regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 (testbench dự án in 'KET QUA: PASS' — nhãn đứng TRƯỚC từ khoá). Nới đúng một chỗ → 846/846 khớp, vẫn bắt đủ bốn ca PASS giả</t>
+        </is>
+      </c>
+      <c r="G33" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="64" t="n">
+        <v>15</v>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>M3-13</t>
+        </is>
+      </c>
+      <c r="C34" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D34" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E34" s="64" t="inlineStr">
+        <is>
+          <t>DEV-344</t>
+        </is>
+      </c>
+      <c r="F34" s="64" t="inlineStr">
+        <is>
+          <t>testbench Verilog THẬT của bài 3: tb_pcpi_dot4 1/1, tb_pcpi_mac 1/1, tb_pcpi_vmini không đo được (tb gọi bản bram HAI CỔNG đã bị bỏ 02/10) — mẫu số là TỆP, không phải phép phá</t>
+        </is>
+      </c>
+      <c r="G34" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="64" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B35" s="64" t="inlineStr">
+        <is>
+          <t>M3-18</t>
+        </is>
+      </c>
+      <c r="C35" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D35" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E35" s="64" t="inlineStr">
+        <is>
+          <t>DEV-345</t>
+        </is>
+      </c>
+      <c r="F35" s="64" t="inlineStr">
+        <is>
+          <t>6 cặp (mạng cổng, .cst) thật → 1 chỗ CHẶN: blinky của riscv-tn20k-b dựng bitstream 4,6 MB với chân đồng hồ do nextpnr tự chọn (rơi đúng chân 4 — bằng may). Cả 7 tệp .cst thật đọc hết, 0 lỗi cú pháp</t>
+        </is>
+      </c>
+      <c r="G35" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="59" t="inlineStr">
+        <is>
+          <t>Việc còn MỞ (ngoài 90 việc chưa làm)</t>
+        </is>
+      </c>
+      <c r="B37" s="59" t="inlineStr">
+        <is>
+          <t>Vì sao còn mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="63" t="inlineStr">
+        <is>
+          <t>Sáu cờ mới đều còn TẮT</t>
+        </is>
+      </c>
+      <c r="B38" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU · TRUY_VET · REQ_PHU · REQ_CHAT_LUONG · KE_HOACH_CONG_KIEM · ERC_TU_DONG. Cả sáu đổi thứ Agent nhìn thấy hoặc đọc mỗi lượt, nên chỉ bộ 76 ca chạy HAI chế độ mới nói được chúng làm Agent khá hơn hay tệ hơn — bộ ấy tốn tiền mô hình nên chưa chạy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="63" t="inlineStr">
+        <is>
+          <t>kiem_cap_goi_tra() chưa thành hàng rào</t>
+        </is>
+      </c>
+      <c r="B39" s="63" t="inlineStr">
+        <is>
+          <t>Soát được mọi phiên đã lưu, nhưng chưa hook nào gọi nó tự động — bắt được chuyện cũ, chưa chặn được chuyện mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="63" t="inlineStr">
+        <is>
+          <t>Luật ERC quá áp chưa nổ trên dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="B40" s="63" t="inlineStr">
+        <is>
+          <t>Đường dẫn đã thông ở M3-07, nhưng ba kho có Fact điện áp thì không có mô hình mạch, và ngược lại. Phải chờ một dự án có cả hai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="63" t="inlineStr">
+        <is>
+          <t>Cột “Mã nguồn” của ma trận truy vết trống ở mọi dự án</t>
+        </is>
+      </c>
+      <c r="B41" s="63" t="inlineStr">
+        <is>
+          <t>Nó đọc hien_thuc_req — trường vừa mới tồn tại, chưa tệp nào trên đĩa từng khai. Nên “chưa hiện thực” ở đó nghĩa là “chưa ai KHAI”, không phải “chưa ai viết”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="63" t="inlineStr">
+        <is>
+          <t>Lỗi _go_dau trong src/eide/tools/design.py</t>
+        </is>
+      </c>
+      <c r="B42" s="63" t="inlineStr">
+        <is>
+          <t>Viết .replace('d','d') nên 'ổn định' và 'ON DINH' không khớp nhau. Hàm ấy đang dùng cho một phép kiểm an toàn (người có thật sự chọn không). Tìm thấy ở M2-03, CHƯA sửa vì ngoài phạm vi — cần bộ ca kiểm riêng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="63" t="inlineStr">
+        <is>
+          <t>subagent req-critic (bước 4 của M2-03)</t>
+        </is>
+      </c>
+      <c r="B43" s="63" t="inlineStr">
+        <is>
+          <t>Kế hoạch ghi “tuỳ chọn, gộp M2-13”. Chưa làm, đúng theo kế hoạch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="63" t="inlineStr">
+        <is>
+          <t>Hai luật kiểm chân FPGA chưa có dữ liệu để nổ</t>
+        </is>
+      </c>
+      <c r="B44" s="63" t="inlineStr">
+        <is>
+          <t>chan_lech_kit và io_type_lech_bank cần Fact chân kit. Không kho nào trong repo có Fact pin:tangnano20k.* hay khoá vccio — nên hôm nay chỉ 3 trong 5 luật của M3-18 kết luận được gì trên dữ liệu thật. Cùng hình dạng với luật ERC quá áp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="63" t="inlineStr">
+        <is>
+          <t>Một bitstream cũ đã dựng với chân đồng hồ tự chọn</t>
+        </is>
+      </c>
+      <c r="B45" s="63" t="inlineStr">
+        <is>
+          <t>blinky của du-lieu/riscv-tn20k-b — xem DEV-345 và README §8. Không sửa hiện vật cũ: đó là dữ liệu của những lượt đo đã chốt. Từ nay phép kiểm chặn trước nextpnr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="63" t="inlineStr">
+        <is>
+          <t>Hai công cụ mới nhất chưa lượt Agent nào GỌI</t>
+        </is>
+      </c>
+      <c r="B46" s="63" t="inlineStr">
+        <is>
+          <t>hdl.sensitivity và hdl.constraints_check: mã của cả hai đã chạy trên hiện vật thật, nhưng đó là tôi gọi hàm, không phải tác tử gọi công cụ. README §8 đếm cả hai vào phần chưa dùng thật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="59" t="inlineStr">
+        <is>
+          <t>Lỗi tìm thấy trong CHÍNH PHÉP ĐO của tôi</t>
+        </is>
+      </c>
+      <c r="B48" s="59" t="inlineStr">
+        <is>
+          <t>Lộ ra ở đâu</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="63" t="inlineStr">
+        <is>
+          <t>Kịch bản đo bị hàng rào của sản phẩm chặn (ghi tệp chưa đọc, E4020) và trả về một con số hợp lý thay vì nổ — 6→2 trông đẹp y như 9→3 đúng</t>
+        </is>
+      </c>
+      <c r="B49" s="63" t="inlineStr">
+        <is>
+          <t>M2-01 · DEV-333</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm dựng trên điều tôi tự nhớ sai: “thiết” bỏ dấu KHÔNG chứa “it”; chỗ va thật là bit/unit/init/exit</t>
+        </is>
+      </c>
+      <c r="B50" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá dài ĐÚNG BẰNG mã gốc (0.6 → 0.0) nên __pycache__ cũ còn hiệu lực — phép đo chạy mã khác với mã trong tệp</t>
+        </is>
+      </c>
+      <c r="B51" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="63" t="inlineStr">
+        <is>
+          <t>Phép đo trả lời ĐÚNG một câu hỏi KHÁC: đếm ở mức dự án ra 0 chỗ cần chặn; câu phải hỏi là “lần ghi NÀY đã được kiểm chưa” → 19/26</t>
+        </is>
+      </c>
+      <c r="B52" s="63" t="inlineStr">
+        <is>
+          <t>M2-06 · DEV-336</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm RỖNG: dàn dựng không có net đất nào, nên nó xanh cả khi tôi bỏ hẳn phép bỏ qua net đất</t>
+        </is>
+      </c>
+      <c r="B53" s="63" t="inlineStr">
+        <is>
+          <t>M3-01 · DEV-338</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="63" t="inlineStr">
+        <is>
+          <t>Hai phép phá chỉ ra THIẾT KẾ sai, không chỉ ca kiểm yếu (miễn net đất quá rộng; nhánh iout_max chưa ca nào chạm tới)</t>
+        </is>
+      </c>
+      <c r="B54" s="63" t="inlineStr">
+        <is>
+          <t>M3-03 · DEV-339</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá của tôi cũng SAI, và ca âm xanh vì lý do khác — hai cái sai che nhau</t>
+        </is>
+      </c>
+      <c r="B55" s="63" t="inlineStr">
+        <is>
+          <t>M3-07 · DEV-341</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm đo chính câu lệnh của mình (đặt bộ đếm = 3 rồi khẳng định nó khác rỗng, trong khi thực tế nó rỗng)</t>
+        </is>
+      </c>
+      <c r="B56" s="63" t="inlineStr">
+        <is>
+          <t>M3-10 · DEV-342</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="63" t="inlineStr">
+        <is>
+          <t>Regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 bản ghi thật; và ba ca kiểm xanh vì lý do sai (tệp giả dùng $4 thay $3; “FAILED” chứa “FAIL”)</t>
+        </is>
+      </c>
+      <c r="B57" s="63" t="inlineStr">
+        <is>
+          <t>M3-12 · DEV-343</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="63" t="inlineStr">
+        <is>
+          <t>"Phá lại thì đỏ 6/6" sai về TẬP, không sai về số: sáu phép phá ấy chọn đúng sáu chỗ đã có ca canh. Phá bằng tập rộng hơn ra 7/9.</t>
+        </is>
+      </c>
+      <c r="B58" s="63" t="inlineStr">
+        <is>
+          <t>M3-13 · DEV-344</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="63" t="inlineStr">
+        <is>
+          <t>409 'blocker' gần như toàn bộ từ một cặp vô nghĩa (mạng cổng của lõi CPU tổng hợp riêng, không bao giờ đem đặt-đi dây). Con số thật là 1.</t>
+        </is>
+      </c>
+      <c r="B59" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="63" t="inlineStr">
+        <is>
+          <t>Phép quét tệp .cst thật chỉ thu 4 trong 7 tệp mà ca kiểm vẫn xanh — câu 'mọi tệp .cst thật đều đọc được' nói về phần phép quét chạm tới.</t>
+        </is>
+      </c>
+      <c r="B60" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="63" t="inlineStr">
+        <is>
+          <t>Một ca kiểm và một phép phá nhắm hai NHÁNH khác nhau, nên ca mới xanh mà phép phá vẫn LỌT. Mất một lượt mới thấy.</t>
+        </is>
+      </c>
+      <c r="B61" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="63" t="n"/>
+      <c r="B62" s="63" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8473,7 +9651,7 @@
       </c>
       <c r="Q58" s="51" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Xong</t>
         </is>
       </c>
       <c r="R58" s="47" t="inlineStr">
@@ -8484,22 +9662,22 @@
       <c r="S58" s="47" t="n"/>
       <c r="T58" s="52" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="U58" s="52" t="inlineStr">
         <is>
-          <t>chưa ghi</t>
+          <t>DEV-344</t>
         </is>
       </c>
       <c r="V58" s="52" t="inlineStr">
         <is>
-          <t>chưa chạy toàn bộ</t>
+          <t>1732 → 1744 (+12)</t>
         </is>
       </c>
       <c r="W58" s="52" t="inlineStr">
         <is>
-          <t>testbench Verilog THẬT của bài 3 (lõi RISC-V): pcpi_dot4 bắt 1/1, pcpi_mac bắt 1/1 (phép phá 'đảo điều kiện if' làm bộ kiểm đỏ); pcpi_vmini CHƯA đo được — tb cần thêm mô-đun ram ngoài phần nó tự include</t>
+          <t>testbench Verilog THẬT của bài 3 (lõi RISC-V), đo lại qua chính đường mã của công cụ trên một BẢN SAO của docs/riscv-tn20k: tb_pcpi_dot4 1/1 (đảo if, 3 chỗ → bộ kiểm ĐỎ), tb_pcpi_mac 1/1 (đảo if, 2 chỗ). tb_pcpi_vmini KHÔNG đo được — và cổng 'bộ kiểm phải XANH trước khi đo' chặn đúng: tb tạo thực thể bram với 5 cổng b_* của bản HAI CỔNG, mà rtl/bram.v đã về một cổng ngày 02/10/2026. Testbench nấc 3c không dịch nổi từ hôm ấy, trong khi bai3/NGOAI-PHAM-VI.md vẫn ghi 'độ nhạy 7/7'.</t>
         </is>
       </c>
       <c r="X58" s="52" t="inlineStr">
@@ -8509,7 +9687,7 @@
       </c>
       <c r="Y58" s="52" t="inlineStr">
         <is>
-          <t>ĐANG DỞ trên nhánh toi-uu/M3-13, CHƯA commit: đã có PHEP_VERILOG, do_do_nhay_hdl(), công cụ hdl.sensitivity, nhãn do_bang='tu_khai' và dòng 'tự khai' trên khối A8.0; 6 phép phá đều đỏ; CÒN LẠI: chạy pytest toàn bộ, kiem_tai_lieu, ghi DEV-LOG, commit</t>
+          <t>MẪU SỐ LÀ TỆP, không phải phép phá: do_do_nhay break ngay khi một phép làm bộ kiểm đỏ, nên '1/1' nghĩa là 1 trong 1 TỆP RTL — không so được với '7/7 phép' của bản đo tay. Nhãn A8.0 và note_vi đã sửa theo do_bang. · 'phá lại thì đỏ 6/6' của bản WIP là 7/9 khi phá bằng tập rộng hơn: hai chỗ LỌT là bang=PHEP_VERILOG và cổng 'bộ kiểm phải XANH'. Bù TC-07/08/09, phá lại 9/9. · Công cụ thứ 128 này CHƯA lượt Agent nào gọi.</t>
         </is>
       </c>
     </row>
@@ -8935,11 +10113,45 @@
       <c r="P63" s="47" t="n"/>
       <c r="Q63" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R63" s="47" t="n"/>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="R63" s="47" t="inlineStr">
+        <is>
+          <t>Agent (Claude Opus 5)</t>
+        </is>
+      </c>
       <c r="S63" s="47" t="n"/>
+      <c r="T63" s="26" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="U63" s="26" t="inlineStr">
+        <is>
+          <t>DEV-345</t>
+        </is>
+      </c>
+      <c r="V63" s="26" t="inlineStr">
+        <is>
+          <t>1744 → 1773 (+29)</t>
+        </is>
+      </c>
+      <c r="W63" s="26" t="inlineStr">
+        <is>
+          <t>6 cặp (mạng cổng, .cst) THẬT trong du-lieu/ → 1 chỗ CHẶN, và nó đã đi tới bitstream: blinky.v của riscv-tn20k-b khai cổng sys_clk, .cst chỉ khai clk_27m, không tệp .cst nào trong repo có IO_LOC cho sys_clk. nextpnr vẫn chạy; blinky.fs 4,6 MB dựng ra 01/10/2026. sys_clk rơi vào X0Y6/IOBA — cùng ô mà clk_27m (chân 4, CÓ IO_LOC) của soc_top được gán, nên bitstream ấy có thể đã chạy đúng: bằng may, không bằng ràng buộc. Và cả 7 tệp .cst thật trong repo đọc hết, 0 dòng sai cú pháp.</t>
+        </is>
+      </c>
+      <c r="X63" s="26" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+      <c r="Y63" s="26" t="inlineStr">
+        <is>
+          <t>409 'blocker' của lượt chạy đầu gần như toàn bộ từ picorv32.json — mạng cổng của lõi CPU tổng hợp riêng để đếm ô, không bao giờ đem đặt-đi dây. Con số thật là 1. · Phép quét tệp .cst thật bản đầu chỉ thu 4/7 tệp mà ca kiểm vẫn xanh. · Hai luật chan_lech_kit và io_type_lech_bank CHƯA có dữ liệu để nổ: không kho nào trong repo có Fact pin:tangnano20k.* hay khoá vccio — nên cst.kiem trả thêm chua_co_fact_chan_kit mức info. · Mã lỗi E4033, không E4031 (loop.py đã dùng cho 'chưa chạy, vì chờ cổng'). · Chưa lượt Agent nào gọi.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="68.25" customHeight="1" s="27">
       <c r="A64" s="46" t="inlineStr">
@@ -13022,7 +14234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13863,7 +15075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14318,7 +15530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -10,13 +10,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng quan" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 07-10-2026" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 08-10-2026" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục tối ưu" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đối chiếu 18 mẫu" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 08-10-2026 (chiều)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục tối ưu" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đối chiếu 18 mẫu" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -2098,17 +2099,17 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -4348,6 +4349,1241 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" customWidth="1" style="27" min="1" max="1"/>
+    <col width="66" customWidth="1" style="27" min="2" max="2"/>
+    <col width="24" customWidth="1" style="27" min="3" max="3"/>
+    <col width="8" customWidth="1" style="27" min="4" max="4"/>
+    <col width="11" customWidth="1" style="27" min="5" max="5"/>
+    <col width="16" customWidth="1" style="27" min="6" max="6"/>
+    <col width="34" customWidth="1" style="27" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="57" t="inlineStr">
+        <is>
+          <t>TIẾN ĐỘ ĐỢT TỐI ƯU TÁC TỬ — chốt chiều 08/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="58" t="inlineStr">
+        <is>
+          <t>Mỗi dòng 'Xong' đều có: mục DEV-LOG tra lại được · số ca kiểm trước→sau · một con số đo trên dữ liệu thật · phần còn nợ. Cột chi tiết nằm ở sheet “Danh mục tối ưu”, cột T–Y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="59" t="inlineStr">
+        <is>
+          <t>Tổng quan</t>
+        </is>
+      </c>
+      <c r="B4" s="59" t="inlineStr">
+        <is>
+          <t>Số việc</t>
+        </is>
+      </c>
+      <c r="C4" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>Xong (đã gộp vào main, đã đẩy)</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="n">
+        <v>17</v>
+      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>17 việc đầu của Giai đoạn 1, theo đúng thứ tự # của kế hoạch</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="60" t="inlineStr">
+        <is>
+          <t>Đang làm (chưa commit)</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="61" t="inlineStr">
+        <is>
+          <t>không việc nào đang dở</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="60" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="n">
+        <v>89</v>
+      </c>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>89 việc còn lại trong 106</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="62" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B8" s="62" t="n">
+        <v>106</v>
+      </c>
+      <c r="C8" s="61" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>Phép đo của cả đợt</t>
+        </is>
+      </c>
+      <c r="B10" s="59" t="inlineStr">
+        <is>
+          <t>Trước (06/10)</t>
+        </is>
+      </c>
+      <c r="C10" s="59" t="inlineStr">
+        <is>
+          <t>Sau (08/10)</t>
+        </is>
+      </c>
+      <c r="D10" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị Python (pytest -q)</t>
+        </is>
+      </c>
+      <c r="B11" s="63" t="inlineStr">
+        <is>
+          <t>1 610</t>
+        </is>
+      </c>
+      <c r="C11" s="63" t="inlineStr">
+        <is>
+          <t>1 791</t>
+        </is>
+      </c>
+      <c r="D11" s="63" t="inlineStr">
+        <is>
+          <t>+181 ca so với 06/10; không ca cũ nào đỏ ở bất kỳ bước nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị giao diện (swift test)</t>
+        </is>
+      </c>
+      <c r="B12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="inlineStr">
+        <is>
+          <t>không nhiệm vụ nào đụng ui/ — kiểu khối A2.2 dùng “table”, Swift đã dựng được</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>kiem_tai_lieu.py</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="C13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ LỆCH CHẮC CHẮN cả hai lượt. Hôm nay nó bắt đúng chuyện cần bắt: hai công cụ mới làm README lệch số công cụ 127 → 129, và số 'cần đọc lại' nhảy 11 → 15 → về 11 sau khi sửa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>thu_sch.py (cờ schematic bật)</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="C14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="D14" s="63" t="inlineStr">
+        <is>
+          <t>chạy ở M3-03 và M3-04, không tụt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t>Mục DEV-LOG mới</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330 → DEV-346</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="inlineStr">
+        <is>
+          <t>17 mục, mỗi việc một mục</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="63" t="inlineStr">
+        <is>
+          <t>Cờ tính năng mới</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>1 (schematic)</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="63" t="inlineStr">
+        <is>
+          <t>6 cờ mới, TẤT CẢ mặc định TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="63" t="inlineStr">
+        <is>
+          <t>Mã lỗi mới</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>E4031 · E4032 · E6012 · E4033 · E4024</t>
+        </is>
+      </c>
+      <c r="D17" s="63" t="inlineStr">
+        <is>
+          <t>E4033 (M3-18) và E4024 (M4-01). M4-01 còn DÙNG LẠI E4008/E4009/E4023 của sim.run — cùng một chuyện thì cùng một mã, một mã mới cho cùng một chuyện là bắt người đọc học hai lần</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="59" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="C19" s="59" t="inlineStr">
+        <is>
+          <t>Mảng</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="E19" s="59" t="inlineStr">
+        <is>
+          <t>DEV-LOG</t>
+        </is>
+      </c>
+      <c r="F19" s="59" t="inlineStr">
+        <is>
+          <t>Ca kiểm</t>
+        </is>
+      </c>
+      <c r="G19" s="59" t="inlineStr">
+        <is>
+          <t>Cờ mặc định</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="63" t="inlineStr">
+        <is>
+          <t>M1-01</t>
+        </is>
+      </c>
+      <c r="C20" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D20" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E20" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330</t>
+        </is>
+      </c>
+      <c r="F20" s="63" t="inlineStr">
+        <is>
+          <t>105/309 phiên thật có lịch sử tự mâu thuẫn — 255 chỗ (156 kết quả thứ hai cùng id, 74 message chen giữa, 24 kết quả lạc lượt, 1 lời gọi không kết quả)</t>
+        </is>
+      </c>
+      <c r="G20" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="63" t="inlineStr">
+        <is>
+          <t>M1-02</t>
+        </is>
+      </c>
+      <c r="C21" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D21" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E21" s="63" t="inlineStr">
+        <is>
+          <t>DEV-331</t>
+        </is>
+      </c>
+      <c r="F21" s="63" t="inlineStr">
+        <is>
+          <t>lược đồ công cụ thật: 25 869 token/lời gọi (trần tool_schema=4000 chưa dòng mã nào đọc). Cờ bật: 4 475 token, giảm 82,7 %; 73 → 18 công cụ</t>
+        </is>
+      </c>
+      <c r="G21" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="63" t="inlineStr">
+        <is>
+          <t>M1-03</t>
+        </is>
+      </c>
+      <c r="C22" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D22" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E22" s="63" t="inlineStr">
+        <is>
+          <t>DEV-332</t>
+        </is>
+      </c>
+      <c r="F22" s="63" t="inlineStr">
+        <is>
+          <t>1 822 lời gọi của tác tử con trong 26 phiên thật, 0 lần qua lớp luật. Toàn công cụ đọc trừ một build.compile — lỗ hổng chưa bị bước vào, không phải được canh</t>
+        </is>
+      </c>
+      <c r="G22" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="63" t="inlineStr">
+        <is>
+          <t>M2-01</t>
+        </is>
+      </c>
+      <c r="C23" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D23" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E23" s="63" t="inlineStr">
+        <is>
+          <t>DEV-333</t>
+        </is>
+      </c>
+      <c r="F23" s="63" t="inlineStr">
+        <is>
+          <t>kịch bản 3 REQ + 3 phương án + 3 tiêu chí + 3 tệp: sửa MỘT REQ làm 9 hiện vật STALE → còn 3. Phép đo đầu ra 6→2 vì bị hàng rào E4020 chặn, đã sửa kịch bản đo</t>
+        </is>
+      </c>
+      <c r="G23" s="63" t="inlineStr">
+        <is>
+          <t>TRUY_VET — TẮT (phần nền chạy cả khi tắt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>M2-02</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D24" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E24" s="63" t="inlineStr">
+        <is>
+          <t>DEV-334</t>
+        </is>
+      </c>
+      <c r="F24" s="63" t="inlineStr">
+        <is>
+          <t>63 kho thật: 5/37 REQ có ít nhất một phép đo; 27 chưa có phương án nào nhận; 0 REQ đi hết chuỗi. Cột 'Mã nguồn' trống ở MỌI dự án vì hien_thuc_req vừa mới tồn tại</t>
+        </is>
+      </c>
+      <c r="G24" s="63" t="inlineStr">
+        <is>
+          <t>REQ_PHU — TẮT (khối A2.2 trên tab không phụ thuộc cờ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="63" t="inlineStr">
+        <is>
+          <t>M2-03</t>
+        </is>
+      </c>
+      <c r="C25" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D25" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E25" s="63" t="inlineStr">
+        <is>
+          <t>DEV-335</t>
+        </is>
+      </c>
+      <c r="F25" s="63" t="inlineStr">
+        <is>
+          <t>37 REQ thật: 25 sạch (67 %), 11 thiếu tiêu chí đo được, 2 có từ mơ hồ. Lần đo đầu ra 3 từ mơ hồ, một là kêu oan ('ít nhất 2 lần' là mức đo được) — đã vá</t>
+        </is>
+      </c>
+      <c r="G25" s="63" t="inlineStr">
+        <is>
+          <t>REQ_CHAT_LUONG — TẮT (module yeu_cau.py luôn có)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="63" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="63" t="inlineStr">
+        <is>
+          <t>M2-06</t>
+        </is>
+      </c>
+      <c r="C26" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D26" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E26" s="63" t="inlineStr">
+        <is>
+          <t>DEV-336</t>
+        </is>
+      </c>
+      <c r="F26" s="63" t="inlineStr">
+        <is>
+          <t>sổ cái thật: 26 lần đánh dấu 'xong' ngay sau một lần ghi mã, 19 lần (73 %) không có phép kiểm nào đạt ở giữa. Phép đo đầu ở mức dự án ra 0 — đúng nhưng đo sai câu hỏi</t>
+        </is>
+      </c>
+      <c r="G26" s="63" t="inlineStr">
+        <is>
+          <t>KE_HOACH_CONG_KIEM — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="63" t="inlineStr">
+        <is>
+          <t>M2-08</t>
+        </is>
+      </c>
+      <c r="C27" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D27" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E27" s="63" t="inlineStr">
+        <is>
+          <t>DEV-337</t>
+        </is>
+      </c>
+      <c r="F27" s="63" t="inlineStr">
+        <is>
+          <t>185 tệp .c thật: 1 758 → 1 786 hàm thấy được (+28 hàm trước đây VÔ HÌNH: 8 ngắt + 20 bị regex tham lam nuốt). 78 hàm nay gắn nhãn 'isr', 70 trong đó vốn đã có trong danh sách</t>
+        </is>
+      </c>
+      <c r="G27" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="63" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="63" t="inlineStr">
+        <is>
+          <t>M3-01</t>
+        </is>
+      </c>
+      <c r="C28" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D28" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E28" s="63" t="inlineStr">
+        <is>
+          <t>DEV-338</t>
+        </is>
+      </c>
+      <c r="F28" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mô hình mạch thật — và lý do đáng hơn con số: 3 kho CÓ Fact v_max thì KHÔNG có mô hình mạch, 5 kho có mạch thì không có Fact ấy; thêm nữa Fact dùng chủ thể chip:X mà ERC không tra tiền tố đó</t>
+        </is>
+      </c>
+      <c r="G28" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="63" t="inlineStr">
+        <is>
+          <t>M3-03</t>
+        </is>
+      </c>
+      <c r="C29" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D29" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E29" s="63" t="inlineStr">
+        <is>
+          <t>DEV-339</t>
+        </is>
+      </c>
+      <c r="F29" s="63" t="inlineStr">
+        <is>
+          <t>8 phát hiện trên 5 mạch thật (6 nguon_khong_cap + 2 net_mot_chan), trong đó net clock I2C nối đúng một chân. SÁU trong tám là 'mô hình chưa khai' chứ không phải 'mạch sai'. robot-canbang: 107 Port lá, KHÔNG Port nào là power_out</t>
+        </is>
+      </c>
+      <c r="G29" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="63" t="n">
+        <v>11</v>
+      </c>
+      <c r="B30" s="63" t="inlineStr">
+        <is>
+          <t>M3-04</t>
+        </is>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D30" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E30" s="63" t="inlineStr">
+        <is>
+          <t>DEV-340</t>
+        </is>
+      </c>
+      <c r="F30" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mạch thật — và đây là con số ĐÚNG (hai lỗi này catastrophic, không bo nào sống tới lúc lưu kho). Đã CẤY hai bộ cấp vào bản sao kho robot-canbang để chứng minh luật sống: nổ đúng 1 blocker trên net +5V thật</t>
+        </is>
+      </c>
+      <c r="G30" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="B31" s="63" t="inlineStr">
+        <is>
+          <t>M3-07</t>
+        </is>
+      </c>
+      <c r="C31" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D31" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E31" s="63" t="inlineStr">
+        <is>
+          <t>DEV-341</t>
+        </is>
+      </c>
+      <c r="F31" s="63" t="inlineStr">
+        <is>
+          <t>Fact tới được ERC: 5 → 17 (+12). Ba kho có Fact datasheet thì TOÀN BỘ mang chủ thể chip:, tức trước đó không một Fact nào tới được ERC. Độ phủ 5 mạch thật nay đọc được</t>
+        </is>
+      </c>
+      <c r="G31" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="63" t="n">
+        <v>13</v>
+      </c>
+      <c r="B32" s="63" t="inlineStr">
+        <is>
+          <t>M3-10</t>
+        </is>
+      </c>
+      <c r="C32" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D32" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E32" s="63" t="inlineStr">
+        <is>
+          <t>DEV-342</t>
+        </is>
+      </c>
+      <c r="F32" s="63" t="inlineStr">
+        <is>
+          <t>chi phí đo thật: mạch lớn nhất trong kho 187 nút → ERC 7,6 ms mỗi lần ghi. Trần 2000 nút, vượt thì NÓI RA chứ không im lặng bỏ qua</t>
+        </is>
+      </c>
+      <c r="G32" s="63" t="inlineStr">
+        <is>
+          <t>ERC_TU_DONG — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="B33" s="63" t="inlineStr">
+        <is>
+          <t>M3-12</t>
+        </is>
+      </c>
+      <c r="C33" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D33" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E33" s="63" t="inlineStr">
+        <is>
+          <t>DEV-343</t>
+        </is>
+      </c>
+      <c r="F33" s="63" t="inlineStr">
+        <is>
+          <t>846 bản ghi mô phỏng thật: regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 (testbench dự án in 'KET QUA: PASS' — nhãn đứng TRƯỚC từ khoá). Nới đúng một chỗ → 846/846 khớp, vẫn bắt đủ bốn ca PASS giả</t>
+        </is>
+      </c>
+      <c r="G33" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="64" t="n">
+        <v>15</v>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>M3-13</t>
+        </is>
+      </c>
+      <c r="C34" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D34" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E34" s="64" t="inlineStr">
+        <is>
+          <t>DEV-344</t>
+        </is>
+      </c>
+      <c r="F34" s="64" t="inlineStr">
+        <is>
+          <t>testbench Verilog THẬT của bài 3: tb_pcpi_dot4 1/1, tb_pcpi_mac 1/1, tb_pcpi_vmini không đo được (tb gọi bản bram HAI CỔNG đã bị bỏ 02/10) — mẫu số là TỆP, không phải phép phá</t>
+        </is>
+      </c>
+      <c r="G34" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="64" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B35" s="64" t="inlineStr">
+        <is>
+          <t>M3-18</t>
+        </is>
+      </c>
+      <c r="C35" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D35" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E35" s="64" t="inlineStr">
+        <is>
+          <t>DEV-345</t>
+        </is>
+      </c>
+      <c r="F35" s="64" t="inlineStr">
+        <is>
+          <t>6 cặp (mạng cổng, .cst) thật → 1 chỗ CHẶN: blinky của riscv-tn20k-b dựng bitstream 4,6 MB với chân đồng hồ do nextpnr tự chọn (rơi đúng chân 4 — bằng may). Cả 7 tệp .cst thật đọc hết, 0 lỗi cú pháp</t>
+        </is>
+      </c>
+      <c r="G35" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="64" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B36" s="64" t="inlineStr">
+        <is>
+          <t>M4-01</t>
+        </is>
+      </c>
+      <c r="C36" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D36" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E36" s="64" t="inlineStr">
+        <is>
+          <t>DEV-346</t>
+        </is>
+      </c>
+      <c r="F36" s="64" t="inlineStr">
+        <is>
+          <t>18 ca chạy trình biên dịch C thật: tệp test in số đo {"T1":300} với ngưỡng &lt;=255 → EIDE phán 1 ca HỎNG. Chưa kho cũ nào có tiêu chí unit test để đo lại trên dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="G36" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="59" t="inlineStr">
+        <is>
+          <t>Việc còn MỞ (ngoài 89 việc chưa làm)</t>
+        </is>
+      </c>
+      <c r="B38" s="59" t="inlineStr">
+        <is>
+          <t>Vì sao còn mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="63" t="inlineStr">
+        <is>
+          <t>Sáu cờ mới đều còn TẮT</t>
+        </is>
+      </c>
+      <c r="B39" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU · TRUY_VET · REQ_PHU · REQ_CHAT_LUONG · KE_HOACH_CONG_KIEM · ERC_TU_DONG. Cả sáu đổi thứ Agent nhìn thấy hoặc đọc mỗi lượt, nên chỉ bộ 76 ca chạy HAI chế độ mới nói được chúng làm Agent khá hơn hay tệ hơn — bộ ấy tốn tiền mô hình nên chưa chạy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="63" t="inlineStr">
+        <is>
+          <t>kiem_cap_goi_tra() chưa thành hàng rào</t>
+        </is>
+      </c>
+      <c r="B40" s="63" t="inlineStr">
+        <is>
+          <t>Soát được mọi phiên đã lưu, nhưng chưa hook nào gọi nó tự động — bắt được chuyện cũ, chưa chặn được chuyện mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="63" t="inlineStr">
+        <is>
+          <t>Luật ERC quá áp chưa nổ trên dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="B41" s="63" t="inlineStr">
+        <is>
+          <t>Đường dẫn đã thông ở M3-07, nhưng ba kho có Fact điện áp thì không có mô hình mạch, và ngược lại. Phải chờ một dự án có cả hai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="63" t="inlineStr">
+        <is>
+          <t>Cột “Mã nguồn” của ma trận truy vết trống ở mọi dự án</t>
+        </is>
+      </c>
+      <c r="B42" s="63" t="inlineStr">
+        <is>
+          <t>Nó đọc hien_thuc_req — trường vừa mới tồn tại, chưa tệp nào trên đĩa từng khai. Nên “chưa hiện thực” ở đó nghĩa là “chưa ai KHAI”, không phải “chưa ai viết”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="63" t="inlineStr">
+        <is>
+          <t>Lỗi _go_dau trong src/eide/tools/design.py</t>
+        </is>
+      </c>
+      <c r="B43" s="63" t="inlineStr">
+        <is>
+          <t>Viết .replace('d','d') nên 'ổn định' và 'ON DINH' không khớp nhau. Hàm ấy đang dùng cho một phép kiểm an toàn (người có thật sự chọn không). Tìm thấy ở M2-03, CHƯA sửa vì ngoài phạm vi — cần bộ ca kiểm riêng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="63" t="inlineStr">
+        <is>
+          <t>subagent req-critic (bước 4 của M2-03)</t>
+        </is>
+      </c>
+      <c r="B44" s="63" t="inlineStr">
+        <is>
+          <t>Kế hoạch ghi “tuỳ chọn, gộp M2-13”. Chưa làm, đúng theo kế hoạch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="63" t="inlineStr">
+        <is>
+          <t>Hai luật kiểm chân FPGA chưa có dữ liệu để nổ</t>
+        </is>
+      </c>
+      <c r="B45" s="63" t="inlineStr">
+        <is>
+          <t>chan_lech_kit và io_type_lech_bank cần Fact chân kit. Không kho nào trong repo có Fact pin:tangnano20k.* hay khoá vccio — nên hôm nay chỉ 3 trong 5 luật của M3-18 kết luận được gì trên dữ liệu thật. Cùng hình dạng với luật ERC quá áp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="63" t="inlineStr">
+        <is>
+          <t>Một bitstream cũ đã dựng với chân đồng hồ tự chọn</t>
+        </is>
+      </c>
+      <c r="B46" s="63" t="inlineStr">
+        <is>
+          <t>blinky của du-lieu/riscv-tn20k-b — xem DEV-345 và README §8. Không sửa hiện vật cũ: đó là dữ liệu của những lượt đo đã chốt. Từ nay phép kiểm chặn trước nextpnr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="63" t="inlineStr">
+        <is>
+          <t>Ba công cụ mới nhất chưa lượt Agent nào GỌI</t>
+        </is>
+      </c>
+      <c r="B47" s="63" t="inlineStr">
+        <is>
+          <t>hdl.sensitivity · hdl.constraints_check · test.criteria. Mã của cả ba đã chạy trên hiện vật thật, nhưng đó là tôi gọi hàm, không phải tác tử gọi công cụ. README §8 đếm cả ba vào phần chưa dùng thật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="59" t="inlineStr">
+        <is>
+          <t>Lỗi tìm thấy trong CHÍNH PHÉP ĐO của tôi</t>
+        </is>
+      </c>
+      <c r="B49" s="59" t="inlineStr">
+        <is>
+          <t>Lộ ra ở đâu</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="63" t="inlineStr">
+        <is>
+          <t>Kịch bản đo bị hàng rào của sản phẩm chặn (ghi tệp chưa đọc, E4020) và trả về một con số hợp lý thay vì nổ — 6→2 trông đẹp y như 9→3 đúng</t>
+        </is>
+      </c>
+      <c r="B50" s="63" t="inlineStr">
+        <is>
+          <t>M2-01 · DEV-333</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm dựng trên điều tôi tự nhớ sai: “thiết” bỏ dấu KHÔNG chứa “it”; chỗ va thật là bit/unit/init/exit</t>
+        </is>
+      </c>
+      <c r="B51" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá dài ĐÚNG BẰNG mã gốc (0.6 → 0.0) nên __pycache__ cũ còn hiệu lực — phép đo chạy mã khác với mã trong tệp</t>
+        </is>
+      </c>
+      <c r="B52" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="63" t="inlineStr">
+        <is>
+          <t>Phép đo trả lời ĐÚNG một câu hỏi KHÁC: đếm ở mức dự án ra 0 chỗ cần chặn; câu phải hỏi là “lần ghi NÀY đã được kiểm chưa” → 19/26</t>
+        </is>
+      </c>
+      <c r="B53" s="63" t="inlineStr">
+        <is>
+          <t>M2-06 · DEV-336</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm RỖNG: dàn dựng không có net đất nào, nên nó xanh cả khi tôi bỏ hẳn phép bỏ qua net đất</t>
+        </is>
+      </c>
+      <c r="B54" s="63" t="inlineStr">
+        <is>
+          <t>M3-01 · DEV-338</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="63" t="inlineStr">
+        <is>
+          <t>Hai phép phá chỉ ra THIẾT KẾ sai, không chỉ ca kiểm yếu (miễn net đất quá rộng; nhánh iout_max chưa ca nào chạm tới)</t>
+        </is>
+      </c>
+      <c r="B55" s="63" t="inlineStr">
+        <is>
+          <t>M3-03 · DEV-339</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá của tôi cũng SAI, và ca âm xanh vì lý do khác — hai cái sai che nhau</t>
+        </is>
+      </c>
+      <c r="B56" s="63" t="inlineStr">
+        <is>
+          <t>M3-07 · DEV-341</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm đo chính câu lệnh của mình (đặt bộ đếm = 3 rồi khẳng định nó khác rỗng, trong khi thực tế nó rỗng)</t>
+        </is>
+      </c>
+      <c r="B57" s="63" t="inlineStr">
+        <is>
+          <t>M3-10 · DEV-342</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="63" t="inlineStr">
+        <is>
+          <t>Regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 bản ghi thật; và ba ca kiểm xanh vì lý do sai (tệp giả dùng $4 thay $3; “FAILED” chứa “FAIL”)</t>
+        </is>
+      </c>
+      <c r="B58" s="63" t="inlineStr">
+        <is>
+          <t>M3-12 · DEV-343</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="63" t="inlineStr">
+        <is>
+          <t>"Phá lại thì đỏ 6/6" sai về TẬP, không sai về số: sáu phép phá ấy chọn đúng sáu chỗ đã có ca canh. Phá bằng tập rộng hơn ra 7/9.</t>
+        </is>
+      </c>
+      <c r="B59" s="63" t="inlineStr">
+        <is>
+          <t>M3-13 · DEV-344</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="63" t="inlineStr">
+        <is>
+          <t>409 'blocker' gần như toàn bộ từ một cặp vô nghĩa (mạng cổng của lõi CPU tổng hợp riêng, không bao giờ đem đặt-đi dây). Con số thật là 1.</t>
+        </is>
+      </c>
+      <c r="B60" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="63" t="inlineStr">
+        <is>
+          <t>Phép quét tệp .cst thật chỉ thu 4 trong 7 tệp mà ca kiểm vẫn xanh — câu 'mọi tệp .cst thật đều đọc được' nói về phần phép quét chạm tới.</t>
+        </is>
+      </c>
+      <c r="B61" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="63" t="inlineStr">
+        <is>
+          <t>Một ca kiểm và một phép phá nhắm hai NHÁNH khác nhau, nên ca mới xanh mà phép phá vẫn LỌT. Mất một lượt mới thấy.</t>
+        </is>
+      </c>
+      <c r="B62" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm xanh nhờ một DÒNG KHÁC: kiểm `"TỰ KHAI" in str(kh)` cả khối nên vẫn xanh khi phá chữ ấy ở dòng Kết luận — summary cũng chứa nó. Phép phá bắt được, ca kiểm thì không.</t>
+        </is>
+      </c>
+      <c r="B63" s="63" t="inlineStr">
+        <is>
+          <t>M4-01 · DEV-346</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="63" t="inlineStr">
+        <is>
+          <t>Một phép phá VÔ HIỆU: `them = [] or [[…]]` không đổi hành vi, nên nó báo LỌT oan và suýt làm tôi viết ca kiểm cho một chỗ vốn đã được canh.</t>
+        </is>
+      </c>
+      <c r="B64" s="63" t="inlineStr">
+        <is>
+          <t>M4-01 · DEV-346</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10575,11 +11811,45 @@
       <c r="P68" s="47" t="n"/>
       <c r="Q68" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R68" s="47" t="n"/>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="R68" s="47" t="inlineStr">
+        <is>
+          <t>Agent (Claude Opus 5)</t>
+        </is>
+      </c>
       <c r="S68" s="47" t="n"/>
+      <c r="T68" s="26" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="U68" s="26" t="inlineStr">
+        <is>
+          <t>DEV-346</t>
+        </is>
+      </c>
+      <c r="V68" s="26" t="inlineStr">
+        <is>
+          <t>1773 → 1791 (+18)</t>
+        </is>
+      </c>
+      <c r="W68" s="26" t="inlineStr">
+        <is>
+          <t>Không đo trên kho cũ được: chưa dự án nào trong du-lieu/ có tiêu chí unit test (loại hiện vật criteria:unit-* vừa mới tồn tại), nên phép đo ở đây là 18 ca chạy trình biên dịch C THẬT trên máy: tệp test in {"do":{"T1":300}} với ngưỡng &lt;=255 → EIDE phán 1 ca HỎNG và câu giải thích mang con số 300. Ca âm: không nêu tiêu chí thì hành vi y như cũ (6 ca test.run trong test_xay_dung.py giữ nguyên, không phải nới ca nào).</t>
+        </is>
+      </c>
+      <c r="X68" s="26" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+      <c r="Y68" s="26" t="inlineStr">
+        <is>
+          <t>Phá lại 24/24, lượt đầu 17/24. Bảy chỗ LỌT: năm câu 'nói ra' tôi viết rồi không canh (ma_tieu_chi vào hiện vật, tiêu chí 0 assert, cổng E4023, E4024-ghi-kho-trước, _kiem_assert bị nới), và HAI ca kiểm xanh nhờ một DÒNG KHÁC — kiểm `"TỰ KHAI" in str(kh)` cả khối nên vẫn xanh khi phá chữ ấy ở dòng Kết luận, vì summary cũng chứa nó. · Một phép phá của tôi VÔ HIỆU: `[] or [[…]]` không đổi gì, báo LỌT oan. · Thêm E4023 cho đường unit test (kế hoạch không nêu). · Phải sửa cả surfaces.py, ngoài danh sách tệp chạm tới: test.run ghi vào loại sim_result nên hiện ở khối của sim.run, và dòng Kết luận ở đó nói 'chương trình mô phỏng tự kiểm' cho MỌI lượt. · Chưa lượt Agent nào gọi.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="79.5" customHeight="1" s="27">
       <c r="A69" s="46" t="inlineStr">
@@ -14234,7 +15504,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15075,7 +16345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15530,7 +16800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -11,13 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 07-10-2026" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 08-10-2026" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 08-10-2026 (chiều)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục tối ưu" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đối chiếu 18 mẫu" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 08-10-2026 (toi)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục tối ưu" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đối chiếu 18 mẫu" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -2099,17 +2100,17 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
+    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
     <mergeCell ref="A41:G41"/>
-    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -5385,7 +5386,6 @@
         </is>
       </c>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="59" t="inlineStr">
         <is>
@@ -5584,6 +5584,1313 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" customWidth="1" style="27" min="1" max="1"/>
+    <col width="66" customWidth="1" style="27" min="2" max="2"/>
+    <col width="24" customWidth="1" style="27" min="3" max="3"/>
+    <col width="8" customWidth="1" style="27" min="4" max="4"/>
+    <col width="11" customWidth="1" style="27" min="5" max="5"/>
+    <col width="16" customWidth="1" style="27" min="6" max="6"/>
+    <col width="34" customWidth="1" style="27" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="57" t="inlineStr">
+        <is>
+          <t>TIẾN ĐỘ ĐỢT TỐI ƯU TÁC TỬ — chốt tối 08/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="58" t="inlineStr">
+        <is>
+          <t>Mỗi dòng 'Xong' đều có: mục DEV-LOG tra lại được · số ca kiểm trước→sau · một con số đo trên dữ liệu thật · phần còn nợ. Cột chi tiết nằm ở sheet “Danh mục tối ưu”, cột T–Y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="59" t="inlineStr">
+        <is>
+          <t>Tổng quan</t>
+        </is>
+      </c>
+      <c r="B4" s="59" t="inlineStr">
+        <is>
+          <t>Số việc</t>
+        </is>
+      </c>
+      <c r="C4" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>Xong (đã gộp vào main, đã đẩy)</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="n">
+        <v>18</v>
+      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>18 việc đầu của Giai đoạn 1, theo đúng thứ tự # của kế hoạch</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="60" t="inlineStr">
+        <is>
+          <t>Đang làm (chưa commit)</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="61" t="inlineStr">
+        <is>
+          <t>không việc nào đang dở</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="60" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="n">
+        <v>88</v>
+      </c>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>88 việc còn lại trong 106</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="62" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B8" s="62" t="n">
+        <v>106</v>
+      </c>
+      <c r="C8" s="61" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>Phép đo của cả đợt</t>
+        </is>
+      </c>
+      <c r="B10" s="59" t="inlineStr">
+        <is>
+          <t>Trước (06/10)</t>
+        </is>
+      </c>
+      <c r="C10" s="59" t="inlineStr">
+        <is>
+          <t>Sau (08/10)</t>
+        </is>
+      </c>
+      <c r="D10" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị Python (pytest -q)</t>
+        </is>
+      </c>
+      <c r="B11" s="63" t="inlineStr">
+        <is>
+          <t>1 610</t>
+        </is>
+      </c>
+      <c r="C11" s="63" t="inlineStr">
+        <is>
+          <t>1 816</t>
+        </is>
+      </c>
+      <c r="D11" s="63" t="inlineStr">
+        <is>
+          <t>+206 ca so với 06/10; không ca cũ nào đỏ ở bất kỳ bước nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị giao diện (swift test)</t>
+        </is>
+      </c>
+      <c r="B12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="inlineStr">
+        <is>
+          <t>không nhiệm vụ nào đụng ui/ — kiểu khối A2.2 dùng “table”, Swift đã dựng được</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>kiem_tai_lieu.py</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="C13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ LỆCH CHẮC CHẮN cả hai lượt. Hôm nay nó bắt đúng chuyện cần bắt: hai công cụ mới làm README lệch số công cụ 127 → 129, và số 'cần đọc lại' nhảy 11 → 15 → về 11 sau khi sửa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>thu_sch.py (cờ schematic bật)</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="C14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="D14" s="63" t="inlineStr">
+        <is>
+          <t>chạy ở M3-03 và M3-04, không tụt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t>Mục DEV-LOG mới</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330 → DEV-347</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="inlineStr">
+        <is>
+          <t>18 mục, mỗi việc một mục</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="63" t="inlineStr">
+        <is>
+          <t>Cờ tính năng mới</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>1 (schematic)</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="63" t="inlineStr">
+        <is>
+          <t>7 cờ mới, TẤT CẢ mặc định TẮT. Cờ thứ 7 là SIM_RUNNER_GIOI_HAN (M4-02) — nó giới hạn fs.write của sim-runner trong sim/; hàng rào chính của M4-02 (POL-N6-sua-test) thì KHÔNG sau cờ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="63" t="inlineStr">
+        <is>
+          <t>Mã lỗi mới</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>E4031 · E4032 · E6012 · E4033 · E4024</t>
+        </is>
+      </c>
+      <c r="D17" s="63" t="inlineStr">
+        <is>
+          <t>M4-02 không thêm mã nào: nó DÙNG LẠI E5006 cho cổng ghi của sim-runner. E4033 (M3-18), E4024 (M4-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="59" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="C19" s="59" t="inlineStr">
+        <is>
+          <t>Mảng</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="E19" s="59" t="inlineStr">
+        <is>
+          <t>DEV-LOG</t>
+        </is>
+      </c>
+      <c r="F19" s="59" t="inlineStr">
+        <is>
+          <t>Ca kiểm</t>
+        </is>
+      </c>
+      <c r="G19" s="59" t="inlineStr">
+        <is>
+          <t>Cờ mặc định</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="63" t="inlineStr">
+        <is>
+          <t>M1-01</t>
+        </is>
+      </c>
+      <c r="C20" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D20" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E20" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330</t>
+        </is>
+      </c>
+      <c r="F20" s="63" t="inlineStr">
+        <is>
+          <t>105/309 phiên thật có lịch sử tự mâu thuẫn — 255 chỗ (156 kết quả thứ hai cùng id, 74 message chen giữa, 24 kết quả lạc lượt, 1 lời gọi không kết quả)</t>
+        </is>
+      </c>
+      <c r="G20" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="63" t="inlineStr">
+        <is>
+          <t>M1-02</t>
+        </is>
+      </c>
+      <c r="C21" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D21" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E21" s="63" t="inlineStr">
+        <is>
+          <t>DEV-331</t>
+        </is>
+      </c>
+      <c r="F21" s="63" t="inlineStr">
+        <is>
+          <t>lược đồ công cụ thật: 25 869 token/lời gọi (trần tool_schema=4000 chưa dòng mã nào đọc). Cờ bật: 4 475 token, giảm 82,7 %; 73 → 18 công cụ</t>
+        </is>
+      </c>
+      <c r="G21" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="63" t="inlineStr">
+        <is>
+          <t>M1-03</t>
+        </is>
+      </c>
+      <c r="C22" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D22" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E22" s="63" t="inlineStr">
+        <is>
+          <t>DEV-332</t>
+        </is>
+      </c>
+      <c r="F22" s="63" t="inlineStr">
+        <is>
+          <t>1 822 lời gọi của tác tử con trong 26 phiên thật, 0 lần qua lớp luật. Toàn công cụ đọc trừ một build.compile — lỗ hổng chưa bị bước vào, không phải được canh</t>
+        </is>
+      </c>
+      <c r="G22" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="63" t="inlineStr">
+        <is>
+          <t>M2-01</t>
+        </is>
+      </c>
+      <c r="C23" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D23" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E23" s="63" t="inlineStr">
+        <is>
+          <t>DEV-333</t>
+        </is>
+      </c>
+      <c r="F23" s="63" t="inlineStr">
+        <is>
+          <t>kịch bản 3 REQ + 3 phương án + 3 tiêu chí + 3 tệp: sửa MỘT REQ làm 9 hiện vật STALE → còn 3. Phép đo đầu ra 6→2 vì bị hàng rào E4020 chặn, đã sửa kịch bản đo</t>
+        </is>
+      </c>
+      <c r="G23" s="63" t="inlineStr">
+        <is>
+          <t>TRUY_VET — TẮT (phần nền chạy cả khi tắt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>M2-02</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D24" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E24" s="63" t="inlineStr">
+        <is>
+          <t>DEV-334</t>
+        </is>
+      </c>
+      <c r="F24" s="63" t="inlineStr">
+        <is>
+          <t>63 kho thật: 5/37 REQ có ít nhất một phép đo; 27 chưa có phương án nào nhận; 0 REQ đi hết chuỗi. Cột 'Mã nguồn' trống ở MỌI dự án vì hien_thuc_req vừa mới tồn tại</t>
+        </is>
+      </c>
+      <c r="G24" s="63" t="inlineStr">
+        <is>
+          <t>REQ_PHU — TẮT (khối A2.2 trên tab không phụ thuộc cờ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="63" t="inlineStr">
+        <is>
+          <t>M2-03</t>
+        </is>
+      </c>
+      <c r="C25" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D25" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E25" s="63" t="inlineStr">
+        <is>
+          <t>DEV-335</t>
+        </is>
+      </c>
+      <c r="F25" s="63" t="inlineStr">
+        <is>
+          <t>37 REQ thật: 25 sạch (67 %), 11 thiếu tiêu chí đo được, 2 có từ mơ hồ. Lần đo đầu ra 3 từ mơ hồ, một là kêu oan ('ít nhất 2 lần' là mức đo được) — đã vá</t>
+        </is>
+      </c>
+      <c r="G25" s="63" t="inlineStr">
+        <is>
+          <t>REQ_CHAT_LUONG — TẮT (module yeu_cau.py luôn có)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="63" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="63" t="inlineStr">
+        <is>
+          <t>M2-06</t>
+        </is>
+      </c>
+      <c r="C26" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D26" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E26" s="63" t="inlineStr">
+        <is>
+          <t>DEV-336</t>
+        </is>
+      </c>
+      <c r="F26" s="63" t="inlineStr">
+        <is>
+          <t>sổ cái thật: 26 lần đánh dấu 'xong' ngay sau một lần ghi mã, 19 lần (73 %) không có phép kiểm nào đạt ở giữa. Phép đo đầu ở mức dự án ra 0 — đúng nhưng đo sai câu hỏi</t>
+        </is>
+      </c>
+      <c r="G26" s="63" t="inlineStr">
+        <is>
+          <t>KE_HOACH_CONG_KIEM — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="63" t="inlineStr">
+        <is>
+          <t>M2-08</t>
+        </is>
+      </c>
+      <c r="C27" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D27" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E27" s="63" t="inlineStr">
+        <is>
+          <t>DEV-337</t>
+        </is>
+      </c>
+      <c r="F27" s="63" t="inlineStr">
+        <is>
+          <t>185 tệp .c thật: 1 758 → 1 786 hàm thấy được (+28 hàm trước đây VÔ HÌNH: 8 ngắt + 20 bị regex tham lam nuốt). 78 hàm nay gắn nhãn 'isr', 70 trong đó vốn đã có trong danh sách</t>
+        </is>
+      </c>
+      <c r="G27" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="63" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="63" t="inlineStr">
+        <is>
+          <t>M3-01</t>
+        </is>
+      </c>
+      <c r="C28" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D28" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E28" s="63" t="inlineStr">
+        <is>
+          <t>DEV-338</t>
+        </is>
+      </c>
+      <c r="F28" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mô hình mạch thật — và lý do đáng hơn con số: 3 kho CÓ Fact v_max thì KHÔNG có mô hình mạch, 5 kho có mạch thì không có Fact ấy; thêm nữa Fact dùng chủ thể chip:X mà ERC không tra tiền tố đó</t>
+        </is>
+      </c>
+      <c r="G28" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="63" t="inlineStr">
+        <is>
+          <t>M3-03</t>
+        </is>
+      </c>
+      <c r="C29" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D29" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E29" s="63" t="inlineStr">
+        <is>
+          <t>DEV-339</t>
+        </is>
+      </c>
+      <c r="F29" s="63" t="inlineStr">
+        <is>
+          <t>8 phát hiện trên 5 mạch thật (6 nguon_khong_cap + 2 net_mot_chan), trong đó net clock I2C nối đúng một chân. SÁU trong tám là 'mô hình chưa khai' chứ không phải 'mạch sai'. robot-canbang: 107 Port lá, KHÔNG Port nào là power_out</t>
+        </is>
+      </c>
+      <c r="G29" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="63" t="n">
+        <v>11</v>
+      </c>
+      <c r="B30" s="63" t="inlineStr">
+        <is>
+          <t>M3-04</t>
+        </is>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D30" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E30" s="63" t="inlineStr">
+        <is>
+          <t>DEV-340</t>
+        </is>
+      </c>
+      <c r="F30" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mạch thật — và đây là con số ĐÚNG (hai lỗi này catastrophic, không bo nào sống tới lúc lưu kho). Đã CẤY hai bộ cấp vào bản sao kho robot-canbang để chứng minh luật sống: nổ đúng 1 blocker trên net +5V thật</t>
+        </is>
+      </c>
+      <c r="G30" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="B31" s="63" t="inlineStr">
+        <is>
+          <t>M3-07</t>
+        </is>
+      </c>
+      <c r="C31" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D31" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E31" s="63" t="inlineStr">
+        <is>
+          <t>DEV-341</t>
+        </is>
+      </c>
+      <c r="F31" s="63" t="inlineStr">
+        <is>
+          <t>Fact tới được ERC: 5 → 17 (+12). Ba kho có Fact datasheet thì TOÀN BỘ mang chủ thể chip:, tức trước đó không một Fact nào tới được ERC. Độ phủ 5 mạch thật nay đọc được</t>
+        </is>
+      </c>
+      <c r="G31" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="63" t="n">
+        <v>13</v>
+      </c>
+      <c r="B32" s="63" t="inlineStr">
+        <is>
+          <t>M3-10</t>
+        </is>
+      </c>
+      <c r="C32" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D32" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E32" s="63" t="inlineStr">
+        <is>
+          <t>DEV-342</t>
+        </is>
+      </c>
+      <c r="F32" s="63" t="inlineStr">
+        <is>
+          <t>chi phí đo thật: mạch lớn nhất trong kho 187 nút → ERC 7,6 ms mỗi lần ghi. Trần 2000 nút, vượt thì NÓI RA chứ không im lặng bỏ qua</t>
+        </is>
+      </c>
+      <c r="G32" s="63" t="inlineStr">
+        <is>
+          <t>ERC_TU_DONG — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="B33" s="63" t="inlineStr">
+        <is>
+          <t>M3-12</t>
+        </is>
+      </c>
+      <c r="C33" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D33" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E33" s="63" t="inlineStr">
+        <is>
+          <t>DEV-343</t>
+        </is>
+      </c>
+      <c r="F33" s="63" t="inlineStr">
+        <is>
+          <t>846 bản ghi mô phỏng thật: regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 (testbench dự án in 'KET QUA: PASS' — nhãn đứng TRƯỚC từ khoá). Nới đúng một chỗ → 846/846 khớp, vẫn bắt đủ bốn ca PASS giả</t>
+        </is>
+      </c>
+      <c r="G33" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="64" t="n">
+        <v>15</v>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>M3-13</t>
+        </is>
+      </c>
+      <c r="C34" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D34" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E34" s="64" t="inlineStr">
+        <is>
+          <t>DEV-344</t>
+        </is>
+      </c>
+      <c r="F34" s="64" t="inlineStr">
+        <is>
+          <t>testbench Verilog THẬT của bài 3: tb_pcpi_dot4 1/1, tb_pcpi_mac 1/1, tb_pcpi_vmini không đo được (tb gọi bản bram HAI CỔNG đã bị bỏ 02/10) — mẫu số là TỆP, không phải phép phá</t>
+        </is>
+      </c>
+      <c r="G34" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="64" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B35" s="64" t="inlineStr">
+        <is>
+          <t>M3-18</t>
+        </is>
+      </c>
+      <c r="C35" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D35" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E35" s="64" t="inlineStr">
+        <is>
+          <t>DEV-345</t>
+        </is>
+      </c>
+      <c r="F35" s="64" t="inlineStr">
+        <is>
+          <t>6 cặp (mạng cổng, .cst) thật → 1 chỗ CHẶN: blinky của riscv-tn20k-b dựng bitstream 4,6 MB với chân đồng hồ do nextpnr tự chọn (rơi đúng chân 4 — bằng may). Cả 7 tệp .cst thật đọc hết, 0 lỗi cú pháp</t>
+        </is>
+      </c>
+      <c r="G35" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="64" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B36" s="64" t="inlineStr">
+        <is>
+          <t>M4-01</t>
+        </is>
+      </c>
+      <c r="C36" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D36" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E36" s="64" t="inlineStr">
+        <is>
+          <t>DEV-346</t>
+        </is>
+      </c>
+      <c r="F36" s="64" t="inlineStr">
+        <is>
+          <t>18 ca chạy trình biên dịch C thật: tệp test in số đo {"T1":300} với ngưỡng &lt;=255 → EIDE phán 1 ca HỎNG. Chưa kho cũ nào có tiêu chí unit test để đo lại trên dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="G36" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="64" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B37" s="64" t="inlineStr">
+        <is>
+          <t>M4-02</t>
+        </is>
+      </c>
+      <c r="C37" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D37" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E37" s="64" t="inlineStr">
+        <is>
+          <t>DEV-347</t>
+        </is>
+      </c>
+      <c r="F37" s="64" t="inlineStr">
+        <is>
+          <t>25 ca dựng đúng trạng thái thật (tệp test 3 ca, 1 ca đỏ, hiện vật dat=False) → fs.write còn 1 ca thì test.weakened=True. Và hàng rào cũ criteria.has_result chưa bao giờ nổ ngoài sim-01</t>
+        </is>
+      </c>
+      <c r="G37" s="64" t="inlineStr">
+        <is>
+          <t>SIM_RUNNER_GIOI_HAN — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="59" t="inlineStr">
+        <is>
+          <t>Việc còn MỞ (ngoài 88 việc chưa làm)</t>
+        </is>
+      </c>
+      <c r="B39" s="59" t="inlineStr">
+        <is>
+          <t>Vì sao còn mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="63" t="inlineStr">
+        <is>
+          <t>Bảy cờ mới đều còn TẮT</t>
+        </is>
+      </c>
+      <c r="B40" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU · TRUY_VET · REQ_PHU · REQ_CHAT_LUONG · KE_HOACH_CONG_KIEM · ERC_TU_DONG · SIM_RUNNER_GIOI_HAN. Cả bảy đổi thứ Agent nhìn thấy, đọc, hoặc LÀM ĐƯỢC mỗi lượt, nên chỉ bộ 76 ca chạy hai chế độ mới nói được chúng làm Agent khá hơn hay tệ hơn. Bộ ấy tốn tiền mô hình nên §3.0 bắt hỏi người dùng trước.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="63" t="inlineStr">
+        <is>
+          <t>kiem_cap_goi_tra() chưa thành hàng rào</t>
+        </is>
+      </c>
+      <c r="B41" s="63" t="inlineStr">
+        <is>
+          <t>Soát được mọi phiên đã lưu, nhưng chưa hook nào gọi nó tự động — bắt được chuyện cũ, chưa chặn được chuyện mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="63" t="inlineStr">
+        <is>
+          <t>Luật ERC quá áp chưa nổ trên dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="B42" s="63" t="inlineStr">
+        <is>
+          <t>Đường dẫn đã thông ở M3-07, nhưng ba kho có Fact điện áp thì không có mô hình mạch, và ngược lại. Phải chờ một dự án có cả hai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="63" t="inlineStr">
+        <is>
+          <t>Cột “Mã nguồn” của ma trận truy vết trống ở mọi dự án</t>
+        </is>
+      </c>
+      <c r="B43" s="63" t="inlineStr">
+        <is>
+          <t>Nó đọc hien_thuc_req — trường vừa mới tồn tại, chưa tệp nào trên đĩa từng khai. Nên “chưa hiện thực” ở đó nghĩa là “chưa ai KHAI”, không phải “chưa ai viết”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="63" t="inlineStr">
+        <is>
+          <t>Lỗi _go_dau trong src/eide/tools/design.py</t>
+        </is>
+      </c>
+      <c r="B44" s="63" t="inlineStr">
+        <is>
+          <t>Viết .replace('d','d') nên 'ổn định' và 'ON DINH' không khớp nhau. Hàm ấy đang dùng cho một phép kiểm an toàn (người có thật sự chọn không). Tìm thấy ở M2-03, CHƯA sửa vì ngoài phạm vi — cần bộ ca kiểm riêng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="63" t="inlineStr">
+        <is>
+          <t>subagent req-critic (bước 4 của M2-03)</t>
+        </is>
+      </c>
+      <c r="B45" s="63" t="inlineStr">
+        <is>
+          <t>Kế hoạch ghi “tuỳ chọn, gộp M2-13”. Chưa làm, đúng theo kế hoạch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="63" t="inlineStr">
+        <is>
+          <t>Hai luật kiểm chân FPGA chưa có dữ liệu để nổ</t>
+        </is>
+      </c>
+      <c r="B46" s="63" t="inlineStr">
+        <is>
+          <t>chan_lech_kit và io_type_lech_bank cần Fact chân kit. Không kho nào trong repo có Fact pin:tangnano20k.* hay khoá vccio — nên hôm nay chỉ 3 trong 5 luật của M3-18 kết luận được gì trên dữ liệu thật. Cùng hình dạng với luật ERC quá áp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="63" t="inlineStr">
+        <is>
+          <t>Một bitstream cũ đã dựng với chân đồng hồ tự chọn</t>
+        </is>
+      </c>
+      <c r="B47" s="63" t="inlineStr">
+        <is>
+          <t>blinky của du-lieu/riscv-tn20k-b — xem DEV-345 và README §8. Không sửa hiện vật cũ: đó là dữ liệu của những lượt đo đã chốt. Từ nay phép kiểm chặn trước nextpnr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="63" t="inlineStr">
+        <is>
+          <t>Ba công cụ mới nhất chưa lượt Agent nào GỌI</t>
+        </is>
+      </c>
+      <c r="B48" s="63" t="inlineStr">
+        <is>
+          <t>hdl.sensitivity · hdl.constraints_check · test.criteria. Mã của cả ba đã chạy trên hiện vật thật, nhưng đó là tôi gọi hàm, không phải tác tử gọi công cụ. README §8 đếm cả ba vào phần chưa dùng thật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="63" t="inlineStr">
+        <is>
+          <t>POL-N6-sua-test chưa nổ trên một phiên thật nào</t>
+        </is>
+      </c>
+      <c r="B49" s="63" t="inlineStr">
+        <is>
+          <t>Hook sua_test_sau_do cấp dữ kiện cho lời gọi SẮP xảy ra, nên không soát lại được phiên đã lưu — khác mọi phép đo trước của đợt này. Nó đã có 25 ca kiểm và phá lại 27/27, nhưng chưa lượt tác tử thật nào chạm vào nó. Cùng hình dạng với ba luật kiểm thiếu dữ liệu ở trên, chỉ khác lý do.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="59" t="inlineStr">
+        <is>
+          <t>Lỗi tìm thấy trong CHÍNH PHÉP ĐO của tôi</t>
+        </is>
+      </c>
+      <c r="B51" s="59" t="inlineStr">
+        <is>
+          <t>Lộ ra ở đâu</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="63" t="inlineStr">
+        <is>
+          <t>Kịch bản đo bị hàng rào của sản phẩm chặn (ghi tệp chưa đọc, E4020) và trả về một con số hợp lý thay vì nổ — 6→2 trông đẹp y như 9→3 đúng</t>
+        </is>
+      </c>
+      <c r="B52" s="63" t="inlineStr">
+        <is>
+          <t>M2-01 · DEV-333</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm dựng trên điều tôi tự nhớ sai: “thiết” bỏ dấu KHÔNG chứa “it”; chỗ va thật là bit/unit/init/exit</t>
+        </is>
+      </c>
+      <c r="B53" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá dài ĐÚNG BẰNG mã gốc (0.6 → 0.0) nên __pycache__ cũ còn hiệu lực — phép đo chạy mã khác với mã trong tệp</t>
+        </is>
+      </c>
+      <c r="B54" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="63" t="inlineStr">
+        <is>
+          <t>Phép đo trả lời ĐÚNG một câu hỏi KHÁC: đếm ở mức dự án ra 0 chỗ cần chặn; câu phải hỏi là “lần ghi NÀY đã được kiểm chưa” → 19/26</t>
+        </is>
+      </c>
+      <c r="B55" s="63" t="inlineStr">
+        <is>
+          <t>M2-06 · DEV-336</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm RỖNG: dàn dựng không có net đất nào, nên nó xanh cả khi tôi bỏ hẳn phép bỏ qua net đất</t>
+        </is>
+      </c>
+      <c r="B56" s="63" t="inlineStr">
+        <is>
+          <t>M3-01 · DEV-338</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="63" t="inlineStr">
+        <is>
+          <t>Hai phép phá chỉ ra THIẾT KẾ sai, không chỉ ca kiểm yếu (miễn net đất quá rộng; nhánh iout_max chưa ca nào chạm tới)</t>
+        </is>
+      </c>
+      <c r="B57" s="63" t="inlineStr">
+        <is>
+          <t>M3-03 · DEV-339</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá của tôi cũng SAI, và ca âm xanh vì lý do khác — hai cái sai che nhau</t>
+        </is>
+      </c>
+      <c r="B58" s="63" t="inlineStr">
+        <is>
+          <t>M3-07 · DEV-341</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm đo chính câu lệnh của mình (đặt bộ đếm = 3 rồi khẳng định nó khác rỗng, trong khi thực tế nó rỗng)</t>
+        </is>
+      </c>
+      <c r="B59" s="63" t="inlineStr">
+        <is>
+          <t>M3-10 · DEV-342</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="63" t="inlineStr">
+        <is>
+          <t>Regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 bản ghi thật; và ba ca kiểm xanh vì lý do sai (tệp giả dùng $4 thay $3; “FAILED” chứa “FAIL”)</t>
+        </is>
+      </c>
+      <c r="B60" s="63" t="inlineStr">
+        <is>
+          <t>M3-12 · DEV-343</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="63" t="inlineStr">
+        <is>
+          <t>"Phá lại thì đỏ 6/6" sai về TẬP, không sai về số: sáu phép phá ấy chọn đúng sáu chỗ đã có ca canh. Phá bằng tập rộng hơn ra 7/9.</t>
+        </is>
+      </c>
+      <c r="B61" s="63" t="inlineStr">
+        <is>
+          <t>M3-13 · DEV-344</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="63" t="inlineStr">
+        <is>
+          <t>409 'blocker' gần như toàn bộ từ một cặp vô nghĩa (mạng cổng của lõi CPU tổng hợp riêng, không bao giờ đem đặt-đi dây). Con số thật là 1.</t>
+        </is>
+      </c>
+      <c r="B62" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="63" t="inlineStr">
+        <is>
+          <t>Phép quét tệp .cst thật chỉ thu 4 trong 7 tệp mà ca kiểm vẫn xanh — câu 'mọi tệp .cst thật đều đọc được' nói về phần phép quét chạm tới.</t>
+        </is>
+      </c>
+      <c r="B63" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="63" t="inlineStr">
+        <is>
+          <t>Một ca kiểm và một phép phá nhắm hai NHÁNH khác nhau, nên ca mới xanh mà phép phá vẫn LỌT. Mất một lượt mới thấy.</t>
+        </is>
+      </c>
+      <c r="B64" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm xanh nhờ một DÒNG KHÁC: kiểm `"TỰ KHAI" in str(kh)` cả khối nên vẫn xanh khi phá chữ ấy ở dòng Kết luận — summary cũng chứa nó. Phép phá bắt được, ca kiểm thì không.</t>
+        </is>
+      </c>
+      <c r="B65" s="63" t="inlineStr">
+        <is>
+          <t>M4-01 · DEV-346</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="63" t="inlineStr">
+        <is>
+          <t>Một phép phá VÔ HIỆU: `them = [] or [[…]]` không đổi hành vi, nên nó báo LỌT oan và suýt làm tôi viết ca kiểm cho một chỗ vốn đã được canh.</t>
+        </is>
+      </c>
+      <c r="B66" s="63" t="inlineStr">
+        <is>
+          <t>M4-01 · DEV-346</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="63" t="inlineStr">
+        <is>
+          <t>HAI phép phá liền nhau VÔ HIỆU ở cùng một dòng: `cu = cu or ""` không đổi hành vi, rồi bỏ is_file() cũng không vì except OSError bắt FileNotFoundError. Phải bỏ cả hai lớp phòng mới phá được.</t>
+        </is>
+      </c>
+      <c r="B67" s="63" t="inlineStr">
+        <is>
+          <t>M4-02 · DEV-347</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="63" t="inlineStr">
+        <is>
+          <t>Một luật mới trỏ tới nhóm dữ kiện chưa khai thì DỪNG CẢ LƯỢT bằng ValueError, không phải 'không nổ' — và nhóm `criteria` của hàng rào N6 cũ cũng chưa bao giờ được khai.</t>
+        </is>
+      </c>
+      <c r="B68" s="63" t="inlineStr">
+        <is>
+          <t>M4-02 · DEV-347</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11933,11 +13240,45 @@
       </c>
       <c r="Q69" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R69" s="47" t="n"/>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="R69" s="47" t="inlineStr">
+        <is>
+          <t>Agent (Claude Opus 5)</t>
+        </is>
+      </c>
       <c r="S69" s="47" t="n"/>
+      <c r="T69" s="26" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="U69" s="26" t="inlineStr">
+        <is>
+          <t>DEV-347</t>
+        </is>
+      </c>
+      <c r="V69" s="26" t="inlineStr">
+        <is>
+          <t>1791 → 1816 (+25)</t>
+        </is>
+      </c>
+      <c r="W69" s="26" t="inlineStr">
+        <is>
+          <t>Không có dữ liệu cũ để đo lại trên: hook này cấp dữ kiện cho lời gọi SẮP xảy ra, không soát lại phiên đã lưu. Phép đo là 25 ca dựng đúng trạng thái thật: tệp test 3 ca với 1 ca đỏ trên đĩa + hiện vật sim_result dat=False trong kho → fs.write còn 1 ca thì test.weakened=True và test.doi_gi nói '7 chỗ canh → 3'. Và một phép đo trên chính hàng rào cũ: criteria.has_result tra cứng sim_result:can-bang, nên POL-N6-doi-tieu-chi CHƯA BAO GIỜ nổ cho sim-ntc hay unit-* — luật viết đúng, đường dẫn tới nó đứt.</t>
+        </is>
+      </c>
+      <c r="X69" s="26" t="inlineStr">
+        <is>
+          <t>SIM_RUNNER_GIOI_HAN — TẮT (hàng rào chính POL-N6-sua-test thì KHÔNG sau cờ)</t>
+        </is>
+      </c>
+      <c r="Y69" s="26" t="inlineStr">
+        <is>
+          <t>Phá lại 27/27, lượt đầu 22/27. · PHÁT HIỆN ngoài phạm vi kế hoạch: một luật trỏ tới nhóm dữ kiện chưa khai thì DỪNG CẢ LƯỢT bằng ValueError, không phải 'không nổ' — _env có danh sách 'nhóm phải luôn tồn tại' và nhóm `test` không có trong đó, nên luật mới làm mọi fs.write đổ. Mở ra thì thấy `criteria` cũng chưa bao giờ có trong danh sách ấy. · HAI phép phá của tôi vô hiệu ở cùng một dòng: `cu = cu or ""` không đổi hành vi, rồi bỏ is_file() cũng không vì except OSError bắt FileNotFoundError. Lần thứ hai liền sau M4-01. · Bốn chỗ LỌT còn lại: tiền tố unit-, số chỗ canh không đổi, testbench ngoài thư mục test/, và luật (khác hook) cho test.criteria.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="90.75" customHeight="1" s="27">
       <c r="A70" s="46" t="inlineStr">
@@ -15504,7 +16845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16345,7 +17686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16800,7 +18141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -12,13 +12,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 08-10-2026" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 08-10-2026 (chiều)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 08-10-2026 (toi)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục tối ưu" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đối chiếu 18 mẫu" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 08-10-2026 (khuya)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục tối ưu" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đối chiếu 18 mẫu" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -2103,13 +2104,13 @@
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
-    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="B53:G53"/>
     <mergeCell ref="B48:G48"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
@@ -2117,6 +2118,273 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="28" customWidth="1" style="26" min="1" max="1"/>
+    <col width="110" customWidth="1" style="26" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="19.5" customHeight="1" s="27">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>PHƯƠNG PHÁP RÀ SOÁT VÀ NGUỒN</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="23.25" customHeight="1" s="27">
+      <c r="A3" s="53" t="inlineStr">
+        <is>
+          <t>Phạm vi</t>
+        </is>
+      </c>
+      <c r="B3" s="47" t="inlineStr">
+        <is>
+          <t>Thư mục EIDE_v3: src/eide (lõi Python), tests/ (69 tệp), tools/ (script phiên), docs/md (tài liệu thiết kế), ui/EIDEApp (Swift — chỉ tham khảo giao thức). Chỉ đọc, không sửa tệp nào của dự án.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="23.25" customHeight="1" s="27">
+      <c r="A4" s="53" t="inlineStr">
+        <is>
+          <t>Thang đối chiếu</t>
+        </is>
+      </c>
+      <c r="B4" s="47" t="inlineStr">
+        <is>
+          <t>Tài liệu 'Các mẫu kiến trúc AI Agent' (10/2026) của anh: 4 mẫu workflow, 9 mẫu single-agent (gồm ReAct), 5 mẫu multi-agent và Human-in-the-loop; nguyên tắc chọn mẫu đơn giản nhất, có trần bước/thời gian/token, có eval trước khi leo thang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="23.25" customHeight="1" s="27">
+      <c r="A5" s="53" t="inlineStr">
+        <is>
+          <t>Cách làm</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t>Chia 5 mảng rà soát song song (lõi tác tử; phân tích–thiết kế PM; mạch–ERC–HDL/FPGA; kiểm thử &amp; kiểm chứng; tri thức–RAG–bộ nhớ). Mỗi phát hiện phải dẫn tệp:dòng hoặc hàm đã đọc. Sau đó kiểm chứng lại trực tiếp các phát hiện P0 then chốt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45.75" customHeight="1" s="27">
+      <c r="A6" s="53" t="inlineStr">
+        <is>
+          <t>P0 đã kiểm lại bằng tay</t>
+        </is>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>subagent.py:309 gọi thẳng registry.run (không qua hook/policy) · hooks/standard.py:562 'task.run' bất kỳ tắt kiểm chứng · build/hdl.py:497 '"PASS" in tren' dò chuỗi con · store/eide_md.py::render cắt đuôi text[:keep] · loop.py:503 resume lấy bo_nen.tom_tat_hien_tai luôn None ở phiên mới · build/dot_bien.py: chay(p) trả False khi không biên dịch được vẫn tính 'thay' · config.py:198 temperature 0.0 + seed cố định · history.ghi_kho không có tham số deps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="23.25" customHeight="1" s="27">
+      <c r="A7" s="53" t="inlineStr">
+        <is>
+          <t>Số liệu đo trong mã</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>Số công cụ (118, 73 core) và kích thước lược đồ (~77,6 nghìn ký tự ≈ 26 nghìn token) do người rà soát mảng 1 đo bằng build_registry(); các số 54% lời gọi là fs.read/grep/glob, 31/120 công cụ chưa nổ lần nào… lấy từ chú thích có số đo trong chính mã nguồn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="23.25" customHeight="1" s="27">
+      <c r="A8" s="53" t="inlineStr">
+        <is>
+          <t>Lưu ý</t>
+        </is>
+      </c>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>Số dòng là tại ngày 06/10/2026, có thể lệch sau khi sửa mã. Khuyến nghị temperature cho dòng Gemini 3 cần kiểm lại riêng cho gemini-3.8-flash bằng A/B trên 76 ca (M1-09). Công sức là ước lượng thô cho một người quen mã.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="27">
+      <c r="A9" s="53" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>Yao et al. (2022). ReAct: Synergizing Reasoning and Acting in Language Models. arXiv:2210.03629.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="27">
+      <c r="A10" s="53" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>Wang et al. (2023). Plan-and-Solve Prompting. arXiv:2305.04091.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="27">
+      <c r="A11" s="53" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="B11" s="47" t="inlineStr">
+        <is>
+          <t>Xu et al. (2023). ReWOO. arXiv:2305.18323.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="27">
+      <c r="A12" s="53" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="B12" s="47" t="inlineStr">
+        <is>
+          <t>Kim et al. (2023). An LLM Compiler for Parallel Function Calling. arXiv:2312.04511.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="27">
+      <c r="A13" s="53" t="inlineStr">
+        <is>
+          <t>[5]</t>
+        </is>
+      </c>
+      <c r="B13" s="47" t="inlineStr">
+        <is>
+          <t>Shinn et al. (2023). Reflexion: Language Agents with Verbal Reinforcement Learning. arXiv:2303.11366.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="27">
+      <c r="A14" s="53" t="inlineStr">
+        <is>
+          <t>[6]</t>
+        </is>
+      </c>
+      <c r="B14" s="47" t="inlineStr">
+        <is>
+          <t>Yao et al. (2023). Tree of Thoughts. arXiv:2305.10601.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="27">
+      <c r="A15" s="53" t="inlineStr">
+        <is>
+          <t>[7]</t>
+        </is>
+      </c>
+      <c r="B15" s="47" t="inlineStr">
+        <is>
+          <t>Zhou et al. (2023). Language Agent Tree Search (LATS). arXiv:2310.04406.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="27">
+      <c r="A16" s="53" t="inlineStr">
+        <is>
+          <t>[8]</t>
+        </is>
+      </c>
+      <c r="B16" s="47" t="inlineStr">
+        <is>
+          <t>Wang et al. (2024). Executable Code Actions Elicit Better LLM Agents (CodeAct). arXiv:2402.01030.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="27">
+      <c r="A17" s="53" t="inlineStr">
+        <is>
+          <t>[9]</t>
+        </is>
+      </c>
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>Asai et al. (2023). Self-RAG. arXiv:2310.11511.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="27">
+      <c r="A18" s="53" t="inlineStr">
+        <is>
+          <t>[10]</t>
+        </is>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>Packer et al. (2023). MemGPT: Towards LLMs as Operating Systems. arXiv:2310.08560.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="27">
+      <c r="A19" s="53" t="inlineStr">
+        <is>
+          <t>[11]</t>
+        </is>
+      </c>
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>Du et al. (2023). Improving Factuality and Reasoning through Multiagent Debate. arXiv:2305.14325.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="27">
+      <c r="A20" s="53" t="inlineStr">
+        <is>
+          <t>[12]</t>
+        </is>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Wu et al. (2023). AutoGen. arXiv:2308.08155.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="27">
+      <c r="A21" s="53" t="inlineStr">
+        <is>
+          <t>[13]</t>
+        </is>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>Anthropic (2024). Building effective agents. anthropic.com/engineering/building-effective-agents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="27">
+      <c r="A22" s="53" t="inlineStr">
+        <is>
+          <t>[14]</t>
+        </is>
+      </c>
+      <c r="B22" s="47" t="inlineStr">
+        <is>
+          <t>Anthropic (2025). How we built our multi-agent research system. anthropic.com/engineering/multi-agent-research-system.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -6891,6 +7159,1386 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" customWidth="1" style="27" min="1" max="1"/>
+    <col width="66" customWidth="1" style="27" min="2" max="2"/>
+    <col width="24" customWidth="1" style="27" min="3" max="3"/>
+    <col width="8" customWidth="1" style="27" min="4" max="4"/>
+    <col width="11" customWidth="1" style="27" min="5" max="5"/>
+    <col width="16" customWidth="1" style="27" min="6" max="6"/>
+    <col width="34" customWidth="1" style="27" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="57" t="inlineStr">
+        <is>
+          <t>TIẾN ĐỘ ĐỢT TỐI ƯU TÁC TỬ — chốt khuya 08/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="58" t="inlineStr">
+        <is>
+          <t>Mỗi dòng 'Xong' đều có: mục DEV-LOG tra lại được · số ca kiểm trước→sau · một con số đo trên dữ liệu thật · phần còn nợ. Cột chi tiết nằm ở sheet “Danh mục tối ưu”, cột T–Y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="59" t="inlineStr">
+        <is>
+          <t>Tổng quan</t>
+        </is>
+      </c>
+      <c r="B4" s="59" t="inlineStr">
+        <is>
+          <t>Số việc</t>
+        </is>
+      </c>
+      <c r="C4" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>Xong (đã gộp vào main, đã đẩy)</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="n">
+        <v>19</v>
+      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>19 việc đầu của Giai đoạn 1, theo đúng thứ tự # của kế hoạch</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="60" t="inlineStr">
+        <is>
+          <t>Đang làm (chưa commit)</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="61" t="inlineStr">
+        <is>
+          <t>không việc nào đang dở</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="60" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="n">
+        <v>87</v>
+      </c>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>87 việc còn lại trong 106</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="62" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B8" s="62" t="n">
+        <v>106</v>
+      </c>
+      <c r="C8" s="61" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>Phép đo của cả đợt</t>
+        </is>
+      </c>
+      <c r="B10" s="59" t="inlineStr">
+        <is>
+          <t>Trước (06/10)</t>
+        </is>
+      </c>
+      <c r="C10" s="59" t="inlineStr">
+        <is>
+          <t>Sau (08/10)</t>
+        </is>
+      </c>
+      <c r="D10" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị Python (pytest -q)</t>
+        </is>
+      </c>
+      <c r="B11" s="63" t="inlineStr">
+        <is>
+          <t>1 610</t>
+        </is>
+      </c>
+      <c r="C11" s="63" t="inlineStr">
+        <is>
+          <t>1 835</t>
+        </is>
+      </c>
+      <c r="D11" s="63" t="inlineStr">
+        <is>
+          <t>+225 ca so với 06/10; không ca cũ nào đỏ ở bất kỳ bước nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị giao diện (swift test)</t>
+        </is>
+      </c>
+      <c r="B12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="inlineStr">
+        <is>
+          <t>không nhiệm vụ nào đụng ui/ — kiểu khối A2.2 dùng “table”, Swift đã dựng được</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>kiem_tai_lieu.py</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="C13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ LỆCH CHẮC CHẮN cả hai lượt. Hôm nay nó bắt đúng chuyện cần bắt: hai công cụ mới làm README lệch số công cụ 127 → 129, và số 'cần đọc lại' nhảy 11 → 15 → về 11 sau khi sửa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>thu_sch.py (cờ schematic bật)</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="C14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="D14" s="63" t="inlineStr">
+        <is>
+          <t>chạy ở M3-03 và M3-04, không tụt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t>Mục DEV-LOG mới</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330 → DEV-348</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="inlineStr">
+        <is>
+          <t>19 mục, mỗi việc một mục</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="63" t="inlineStr">
+        <is>
+          <t>Cờ tính năng mới</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>1 (schematic)</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="63" t="inlineStr">
+        <is>
+          <t>7 cờ mới, TẤT CẢ mặc định TẮT. Cờ thứ 7 là SIM_RUNNER_GIOI_HAN (M4-02) — nó giới hạn fs.write của sim-runner trong sim/; hàng rào chính của M4-02 (POL-N6-sua-test) thì KHÔNG sau cờ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="63" t="inlineStr">
+        <is>
+          <t>Mã lỗi mới</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>E4031 · E4032 · E6012 · E4033 · E4024</t>
+        </is>
+      </c>
+      <c r="D17" s="63" t="inlineStr">
+        <is>
+          <t>M4-05 không thêm mã nào. M4-02 cũng không (dùng lại E5006). E4033 (M3-18), E4024 (M4-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="59" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="C19" s="59" t="inlineStr">
+        <is>
+          <t>Mảng</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="E19" s="59" t="inlineStr">
+        <is>
+          <t>DEV-LOG</t>
+        </is>
+      </c>
+      <c r="F19" s="59" t="inlineStr">
+        <is>
+          <t>Ca kiểm</t>
+        </is>
+      </c>
+      <c r="G19" s="59" t="inlineStr">
+        <is>
+          <t>Cờ mặc định</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="63" t="inlineStr">
+        <is>
+          <t>M1-01</t>
+        </is>
+      </c>
+      <c r="C20" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D20" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E20" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330</t>
+        </is>
+      </c>
+      <c r="F20" s="63" t="inlineStr">
+        <is>
+          <t>105/309 phiên thật có lịch sử tự mâu thuẫn — 255 chỗ (156 kết quả thứ hai cùng id, 74 message chen giữa, 24 kết quả lạc lượt, 1 lời gọi không kết quả)</t>
+        </is>
+      </c>
+      <c r="G20" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="63" t="inlineStr">
+        <is>
+          <t>M1-02</t>
+        </is>
+      </c>
+      <c r="C21" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D21" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E21" s="63" t="inlineStr">
+        <is>
+          <t>DEV-331</t>
+        </is>
+      </c>
+      <c r="F21" s="63" t="inlineStr">
+        <is>
+          <t>lược đồ công cụ thật: 25 869 token/lời gọi (trần tool_schema=4000 chưa dòng mã nào đọc). Cờ bật: 4 475 token, giảm 82,7 %; 73 → 18 công cụ</t>
+        </is>
+      </c>
+      <c r="G21" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="63" t="inlineStr">
+        <is>
+          <t>M1-03</t>
+        </is>
+      </c>
+      <c r="C22" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D22" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E22" s="63" t="inlineStr">
+        <is>
+          <t>DEV-332</t>
+        </is>
+      </c>
+      <c r="F22" s="63" t="inlineStr">
+        <is>
+          <t>1 822 lời gọi của tác tử con trong 26 phiên thật, 0 lần qua lớp luật. Toàn công cụ đọc trừ một build.compile — lỗ hổng chưa bị bước vào, không phải được canh</t>
+        </is>
+      </c>
+      <c r="G22" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="63" t="inlineStr">
+        <is>
+          <t>M2-01</t>
+        </is>
+      </c>
+      <c r="C23" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D23" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E23" s="63" t="inlineStr">
+        <is>
+          <t>DEV-333</t>
+        </is>
+      </c>
+      <c r="F23" s="63" t="inlineStr">
+        <is>
+          <t>kịch bản 3 REQ + 3 phương án + 3 tiêu chí + 3 tệp: sửa MỘT REQ làm 9 hiện vật STALE → còn 3. Phép đo đầu ra 6→2 vì bị hàng rào E4020 chặn, đã sửa kịch bản đo</t>
+        </is>
+      </c>
+      <c r="G23" s="63" t="inlineStr">
+        <is>
+          <t>TRUY_VET — TẮT (phần nền chạy cả khi tắt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>M2-02</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D24" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E24" s="63" t="inlineStr">
+        <is>
+          <t>DEV-334</t>
+        </is>
+      </c>
+      <c r="F24" s="63" t="inlineStr">
+        <is>
+          <t>63 kho thật: 5/37 REQ có ít nhất một phép đo; 27 chưa có phương án nào nhận; 0 REQ đi hết chuỗi. Cột 'Mã nguồn' trống ở MỌI dự án vì hien_thuc_req vừa mới tồn tại</t>
+        </is>
+      </c>
+      <c r="G24" s="63" t="inlineStr">
+        <is>
+          <t>REQ_PHU — TẮT (khối A2.2 trên tab không phụ thuộc cờ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="63" t="inlineStr">
+        <is>
+          <t>M2-03</t>
+        </is>
+      </c>
+      <c r="C25" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D25" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E25" s="63" t="inlineStr">
+        <is>
+          <t>DEV-335</t>
+        </is>
+      </c>
+      <c r="F25" s="63" t="inlineStr">
+        <is>
+          <t>37 REQ thật: 25 sạch (67 %), 11 thiếu tiêu chí đo được, 2 có từ mơ hồ. Lần đo đầu ra 3 từ mơ hồ, một là kêu oan ('ít nhất 2 lần' là mức đo được) — đã vá</t>
+        </is>
+      </c>
+      <c r="G25" s="63" t="inlineStr">
+        <is>
+          <t>REQ_CHAT_LUONG — TẮT (module yeu_cau.py luôn có)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="63" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="63" t="inlineStr">
+        <is>
+          <t>M2-06</t>
+        </is>
+      </c>
+      <c r="C26" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D26" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E26" s="63" t="inlineStr">
+        <is>
+          <t>DEV-336</t>
+        </is>
+      </c>
+      <c r="F26" s="63" t="inlineStr">
+        <is>
+          <t>sổ cái thật: 26 lần đánh dấu 'xong' ngay sau một lần ghi mã, 19 lần (73 %) không có phép kiểm nào đạt ở giữa. Phép đo đầu ở mức dự án ra 0 — đúng nhưng đo sai câu hỏi</t>
+        </is>
+      </c>
+      <c r="G26" s="63" t="inlineStr">
+        <is>
+          <t>KE_HOACH_CONG_KIEM — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="63" t="inlineStr">
+        <is>
+          <t>M2-08</t>
+        </is>
+      </c>
+      <c r="C27" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D27" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E27" s="63" t="inlineStr">
+        <is>
+          <t>DEV-337</t>
+        </is>
+      </c>
+      <c r="F27" s="63" t="inlineStr">
+        <is>
+          <t>185 tệp .c thật: 1 758 → 1 786 hàm thấy được (+28 hàm trước đây VÔ HÌNH: 8 ngắt + 20 bị regex tham lam nuốt). 78 hàm nay gắn nhãn 'isr', 70 trong đó vốn đã có trong danh sách</t>
+        </is>
+      </c>
+      <c r="G27" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="63" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="63" t="inlineStr">
+        <is>
+          <t>M3-01</t>
+        </is>
+      </c>
+      <c r="C28" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D28" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E28" s="63" t="inlineStr">
+        <is>
+          <t>DEV-338</t>
+        </is>
+      </c>
+      <c r="F28" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mô hình mạch thật — và lý do đáng hơn con số: 3 kho CÓ Fact v_max thì KHÔNG có mô hình mạch, 5 kho có mạch thì không có Fact ấy; thêm nữa Fact dùng chủ thể chip:X mà ERC không tra tiền tố đó</t>
+        </is>
+      </c>
+      <c r="G28" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="63" t="inlineStr">
+        <is>
+          <t>M3-03</t>
+        </is>
+      </c>
+      <c r="C29" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D29" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E29" s="63" t="inlineStr">
+        <is>
+          <t>DEV-339</t>
+        </is>
+      </c>
+      <c r="F29" s="63" t="inlineStr">
+        <is>
+          <t>8 phát hiện trên 5 mạch thật (6 nguon_khong_cap + 2 net_mot_chan), trong đó net clock I2C nối đúng một chân. SÁU trong tám là 'mô hình chưa khai' chứ không phải 'mạch sai'. robot-canbang: 107 Port lá, KHÔNG Port nào là power_out</t>
+        </is>
+      </c>
+      <c r="G29" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="63" t="n">
+        <v>11</v>
+      </c>
+      <c r="B30" s="63" t="inlineStr">
+        <is>
+          <t>M3-04</t>
+        </is>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D30" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E30" s="63" t="inlineStr">
+        <is>
+          <t>DEV-340</t>
+        </is>
+      </c>
+      <c r="F30" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mạch thật — và đây là con số ĐÚNG (hai lỗi này catastrophic, không bo nào sống tới lúc lưu kho). Đã CẤY hai bộ cấp vào bản sao kho robot-canbang để chứng minh luật sống: nổ đúng 1 blocker trên net +5V thật</t>
+        </is>
+      </c>
+      <c r="G30" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="B31" s="63" t="inlineStr">
+        <is>
+          <t>M3-07</t>
+        </is>
+      </c>
+      <c r="C31" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D31" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E31" s="63" t="inlineStr">
+        <is>
+          <t>DEV-341</t>
+        </is>
+      </c>
+      <c r="F31" s="63" t="inlineStr">
+        <is>
+          <t>Fact tới được ERC: 5 → 17 (+12). Ba kho có Fact datasheet thì TOÀN BỘ mang chủ thể chip:, tức trước đó không một Fact nào tới được ERC. Độ phủ 5 mạch thật nay đọc được</t>
+        </is>
+      </c>
+      <c r="G31" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="63" t="n">
+        <v>13</v>
+      </c>
+      <c r="B32" s="63" t="inlineStr">
+        <is>
+          <t>M3-10</t>
+        </is>
+      </c>
+      <c r="C32" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D32" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E32" s="63" t="inlineStr">
+        <is>
+          <t>DEV-342</t>
+        </is>
+      </c>
+      <c r="F32" s="63" t="inlineStr">
+        <is>
+          <t>chi phí đo thật: mạch lớn nhất trong kho 187 nút → ERC 7,6 ms mỗi lần ghi. Trần 2000 nút, vượt thì NÓI RA chứ không im lặng bỏ qua</t>
+        </is>
+      </c>
+      <c r="G32" s="63" t="inlineStr">
+        <is>
+          <t>ERC_TU_DONG — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="B33" s="63" t="inlineStr">
+        <is>
+          <t>M3-12</t>
+        </is>
+      </c>
+      <c r="C33" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D33" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E33" s="63" t="inlineStr">
+        <is>
+          <t>DEV-343</t>
+        </is>
+      </c>
+      <c r="F33" s="63" t="inlineStr">
+        <is>
+          <t>846 bản ghi mô phỏng thật: regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 (testbench dự án in 'KET QUA: PASS' — nhãn đứng TRƯỚC từ khoá). Nới đúng một chỗ → 846/846 khớp, vẫn bắt đủ bốn ca PASS giả</t>
+        </is>
+      </c>
+      <c r="G33" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="64" t="n">
+        <v>15</v>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>M3-13</t>
+        </is>
+      </c>
+      <c r="C34" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D34" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E34" s="64" t="inlineStr">
+        <is>
+          <t>DEV-344</t>
+        </is>
+      </c>
+      <c r="F34" s="64" t="inlineStr">
+        <is>
+          <t>testbench Verilog THẬT của bài 3: tb_pcpi_dot4 1/1, tb_pcpi_mac 1/1, tb_pcpi_vmini không đo được (tb gọi bản bram HAI CỔNG đã bị bỏ 02/10) — mẫu số là TỆP, không phải phép phá</t>
+        </is>
+      </c>
+      <c r="G34" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="64" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B35" s="64" t="inlineStr">
+        <is>
+          <t>M3-18</t>
+        </is>
+      </c>
+      <c r="C35" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D35" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E35" s="64" t="inlineStr">
+        <is>
+          <t>DEV-345</t>
+        </is>
+      </c>
+      <c r="F35" s="64" t="inlineStr">
+        <is>
+          <t>6 cặp (mạng cổng, .cst) thật → 1 chỗ CHẶN: blinky của riscv-tn20k-b dựng bitstream 4,6 MB với chân đồng hồ do nextpnr tự chọn (rơi đúng chân 4 — bằng may). Cả 7 tệp .cst thật đọc hết, 0 lỗi cú pháp</t>
+        </is>
+      </c>
+      <c r="G35" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="64" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B36" s="64" t="inlineStr">
+        <is>
+          <t>M4-01</t>
+        </is>
+      </c>
+      <c r="C36" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D36" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E36" s="64" t="inlineStr">
+        <is>
+          <t>DEV-346</t>
+        </is>
+      </c>
+      <c r="F36" s="64" t="inlineStr">
+        <is>
+          <t>18 ca chạy trình biên dịch C thật: tệp test in số đo {"T1":300} với ngưỡng &lt;=255 → EIDE phán 1 ca HỎNG. Chưa kho cũ nào có tiêu chí unit test để đo lại trên dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="G36" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="64" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B37" s="64" t="inlineStr">
+        <is>
+          <t>M4-02</t>
+        </is>
+      </c>
+      <c r="C37" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D37" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E37" s="64" t="inlineStr">
+        <is>
+          <t>DEV-347</t>
+        </is>
+      </c>
+      <c r="F37" s="64" t="inlineStr">
+        <is>
+          <t>25 ca dựng đúng trạng thái thật (tệp test 3 ca, 1 ca đỏ, hiện vật dat=False) → fs.write còn 1 ca thì test.weakened=True. Và hàng rào cũ criteria.has_result chưa bao giờ nổ ngoài sim-01</t>
+        </is>
+      </c>
+      <c r="G37" s="64" t="inlineStr">
+        <is>
+          <t>SIM_RUNNER_GIOI_HAN — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="64" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B38" s="64" t="inlineStr">
+        <is>
+          <t>M4-05</t>
+        </is>
+      </c>
+      <c r="C38" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D38" s="64" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E38" s="64" t="inlineStr">
+        <is>
+          <t>DEV-348</t>
+        </is>
+      </c>
+      <c r="F38" s="64" t="inlineStr">
+        <is>
+          <t>du-lieu/rtos-sinhvien, chạy CẢ HAI hành vi: cũ so_thay=1, mới so_thay=0 — logo_ptit.c từ 'bộ kiểm ĐỎ' thành 'mọi đột biến đều làm hỏng biên dịch'. Một ô xanh giả, đã sửa</t>
+        </is>
+      </c>
+      <c r="G38" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="59" t="inlineStr">
+        <is>
+          <t>Việc còn MỞ (ngoài 87 việc chưa làm)</t>
+        </is>
+      </c>
+      <c r="B40" s="59" t="inlineStr">
+        <is>
+          <t>Vì sao còn mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="63" t="inlineStr">
+        <is>
+          <t>Bảy cờ mới đều còn TẮT</t>
+        </is>
+      </c>
+      <c r="B41" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU · TRUY_VET · REQ_PHU · REQ_CHAT_LUONG · KE_HOACH_CONG_KIEM · ERC_TU_DONG · SIM_RUNNER_GIOI_HAN. Cả bảy đổi thứ Agent nhìn thấy, đọc, hoặc LÀM ĐƯỢC mỗi lượt, nên chỉ bộ 76 ca chạy hai chế độ mới nói được chúng làm Agent khá hơn hay tệ hơn. Bộ ấy tốn tiền mô hình nên §3.0 bắt hỏi người dùng trước.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="63" t="inlineStr">
+        <is>
+          <t>kiem_cap_goi_tra() chưa thành hàng rào</t>
+        </is>
+      </c>
+      <c r="B42" s="63" t="inlineStr">
+        <is>
+          <t>Soát được mọi phiên đã lưu, nhưng chưa hook nào gọi nó tự động — bắt được chuyện cũ, chưa chặn được chuyện mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="63" t="inlineStr">
+        <is>
+          <t>Luật ERC quá áp chưa nổ trên dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="B43" s="63" t="inlineStr">
+        <is>
+          <t>Đường dẫn đã thông ở M3-07, nhưng ba kho có Fact điện áp thì không có mô hình mạch, và ngược lại. Phải chờ một dự án có cả hai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="63" t="inlineStr">
+        <is>
+          <t>Cột “Mã nguồn” của ma trận truy vết trống ở mọi dự án</t>
+        </is>
+      </c>
+      <c r="B44" s="63" t="inlineStr">
+        <is>
+          <t>Nó đọc hien_thuc_req — trường vừa mới tồn tại, chưa tệp nào trên đĩa từng khai. Nên “chưa hiện thực” ở đó nghĩa là “chưa ai KHAI”, không phải “chưa ai viết”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="63" t="inlineStr">
+        <is>
+          <t>Lỗi _go_dau trong src/eide/tools/design.py</t>
+        </is>
+      </c>
+      <c r="B45" s="63" t="inlineStr">
+        <is>
+          <t>Viết .replace('d','d') nên 'ổn định' và 'ON DINH' không khớp nhau. Hàm ấy đang dùng cho một phép kiểm an toàn (người có thật sự chọn không). Tìm thấy ở M2-03, CHƯA sửa vì ngoài phạm vi — cần bộ ca kiểm riêng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="63" t="inlineStr">
+        <is>
+          <t>subagent req-critic (bước 4 của M2-03)</t>
+        </is>
+      </c>
+      <c r="B46" s="63" t="inlineStr">
+        <is>
+          <t>Kế hoạch ghi “tuỳ chọn, gộp M2-13”. Chưa làm, đúng theo kế hoạch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="63" t="inlineStr">
+        <is>
+          <t>Hai luật kiểm chân FPGA chưa có dữ liệu để nổ</t>
+        </is>
+      </c>
+      <c r="B47" s="63" t="inlineStr">
+        <is>
+          <t>chan_lech_kit và io_type_lech_bank cần Fact chân kit. Không kho nào trong repo có Fact pin:tangnano20k.* hay khoá vccio — nên hôm nay chỉ 3 trong 5 luật của M3-18 kết luận được gì trên dữ liệu thật. Cùng hình dạng với luật ERC quá áp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="63" t="inlineStr">
+        <is>
+          <t>Một bitstream cũ đã dựng với chân đồng hồ tự chọn</t>
+        </is>
+      </c>
+      <c r="B48" s="63" t="inlineStr">
+        <is>
+          <t>blinky của du-lieu/riscv-tn20k-b — xem DEV-345 và README §8. Không sửa hiện vật cũ: đó là dữ liệu của những lượt đo đã chốt. Từ nay phép kiểm chặn trước nextpnr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="63" t="inlineStr">
+        <is>
+          <t>Ba công cụ mới nhất chưa lượt Agent nào GỌI</t>
+        </is>
+      </c>
+      <c r="B49" s="63" t="inlineStr">
+        <is>
+          <t>hdl.sensitivity · hdl.constraints_check · test.criteria. Mã của cả ba đã chạy trên hiện vật thật, nhưng đó là tôi gọi hàm, không phải tác tử gọi công cụ. README §8 đếm cả ba vào phần chưa dùng thật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="63" t="inlineStr">
+        <is>
+          <t>Bộ kiểm C của ba dự án firmware thật đều KHÔNG đo được độ nhạy</t>
+        </is>
+      </c>
+      <c r="B50" s="63" t="inlineStr">
+        <is>
+          <t>rtos-sinhvien: 0/12 tệp đo được (4 font khong_thay, control_rtos.c trùng ký hiệu, main.c không dịch trên máy chủ, logo_ptit.c mọi mutant hỏng biên dịch). stm32f469-freertos và thu-nghiem-g6: bộ kiểm ĐỎ SẴN. Đây là trạng thái của dữ liệu đo, không phải lỗi sản phẩm — nhưng nó nghĩa là chưa dự án firmware nào trong repo có một con số độ nhạy đáng tin. Xem DEV-348.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="63" t="inlineStr">
+        <is>
+          <t>POL-N6-sua-test chưa nổ trên một phiên thật nào</t>
+        </is>
+      </c>
+      <c r="B51" s="63" t="inlineStr">
+        <is>
+          <t>Hook sua_test_sau_do cấp dữ kiện cho lời gọi SẮP xảy ra, nên không soát lại được phiên đã lưu — khác mọi phép đo trước của đợt này. Nó đã có 25 ca kiểm và phá lại 27/27, nhưng chưa lượt tác tử thật nào chạm vào nó. Cùng hình dạng với ba luật kiểm thiếu dữ liệu ở trên, chỉ khác lý do.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="59" t="inlineStr">
+        <is>
+          <t>Lỗi tìm thấy trong CHÍNH PHÉP ĐO của tôi</t>
+        </is>
+      </c>
+      <c r="B53" s="59" t="inlineStr">
+        <is>
+          <t>Lộ ra ở đâu</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="63" t="inlineStr">
+        <is>
+          <t>Kịch bản đo bị hàng rào của sản phẩm chặn (ghi tệp chưa đọc, E4020) và trả về một con số hợp lý thay vì nổ — 6→2 trông đẹp y như 9→3 đúng</t>
+        </is>
+      </c>
+      <c r="B54" s="63" t="inlineStr">
+        <is>
+          <t>M2-01 · DEV-333</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm dựng trên điều tôi tự nhớ sai: “thiết” bỏ dấu KHÔNG chứa “it”; chỗ va thật là bit/unit/init/exit</t>
+        </is>
+      </c>
+      <c r="B55" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá dài ĐÚNG BẰNG mã gốc (0.6 → 0.0) nên __pycache__ cũ còn hiệu lực — phép đo chạy mã khác với mã trong tệp</t>
+        </is>
+      </c>
+      <c r="B56" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="63" t="inlineStr">
+        <is>
+          <t>Phép đo trả lời ĐÚNG một câu hỏi KHÁC: đếm ở mức dự án ra 0 chỗ cần chặn; câu phải hỏi là “lần ghi NÀY đã được kiểm chưa” → 19/26</t>
+        </is>
+      </c>
+      <c r="B57" s="63" t="inlineStr">
+        <is>
+          <t>M2-06 · DEV-336</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm RỖNG: dàn dựng không có net đất nào, nên nó xanh cả khi tôi bỏ hẳn phép bỏ qua net đất</t>
+        </is>
+      </c>
+      <c r="B58" s="63" t="inlineStr">
+        <is>
+          <t>M3-01 · DEV-338</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="63" t="inlineStr">
+        <is>
+          <t>Hai phép phá chỉ ra THIẾT KẾ sai, không chỉ ca kiểm yếu (miễn net đất quá rộng; nhánh iout_max chưa ca nào chạm tới)</t>
+        </is>
+      </c>
+      <c r="B59" s="63" t="inlineStr">
+        <is>
+          <t>M3-03 · DEV-339</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá của tôi cũng SAI, và ca âm xanh vì lý do khác — hai cái sai che nhau</t>
+        </is>
+      </c>
+      <c r="B60" s="63" t="inlineStr">
+        <is>
+          <t>M3-07 · DEV-341</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm đo chính câu lệnh của mình (đặt bộ đếm = 3 rồi khẳng định nó khác rỗng, trong khi thực tế nó rỗng)</t>
+        </is>
+      </c>
+      <c r="B61" s="63" t="inlineStr">
+        <is>
+          <t>M3-10 · DEV-342</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="63" t="inlineStr">
+        <is>
+          <t>Regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 bản ghi thật; và ba ca kiểm xanh vì lý do sai (tệp giả dùng $4 thay $3; “FAILED” chứa “FAIL”)</t>
+        </is>
+      </c>
+      <c r="B62" s="63" t="inlineStr">
+        <is>
+          <t>M3-12 · DEV-343</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="63" t="inlineStr">
+        <is>
+          <t>"Phá lại thì đỏ 6/6" sai về TẬP, không sai về số: sáu phép phá ấy chọn đúng sáu chỗ đã có ca canh. Phá bằng tập rộng hơn ra 7/9.</t>
+        </is>
+      </c>
+      <c r="B63" s="63" t="inlineStr">
+        <is>
+          <t>M3-13 · DEV-344</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="63" t="inlineStr">
+        <is>
+          <t>409 'blocker' gần như toàn bộ từ một cặp vô nghĩa (mạng cổng của lõi CPU tổng hợp riêng, không bao giờ đem đặt-đi dây). Con số thật là 1.</t>
+        </is>
+      </c>
+      <c r="B64" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="63" t="inlineStr">
+        <is>
+          <t>Phép quét tệp .cst thật chỉ thu 4 trong 7 tệp mà ca kiểm vẫn xanh — câu 'mọi tệp .cst thật đều đọc được' nói về phần phép quét chạm tới.</t>
+        </is>
+      </c>
+      <c r="B65" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="63" t="inlineStr">
+        <is>
+          <t>Một ca kiểm và một phép phá nhắm hai NHÁNH khác nhau, nên ca mới xanh mà phép phá vẫn LỌT. Mất một lượt mới thấy.</t>
+        </is>
+      </c>
+      <c r="B66" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm xanh nhờ một DÒNG KHÁC: kiểm `"TỰ KHAI" in str(kh)` cả khối nên vẫn xanh khi phá chữ ấy ở dòng Kết luận — summary cũng chứa nó. Phép phá bắt được, ca kiểm thì không.</t>
+        </is>
+      </c>
+      <c r="B67" s="63" t="inlineStr">
+        <is>
+          <t>M4-01 · DEV-346</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="63" t="inlineStr">
+        <is>
+          <t>Một phép phá VÔ HIỆU: `them = [] or [[…]]` không đổi hành vi, nên nó báo LỌT oan và suýt làm tôi viết ca kiểm cho một chỗ vốn đã được canh.</t>
+        </is>
+      </c>
+      <c r="B68" s="63" t="inlineStr">
+        <is>
+          <t>M4-01 · DEV-346</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="63" t="inlineStr">
+        <is>
+          <t>HAI phép phá liền nhau VÔ HIỆU ở cùng một dòng: `cu = cu or ""` không đổi hành vi, rồi bỏ is_file() cũng không vì except OSError bắt FileNotFoundError. Phải bỏ cả hai lớp phòng mới phá được.</t>
+        </is>
+      </c>
+      <c r="B69" s="63" t="inlineStr">
+        <is>
+          <t>M4-02 · DEV-347</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="63" t="inlineStr">
+        <is>
+          <t>Một luật mới trỏ tới nhóm dữ kiện chưa khai thì DỪNG CẢ LƯỢT bằng ValueError, không phải 'không nổ' — và nhóm `criteria` của hàng rào N6 cũ cũng chưa bao giờ được khai.</t>
+        </is>
+      </c>
+      <c r="B70" s="63" t="inlineStr">
+        <is>
+          <t>M4-02 · DEV-347</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="63" t="inlineStr">
+        <is>
+          <t>Phép đo ĐỔ ngay lượt đầu trên dữ liệu thật (IndexError), và lỗi ấy nghĩa là test.sensitivity chưa bao giờ chạy nổi trên một tệp firmware thật — mọi con số cũ đều từ tệp nhỏ do ca kiểm tự dựng.</t>
+        </is>
+      </c>
+      <c r="B71" s="63" t="inlineStr">
+        <is>
+          <t>M4-05 · DEV-348</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="63" t="inlineStr">
+        <is>
+          <t>Bốn chỗ LỌT cùng một hình dạng: luật ĐÚNG, nằm ở chỗ ca kiểm không với tới — hai closure, một bảng phép không dựng nổi ca, và một tầng báo lại mà mọi ca cũ đều đi qua với stillborn == 0.</t>
+        </is>
+      </c>
+      <c r="B72" s="63" t="inlineStr">
+        <is>
+          <t>M4-05 · DEV-348</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13530,13 +15178,47 @@
       <c r="P72" s="47" t="n"/>
       <c r="Q72" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R72" s="47" t="n"/>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="R72" s="47" t="inlineStr">
+        <is>
+          <t>Agent (Claude Opus 5)</t>
+        </is>
+      </c>
       <c r="S72" s="47" t="inlineStr">
         <is>
           <t>Kéo lên giai đoạn sớm hơn vì là tiền đề (xem §5 kế hoạch)</t>
+        </is>
+      </c>
+      <c r="T72" s="26" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="U72" s="26" t="inlineStr">
+        <is>
+          <t>DEV-348</t>
+        </is>
+      </c>
+      <c r="V72" s="26" t="inlineStr">
+        <is>
+          <t>1816 → 1835 (+19)</t>
+        </is>
+      </c>
+      <c r="W72" s="26" t="inlineStr">
+        <is>
+          <t>du-lieu/rtos-sinhvien (12 tệp sản phẩm, 1 tệp test), chạy CẢ HAI hành vi trên cùng dữ liệu: CŨ so_thay=1 (logo_ptit.c 'thay' — bộ kiểm ĐỎ), MỚI so_thay=0 (logo_ptit.c 'mọi đột biến đều làm hỏng biên dịch'). Con số cũ là 1/5 bắt được; sự thật là 0 tệp đo được. Hai dự án firmware thật còn lại (stm32f469-freertos, thu-nghiem-g6) có bộ kiểm ĐỎ SẴN nên không đo được gì. Và kiểm lại DEV-344: bài 3 vẫn tb_pcpi_dot4 1/1, tb_pcpi_mac 1/1, stillborn=0 — con số ấy ĐỨNG, do năm phép PHEP_VERILOG đều hợp lệ về cú pháp.</t>
+        </is>
+      </c>
+      <c r="X72" s="26" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+      <c r="Y72" s="26" t="inlineStr">
+        <is>
+          <t>Nhiệm vụ nhỏ nhất của đợt (P1·S) và tìm ra nhiều lỗi thật nhất — BA lỗi ngoài việc được giao, cả ba chỉ lộ ra khi CHẠY phép đo trên dữ liệu thật: (2) test.sensitivity ĐỔ IndexError trên mọi tệp firmware thật, vì chỗ giữ chú thích \x00{i}\x00 bị chính phép phá đổi số thành 99999 từ chỗ giữ thứ 11 — đường đo độ nhạy cho C chưa bao giờ chạy nổi trên một tệp thật; (3) mo_phong chạy lại sim.vvp CŨ khi biên dịch đổ, cho dat=True và pass_fail='PASS' — _don_tep_ra đã có từ 01/10 cho đúng chuyện này ở nextpnr, chỉ mo_phong là không gọi, và nó là TIỀN ĐỀ của chính nhiệm vụ này; (4) loi_nguoi_doc in 'nhìn thấy cả 0/1 tệp — phá tệp nào cũng có ca đỏ'. · Phá lại 22/22, lượt đầu 15/20; bốn chỗ LỌT cùng hình dạng: luật ĐÚNG nhưng nằm ở chỗ ca kiểm không với tới (hai closure, bảng phép không dựng nổi ca, và tầng báo lại). · Tập phép phá lần này TỰ KIỂM: so byte trước–sau và in [VÔ HIỆU] nếu không đổi gì.</t>
         </is>
       </c>
     </row>
@@ -16845,7 +18527,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17686,7 +19368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18139,271 +19821,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="28" customWidth="1" style="26" min="1" max="1"/>
-    <col width="110" customWidth="1" style="26" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="19.5" customHeight="1" s="27">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>PHƯƠNG PHÁP RÀ SOÁT VÀ NGUỒN</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="23.25" customHeight="1" s="27">
-      <c r="A3" s="53" t="inlineStr">
-        <is>
-          <t>Phạm vi</t>
-        </is>
-      </c>
-      <c r="B3" s="47" t="inlineStr">
-        <is>
-          <t>Thư mục EIDE_v3: src/eide (lõi Python), tests/ (69 tệp), tools/ (script phiên), docs/md (tài liệu thiết kế), ui/EIDEApp (Swift — chỉ tham khảo giao thức). Chỉ đọc, không sửa tệp nào của dự án.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="23.25" customHeight="1" s="27">
-      <c r="A4" s="53" t="inlineStr">
-        <is>
-          <t>Thang đối chiếu</t>
-        </is>
-      </c>
-      <c r="B4" s="47" t="inlineStr">
-        <is>
-          <t>Tài liệu 'Các mẫu kiến trúc AI Agent' (10/2026) của anh: 4 mẫu workflow, 9 mẫu single-agent (gồm ReAct), 5 mẫu multi-agent và Human-in-the-loop; nguyên tắc chọn mẫu đơn giản nhất, có trần bước/thời gian/token, có eval trước khi leo thang.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="23.25" customHeight="1" s="27">
-      <c r="A5" s="53" t="inlineStr">
-        <is>
-          <t>Cách làm</t>
-        </is>
-      </c>
-      <c r="B5" s="47" t="inlineStr">
-        <is>
-          <t>Chia 5 mảng rà soát song song (lõi tác tử; phân tích–thiết kế PM; mạch–ERC–HDL/FPGA; kiểm thử &amp; kiểm chứng; tri thức–RAG–bộ nhớ). Mỗi phát hiện phải dẫn tệp:dòng hoặc hàm đã đọc. Sau đó kiểm chứng lại trực tiếp các phát hiện P0 then chốt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45.75" customHeight="1" s="27">
-      <c r="A6" s="53" t="inlineStr">
-        <is>
-          <t>P0 đã kiểm lại bằng tay</t>
-        </is>
-      </c>
-      <c r="B6" s="47" t="inlineStr">
-        <is>
-          <t>subagent.py:309 gọi thẳng registry.run (không qua hook/policy) · hooks/standard.py:562 'task.run' bất kỳ tắt kiểm chứng · build/hdl.py:497 '"PASS" in tren' dò chuỗi con · store/eide_md.py::render cắt đuôi text[:keep] · loop.py:503 resume lấy bo_nen.tom_tat_hien_tai luôn None ở phiên mới · build/dot_bien.py: chay(p) trả False khi không biên dịch được vẫn tính 'thay' · config.py:198 temperature 0.0 + seed cố định · history.ghi_kho không có tham số deps.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="23.25" customHeight="1" s="27">
-      <c r="A7" s="53" t="inlineStr">
-        <is>
-          <t>Số liệu đo trong mã</t>
-        </is>
-      </c>
-      <c r="B7" s="47" t="inlineStr">
-        <is>
-          <t>Số công cụ (118, 73 core) và kích thước lược đồ (~77,6 nghìn ký tự ≈ 26 nghìn token) do người rà soát mảng 1 đo bằng build_registry(); các số 54% lời gọi là fs.read/grep/glob, 31/120 công cụ chưa nổ lần nào… lấy từ chú thích có số đo trong chính mã nguồn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="23.25" customHeight="1" s="27">
-      <c r="A8" s="53" t="inlineStr">
-        <is>
-          <t>Lưu ý</t>
-        </is>
-      </c>
-      <c r="B8" s="47" t="inlineStr">
-        <is>
-          <t>Số dòng là tại ngày 06/10/2026, có thể lệch sau khi sửa mã. Khuyến nghị temperature cho dòng Gemini 3 cần kiểm lại riêng cho gemini-3.8-flash bằng A/B trên 76 ca (M1-09). Công sức là ước lượng thô cho một người quen mã.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="27">
-      <c r="A9" s="53" t="inlineStr">
-        <is>
-          <t>[1]</t>
-        </is>
-      </c>
-      <c r="B9" s="47" t="inlineStr">
-        <is>
-          <t>Yao et al. (2022). ReAct: Synergizing Reasoning and Acting in Language Models. arXiv:2210.03629.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="27">
-      <c r="A10" s="53" t="inlineStr">
-        <is>
-          <t>[2]</t>
-        </is>
-      </c>
-      <c r="B10" s="47" t="inlineStr">
-        <is>
-          <t>Wang et al. (2023). Plan-and-Solve Prompting. arXiv:2305.04091.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="27">
-      <c r="A11" s="53" t="inlineStr">
-        <is>
-          <t>[3]</t>
-        </is>
-      </c>
-      <c r="B11" s="47" t="inlineStr">
-        <is>
-          <t>Xu et al. (2023). ReWOO. arXiv:2305.18323.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="27">
-      <c r="A12" s="53" t="inlineStr">
-        <is>
-          <t>[4]</t>
-        </is>
-      </c>
-      <c r="B12" s="47" t="inlineStr">
-        <is>
-          <t>Kim et al. (2023). An LLM Compiler for Parallel Function Calling. arXiv:2312.04511.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="27">
-      <c r="A13" s="53" t="inlineStr">
-        <is>
-          <t>[5]</t>
-        </is>
-      </c>
-      <c r="B13" s="47" t="inlineStr">
-        <is>
-          <t>Shinn et al. (2023). Reflexion: Language Agents with Verbal Reinforcement Learning. arXiv:2303.11366.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="27">
-      <c r="A14" s="53" t="inlineStr">
-        <is>
-          <t>[6]</t>
-        </is>
-      </c>
-      <c r="B14" s="47" t="inlineStr">
-        <is>
-          <t>Yao et al. (2023). Tree of Thoughts. arXiv:2305.10601.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="27">
-      <c r="A15" s="53" t="inlineStr">
-        <is>
-          <t>[7]</t>
-        </is>
-      </c>
-      <c r="B15" s="47" t="inlineStr">
-        <is>
-          <t>Zhou et al. (2023). Language Agent Tree Search (LATS). arXiv:2310.04406.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="27">
-      <c r="A16" s="53" t="inlineStr">
-        <is>
-          <t>[8]</t>
-        </is>
-      </c>
-      <c r="B16" s="47" t="inlineStr">
-        <is>
-          <t>Wang et al. (2024). Executable Code Actions Elicit Better LLM Agents (CodeAct). arXiv:2402.01030.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="27">
-      <c r="A17" s="53" t="inlineStr">
-        <is>
-          <t>[9]</t>
-        </is>
-      </c>
-      <c r="B17" s="47" t="inlineStr">
-        <is>
-          <t>Asai et al. (2023). Self-RAG. arXiv:2310.11511.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="27">
-      <c r="A18" s="53" t="inlineStr">
-        <is>
-          <t>[10]</t>
-        </is>
-      </c>
-      <c r="B18" s="47" t="inlineStr">
-        <is>
-          <t>Packer et al. (2023). MemGPT: Towards LLMs as Operating Systems. arXiv:2310.08560.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="27">
-      <c r="A19" s="53" t="inlineStr">
-        <is>
-          <t>[11]</t>
-        </is>
-      </c>
-      <c r="B19" s="47" t="inlineStr">
-        <is>
-          <t>Du et al. (2023). Improving Factuality and Reasoning through Multiagent Debate. arXiv:2305.14325.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="27">
-      <c r="A20" s="53" t="inlineStr">
-        <is>
-          <t>[12]</t>
-        </is>
-      </c>
-      <c r="B20" s="47" t="inlineStr">
-        <is>
-          <t>Wu et al. (2023). AutoGen. arXiv:2308.08155.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="27">
-      <c r="A21" s="53" t="inlineStr">
-        <is>
-          <t>[13]</t>
-        </is>
-      </c>
-      <c r="B21" s="47" t="inlineStr">
-        <is>
-          <t>Anthropic (2024). Building effective agents. anthropic.com/engineering/building-effective-agents.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="27">
-      <c r="A22" s="53" t="inlineStr">
-        <is>
-          <t>[14]</t>
-        </is>
-      </c>
-      <c r="B22" s="47" t="inlineStr">
-        <is>
-          <t>Anthropic (2025). How we built our multi-agent research system. anthropic.com/engineering/multi-agent-research-system.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
 </file>
--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -13,13 +13,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 08-10-2026 (chiều)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 08-10-2026 (toi)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 08-10-2026 (khuya)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục tối ưu" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đối chiếu 18 mẫu" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 09-10-2026" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục tối ưu" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đối chiếu 18 mẫu" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -2104,13 +2105,13 @@
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
+    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B48:G48"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
@@ -2122,6 +2123,461 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="5" customWidth="1" style="26" min="1" max="1"/>
+    <col width="34" customWidth="1" style="26" min="2" max="3"/>
+    <col width="55" customWidth="1" style="26" min="4" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="19.5" customHeight="1" s="27">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>ĐIỂM MẠNH HIỆN CÓ — GIỮ NGUYÊN, KHÔNG ĐỀ XUẤT TRÙNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="27">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>Cơ chế</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>Vị trí</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="inlineStr">
+        <is>
+          <t>Vì sao giá trị</t>
+        </is>
+      </c>
+      <c r="E3" s="31" t="inlineStr">
+        <is>
+          <t>Cách tận dụng khi tối ưu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34.5" customHeight="1" s="27">
+      <c r="A4" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="53" t="inlineStr">
+        <is>
+          <t>Ba lớp xác định quanh mọi lời gọi công cụ</t>
+        </is>
+      </c>
+      <c r="C4" s="47" t="inlineStr">
+        <is>
+          <t>loop.py::_one_tool; hooks/; policy/engine.py</t>
+        </is>
+      </c>
+      <c r="D4" s="47" t="inlineStr">
+        <is>
+          <t>Mô hình không có đường nào làm việc mà không qua pre_tool_use → policy → post_tool_use; lỗi quay về mô hình như dữ liệu kèm hướng dẫn.</t>
+        </is>
+      </c>
+      <c r="E4" s="47" t="inlineStr">
+        <is>
+          <t>Tách thành hàm dùng chung để tác tử con cũng đi qua (M1-03).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="23.25" customHeight="1" s="27">
+      <c r="A5" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="53" t="inlineStr">
+        <is>
+          <t>Transcript ghi trước (write-ahead)</t>
+        </is>
+      </c>
+      <c r="C5" s="47" t="inlineStr">
+        <is>
+          <t>loop.py::DanhSachGhiDia; memory/transcript.py</t>
+        </is>
+      </c>
+      <c r="D5" s="47" t="inlineStr">
+        <is>
+          <t>Mọi message xuống đĩa trước khi vào RAM; phát hiện phiên dừng giữa chừng và công cụ có tác dụng phụ chưa có kết quả.</t>
+        </is>
+      </c>
+      <c r="E5" s="47" t="inlineStr">
+        <is>
+          <t>Nền cho checkpoint HITL và resume đầy đủ (M5-17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="23.25" customHeight="1" s="27">
+      <c r="A6" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="53" t="inlineStr">
+        <is>
+          <t>Thẻ cổng + nhớ duyệt trong lượt</t>
+        </is>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t>loop.py::_da_duyet_roi</t>
+        </is>
+      </c>
+      <c r="D6" s="47" t="inlineStr">
+        <is>
+          <t>Bớt 16 thẻ G-DATA cho cùng một công cụ, nhưng vẫn hỏi lại với thao tác không hoàn tác, never_auto, ≥R4.</t>
+        </is>
+      </c>
+      <c r="E6" s="47" t="inlineStr">
+        <is>
+          <t>Giữ quy tắc này khi thêm cổng G-QUAL cho sửa test (M4-02).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="23.25" customHeight="1" s="27">
+      <c r="A7" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="53" t="inlineStr">
+        <is>
+          <t>Plan mode khoá công cụ ghi + kiểm kế hoạch bằng mã</t>
+        </is>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>ke_hoach.py; loop.py::_khoa_khi_soan_ke_hoach</t>
+        </is>
+      </c>
+      <c r="D7" s="47" t="inlineStr">
+        <is>
+          <t>Trình cách làm trước khi tiêu lời gọi; đòi bước chọn kiến trúc và code.analyze.</t>
+        </is>
+      </c>
+      <c r="E7" s="47" t="inlineStr">
+        <is>
+          <t>Mở rộng bằng tiêu chí xong + plan.revise (M1-13, M2-06).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="23.25" customHeight="1" s="27">
+      <c r="A8" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="53" t="inlineStr">
+        <is>
+          <t>Phát hiện quay vòng + câu thay cho im lặng / hết ngân sách</t>
+        </is>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>loop.py::_nhac_neu_dang_quay_vong, _cau_im_lang, _cau_het_ngan_sach</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
+        <is>
+          <t>Biến chỗ mù của mô hình thành tín hiệu; luôn nói ra đã làm gì và cần gõ gì để đi tiếp.</t>
+        </is>
+      </c>
+      <c r="E8" s="47" t="inlineStr">
+        <is>
+          <t>Bổ sung chống lời gọi trùng y hệt và leo thang (M1-17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34.5" customHeight="1" s="27">
+      <c r="A9" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="53" t="inlineStr">
+        <is>
+          <t>Tiêu chí-trước cho mô phỏng, EIDE phán bằng mã</t>
+        </is>
+      </c>
+      <c r="C9" s="47" t="inlineStr">
+        <is>
+          <t>build/tieu_chi.py::xet_ket_qua; tools/xay_dung.py::sim_run</t>
+        </is>
+      </c>
+      <c r="D9" s="47" t="inlineStr">
+        <is>
+          <t>Chương trình chỉ đo, EIDE so ngưỡng có nguồn; ba trạng thái dat/khong_dat/chua_do_duoc; đổi ngưỡng sau kết quả phải qua G-QUAL.</t>
+        </is>
+      </c>
+      <c r="E9" s="47" t="inlineStr">
+        <is>
+          <t>Dùng làm lõi chung cho unit test, HDL, HIL (M4-01, M4-14, M3-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="23.25" customHeight="1" s="27">
+      <c r="A10" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="53" t="inlineStr">
+        <is>
+          <t>Đọc ngược Flash khi nạp</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>tools/mach_that.py::target_verify</t>
+        </is>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
+        <is>
+          <t>So từng byte sau khi nạp, và nói thẳng khi công cụ nạp không hỗ trợ verify.</t>
+        </is>
+      </c>
+      <c r="E10" s="47" t="inlineStr">
+        <is>
+          <t>Nối với hil.run để kiểm thử trên bo có máy chấm (M4-14).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="23.25" customHeight="1" s="27">
+      <c r="A11" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="53" t="inlineStr">
+        <is>
+          <t>Tác tử tự viết công cụ có test và duyệt</t>
+        </is>
+      </c>
+      <c r="C11" s="47" t="inlineStr">
+        <is>
+          <t>nang_luc.py; tools/nang_luc.py (tool.propose)</t>
+        </is>
+      </c>
+      <c r="D11" s="47" t="inlineStr">
+        <is>
+          <t>Năng lực tự mở rộng có kiểm soát; công cụ đã duyệt được nạp lại khi mở dự án.</t>
+        </is>
+      </c>
+      <c r="E11" s="47" t="inlineStr">
+        <is>
+          <t>Làm đích nâng cấp cho đoạn py.phan_tich dùng lại ≥3 lần (M1-21).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="23.25" customHeight="1" s="27">
+      <c r="A12" s="48" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="53" t="inlineStr">
+        <is>
+          <t>Kiểm xuất xứ quyết định của người</t>
+        </is>
+      </c>
+      <c r="C12" s="47" t="inlineStr">
+        <is>
+          <t>tools/design.py::_kiem_nguoi_that_su_chon</t>
+        </is>
+      </c>
+      <c r="D12" s="47" t="inlineStr">
+        <is>
+          <t>Chặn tác tử tự nhận 'người đã chọn' mà không có câu trích thật trong sổ cái.</t>
+        </is>
+      </c>
+      <c r="E12" s="47" t="inlineStr">
+        <is>
+          <t>Áp lại cho store.req_create/req_update (M2-19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="23.25" customHeight="1" s="27">
+      <c r="A13" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="53" t="inlineStr">
+        <is>
+          <t>Chốt hằng số không nguồn (constant_guard, N1)</t>
+        </is>
+      </c>
+      <c r="C13" s="47" t="inlineStr">
+        <is>
+          <t>hooks/standard.py</t>
+        </is>
+      </c>
+      <c r="D13" s="47" t="inlineStr">
+        <is>
+          <t>Số trong mã phải có Fact hoặc lời người; chặn số nhớ/bịa.</t>
+        </is>
+      </c>
+      <c r="E13" s="47" t="inlineStr">
+        <is>
+          <t>Cần chạy cả cho tác tử con (M1-03) và cho câu trả lời văn xuôi (M5-02).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="23.25" customHeight="1" s="27">
+      <c r="A14" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="53" t="inlineStr">
+        <is>
+          <t>Phong bì kết quả + blob</t>
+        </is>
+      </c>
+      <c r="C14" s="47" t="inlineStr">
+        <is>
+          <t>memory/envelope.py; memory/compact.py (C1)</t>
+        </is>
+      </c>
+      <c r="D14" s="47" t="inlineStr">
+        <is>
+          <t>Kết quả dài không đi nguyên văn vào transcript; mô hình đọc lại bằng blob.read.</t>
+        </is>
+      </c>
+      <c r="E14" s="47" t="inlineStr">
+        <is>
+          <t>Thêm chính sách riêng cho doc.read / fact.* (M5-13) và cho tác tử con (M1-05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="23.25" customHeight="1" s="27">
+      <c r="A15" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="53" t="inlineStr">
+        <is>
+          <t>Bộ dò 'ok nhưng rỗng'</t>
+        </is>
+      </c>
+      <c r="C15" s="47" t="inlineStr">
+        <is>
+          <t>ket_qua.py::khong_noi_gi</t>
+        </is>
+      </c>
+      <c r="D15" s="47" t="inlineStr">
+        <is>
+          <t>Phân biệt lời gọi thành công với kết quả có nội dung; nhắc một lần mỗi công cụ.</t>
+        </is>
+      </c>
+      <c r="E15" s="47" t="inlineStr">
+        <is>
+          <t>Dời lời nhắc ra sau message tool để không lệch cặp gọi–trả (M1-01).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="23.25" customHeight="1" s="27">
+      <c r="A16" s="48" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="53" t="inlineStr">
+        <is>
+          <t>Bộ nhớ có tombstone + duyệt trước khi nhớ người dùng</t>
+        </is>
+      </c>
+      <c r="C16" s="47" t="inlineStr">
+        <is>
+          <t>store/eide_md.py; memory/nguoi_dung.py</t>
+        </is>
+      </c>
+      <c r="D16" s="47" t="inlineStr">
+        <is>
+          <t>Điều đã quên không hồi sinh; không ghi bộ nhớ người dùng khi chưa bấm đồng ý.</t>
+        </is>
+      </c>
+      <c r="E16" s="47" t="inlineStr">
+        <is>
+          <t>Giữ khi thêm hiện vật 'lesson' (M5-14).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="27">
+      <c r="A17" s="48" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="53" t="inlineStr">
+        <is>
+          <t>Sơ đồ kiến trúc chỉ vẽ khi có cạnh thật</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="inlineStr">
+        <is>
+          <t>kien_truc.py</t>
+        </is>
+      </c>
+      <c r="D17" s="47" t="inlineStr">
+        <is>
+          <t>Không vẽ sơ đồ trang trí; nói rõ vì sao không vẽ được.</t>
+        </is>
+      </c>
+      <c r="E17" s="47" t="inlineStr">
+        <is>
+          <t>Mở rộng kiểm phân tầng (M2-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="23.25" customHeight="1" s="27">
+      <c r="A18" s="48" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="53" t="inlineStr">
+        <is>
+          <t>Bộ 76 ca + ReplayGateway/RecordingGateway</t>
+        </is>
+      </c>
+      <c r="C18" s="47" t="inlineStr">
+        <is>
+          <t>tools/bo_usecase.py; llm/offline.py</t>
+        </is>
+      </c>
+      <c r="D18" s="47" t="inlineStr">
+        <is>
+          <t>Đã có hạ tầng phát lại 0 token, chỉ chưa được dùng trong pytest/CI.</t>
+        </is>
+      </c>
+      <c r="E18" s="47" t="inlineStr">
+        <is>
+          <t>Dựng eval phát lại + CI (M4-21).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="102" customHeight="1" s="27">
+      <c r="A19" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="53" t="inlineStr">
+        <is>
+          <t>Tổng hợp điểm mạnh mảng kiểm thử (từ người rà soát mảng 4)</t>
+        </is>
+      </c>
+      <c r="C19" s="47" t="inlineStr">
+        <is>
+          <t>build/tieu_chi.py::xet_ket_qua; tools/xay_dung.py::sim_run (E4008/E4009/E4023); ket_qua.py::khong_noi_gi; kiem_chung.py::co_viec_chua_kiem; tools/mach_that.py::target_verify; loop.py dòng ~1070 (đổi ngưỡng → STALE)</t>
+        </is>
+      </c>
+      <c r="D19" s="47" t="inlineStr">
+        <is>
+          <t>Đã có: criteria-first thật cho sim.run (chưa có tiêu chí thì từ chối, chưa có trich_loi người xác nhận thì từ chối); EIDE phán bằng code, thiếu số đo = chua_do_duoc; chặn lệch cặp tiêu chí/nguồn (E4023); khai phần không mô phỏng được đi kèm kết luận; đổi ngưỡng sau khi có kết quả đi qua G-QUAL; bộ dò 'ok nhưng rỗng'; Stop hook đòi verifier đọc từ sổ cái bền qua lần khởi động lại; target.verify đọc ngược Flash so từng byte; test.sensitivity phát hiện test tự định nghĩa lại hàm (khong_nap_duoc); test.run báo tệp sản phẩm nào được dịch cùng.</t>
+        </is>
+      </c>
+      <c r="E19" s="47" t="inlineStr">
+        <is>
+          <t>Dùng lại tieu_chi.py (Assert/TieuChi/xet_ket_qua) làm lõi chung cho test.criteria, hil.criteria và khuôn {"do":…} của HDL, thay vì viết ba máy chấm. Giữ nguyên ngữ nghĩa ba trạng thái dat/khong_dat/chua_do_duoc ở mọi nơi.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7164,7 +7620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" style="27" min="1" max="1"/>
@@ -7190,6 +7646,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="59" t="inlineStr">
         <is>
@@ -7263,6 +7720,7 @@
       </c>
       <c r="C8" s="61" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="59" t="inlineStr">
         <is>
@@ -7439,6 +7897,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="59" t="inlineStr">
         <is>
@@ -8149,6 +8608,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="59" t="inlineStr">
         <is>
@@ -8293,6 +8753,7 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="59" t="inlineStr">
         <is>
@@ -8533,12 +8994,1473 @@
         </is>
       </c>
     </row>
+    <row r="73"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G89"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" customWidth="1" style="27" min="1" max="1"/>
+    <col width="66" customWidth="1" style="27" min="2" max="2"/>
+    <col width="24" customWidth="1" style="27" min="3" max="3"/>
+    <col width="8" customWidth="1" style="27" min="4" max="4"/>
+    <col width="11" customWidth="1" style="27" min="5" max="5"/>
+    <col width="16" customWidth="1" style="27" min="6" max="6"/>
+    <col width="34" customWidth="1" style="27" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="57" t="inlineStr">
+        <is>
+          <t>TIẾN ĐỘ ĐỢT TỐI ƯU TÁC TỬ — chốt ngày 09/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="58" t="inlineStr">
+        <is>
+          <t>Mỗi dòng 'Xong' đều có: mục DEV-LOG tra lại được · số ca kiểm trước→sau · một con số đo trên dữ liệu thật · phần còn nợ. Cột chi tiết nằm ở sheet “Danh mục tối ưu”, cột T–Y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="59" t="inlineStr">
+        <is>
+          <t>Tổng quan</t>
+        </is>
+      </c>
+      <c r="B4" s="59" t="inlineStr">
+        <is>
+          <t>Số việc</t>
+        </is>
+      </c>
+      <c r="C4" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>Xong (đã gộp vào main, đã đẩy)</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>20 việc đầu của Giai đoạn 1, theo đúng thứ tự # của kế hoạch</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="60" t="inlineStr">
+        <is>
+          <t>Đang làm (chưa commit)</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="61" t="inlineStr">
+        <is>
+          <t>không việc nào đang dở</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="60" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="n">
+        <v>86</v>
+      </c>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>86 việc còn lại trong 106</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="62" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B8" s="62" t="n">
+        <v>106</v>
+      </c>
+      <c r="C8" s="61" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>Phép đo của cả đợt</t>
+        </is>
+      </c>
+      <c r="B10" s="59" t="inlineStr">
+        <is>
+          <t>Trước (06/10)</t>
+        </is>
+      </c>
+      <c r="C10" s="59" t="inlineStr">
+        <is>
+          <t>Sau (08/10)</t>
+        </is>
+      </c>
+      <c r="D10" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị Python (pytest -q)</t>
+        </is>
+      </c>
+      <c r="B11" s="63" t="inlineStr">
+        <is>
+          <t>1 610</t>
+        </is>
+      </c>
+      <c r="C11" s="63" t="inlineStr">
+        <is>
+          <t>1 846</t>
+        </is>
+      </c>
+      <c r="D11" s="63" t="inlineStr">
+        <is>
+          <t>+236 ca so với 06/10; không ca cũ nào đỏ ở bất kỳ bước nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị giao diện (swift test)</t>
+        </is>
+      </c>
+      <c r="B12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="inlineStr">
+        <is>
+          <t>không nhiệm vụ nào đụng ui/ — kiểu khối A2.2 dùng “table”, Swift đã dựng được</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>kiem_tai_lieu.py</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="C13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ LỆCH CHẮC CHẮN cả hai lượt. Hôm nay nó bắt đúng chuyện cần bắt: hai công cụ mới làm README lệch số công cụ 127 → 129, và số 'cần đọc lại' nhảy 11 → 15 → về 11 sau khi sửa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>thu_sch.py (cờ schematic bật)</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="C14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="D14" s="63" t="inlineStr">
+        <is>
+          <t>chạy ở M3-03 và M3-04, không tụt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t>Mục DEV-LOG mới</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330 → DEV-349</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="inlineStr">
+        <is>
+          <t>20 mục, mỗi việc một mục</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="63" t="inlineStr">
+        <is>
+          <t>Cờ tính năng mới</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>1 (schematic)</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="63" t="inlineStr">
+        <is>
+          <t>7 cờ mới, TẤT CẢ mặc định TẮT. Cờ thứ 7 là SIM_RUNNER_GIOI_HAN (M4-02) — nó giới hạn fs.write của sim-runner trong sim/; hàng rào chính của M4-02 (POL-N6-sua-test) thì KHÔNG sau cờ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="63" t="inlineStr">
+        <is>
+          <t>Mã lỗi mới</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>E4031 · E4032 · E6012 · E4033 · E4024</t>
+        </is>
+      </c>
+      <c r="D17" s="63" t="inlineStr">
+        <is>
+          <t>M4-05 không thêm mã nào. M4-02 cũng không (dùng lại E5006). E4033 (M3-18), E4024 (M4-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="59" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="C19" s="59" t="inlineStr">
+        <is>
+          <t>Mảng</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="E19" s="59" t="inlineStr">
+        <is>
+          <t>DEV-LOG</t>
+        </is>
+      </c>
+      <c r="F19" s="59" t="inlineStr">
+        <is>
+          <t>Ca kiểm</t>
+        </is>
+      </c>
+      <c r="G19" s="59" t="inlineStr">
+        <is>
+          <t>Cờ mặc định</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="63" t="inlineStr">
+        <is>
+          <t>M1-01</t>
+        </is>
+      </c>
+      <c r="C20" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D20" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E20" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330</t>
+        </is>
+      </c>
+      <c r="F20" s="63" t="inlineStr">
+        <is>
+          <t>105/309 phiên thật có lịch sử tự mâu thuẫn — 255 chỗ (156 kết quả thứ hai cùng id, 74 message chen giữa, 24 kết quả lạc lượt, 1 lời gọi không kết quả)</t>
+        </is>
+      </c>
+      <c r="G20" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="63" t="inlineStr">
+        <is>
+          <t>M1-02</t>
+        </is>
+      </c>
+      <c r="C21" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D21" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E21" s="63" t="inlineStr">
+        <is>
+          <t>DEV-331</t>
+        </is>
+      </c>
+      <c r="F21" s="63" t="inlineStr">
+        <is>
+          <t>lược đồ công cụ thật: 25 869 token/lời gọi (trần tool_schema=4000 chưa dòng mã nào đọc). Cờ bật: 4 475 token, giảm 82,7 %; 73 → 18 công cụ</t>
+        </is>
+      </c>
+      <c r="G21" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="63" t="inlineStr">
+        <is>
+          <t>M1-03</t>
+        </is>
+      </c>
+      <c r="C22" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D22" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E22" s="63" t="inlineStr">
+        <is>
+          <t>DEV-332</t>
+        </is>
+      </c>
+      <c r="F22" s="63" t="inlineStr">
+        <is>
+          <t>1 822 lời gọi của tác tử con trong 26 phiên thật, 0 lần qua lớp luật. Toàn công cụ đọc trừ một build.compile — lỗ hổng chưa bị bước vào, không phải được canh</t>
+        </is>
+      </c>
+      <c r="G22" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="63" t="inlineStr">
+        <is>
+          <t>M2-01</t>
+        </is>
+      </c>
+      <c r="C23" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D23" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E23" s="63" t="inlineStr">
+        <is>
+          <t>DEV-333</t>
+        </is>
+      </c>
+      <c r="F23" s="63" t="inlineStr">
+        <is>
+          <t>kịch bản 3 REQ + 3 phương án + 3 tiêu chí + 3 tệp: sửa MỘT REQ làm 9 hiện vật STALE → còn 3. Phép đo đầu ra 6→2 vì bị hàng rào E4020 chặn, đã sửa kịch bản đo</t>
+        </is>
+      </c>
+      <c r="G23" s="63" t="inlineStr">
+        <is>
+          <t>TRUY_VET — TẮT (phần nền chạy cả khi tắt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>M2-02</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D24" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E24" s="63" t="inlineStr">
+        <is>
+          <t>DEV-334</t>
+        </is>
+      </c>
+      <c r="F24" s="63" t="inlineStr">
+        <is>
+          <t>63 kho thật: 5/37 REQ có ít nhất một phép đo; 27 chưa có phương án nào nhận; 0 REQ đi hết chuỗi. Cột 'Mã nguồn' trống ở MỌI dự án vì hien_thuc_req vừa mới tồn tại</t>
+        </is>
+      </c>
+      <c r="G24" s="63" t="inlineStr">
+        <is>
+          <t>REQ_PHU — TẮT (khối A2.2 trên tab không phụ thuộc cờ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="63" t="inlineStr">
+        <is>
+          <t>M2-03</t>
+        </is>
+      </c>
+      <c r="C25" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D25" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E25" s="63" t="inlineStr">
+        <is>
+          <t>DEV-335</t>
+        </is>
+      </c>
+      <c r="F25" s="63" t="inlineStr">
+        <is>
+          <t>37 REQ thật: 25 sạch (67 %), 11 thiếu tiêu chí đo được, 2 có từ mơ hồ. Lần đo đầu ra 3 từ mơ hồ, một là kêu oan ('ít nhất 2 lần' là mức đo được) — đã vá</t>
+        </is>
+      </c>
+      <c r="G25" s="63" t="inlineStr">
+        <is>
+          <t>REQ_CHAT_LUONG — TẮT (module yeu_cau.py luôn có)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="63" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="63" t="inlineStr">
+        <is>
+          <t>M2-06</t>
+        </is>
+      </c>
+      <c r="C26" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D26" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E26" s="63" t="inlineStr">
+        <is>
+          <t>DEV-336</t>
+        </is>
+      </c>
+      <c r="F26" s="63" t="inlineStr">
+        <is>
+          <t>sổ cái thật: 26 lần đánh dấu 'xong' ngay sau một lần ghi mã, 19 lần (73 %) không có phép kiểm nào đạt ở giữa. Phép đo đầu ở mức dự án ra 0 — đúng nhưng đo sai câu hỏi</t>
+        </is>
+      </c>
+      <c r="G26" s="63" t="inlineStr">
+        <is>
+          <t>KE_HOACH_CONG_KIEM — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="63" t="inlineStr">
+        <is>
+          <t>M2-08</t>
+        </is>
+      </c>
+      <c r="C27" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D27" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E27" s="63" t="inlineStr">
+        <is>
+          <t>DEV-337</t>
+        </is>
+      </c>
+      <c r="F27" s="63" t="inlineStr">
+        <is>
+          <t>185 tệp .c thật: 1 758 → 1 786 hàm thấy được (+28 hàm trước đây VÔ HÌNH: 8 ngắt + 20 bị regex tham lam nuốt). 78 hàm nay gắn nhãn 'isr', 70 trong đó vốn đã có trong danh sách</t>
+        </is>
+      </c>
+      <c r="G27" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="63" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="63" t="inlineStr">
+        <is>
+          <t>M3-01</t>
+        </is>
+      </c>
+      <c r="C28" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D28" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E28" s="63" t="inlineStr">
+        <is>
+          <t>DEV-338</t>
+        </is>
+      </c>
+      <c r="F28" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mô hình mạch thật — và lý do đáng hơn con số: 3 kho CÓ Fact v_max thì KHÔNG có mô hình mạch, 5 kho có mạch thì không có Fact ấy; thêm nữa Fact dùng chủ thể chip:X mà ERC không tra tiền tố đó</t>
+        </is>
+      </c>
+      <c r="G28" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="63" t="inlineStr">
+        <is>
+          <t>M3-03</t>
+        </is>
+      </c>
+      <c r="C29" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D29" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E29" s="63" t="inlineStr">
+        <is>
+          <t>DEV-339</t>
+        </is>
+      </c>
+      <c r="F29" s="63" t="inlineStr">
+        <is>
+          <t>8 phát hiện trên 5 mạch thật (6 nguon_khong_cap + 2 net_mot_chan), trong đó net clock I2C nối đúng một chân. SÁU trong tám là 'mô hình chưa khai' chứ không phải 'mạch sai'. robot-canbang: 107 Port lá, KHÔNG Port nào là power_out</t>
+        </is>
+      </c>
+      <c r="G29" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="63" t="n">
+        <v>11</v>
+      </c>
+      <c r="B30" s="63" t="inlineStr">
+        <is>
+          <t>M3-04</t>
+        </is>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D30" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E30" s="63" t="inlineStr">
+        <is>
+          <t>DEV-340</t>
+        </is>
+      </c>
+      <c r="F30" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mạch thật — và đây là con số ĐÚNG (hai lỗi này catastrophic, không bo nào sống tới lúc lưu kho). Đã CẤY hai bộ cấp vào bản sao kho robot-canbang để chứng minh luật sống: nổ đúng 1 blocker trên net +5V thật</t>
+        </is>
+      </c>
+      <c r="G30" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="B31" s="63" t="inlineStr">
+        <is>
+          <t>M3-07</t>
+        </is>
+      </c>
+      <c r="C31" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D31" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E31" s="63" t="inlineStr">
+        <is>
+          <t>DEV-341</t>
+        </is>
+      </c>
+      <c r="F31" s="63" t="inlineStr">
+        <is>
+          <t>Fact tới được ERC: 5 → 17 (+12). Ba kho có Fact datasheet thì TOÀN BỘ mang chủ thể chip:, tức trước đó không một Fact nào tới được ERC. Độ phủ 5 mạch thật nay đọc được</t>
+        </is>
+      </c>
+      <c r="G31" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="63" t="n">
+        <v>13</v>
+      </c>
+      <c r="B32" s="63" t="inlineStr">
+        <is>
+          <t>M3-10</t>
+        </is>
+      </c>
+      <c r="C32" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D32" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E32" s="63" t="inlineStr">
+        <is>
+          <t>DEV-342</t>
+        </is>
+      </c>
+      <c r="F32" s="63" t="inlineStr">
+        <is>
+          <t>chi phí đo thật: mạch lớn nhất trong kho 187 nút → ERC 7,6 ms mỗi lần ghi. Trần 2000 nút, vượt thì NÓI RA chứ không im lặng bỏ qua</t>
+        </is>
+      </c>
+      <c r="G32" s="63" t="inlineStr">
+        <is>
+          <t>ERC_TU_DONG — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="B33" s="63" t="inlineStr">
+        <is>
+          <t>M3-12</t>
+        </is>
+      </c>
+      <c r="C33" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D33" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E33" s="63" t="inlineStr">
+        <is>
+          <t>DEV-343</t>
+        </is>
+      </c>
+      <c r="F33" s="63" t="inlineStr">
+        <is>
+          <t>846 bản ghi mô phỏng thật: regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 (testbench dự án in 'KET QUA: PASS' — nhãn đứng TRƯỚC từ khoá). Nới đúng một chỗ → 846/846 khớp, vẫn bắt đủ bốn ca PASS giả</t>
+        </is>
+      </c>
+      <c r="G33" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="64" t="n">
+        <v>15</v>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>M3-13</t>
+        </is>
+      </c>
+      <c r="C34" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D34" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E34" s="64" t="inlineStr">
+        <is>
+          <t>DEV-344</t>
+        </is>
+      </c>
+      <c r="F34" s="64" t="inlineStr">
+        <is>
+          <t>testbench Verilog THẬT của bài 3: tb_pcpi_dot4 1/1, tb_pcpi_mac 1/1, tb_pcpi_vmini không đo được (tb gọi bản bram HAI CỔNG đã bị bỏ 02/10) — mẫu số là TỆP, không phải phép phá</t>
+        </is>
+      </c>
+      <c r="G34" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="64" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B35" s="64" t="inlineStr">
+        <is>
+          <t>M3-18</t>
+        </is>
+      </c>
+      <c r="C35" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D35" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E35" s="64" t="inlineStr">
+        <is>
+          <t>DEV-345</t>
+        </is>
+      </c>
+      <c r="F35" s="64" t="inlineStr">
+        <is>
+          <t>6 cặp (mạng cổng, .cst) thật → 1 chỗ CHẶN: blinky của riscv-tn20k-b dựng bitstream 4,6 MB với chân đồng hồ do nextpnr tự chọn (rơi đúng chân 4 — bằng may). Cả 7 tệp .cst thật đọc hết, 0 lỗi cú pháp</t>
+        </is>
+      </c>
+      <c r="G35" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="64" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B36" s="64" t="inlineStr">
+        <is>
+          <t>M4-01</t>
+        </is>
+      </c>
+      <c r="C36" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D36" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E36" s="64" t="inlineStr">
+        <is>
+          <t>DEV-346</t>
+        </is>
+      </c>
+      <c r="F36" s="64" t="inlineStr">
+        <is>
+          <t>18 ca chạy trình biên dịch C thật: tệp test in số đo {"T1":300} với ngưỡng &lt;=255 → EIDE phán 1 ca HỎNG. Chưa kho cũ nào có tiêu chí unit test để đo lại trên dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="G36" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="64" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B37" s="64" t="inlineStr">
+        <is>
+          <t>M4-02</t>
+        </is>
+      </c>
+      <c r="C37" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D37" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E37" s="64" t="inlineStr">
+        <is>
+          <t>DEV-347</t>
+        </is>
+      </c>
+      <c r="F37" s="64" t="inlineStr">
+        <is>
+          <t>25 ca dựng đúng trạng thái thật (tệp test 3 ca, 1 ca đỏ, hiện vật dat=False) → fs.write còn 1 ca thì test.weakened=True. Và hàng rào cũ criteria.has_result chưa bao giờ nổ ngoài sim-01</t>
+        </is>
+      </c>
+      <c r="G37" s="64" t="inlineStr">
+        <is>
+          <t>SIM_RUNNER_GIOI_HAN — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="64" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B38" s="64" t="inlineStr">
+        <is>
+          <t>M4-05</t>
+        </is>
+      </c>
+      <c r="C38" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D38" s="64" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E38" s="64" t="inlineStr">
+        <is>
+          <t>DEV-348</t>
+        </is>
+      </c>
+      <c r="F38" s="64" t="inlineStr">
+        <is>
+          <t>du-lieu/rtos-sinhvien, chạy CẢ HAI hành vi: cũ so_thay=1, mới so_thay=0 — logo_ptit.c từ 'bộ kiểm ĐỎ' thành 'mọi đột biến đều làm hỏng biên dịch'. Một ô xanh giả, đã sửa</t>
+        </is>
+      </c>
+      <c r="G38" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B39" s="64" t="inlineStr">
+        <is>
+          <t>M4-19</t>
+        </is>
+      </c>
+      <c r="C39" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D39" s="64" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E39" s="64" t="inlineStr">
+        <is>
+          <t>DEV-349</t>
+        </is>
+      </c>
+      <c r="F39" s="64" t="inlineStr">
+        <is>
+          <t>chạy TẠI CHỖ trên ba dự án firmware thật: kết luận giống hệt lượt đột biến tại chỗ của M4-05, và 50/50 tệp giữ nguyên cả sha256 lẫn mtime</t>
+        </is>
+      </c>
+      <c r="G39" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="59" t="inlineStr">
+        <is>
+          <t>Việc còn MỞ (ngoài 86 việc chưa làm)</t>
+        </is>
+      </c>
+      <c r="B41" s="59" t="inlineStr">
+        <is>
+          <t>Vì sao còn mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="63" t="inlineStr">
+        <is>
+          <t>Bảy cờ mới đều còn TẮT</t>
+        </is>
+      </c>
+      <c r="B42" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU · TRUY_VET · REQ_PHU · REQ_CHAT_LUONG · KE_HOACH_CONG_KIEM · ERC_TU_DONG · SIM_RUNNER_GIOI_HAN. Cả bảy đổi thứ Agent nhìn thấy, đọc, hoặc LÀM ĐƯỢC mỗi lượt, nên chỉ bộ 76 ca chạy hai chế độ mới nói được chúng làm Agent khá hơn hay tệ hơn. Bộ ấy tốn tiền mô hình nên §3.0 bắt hỏi người dùng trước.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="63" t="inlineStr">
+        <is>
+          <t>kiem_cap_goi_tra() chưa thành hàng rào</t>
+        </is>
+      </c>
+      <c r="B43" s="63" t="inlineStr">
+        <is>
+          <t>Soát được mọi phiên đã lưu, nhưng chưa hook nào gọi nó tự động — bắt được chuyện cũ, chưa chặn được chuyện mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="63" t="inlineStr">
+        <is>
+          <t>Luật ERC quá áp chưa nổ trên dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="B44" s="63" t="inlineStr">
+        <is>
+          <t>Đường dẫn đã thông ở M3-07, nhưng ba kho có Fact điện áp thì không có mô hình mạch, và ngược lại. Phải chờ một dự án có cả hai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="63" t="inlineStr">
+        <is>
+          <t>Cột “Mã nguồn” của ma trận truy vết trống ở mọi dự án</t>
+        </is>
+      </c>
+      <c r="B45" s="63" t="inlineStr">
+        <is>
+          <t>Nó đọc hien_thuc_req — trường vừa mới tồn tại, chưa tệp nào trên đĩa từng khai. Nên “chưa hiện thực” ở đó nghĩa là “chưa ai KHAI”, không phải “chưa ai viết”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="63" t="inlineStr">
+        <is>
+          <t>Lỗi _go_dau trong src/eide/tools/design.py</t>
+        </is>
+      </c>
+      <c r="B46" s="63" t="inlineStr">
+        <is>
+          <t>Viết .replace('d','d') nên 'ổn định' và 'ON DINH' không khớp nhau. Hàm ấy đang dùng cho một phép kiểm an toàn (người có thật sự chọn không). Tìm thấy ở M2-03, CHƯA sửa vì ngoài phạm vi — cần bộ ca kiểm riêng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="63" t="inlineStr">
+        <is>
+          <t>subagent req-critic (bước 4 của M2-03)</t>
+        </is>
+      </c>
+      <c r="B47" s="63" t="inlineStr">
+        <is>
+          <t>Kế hoạch ghi “tuỳ chọn, gộp M2-13”. Chưa làm, đúng theo kế hoạch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="63" t="inlineStr">
+        <is>
+          <t>Hai luật kiểm chân FPGA chưa có dữ liệu để nổ</t>
+        </is>
+      </c>
+      <c r="B48" s="63" t="inlineStr">
+        <is>
+          <t>chan_lech_kit và io_type_lech_bank cần Fact chân kit. Không kho nào trong repo có Fact pin:tangnano20k.* hay khoá vccio — nên hôm nay chỉ 3 trong 5 luật của M3-18 kết luận được gì trên dữ liệu thật. Cùng hình dạng với luật ERC quá áp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="63" t="inlineStr">
+        <is>
+          <t>Một bitstream cũ đã dựng với chân đồng hồ tự chọn</t>
+        </is>
+      </c>
+      <c r="B49" s="63" t="inlineStr">
+        <is>
+          <t>blinky của du-lieu/riscv-tn20k-b — xem DEV-345 và README §8. Không sửa hiện vật cũ: đó là dữ liệu của những lượt đo đã chốt. Từ nay phép kiểm chặn trước nextpnr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="63" t="inlineStr">
+        <is>
+          <t>Ba công cụ mới nhất chưa lượt Agent nào GỌI</t>
+        </is>
+      </c>
+      <c r="B50" s="63" t="inlineStr">
+        <is>
+          <t>hdl.sensitivity · hdl.constraints_check · test.criteria. Mã của cả ba đã chạy trên hiện vật thật, nhưng đó là tôi gọi hàm, không phải tác tử gọi công cụ. README §8 đếm cả ba vào phần chưa dùng thật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="63" t="inlineStr">
+        <is>
+          <t>Bộ kiểm C của ba dự án firmware thật đều KHÔNG đo được độ nhạy</t>
+        </is>
+      </c>
+      <c r="B51" s="63" t="inlineStr">
+        <is>
+          <t>rtos-sinhvien: 0/12 tệp đo được (4 font khong_thay, control_rtos.c trùng ký hiệu, main.c không dịch trên máy chủ, logo_ptit.c mọi mutant hỏng biên dịch). stm32f469-freertos và thu-nghiem-g6: bộ kiểm ĐỎ SẴN. Đây là trạng thái của dữ liệu đo, không phải lỗi sản phẩm — nhưng nó nghĩa là chưa dự án firmware nào trong repo có một con số độ nhạy đáng tin. Xem DEV-348.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="63" t="inlineStr">
+        <is>
+          <t>POL-N6-sua-test chưa nổ trên một phiên thật nào</t>
+        </is>
+      </c>
+      <c r="B52" s="63" t="inlineStr">
+        <is>
+          <t>Hook sua_test_sau_do cấp dữ kiện cho lời gọi SẮP xảy ra, nên không soát lại được phiên đã lưu — khác mọi phép đo trước của đợt này. Nó đã có 25 ca kiểm và phá lại 27/27, nhưng chưa lượt tác tử thật nào chạm vào nó. Cùng hình dạng với ba luật kiểm thiếu dữ liệu ở trên, chỉ khác lý do.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="59" t="inlineStr">
+        <is>
+          <t>Lỗi tìm thấy trong CHÍNH PHÉP ĐO của tôi</t>
+        </is>
+      </c>
+      <c r="B54" s="59" t="inlineStr">
+        <is>
+          <t>Lộ ra ở đâu</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="63" t="inlineStr">
+        <is>
+          <t>Kịch bản đo bị hàng rào của sản phẩm chặn (ghi tệp chưa đọc, E4020) và trả về một con số hợp lý thay vì nổ — 6→2 trông đẹp y như 9→3 đúng</t>
+        </is>
+      </c>
+      <c r="B55" s="63" t="inlineStr">
+        <is>
+          <t>M2-01 · DEV-333</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm dựng trên điều tôi tự nhớ sai: “thiết” bỏ dấu KHÔNG chứa “it”; chỗ va thật là bit/unit/init/exit</t>
+        </is>
+      </c>
+      <c r="B56" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá dài ĐÚNG BẰNG mã gốc (0.6 → 0.0) nên __pycache__ cũ còn hiệu lực — phép đo chạy mã khác với mã trong tệp</t>
+        </is>
+      </c>
+      <c r="B57" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="63" t="inlineStr">
+        <is>
+          <t>Phép đo trả lời ĐÚNG một câu hỏi KHÁC: đếm ở mức dự án ra 0 chỗ cần chặn; câu phải hỏi là “lần ghi NÀY đã được kiểm chưa” → 19/26</t>
+        </is>
+      </c>
+      <c r="B58" s="63" t="inlineStr">
+        <is>
+          <t>M2-06 · DEV-336</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm RỖNG: dàn dựng không có net đất nào, nên nó xanh cả khi tôi bỏ hẳn phép bỏ qua net đất</t>
+        </is>
+      </c>
+      <c r="B59" s="63" t="inlineStr">
+        <is>
+          <t>M3-01 · DEV-338</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="63" t="inlineStr">
+        <is>
+          <t>Hai phép phá chỉ ra THIẾT KẾ sai, không chỉ ca kiểm yếu (miễn net đất quá rộng; nhánh iout_max chưa ca nào chạm tới)</t>
+        </is>
+      </c>
+      <c r="B60" s="63" t="inlineStr">
+        <is>
+          <t>M3-03 · DEV-339</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá của tôi cũng SAI, và ca âm xanh vì lý do khác — hai cái sai che nhau</t>
+        </is>
+      </c>
+      <c r="B61" s="63" t="inlineStr">
+        <is>
+          <t>M3-07 · DEV-341</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm đo chính câu lệnh của mình (đặt bộ đếm = 3 rồi khẳng định nó khác rỗng, trong khi thực tế nó rỗng)</t>
+        </is>
+      </c>
+      <c r="B62" s="63" t="inlineStr">
+        <is>
+          <t>M3-10 · DEV-342</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="63" t="inlineStr">
+        <is>
+          <t>Regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 bản ghi thật; và ba ca kiểm xanh vì lý do sai (tệp giả dùng $4 thay $3; “FAILED” chứa “FAIL”)</t>
+        </is>
+      </c>
+      <c r="B63" s="63" t="inlineStr">
+        <is>
+          <t>M3-12 · DEV-343</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="63" t="inlineStr">
+        <is>
+          <t>"Phá lại thì đỏ 6/6" sai về TẬP, không sai về số: sáu phép phá ấy chọn đúng sáu chỗ đã có ca canh. Phá bằng tập rộng hơn ra 7/9.</t>
+        </is>
+      </c>
+      <c r="B64" s="63" t="inlineStr">
+        <is>
+          <t>M3-13 · DEV-344</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="63" t="inlineStr">
+        <is>
+          <t>409 'blocker' gần như toàn bộ từ một cặp vô nghĩa (mạng cổng của lõi CPU tổng hợp riêng, không bao giờ đem đặt-đi dây). Con số thật là 1.</t>
+        </is>
+      </c>
+      <c r="B65" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="63" t="inlineStr">
+        <is>
+          <t>Phép quét tệp .cst thật chỉ thu 4 trong 7 tệp mà ca kiểm vẫn xanh — câu 'mọi tệp .cst thật đều đọc được' nói về phần phép quét chạm tới.</t>
+        </is>
+      </c>
+      <c r="B66" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="63" t="inlineStr">
+        <is>
+          <t>Một ca kiểm và một phép phá nhắm hai NHÁNH khác nhau, nên ca mới xanh mà phép phá vẫn LỌT. Mất một lượt mới thấy.</t>
+        </is>
+      </c>
+      <c r="B67" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm xanh nhờ một DÒNG KHÁC: kiểm `"TỰ KHAI" in str(kh)` cả khối nên vẫn xanh khi phá chữ ấy ở dòng Kết luận — summary cũng chứa nó. Phép phá bắt được, ca kiểm thì không.</t>
+        </is>
+      </c>
+      <c r="B68" s="63" t="inlineStr">
+        <is>
+          <t>M4-01 · DEV-346</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="63" t="inlineStr">
+        <is>
+          <t>Một phép phá VÔ HIỆU: `them = [] or [[…]]` không đổi hành vi, nên nó báo LỌT oan và suýt làm tôi viết ca kiểm cho một chỗ vốn đã được canh.</t>
+        </is>
+      </c>
+      <c r="B69" s="63" t="inlineStr">
+        <is>
+          <t>M4-01 · DEV-346</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="63" t="inlineStr">
+        <is>
+          <t>HAI phép phá liền nhau VÔ HIỆU ở cùng một dòng: `cu = cu or ""` không đổi hành vi, rồi bỏ is_file() cũng không vì except OSError bắt FileNotFoundError. Phải bỏ cả hai lớp phòng mới phá được.</t>
+        </is>
+      </c>
+      <c r="B70" s="63" t="inlineStr">
+        <is>
+          <t>M4-02 · DEV-347</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="63" t="inlineStr">
+        <is>
+          <t>Một luật mới trỏ tới nhóm dữ kiện chưa khai thì DỪNG CẢ LƯỢT bằng ValueError, không phải 'không nổ' — và nhóm `criteria` của hàng rào N6 cũ cũng chưa bao giờ được khai.</t>
+        </is>
+      </c>
+      <c r="B71" s="63" t="inlineStr">
+        <is>
+          <t>M4-02 · DEV-347</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="63" t="inlineStr">
+        <is>
+          <t>Phép đo ĐỔ ngay lượt đầu trên dữ liệu thật (IndexError), và lỗi ấy nghĩa là test.sensitivity chưa bao giờ chạy nổi trên một tệp firmware thật — mọi con số cũ đều từ tệp nhỏ do ca kiểm tự dựng.</t>
+        </is>
+      </c>
+      <c r="B72" s="63" t="inlineStr">
+        <is>
+          <t>M4-05 · DEV-348</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="63" t="inlineStr">
+        <is>
+          <t>Bốn chỗ LỌT cùng một hình dạng: luật ĐÚNG, nằm ở chỗ ca kiểm không với tới — hai closure, một bảng phép không dựng nổi ca, và một tầng báo lại mà mọi ca cũ đều đi qua với stillborn == 0.</t>
+        </is>
+      </c>
+      <c r="B73" s="63" t="inlineStr">
+        <is>
+          <t>M4-05 · DEV-348</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Tôi thêm MỘT cờ biên dịch để tránh một cáo buộc sai, và nó sinh ra MƯỜI MỘT cáo buộc sai khác: -I che header hệ thống, nên 11/12 tệp bị xếp là 'không dịch được trên máy chủ'. Phải là -iquote.</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>M4-19 · DEV-349</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Gắn cờ biên dịch cho cả LƯỢT MỐC là đổi chính cái mốc mà mọi so sánh dựa vào — mốc của cả ba dự án thật từ XANH thành ĐỎ.</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>M4-19 · DEV-349</t>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16424,13 +18346,47 @@
       <c r="P86" s="47" t="n"/>
       <c r="Q86" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R86" s="47" t="n"/>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="R86" s="47" t="inlineStr">
+        <is>
+          <t>Agent (Claude Opus 5)</t>
+        </is>
+      </c>
       <c r="S86" s="47" t="inlineStr">
         <is>
           <t>Kéo lên giai đoạn sớm hơn vì là tiền đề (xem §5 kế hoạch)</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>DEV-349</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>1835 → 1846 (+11)</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Chạy test.sensitivity TẠI CHỖ trên ba dự án firmware thật — không sao ra đâu cả, đó chính là điều cần chứng minh. Kết luận GIỐNG HỆT lượt đột biến tại chỗ của M4-05 (rtos-sinhvien: thay 0 · khong_thay 4 · khong_nap 3 · chua_do 5 · stillborn 1), và 50/50 tệp firmware của ba dự án giữ nguyên CẢ sha256 LẪN st_mtime_ns. mtime đáng kể riêng: nó là thứ make đọc, nên một phép đo ghi lại y nguyên nội dung vẫn làm cả cây dựng lại.</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>HAI lần tôi tự tay làm phép đo cáo buộc sai, cả hai chỉ lộ ra trên dữ liệu thật: (1) gắn -I cho CẢ lượt mốc → mốc của rtos-sinhvien từ XANH thành ĐỎ, cả ba dự án thành 'không đo được'; (2) -I thay vì -iquote → firmware/ của rtos-sinhvien có stdio.h RIÊNG, nên #include &lt;stdio.h&gt; của tệp test khớp vào bản giả của bo (FILE thành undeclared) và 11 TRONG 12 tệp bị xếp là khong_nap_duoc. Tôi thêm một cờ để tránh một cáo buộc sai, và nó sinh ra mười một cáo buộc sai khác. · Sau khi đổi sang -iquote thì guard của lần 1 không còn đổi hành vi — đã BỎ nhánh ấy, không viết ca cho nó. · hdl.sensitivity KHÔNG dùng được thu_muc_tam vì chay của nó bỏ qua đối số và dịch lại cả thư mục nguồn. · Phá lại 13/13, lượt đầu 7/13; năm chỗ LỌT là năm chỗ tôi đã nghĩ 'cái này hiển nhiên'.</t>
         </is>
       </c>
     </row>
@@ -18527,7 +20483,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19366,459 +21322,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="5" customWidth="1" style="26" min="1" max="1"/>
-    <col width="34" customWidth="1" style="26" min="2" max="3"/>
-    <col width="55" customWidth="1" style="26" min="4" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="19.5" customHeight="1" s="27">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>ĐIỂM MẠNH HIỆN CÓ — GIỮ NGUYÊN, KHÔNG ĐỀ XUẤT TRÙNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="27">
-      <c r="A3" s="31" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" s="31" t="inlineStr">
-        <is>
-          <t>Cơ chế</t>
-        </is>
-      </c>
-      <c r="C3" s="31" t="inlineStr">
-        <is>
-          <t>Vị trí</t>
-        </is>
-      </c>
-      <c r="D3" s="31" t="inlineStr">
-        <is>
-          <t>Vì sao giá trị</t>
-        </is>
-      </c>
-      <c r="E3" s="31" t="inlineStr">
-        <is>
-          <t>Cách tận dụng khi tối ưu</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34.5" customHeight="1" s="27">
-      <c r="A4" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="53" t="inlineStr">
-        <is>
-          <t>Ba lớp xác định quanh mọi lời gọi công cụ</t>
-        </is>
-      </c>
-      <c r="C4" s="47" t="inlineStr">
-        <is>
-          <t>loop.py::_one_tool; hooks/; policy/engine.py</t>
-        </is>
-      </c>
-      <c r="D4" s="47" t="inlineStr">
-        <is>
-          <t>Mô hình không có đường nào làm việc mà không qua pre_tool_use → policy → post_tool_use; lỗi quay về mô hình như dữ liệu kèm hướng dẫn.</t>
-        </is>
-      </c>
-      <c r="E4" s="47" t="inlineStr">
-        <is>
-          <t>Tách thành hàm dùng chung để tác tử con cũng đi qua (M1-03).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="23.25" customHeight="1" s="27">
-      <c r="A5" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="53" t="inlineStr">
-        <is>
-          <t>Transcript ghi trước (write-ahead)</t>
-        </is>
-      </c>
-      <c r="C5" s="47" t="inlineStr">
-        <is>
-          <t>loop.py::DanhSachGhiDia; memory/transcript.py</t>
-        </is>
-      </c>
-      <c r="D5" s="47" t="inlineStr">
-        <is>
-          <t>Mọi message xuống đĩa trước khi vào RAM; phát hiện phiên dừng giữa chừng và công cụ có tác dụng phụ chưa có kết quả.</t>
-        </is>
-      </c>
-      <c r="E5" s="47" t="inlineStr">
-        <is>
-          <t>Nền cho checkpoint HITL và resume đầy đủ (M5-17).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="23.25" customHeight="1" s="27">
-      <c r="A6" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="53" t="inlineStr">
-        <is>
-          <t>Thẻ cổng + nhớ duyệt trong lượt</t>
-        </is>
-      </c>
-      <c r="C6" s="47" t="inlineStr">
-        <is>
-          <t>loop.py::_da_duyet_roi</t>
-        </is>
-      </c>
-      <c r="D6" s="47" t="inlineStr">
-        <is>
-          <t>Bớt 16 thẻ G-DATA cho cùng một công cụ, nhưng vẫn hỏi lại với thao tác không hoàn tác, never_auto, ≥R4.</t>
-        </is>
-      </c>
-      <c r="E6" s="47" t="inlineStr">
-        <is>
-          <t>Giữ quy tắc này khi thêm cổng G-QUAL cho sửa test (M4-02).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="23.25" customHeight="1" s="27">
-      <c r="A7" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="53" t="inlineStr">
-        <is>
-          <t>Plan mode khoá công cụ ghi + kiểm kế hoạch bằng mã</t>
-        </is>
-      </c>
-      <c r="C7" s="47" t="inlineStr">
-        <is>
-          <t>ke_hoach.py; loop.py::_khoa_khi_soan_ke_hoach</t>
-        </is>
-      </c>
-      <c r="D7" s="47" t="inlineStr">
-        <is>
-          <t>Trình cách làm trước khi tiêu lời gọi; đòi bước chọn kiến trúc và code.analyze.</t>
-        </is>
-      </c>
-      <c r="E7" s="47" t="inlineStr">
-        <is>
-          <t>Mở rộng bằng tiêu chí xong + plan.revise (M1-13, M2-06).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="23.25" customHeight="1" s="27">
-      <c r="A8" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="53" t="inlineStr">
-        <is>
-          <t>Phát hiện quay vòng + câu thay cho im lặng / hết ngân sách</t>
-        </is>
-      </c>
-      <c r="C8" s="47" t="inlineStr">
-        <is>
-          <t>loop.py::_nhac_neu_dang_quay_vong, _cau_im_lang, _cau_het_ngan_sach</t>
-        </is>
-      </c>
-      <c r="D8" s="47" t="inlineStr">
-        <is>
-          <t>Biến chỗ mù của mô hình thành tín hiệu; luôn nói ra đã làm gì và cần gõ gì để đi tiếp.</t>
-        </is>
-      </c>
-      <c r="E8" s="47" t="inlineStr">
-        <is>
-          <t>Bổ sung chống lời gọi trùng y hệt và leo thang (M1-17).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34.5" customHeight="1" s="27">
-      <c r="A9" s="48" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="53" t="inlineStr">
-        <is>
-          <t>Tiêu chí-trước cho mô phỏng, EIDE phán bằng mã</t>
-        </is>
-      </c>
-      <c r="C9" s="47" t="inlineStr">
-        <is>
-          <t>build/tieu_chi.py::xet_ket_qua; tools/xay_dung.py::sim_run</t>
-        </is>
-      </c>
-      <c r="D9" s="47" t="inlineStr">
-        <is>
-          <t>Chương trình chỉ đo, EIDE so ngưỡng có nguồn; ba trạng thái dat/khong_dat/chua_do_duoc; đổi ngưỡng sau kết quả phải qua G-QUAL.</t>
-        </is>
-      </c>
-      <c r="E9" s="47" t="inlineStr">
-        <is>
-          <t>Dùng làm lõi chung cho unit test, HDL, HIL (M4-01, M4-14, M3-12).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="23.25" customHeight="1" s="27">
-      <c r="A10" s="48" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="53" t="inlineStr">
-        <is>
-          <t>Đọc ngược Flash khi nạp</t>
-        </is>
-      </c>
-      <c r="C10" s="47" t="inlineStr">
-        <is>
-          <t>tools/mach_that.py::target_verify</t>
-        </is>
-      </c>
-      <c r="D10" s="47" t="inlineStr">
-        <is>
-          <t>So từng byte sau khi nạp, và nói thẳng khi công cụ nạp không hỗ trợ verify.</t>
-        </is>
-      </c>
-      <c r="E10" s="47" t="inlineStr">
-        <is>
-          <t>Nối với hil.run để kiểm thử trên bo có máy chấm (M4-14).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="23.25" customHeight="1" s="27">
-      <c r="A11" s="48" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="53" t="inlineStr">
-        <is>
-          <t>Tác tử tự viết công cụ có test và duyệt</t>
-        </is>
-      </c>
-      <c r="C11" s="47" t="inlineStr">
-        <is>
-          <t>nang_luc.py; tools/nang_luc.py (tool.propose)</t>
-        </is>
-      </c>
-      <c r="D11" s="47" t="inlineStr">
-        <is>
-          <t>Năng lực tự mở rộng có kiểm soát; công cụ đã duyệt được nạp lại khi mở dự án.</t>
-        </is>
-      </c>
-      <c r="E11" s="47" t="inlineStr">
-        <is>
-          <t>Làm đích nâng cấp cho đoạn py.phan_tich dùng lại ≥3 lần (M1-21).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="23.25" customHeight="1" s="27">
-      <c r="A12" s="48" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="53" t="inlineStr">
-        <is>
-          <t>Kiểm xuất xứ quyết định của người</t>
-        </is>
-      </c>
-      <c r="C12" s="47" t="inlineStr">
-        <is>
-          <t>tools/design.py::_kiem_nguoi_that_su_chon</t>
-        </is>
-      </c>
-      <c r="D12" s="47" t="inlineStr">
-        <is>
-          <t>Chặn tác tử tự nhận 'người đã chọn' mà không có câu trích thật trong sổ cái.</t>
-        </is>
-      </c>
-      <c r="E12" s="47" t="inlineStr">
-        <is>
-          <t>Áp lại cho store.req_create/req_update (M2-19).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="23.25" customHeight="1" s="27">
-      <c r="A13" s="48" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="53" t="inlineStr">
-        <is>
-          <t>Chốt hằng số không nguồn (constant_guard, N1)</t>
-        </is>
-      </c>
-      <c r="C13" s="47" t="inlineStr">
-        <is>
-          <t>hooks/standard.py</t>
-        </is>
-      </c>
-      <c r="D13" s="47" t="inlineStr">
-        <is>
-          <t>Số trong mã phải có Fact hoặc lời người; chặn số nhớ/bịa.</t>
-        </is>
-      </c>
-      <c r="E13" s="47" t="inlineStr">
-        <is>
-          <t>Cần chạy cả cho tác tử con (M1-03) và cho câu trả lời văn xuôi (M5-02).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="23.25" customHeight="1" s="27">
-      <c r="A14" s="48" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="53" t="inlineStr">
-        <is>
-          <t>Phong bì kết quả + blob</t>
-        </is>
-      </c>
-      <c r="C14" s="47" t="inlineStr">
-        <is>
-          <t>memory/envelope.py; memory/compact.py (C1)</t>
-        </is>
-      </c>
-      <c r="D14" s="47" t="inlineStr">
-        <is>
-          <t>Kết quả dài không đi nguyên văn vào transcript; mô hình đọc lại bằng blob.read.</t>
-        </is>
-      </c>
-      <c r="E14" s="47" t="inlineStr">
-        <is>
-          <t>Thêm chính sách riêng cho doc.read / fact.* (M5-13) và cho tác tử con (M1-05).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="23.25" customHeight="1" s="27">
-      <c r="A15" s="48" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="53" t="inlineStr">
-        <is>
-          <t>Bộ dò 'ok nhưng rỗng'</t>
-        </is>
-      </c>
-      <c r="C15" s="47" t="inlineStr">
-        <is>
-          <t>ket_qua.py::khong_noi_gi</t>
-        </is>
-      </c>
-      <c r="D15" s="47" t="inlineStr">
-        <is>
-          <t>Phân biệt lời gọi thành công với kết quả có nội dung; nhắc một lần mỗi công cụ.</t>
-        </is>
-      </c>
-      <c r="E15" s="47" t="inlineStr">
-        <is>
-          <t>Dời lời nhắc ra sau message tool để không lệch cặp gọi–trả (M1-01).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="23.25" customHeight="1" s="27">
-      <c r="A16" s="48" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="53" t="inlineStr">
-        <is>
-          <t>Bộ nhớ có tombstone + duyệt trước khi nhớ người dùng</t>
-        </is>
-      </c>
-      <c r="C16" s="47" t="inlineStr">
-        <is>
-          <t>store/eide_md.py; memory/nguoi_dung.py</t>
-        </is>
-      </c>
-      <c r="D16" s="47" t="inlineStr">
-        <is>
-          <t>Điều đã quên không hồi sinh; không ghi bộ nhớ người dùng khi chưa bấm đồng ý.</t>
-        </is>
-      </c>
-      <c r="E16" s="47" t="inlineStr">
-        <is>
-          <t>Giữ khi thêm hiện vật 'lesson' (M5-14).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="27">
-      <c r="A17" s="48" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="53" t="inlineStr">
-        <is>
-          <t>Sơ đồ kiến trúc chỉ vẽ khi có cạnh thật</t>
-        </is>
-      </c>
-      <c r="C17" s="47" t="inlineStr">
-        <is>
-          <t>kien_truc.py</t>
-        </is>
-      </c>
-      <c r="D17" s="47" t="inlineStr">
-        <is>
-          <t>Không vẽ sơ đồ trang trí; nói rõ vì sao không vẽ được.</t>
-        </is>
-      </c>
-      <c r="E17" s="47" t="inlineStr">
-        <is>
-          <t>Mở rộng kiểm phân tầng (M2-12).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="23.25" customHeight="1" s="27">
-      <c r="A18" s="48" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="53" t="inlineStr">
-        <is>
-          <t>Bộ 76 ca + ReplayGateway/RecordingGateway</t>
-        </is>
-      </c>
-      <c r="C18" s="47" t="inlineStr">
-        <is>
-          <t>tools/bo_usecase.py; llm/offline.py</t>
-        </is>
-      </c>
-      <c r="D18" s="47" t="inlineStr">
-        <is>
-          <t>Đã có hạ tầng phát lại 0 token, chỉ chưa được dùng trong pytest/CI.</t>
-        </is>
-      </c>
-      <c r="E18" s="47" t="inlineStr">
-        <is>
-          <t>Dựng eval phát lại + CI (M4-21).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="102" customHeight="1" s="27">
-      <c r="A19" s="48" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="53" t="inlineStr">
-        <is>
-          <t>Tổng hợp điểm mạnh mảng kiểm thử (từ người rà soát mảng 4)</t>
-        </is>
-      </c>
-      <c r="C19" s="47" t="inlineStr">
-        <is>
-          <t>build/tieu_chi.py::xet_ket_qua; tools/xay_dung.py::sim_run (E4008/E4009/E4023); ket_qua.py::khong_noi_gi; kiem_chung.py::co_viec_chua_kiem; tools/mach_that.py::target_verify; loop.py dòng ~1070 (đổi ngưỡng → STALE)</t>
-        </is>
-      </c>
-      <c r="D19" s="47" t="inlineStr">
-        <is>
-          <t>Đã có: criteria-first thật cho sim.run (chưa có tiêu chí thì từ chối, chưa có trich_loi người xác nhận thì từ chối); EIDE phán bằng code, thiếu số đo = chua_do_duoc; chặn lệch cặp tiêu chí/nguồn (E4023); khai phần không mô phỏng được đi kèm kết luận; đổi ngưỡng sau khi có kết quả đi qua G-QUAL; bộ dò 'ok nhưng rỗng'; Stop hook đòi verifier đọc từ sổ cái bền qua lần khởi động lại; target.verify đọc ngược Flash so từng byte; test.sensitivity phát hiện test tự định nghĩa lại hàm (khong_nap_duoc); test.run báo tệp sản phẩm nào được dịch cùng.</t>
-        </is>
-      </c>
-      <c r="E19" s="47" t="inlineStr">
-        <is>
-          <t>Dùng lại tieu_chi.py (Assert/TieuChi/xet_ket_qua) làm lõi chung cho test.criteria, hil.criteria và khuôn {"do":…} của HDL, thay vì viết ba máy chấm. Giữ nguyên ngữ nghĩa ba trạng thái dat/khong_dat/chua_do_duoc ở mọi nơi.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
 </file>
--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -14,13 +14,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 08-10-2026 (toi)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 08-10-2026 (khuya)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 09-10-2026" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục tối ưu" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đối chiếu 18 mẫu" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 09-10-2026 (chiều)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục tối ưu" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đối chiếu 18 mẫu" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -2105,13 +2106,13 @@
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
-    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="B53:G53"/>
     <mergeCell ref="B48:G48"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
@@ -2128,6 +2129,847 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="16" customWidth="1" style="26" min="1" max="1"/>
+    <col width="24" customWidth="1" style="26" min="2" max="2"/>
+    <col width="16" customWidth="1" style="26" min="3" max="3"/>
+    <col width="55" customWidth="1" style="26" min="4" max="4"/>
+    <col width="65" customWidth="1" style="26" min="5" max="5"/>
+    <col width="13" customWidth="1" style="26" min="6" max="7"/>
+    <col width="11" customWidth="1" style="26" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="19.5" customHeight="1" s="27">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>ĐỐI CHIẾU EIDE v3 VỚI 18 MẪU KIẾN TRÚC AGENT (+ HITL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="27">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Hiện trạng đánh giá từ mã; cột 'Số đề xuất liên quan' đếm tự động các dòng ở sheet Danh mục có nhắc tên mẫu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="23.25" customHeight="1" s="27">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>Mẫu</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>Hiện trạng trong EIDE</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>Bằng chứng trong mã</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>Hướng áp dụng cho EIDE</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
+          <t>Mức phù hợp</t>
+        </is>
+      </c>
+      <c r="G4" s="31" t="inlineStr">
+        <is>
+          <t>Số đề xuất liên quan</t>
+        </is>
+      </c>
+      <c r="H4" s="31" t="inlineStr">
+        <is>
+          <t>P0 liên quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="23.25" customHeight="1" s="27">
+      <c r="A5" s="47" t="inlineStr">
+        <is>
+          <t>A. Workflow</t>
+        </is>
+      </c>
+      <c r="B5" s="53" t="inlineStr">
+        <is>
+          <t>Prompt Chaining</t>
+        </is>
+      </c>
+      <c r="C5" s="54" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="D5" s="47" t="inlineStr">
+        <is>
+          <t>Hook S0 (0 token), kiem_ke_hoach, constant_guard, cổng G-* là các cổng kiểm bằng mã.</t>
+        </is>
+      </c>
+      <c r="E5" s="47" t="inlineStr">
+        <is>
+          <t>Chưa có chuỗi chặng có cổng cho HDL (lint→sim→độ nhạy→ràng buộc→synth→pnr) và cho sinh mã từng bước (mỗi bước phải build/test).</t>
+        </is>
+      </c>
+      <c r="F5" s="48" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="G5" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Prompt Chaining*")</f>
+        <v/>
+      </c>
+      <c r="H5" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Prompt Chaining*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="23.25" customHeight="1" s="27">
+      <c r="A6" s="47" t="inlineStr">
+        <is>
+          <t>A. Workflow</t>
+        </is>
+      </c>
+      <c r="B6" s="53" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="C6" s="54" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="D6" s="47" t="inlineStr">
+        <is>
+          <t>S0 phân loại câu người dùng; công cụ core/ẩn + mở khoá theo ngữ cảnh (_mo_khoa_theo_ngu_canh).</t>
+        </is>
+      </c>
+      <c r="E6" s="47" t="inlineStr">
+        <is>
+          <t>Định tuyến bộ công cụ theo loại việc (giảm 73→~20 công cụ hiện), định tuyến mức suy nghĩ (thinking) theo bước vì chỉ được dùng một model.</t>
+        </is>
+      </c>
+      <c r="F6" s="48" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="G6" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Routing*")</f>
+        <v/>
+      </c>
+      <c r="H6" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Routing*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="23.25" customHeight="1" s="27">
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>A. Workflow</t>
+        </is>
+      </c>
+      <c r="B7" s="53" t="inlineStr">
+        <is>
+          <t>Parallelization</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="D7" s="47" t="inlineStr">
+        <is>
+          <t>Mọi lời gọi công cụ chạy tuần tự; không có bỏ phiếu.</t>
+        </is>
+      </c>
+      <c r="E7" s="47" t="inlineStr">
+        <is>
+          <t>Song song các lời gọi chỉ-đọc trong một phản hồi; task.run_many cho nhiều worker chỉ-đọc; 2 verifier độc lập cho khẳng định R3/R4.</t>
+        </is>
+      </c>
+      <c r="F7" s="48" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="G7" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Parallelization*")</f>
+        <v/>
+      </c>
+      <c r="H7" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Parallelization*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="23.25" customHeight="1" s="27">
+      <c r="A8" s="47" t="inlineStr">
+        <is>
+          <t>A. Workflow</t>
+        </is>
+      </c>
+      <c r="B8" s="53" t="inlineStr">
+        <is>
+          <t>Evaluator–Optimizer</t>
+        </is>
+      </c>
+      <c r="C8" s="54" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
+        <is>
+          <t>sim.criteria + xet_ket_qua (EIDE phán), subagent verifier, hook đòi tự kiểm.</t>
+        </is>
+      </c>
+      <c r="E8" s="47" t="inlineStr">
+        <is>
+          <t>Thêm vòng sửa có trần: ERC delta sau mỗi ckm.*, test.harden khi đột biến sống, sửa sau khi verifier bác, phiếu kiểm nén C2 thật.</t>
+        </is>
+      </c>
+      <c r="F8" s="48" t="inlineStr">
+        <is>
+          <t>Rất cao</t>
+        </is>
+      </c>
+      <c r="G8" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Evaluator*")</f>
+        <v/>
+      </c>
+      <c r="H8" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Evaluator*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="23.25" customHeight="1" s="27">
+      <c r="A9" s="47" t="inlineStr">
+        <is>
+          <t>B. Single-agent</t>
+        </is>
+      </c>
+      <c r="B9" s="53" t="inlineStr">
+        <is>
+          <t>ReAct</t>
+        </is>
+      </c>
+      <c r="C9" s="56" t="inlineStr">
+        <is>
+          <t>Đã có (lõi)</t>
+        </is>
+      </c>
+      <c r="D9" s="47" t="inlineStr">
+        <is>
+          <t>loop.py: vòng native tool-calling, ngân sách 40 lời gọi/300 s, phát hiện quay vòng, câu thay cho im lặng.</t>
+        </is>
+      </c>
+      <c r="E9" s="47" t="inlineStr">
+        <is>
+          <t>Sửa toàn vẹn cặp gọi–trả, xử lý finish_reason, chống lời gọi trùng y hệt, thử temperature theo khuyến nghị Gemini 3.</t>
+        </is>
+      </c>
+      <c r="F9" s="48" t="inlineStr">
+        <is>
+          <t>Rất cao</t>
+        </is>
+      </c>
+      <c r="G9" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*ReAct*")</f>
+        <v/>
+      </c>
+      <c r="H9" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*ReAct*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="23.25" customHeight="1" s="27">
+      <c r="A10" s="47" t="inlineStr">
+        <is>
+          <t>B. Single-agent</t>
+        </is>
+      </c>
+      <c r="B10" s="53" t="inlineStr">
+        <is>
+          <t>Plan-and-Execute</t>
+        </is>
+      </c>
+      <c r="C10" s="54" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
+        <is>
+          <t>Plan mode khoá công cụ ghi, kiểm kế hoạch bằng mã, G-SCOPE duyệt, plan.step_done đòi hiện vật.</t>
+        </is>
+      </c>
+      <c r="E10" s="47" t="inlineStr">
+        <is>
+          <t>Thêm plan.revise (Replanner), phụ thuộc giữa bước, tiêu chí xong kiểm được bằng máy, ngân sách con theo bước.</t>
+        </is>
+      </c>
+      <c r="F10" s="48" t="inlineStr">
+        <is>
+          <t>Rất cao</t>
+        </is>
+      </c>
+      <c r="G10" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Plan-and-Execute*")</f>
+        <v/>
+      </c>
+      <c r="H10" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Plan-and-Execute*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="23.25" customHeight="1" s="27">
+      <c r="A11" s="47" t="inlineStr">
+        <is>
+          <t>B. Single-agent</t>
+        </is>
+      </c>
+      <c r="B11" s="53" t="inlineStr">
+        <is>
+          <t>ReWOO</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="D11" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="47" t="inlineStr">
+        <is>
+          <t>Phù hợp cho chuỗi tra cứu biết trước (nạp datasheet → trích khoá ERC → so sánh). Có thể gộp vào kb.ask / part.select thay vì làm riêng.</t>
+        </is>
+      </c>
+      <c r="F11" s="48" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="G11" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*ReWOO*")</f>
+        <v/>
+      </c>
+      <c r="H11" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*ReWOO*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="23.25" customHeight="1" s="27">
+      <c r="A12" s="47" t="inlineStr">
+        <is>
+          <t>B. Single-agent</t>
+        </is>
+      </c>
+      <c r="B12" s="53" t="inlineStr">
+        <is>
+          <t>LLMCompiler</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="D12" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="47" t="inlineStr">
+        <is>
+          <t>Bản nhẹ: DAG chỉ cho lời gọi đọc độc lập trong cùng phản hồi (pha kiểm quyền tuần tự, pha chạy song song).</t>
+        </is>
+      </c>
+      <c r="F12" s="48" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="G12" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*LLMCompiler*")</f>
+        <v/>
+      </c>
+      <c r="H12" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*LLMCompiler*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="23.25" customHeight="1" s="27">
+      <c r="A13" s="47" t="inlineStr">
+        <is>
+          <t>B. Single-agent</t>
+        </is>
+      </c>
+      <c r="B13" s="53" t="inlineStr">
+        <is>
+          <t>Reflexion</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="D13" s="47" t="inlineStr">
+        <is>
+          <t>Thất bại được ghi sổ cái nhưng không chưng cất thành bài học; bài học chỉ nằm trong chú thích mã.</t>
+        </is>
+      </c>
+      <c r="E13" s="47" t="inlineStr">
+        <is>
+          <t>Hiện vật 'lesson' theo chữ ký lỗi (công cụ + mã lỗi + chip), sinh sau chuỗi lỗi→sửa thành công, tra lại khi gặp lỗi tương tự; mục Bài học trong EIDE.md.</t>
+        </is>
+      </c>
+      <c r="F13" s="48" t="inlineStr">
+        <is>
+          <t>Rất cao</t>
+        </is>
+      </c>
+      <c r="G13" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Reflexion*")</f>
+        <v/>
+      </c>
+      <c r="H13" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Reflexion*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="23.25" customHeight="1" s="27">
+      <c r="A14" s="47" t="inlineStr">
+        <is>
+          <t>B. Single-agent</t>
+        </is>
+      </c>
+      <c r="B14" s="53" t="inlineStr">
+        <is>
+          <t>Tree of Thoughts / LATS</t>
+        </is>
+      </c>
+      <c r="C14" s="55" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="D14" s="47" t="inlineStr">
+        <is>
+          <t>Có option_create/option_choose nhưng do một mạch suy nghĩ sinh ra, không chấm điểm.</t>
+        </is>
+      </c>
+      <c r="E14" s="47" t="inlineStr">
+        <is>
+          <t>Chỉ dùng cho quyết định kiến trúc: design.explore sinh ≤3 phương án độc lập + chấm theo rubric REQ. Không áp ToT cho vòng thường (quá đắt).</t>
+        </is>
+      </c>
+      <c r="F14" s="48" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="G14" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Tree of Thoughts*")</f>
+        <v/>
+      </c>
+      <c r="H14" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Tree of Thoughts*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="23.25" customHeight="1" s="27">
+      <c r="A15" s="47" t="inlineStr">
+        <is>
+          <t>B. Single-agent</t>
+        </is>
+      </c>
+      <c r="B15" s="53" t="inlineStr">
+        <is>
+          <t>CodeAct</t>
+        </is>
+      </c>
+      <c r="C15" s="54" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="D15" s="47" t="inlineStr">
+        <is>
+          <t>tool.propose cho tác tử tự viết công cụ lâu dài (có test, có duyệt); 3 công thức đóng trong khoi_thu_vien.</t>
+        </is>
+      </c>
+      <c r="E15" s="47" t="inlineStr">
+        <is>
+          <t>Thêm calc.eval (biểu thức có đơn vị, không eval tự do) và py.phan_tich chỉ-đọc trong sandbox cho phân tích dùng một lần.</t>
+        </is>
+      </c>
+      <c r="F15" s="48" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="G15" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*CodeAct*")</f>
+        <v/>
+      </c>
+      <c r="H15" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*CodeAct*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="34.5" customHeight="1" s="27">
+      <c r="A16" s="47" t="inlineStr">
+        <is>
+          <t>B. Single-agent</t>
+        </is>
+      </c>
+      <c r="B16" s="53" t="inlineStr">
+        <is>
+          <t>Agentic RAG</t>
+        </is>
+      </c>
+      <c r="C16" s="55" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="D16" s="47" t="inlineStr">
+        <is>
+          <t>doc.read khớp chuỗi con trong MỘT tài liệu, không xếp hạng; SVD được phân loại 'đầy đủ' nhưng không có bộ đọc; PDF không có cấu trúc bảng.</t>
+        </is>
+      </c>
+      <c r="E16" s="47" t="inlineStr">
+        <is>
+          <t>doc.search lai (FTS5/BM25 + embedding + RRF), kb.ask có định tuyến nguồn – chấm liên quan – viết lại truy vấn – kiểm bám nguồn từng con số.</t>
+        </is>
+      </c>
+      <c r="F16" s="48" t="inlineStr">
+        <is>
+          <t>Rất cao</t>
+        </is>
+      </c>
+      <c r="G16" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Agentic RAG*")</f>
+        <v/>
+      </c>
+      <c r="H16" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Agentic RAG*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="23.25" customHeight="1" s="27">
+      <c r="A17" s="47" t="inlineStr">
+        <is>
+          <t>B. Single-agent</t>
+        </is>
+      </c>
+      <c r="B17" s="53" t="inlineStr">
+        <is>
+          <t>Memory-augmented (MemGPT)</t>
+        </is>
+      </c>
+      <c r="C17" s="54" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="D17" s="47" t="inlineStr">
+        <is>
+          <t>EIDE.md theo dự án, bộ nhớ người dùng có duyệt, nén C1–C4 có blob, tombstone chống hồi sinh, khối resume.</t>
+        </is>
+      </c>
+      <c r="E17" s="47" t="inlineStr">
+        <is>
+          <t>Sửa resume không nạp bản tóm tắt, render EIDE.md cắt mất §Đừng, supersede Fact, hết hạn/mâu thuẫn, phiếu kiểm nén thật.</t>
+        </is>
+      </c>
+      <c r="F17" s="48" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="G17" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Memory*")</f>
+        <v/>
+      </c>
+      <c r="H17" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Memory*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="23.25" customHeight="1" s="27">
+      <c r="A18" s="47" t="inlineStr">
+        <is>
+          <t>C. Multi-agent</t>
+        </is>
+      </c>
+      <c r="B18" s="53" t="inlineStr">
+        <is>
+          <t>Supervisor–Workers</t>
+        </is>
+      </c>
+      <c r="C18" s="54" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="D18" s="47" t="inlineStr">
+        <is>
+          <t>task.run với 6+ loại tác tử con, ngữ cảnh sạch, công cụ lọc, báo cáo 6 trường.</t>
+        </is>
+      </c>
+      <c r="E18" s="47" t="inlineStr">
+        <is>
+          <t>Đưa tác tử con qua cùng hook/policy, ngân sách theo lời gọi + giây, cắt kết quả, nộp báo cáo bằng function call, chạy song song worker chỉ-đọc.</t>
+        </is>
+      </c>
+      <c r="F18" s="48" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="G18" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Supervisor*")</f>
+        <v/>
+      </c>
+      <c r="H18" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Supervisor*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="23.25" customHeight="1" s="27">
+      <c r="A19" s="47" t="inlineStr">
+        <is>
+          <t>C. Multi-agent</t>
+        </is>
+      </c>
+      <c r="B19" s="53" t="inlineStr">
+        <is>
+          <t>Hierarchical</t>
+        </is>
+      </c>
+      <c r="C19" s="55" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="D19" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="47" t="inlineStr">
+        <is>
+          <t>Chưa cần: một supervisor một tầng chưa được chứng minh là thiếu. Chỉ xét khi có dự án nhiều miền (mạch + FPGA + firmware) chạy dài nhiều ngày.</t>
+        </is>
+      </c>
+      <c r="F19" s="48" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="G19" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Hierarchical*")</f>
+        <v/>
+      </c>
+      <c r="H19" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Hierarchical*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="23.25" customHeight="1" s="27">
+      <c r="A20" s="47" t="inlineStr">
+        <is>
+          <t>C. Multi-agent</t>
+        </is>
+      </c>
+      <c r="B20" s="53" t="inlineStr">
+        <is>
+          <t>Swarm / Handoff</t>
+        </is>
+      </c>
+      <c r="C20" s="55" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="D20" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="47" t="inlineStr">
+        <is>
+          <t>Không khuyến nghị: EIDE có một người dùng, một giao diện; chuyển giao ngang hàng làm mất bức tranh toàn cục.</t>
+        </is>
+      </c>
+      <c r="F20" s="48" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="G20" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Swarm*")</f>
+        <v/>
+      </c>
+      <c r="H20" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Swarm*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="34.5" customHeight="1" s="27">
+      <c r="A21" s="47" t="inlineStr">
+        <is>
+          <t>C. Multi-agent</t>
+        </is>
+      </c>
+      <c r="B21" s="53" t="inlineStr">
+        <is>
+          <t>Debate</t>
+        </is>
+      </c>
+      <c r="C21" s="55" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="D21" s="47" t="inlineStr">
+        <is>
+          <t>design-review chỉ soi mạch và chỉ chạy khi tác tử chính tự giao.</t>
+        </is>
+      </c>
+      <c r="E21" s="47" t="inlineStr">
+        <is>
+          <t>Phản biện tự động khi chốt ADR (phan-bien / sw-design-review), criteria-critic trước khi người duyệt tiêu chí, req-critic cho đặc tả. Trần 1 vòng phản biện + 1 vòng sửa.</t>
+        </is>
+      </c>
+      <c r="F21" s="48" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="G21" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Debate*")</f>
+        <v/>
+      </c>
+      <c r="H21" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Debate*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="23.25" customHeight="1" s="27">
+      <c r="A22" s="47" t="inlineStr">
+        <is>
+          <t>C. Multi-agent</t>
+        </is>
+      </c>
+      <c r="B22" s="53" t="inlineStr">
+        <is>
+          <t>Blackboard</t>
+        </is>
+      </c>
+      <c r="C22" s="54" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="D22" s="47" t="inlineStr">
+        <is>
+          <t>Kho hiện vật + sổ cái + lan STALE (deps.py) đóng vai bảng trạng thái chung.</t>
+        </is>
+      </c>
+      <c r="E22" s="47" t="inlineStr">
+        <is>
+          <t>Ghi deps.upstream thật (hiện luôn rỗng) để STALE đúng chỗ và có ma trận truy vết REQ→thiết kế→mã→test; address_map dùng chung RTL↔firmware.</t>
+        </is>
+      </c>
+      <c r="F22" s="48" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="G22" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Blackboard*")</f>
+        <v/>
+      </c>
+      <c r="H22" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Blackboard*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="23.25" customHeight="1" s="27">
+      <c r="A23" s="47" t="inlineStr">
+        <is>
+          <t>D. Cắt ngang</t>
+        </is>
+      </c>
+      <c r="B23" s="53" t="inlineStr">
+        <is>
+          <t>Human-in-the-loop</t>
+        </is>
+      </c>
+      <c r="C23" s="56" t="inlineStr">
+        <is>
+          <t>Đã có (mạnh)</t>
+        </is>
+      </c>
+      <c r="D23" s="47" t="inlineStr">
+        <is>
+          <t>Policy R0–R4, thẻ cổng G-*, nhớ duyệt trong lượt (trừ không hoàn tác/never_auto/≥R4), soft-lock tệp, kiểm xuất xứ quyết định người.</t>
+        </is>
+      </c>
+      <c r="E23" s="47" t="inlineStr">
+        <is>
+          <t>Thất bại an toàn khi luật policy lỗi; cổng G-QUAL cho việc sửa test sau khi đỏ; HITL cho đo mạch thật; tác tử con hiện đi vòng qua HITL.</t>
+        </is>
+      </c>
+      <c r="F23" s="48" t="inlineStr">
+        <is>
+          <t>Rất cao</t>
+        </is>
+      </c>
+      <c r="G23" s="48">
+        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Human-in-the-loop*")</f>
+        <v/>
+      </c>
+      <c r="H23" s="48">
+        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Human-in-the-loop*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
@@ -2577,7 +3419,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7620,7 +8462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" style="27" min="1" max="1"/>
@@ -7646,7 +8488,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="59" t="inlineStr">
         <is>
@@ -7720,7 +8561,6 @@
       </c>
       <c r="C8" s="61" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="59" t="inlineStr">
         <is>
@@ -7897,7 +8737,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="59" t="inlineStr">
         <is>
@@ -8608,7 +9447,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="59" t="inlineStr">
         <is>
@@ -8753,7 +9591,6 @@
         </is>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="59" t="inlineStr">
         <is>
@@ -8994,7 +9831,6 @@
         </is>
       </c>
     </row>
-    <row r="73"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9006,7 +9842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" style="27" min="1" max="1"/>
@@ -9032,7 +9868,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="59" t="inlineStr">
         <is>
@@ -9106,7 +9941,6 @@
       </c>
       <c r="C8" s="61" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="59" t="inlineStr">
         <is>
@@ -9283,7 +10117,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="59" t="inlineStr">
         <is>
@@ -10031,7 +10864,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="59" t="inlineStr">
         <is>
@@ -10176,7 +11008,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="59" t="inlineStr">
         <is>
@@ -10418,49 +11249,1537 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="26" t="inlineStr">
         <is>
           <t>Tôi thêm MỘT cờ biên dịch để tránh một cáo buộc sai, và nó sinh ra MƯỜI MỘT cáo buộc sai khác: -I che header hệ thống, nên 11/12 tệp bị xếp là 'không dịch được trên máy chủ'. Phải là -iquote.</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="26" t="inlineStr">
         <is>
           <t>M4-19 · DEV-349</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="26" t="inlineStr">
         <is>
           <t>Gắn cờ biên dịch cho cả LƯỢT MỐC là đổi chính cái mốc mà mọi so sánh dựa vào — mốc của cả ba dự án thật từ XANH thành ĐỎ.</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="26" t="inlineStr">
         <is>
           <t>M4-19 · DEV-349</t>
         </is>
       </c>
     </row>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" customWidth="1" style="27" min="1" max="1"/>
+    <col width="66" customWidth="1" style="27" min="2" max="2"/>
+    <col width="24" customWidth="1" style="27" min="3" max="3"/>
+    <col width="8" customWidth="1" style="27" min="4" max="4"/>
+    <col width="11" customWidth="1" style="27" min="5" max="5"/>
+    <col width="16" customWidth="1" style="27" min="6" max="6"/>
+    <col width="34" customWidth="1" style="27" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="57" t="inlineStr">
+        <is>
+          <t>TIẾN ĐỘ ĐỢT TỐI ƯU TÁC TỬ — chốt chiều 09/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="58" t="inlineStr">
+        <is>
+          <t>Mỗi dòng 'Xong' đều có: mục DEV-LOG tra lại được · số ca kiểm trước→sau · một con số đo trên dữ liệu thật · phần còn nợ. Cột chi tiết nằm ở sheet “Danh mục tối ưu”, cột T–Y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="59" t="inlineStr">
+        <is>
+          <t>Tổng quan</t>
+        </is>
+      </c>
+      <c r="B4" s="59" t="inlineStr">
+        <is>
+          <t>Số việc</t>
+        </is>
+      </c>
+      <c r="C4" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>Xong (đã gộp vào main, đã đẩy)</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="n">
+        <v>21</v>
+      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>21 việc đầu của Giai đoạn 1, theo đúng thứ tự # của kế hoạch</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="60" t="inlineStr">
+        <is>
+          <t>Đang làm (chưa commit)</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="61" t="inlineStr">
+        <is>
+          <t>không việc nào đang dở</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="60" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="n">
+        <v>85</v>
+      </c>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>85 việc còn lại trong 106</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="62" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B8" s="62" t="n">
+        <v>106</v>
+      </c>
+      <c r="C8" s="61" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>Phép đo của cả đợt</t>
+        </is>
+      </c>
+      <c r="B10" s="59" t="inlineStr">
+        <is>
+          <t>Trước (06/10)</t>
+        </is>
+      </c>
+      <c r="C10" s="59" t="inlineStr">
+        <is>
+          <t>Sau (09/10)</t>
+        </is>
+      </c>
+      <c r="D10" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị Python (pytest -q)</t>
+        </is>
+      </c>
+      <c r="B11" s="63" t="inlineStr">
+        <is>
+          <t>1 610</t>
+        </is>
+      </c>
+      <c r="C11" s="63" t="inlineStr">
+        <is>
+          <t>1 862</t>
+        </is>
+      </c>
+      <c r="D11" s="63" t="inlineStr">
+        <is>
+          <t>+252 ca so với 06/10; không ca cũ nào đỏ ở bất kỳ bước nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị giao diện (swift test)</t>
+        </is>
+      </c>
+      <c r="B12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="inlineStr">
+        <is>
+          <t>không nhiệm vụ nào đụng ui/ — kiểu khối A2.2 dùng “table”, Swift đã dựng được</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>kiem_tai_lieu.py</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="C13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ LỆCH CHẮC CHẮN cả hai lượt. Hôm nay nó bắt đúng chuyện cần bắt: hai công cụ mới làm README lệch số công cụ 127 → 129, và số 'cần đọc lại' nhảy 11 → 15 → về 11 sau khi sửa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>thu_sch.py (cờ schematic bật)</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="C14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="D14" s="63" t="inlineStr">
+        <is>
+          <t>chạy ở M3-03 và M3-04, không tụt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t>Mục DEV-LOG mới</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330 → DEV-350</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="inlineStr">
+        <is>
+          <t>21 mục, mỗi việc một mục</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="63" t="inlineStr">
+        <is>
+          <t>Cờ tính năng mới</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>1 (schematic)</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="63" t="inlineStr">
+        <is>
+          <t>7 cờ mới, TẤT CẢ mặc định TẮT. Cờ thứ 7 là SIM_RUNNER_GIOI_HAN (M4-02) — nó giới hạn fs.write của sim-runner trong sim/; hàng rào chính của M4-02 (POL-N6-sua-test) thì KHÔNG sau cờ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="63" t="inlineStr">
+        <is>
+          <t>Mã lỗi mới</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>E4031 · E4032 · E6012 · E4033 · E4024</t>
+        </is>
+      </c>
+      <c r="D17" s="63" t="inlineStr">
+        <is>
+          <t>M4-04, M4-05 và M4-19 không thêm mã nào; M4-02 dùng lại E5006. E4033 (M3-18), E4024 (M4-01). M4-01 còn DÙNG LẠI E4008/E4009/E4023 của sim.run — cùng một chuyện thì cùng một mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="59" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="C19" s="59" t="inlineStr">
+        <is>
+          <t>Mảng</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="E19" s="59" t="inlineStr">
+        <is>
+          <t>DEV-LOG</t>
+        </is>
+      </c>
+      <c r="F19" s="59" t="inlineStr">
+        <is>
+          <t>Ca kiểm</t>
+        </is>
+      </c>
+      <c r="G19" s="59" t="inlineStr">
+        <is>
+          <t>Cờ mặc định</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="63" t="inlineStr">
+        <is>
+          <t>M1-01</t>
+        </is>
+      </c>
+      <c r="C20" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D20" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E20" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330</t>
+        </is>
+      </c>
+      <c r="F20" s="63" t="inlineStr">
+        <is>
+          <t>105/309 phiên thật có lịch sử tự mâu thuẫn — 255 chỗ (156 kết quả thứ hai cùng id, 74 message chen giữa, 24 kết quả lạc lượt, 1 lời gọi không kết quả)</t>
+        </is>
+      </c>
+      <c r="G20" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="63" t="inlineStr">
+        <is>
+          <t>M1-02</t>
+        </is>
+      </c>
+      <c r="C21" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D21" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E21" s="63" t="inlineStr">
+        <is>
+          <t>DEV-331</t>
+        </is>
+      </c>
+      <c r="F21" s="63" t="inlineStr">
+        <is>
+          <t>lược đồ công cụ thật: 25 869 token/lời gọi (trần tool_schema=4000 chưa dòng mã nào đọc). Cờ bật: 4 475 token, giảm 82,7 %; 73 → 18 công cụ</t>
+        </is>
+      </c>
+      <c r="G21" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="63" t="inlineStr">
+        <is>
+          <t>M1-03</t>
+        </is>
+      </c>
+      <c r="C22" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D22" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E22" s="63" t="inlineStr">
+        <is>
+          <t>DEV-332</t>
+        </is>
+      </c>
+      <c r="F22" s="63" t="inlineStr">
+        <is>
+          <t>1 822 lời gọi của tác tử con trong 26 phiên thật, 0 lần qua lớp luật. Toàn công cụ đọc trừ một build.compile — lỗ hổng chưa bị bước vào, không phải được canh</t>
+        </is>
+      </c>
+      <c r="G22" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="63" t="inlineStr">
+        <is>
+          <t>M2-01</t>
+        </is>
+      </c>
+      <c r="C23" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D23" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E23" s="63" t="inlineStr">
+        <is>
+          <t>DEV-333</t>
+        </is>
+      </c>
+      <c r="F23" s="63" t="inlineStr">
+        <is>
+          <t>kịch bản 3 REQ + 3 phương án + 3 tiêu chí + 3 tệp: sửa MỘT REQ làm 9 hiện vật STALE → còn 3. Phép đo đầu ra 6→2 vì bị hàng rào E4020 chặn, đã sửa kịch bản đo</t>
+        </is>
+      </c>
+      <c r="G23" s="63" t="inlineStr">
+        <is>
+          <t>TRUY_VET — TẮT (phần nền chạy cả khi tắt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>M2-02</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D24" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E24" s="63" t="inlineStr">
+        <is>
+          <t>DEV-334</t>
+        </is>
+      </c>
+      <c r="F24" s="63" t="inlineStr">
+        <is>
+          <t>63 kho thật: 5/37 REQ có ít nhất một phép đo; 27 chưa có phương án nào nhận; 0 REQ đi hết chuỗi. Cột 'Mã nguồn' trống ở MỌI dự án vì hien_thuc_req vừa mới tồn tại</t>
+        </is>
+      </c>
+      <c r="G24" s="63" t="inlineStr">
+        <is>
+          <t>REQ_PHU — TẮT (khối A2.2 trên tab không phụ thuộc cờ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="63" t="inlineStr">
+        <is>
+          <t>M2-03</t>
+        </is>
+      </c>
+      <c r="C25" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D25" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E25" s="63" t="inlineStr">
+        <is>
+          <t>DEV-335</t>
+        </is>
+      </c>
+      <c r="F25" s="63" t="inlineStr">
+        <is>
+          <t>37 REQ thật: 25 sạch (67 %), 11 thiếu tiêu chí đo được, 2 có từ mơ hồ. Lần đo đầu ra 3 từ mơ hồ, một là kêu oan ('ít nhất 2 lần' là mức đo được) — đã vá</t>
+        </is>
+      </c>
+      <c r="G25" s="63" t="inlineStr">
+        <is>
+          <t>REQ_CHAT_LUONG — TẮT (module yeu_cau.py luôn có)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="63" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="63" t="inlineStr">
+        <is>
+          <t>M2-06</t>
+        </is>
+      </c>
+      <c r="C26" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D26" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E26" s="63" t="inlineStr">
+        <is>
+          <t>DEV-336</t>
+        </is>
+      </c>
+      <c r="F26" s="63" t="inlineStr">
+        <is>
+          <t>sổ cái thật: 26 lần đánh dấu 'xong' ngay sau một lần ghi mã, 19 lần (73 %) không có phép kiểm nào đạt ở giữa. Phép đo đầu ở mức dự án ra 0 — đúng nhưng đo sai câu hỏi</t>
+        </is>
+      </c>
+      <c r="G26" s="63" t="inlineStr">
+        <is>
+          <t>KE_HOACH_CONG_KIEM — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="63" t="inlineStr">
+        <is>
+          <t>M2-08</t>
+        </is>
+      </c>
+      <c r="C27" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D27" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E27" s="63" t="inlineStr">
+        <is>
+          <t>DEV-337</t>
+        </is>
+      </c>
+      <c r="F27" s="63" t="inlineStr">
+        <is>
+          <t>185 tệp .c thật: 1 758 → 1 786 hàm thấy được (+28 hàm trước đây VÔ HÌNH: 8 ngắt + 20 bị regex tham lam nuốt). 78 hàm nay gắn nhãn 'isr', 70 trong đó vốn đã có trong danh sách</t>
+        </is>
+      </c>
+      <c r="G27" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="63" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="63" t="inlineStr">
+        <is>
+          <t>M3-01</t>
+        </is>
+      </c>
+      <c r="C28" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D28" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E28" s="63" t="inlineStr">
+        <is>
+          <t>DEV-338</t>
+        </is>
+      </c>
+      <c r="F28" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mô hình mạch thật — và lý do đáng hơn con số: 3 kho CÓ Fact v_max thì KHÔNG có mô hình mạch, 5 kho có mạch thì không có Fact ấy; thêm nữa Fact dùng chủ thể chip:X mà ERC không tra tiền tố đó</t>
+        </is>
+      </c>
+      <c r="G28" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="63" t="inlineStr">
+        <is>
+          <t>M3-03</t>
+        </is>
+      </c>
+      <c r="C29" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D29" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E29" s="63" t="inlineStr">
+        <is>
+          <t>DEV-339</t>
+        </is>
+      </c>
+      <c r="F29" s="63" t="inlineStr">
+        <is>
+          <t>8 phát hiện trên 5 mạch thật (6 nguon_khong_cap + 2 net_mot_chan), trong đó net clock I2C nối đúng một chân. SÁU trong tám là 'mô hình chưa khai' chứ không phải 'mạch sai'. robot-canbang: 107 Port lá, KHÔNG Port nào là power_out</t>
+        </is>
+      </c>
+      <c r="G29" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="63" t="n">
+        <v>11</v>
+      </c>
+      <c r="B30" s="63" t="inlineStr">
+        <is>
+          <t>M3-04</t>
+        </is>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D30" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E30" s="63" t="inlineStr">
+        <is>
+          <t>DEV-340</t>
+        </is>
+      </c>
+      <c r="F30" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mạch thật — và đây là con số ĐÚNG (hai lỗi này catastrophic, không bo nào sống tới lúc lưu kho). Đã CẤY hai bộ cấp vào bản sao kho robot-canbang để chứng minh luật sống: nổ đúng 1 blocker trên net +5V thật</t>
+        </is>
+      </c>
+      <c r="G30" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="B31" s="63" t="inlineStr">
+        <is>
+          <t>M3-07</t>
+        </is>
+      </c>
+      <c r="C31" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D31" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E31" s="63" t="inlineStr">
+        <is>
+          <t>DEV-341</t>
+        </is>
+      </c>
+      <c r="F31" s="63" t="inlineStr">
+        <is>
+          <t>Fact tới được ERC: 5 → 17 (+12). Ba kho có Fact datasheet thì TOÀN BỘ mang chủ thể chip:, tức trước đó không một Fact nào tới được ERC. Độ phủ 5 mạch thật nay đọc được</t>
+        </is>
+      </c>
+      <c r="G31" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="63" t="n">
+        <v>13</v>
+      </c>
+      <c r="B32" s="63" t="inlineStr">
+        <is>
+          <t>M3-10</t>
+        </is>
+      </c>
+      <c r="C32" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D32" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E32" s="63" t="inlineStr">
+        <is>
+          <t>DEV-342</t>
+        </is>
+      </c>
+      <c r="F32" s="63" t="inlineStr">
+        <is>
+          <t>chi phí đo thật: mạch lớn nhất trong kho 187 nút → ERC 7,6 ms mỗi lần ghi. Trần 2000 nút, vượt thì NÓI RA chứ không im lặng bỏ qua</t>
+        </is>
+      </c>
+      <c r="G32" s="63" t="inlineStr">
+        <is>
+          <t>ERC_TU_DONG — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="B33" s="63" t="inlineStr">
+        <is>
+          <t>M3-12</t>
+        </is>
+      </c>
+      <c r="C33" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D33" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E33" s="63" t="inlineStr">
+        <is>
+          <t>DEV-343</t>
+        </is>
+      </c>
+      <c r="F33" s="63" t="inlineStr">
+        <is>
+          <t>846 bản ghi mô phỏng thật: regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 (testbench dự án in 'KET QUA: PASS' — nhãn đứng TRƯỚC từ khoá). Nới đúng một chỗ → 846/846 khớp, vẫn bắt đủ bốn ca PASS giả</t>
+        </is>
+      </c>
+      <c r="G33" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="64" t="n">
+        <v>15</v>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>M3-13</t>
+        </is>
+      </c>
+      <c r="C34" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D34" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E34" s="64" t="inlineStr">
+        <is>
+          <t>DEV-344</t>
+        </is>
+      </c>
+      <c r="F34" s="64" t="inlineStr">
+        <is>
+          <t>testbench Verilog THẬT của bài 3: tb_pcpi_dot4 1/1, tb_pcpi_mac 1/1, tb_pcpi_vmini không đo được (tb gọi bản bram HAI CỔNG đã bị bỏ 02/10) — mẫu số là TỆP, không phải phép phá</t>
+        </is>
+      </c>
+      <c r="G34" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="64" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B35" s="64" t="inlineStr">
+        <is>
+          <t>M3-18</t>
+        </is>
+      </c>
+      <c r="C35" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D35" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E35" s="64" t="inlineStr">
+        <is>
+          <t>DEV-345</t>
+        </is>
+      </c>
+      <c r="F35" s="64" t="inlineStr">
+        <is>
+          <t>6 cặp (mạng cổng, .cst) thật → 1 chỗ CHẶN: blinky của riscv-tn20k-b dựng bitstream 4,6 MB với chân đồng hồ do nextpnr tự chọn (rơi đúng chân 4 — bằng may). Cả 7 tệp .cst thật đọc hết, 0 lỗi cú pháp</t>
+        </is>
+      </c>
+      <c r="G35" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="64" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B36" s="64" t="inlineStr">
+        <is>
+          <t>M4-01</t>
+        </is>
+      </c>
+      <c r="C36" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D36" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E36" s="64" t="inlineStr">
+        <is>
+          <t>DEV-346</t>
+        </is>
+      </c>
+      <c r="F36" s="64" t="inlineStr">
+        <is>
+          <t>18 ca chạy trình biên dịch C thật: tệp test in số đo {"T1":300} với ngưỡng &lt;=255 → EIDE phán 1 ca HỎNG. Chưa kho cũ nào có tiêu chí unit test để đo lại trên dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="G36" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="64" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B37" s="64" t="inlineStr">
+        <is>
+          <t>M4-02</t>
+        </is>
+      </c>
+      <c r="C37" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D37" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E37" s="64" t="inlineStr">
+        <is>
+          <t>DEV-347</t>
+        </is>
+      </c>
+      <c r="F37" s="64" t="inlineStr">
+        <is>
+          <t>25 ca dựng đúng trạng thái thật (tệp test 3 ca, 1 ca đỏ, hiện vật dat=False) → fs.write còn 1 ca thì test.weakened=True. Và hàng rào cũ criteria.has_result chưa bao giờ nổ ngoài sim-01</t>
+        </is>
+      </c>
+      <c r="G37" s="64" t="inlineStr">
+        <is>
+          <t>SIM_RUNNER_GIOI_HAN — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="64" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B38" s="64" t="inlineStr">
+        <is>
+          <t>M4-05</t>
+        </is>
+      </c>
+      <c r="C38" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D38" s="64" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E38" s="64" t="inlineStr">
+        <is>
+          <t>DEV-348</t>
+        </is>
+      </c>
+      <c r="F38" s="64" t="inlineStr">
+        <is>
+          <t>du-lieu/rtos-sinhvien, chạy CẢ HAI hành vi: cũ so_thay=1, mới so_thay=0 — logo_ptit.c từ 'bộ kiểm ĐỎ' thành 'mọi đột biến đều làm hỏng biên dịch'. Một ô xanh giả, đã sửa</t>
+        </is>
+      </c>
+      <c r="G38" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B39" s="64" t="inlineStr">
+        <is>
+          <t>M4-19</t>
+        </is>
+      </c>
+      <c r="C39" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D39" s="64" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E39" s="64" t="inlineStr">
+        <is>
+          <t>DEV-349</t>
+        </is>
+      </c>
+      <c r="F39" s="64" t="inlineStr">
+        <is>
+          <t>chạy TẠI CHỖ trên ba dự án firmware thật: kết luận giống hệt lượt đột biến tại chỗ của M4-05, và 50/50 tệp giữ nguyên cả sha256 lẫn mtime</t>
+        </is>
+      </c>
+      <c r="G39" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="64" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B40" s="64" t="inlineStr">
+        <is>
+          <t>M4-04</t>
+        </is>
+      </c>
+      <c r="C40" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D40" s="64" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E40" s="64" t="inlineStr">
+        <is>
+          <t>DEV-350</t>
+        </is>
+      </c>
+      <c r="F40" s="64" t="inlineStr">
+        <is>
+          <t>TÁI HIỆN được ca DANH-GIA §2.2 bằng máy trên control_rtos.c thật: bảng cũ 0 đột biến cho hằng hex, bảng mới dòng 147 → mutant SỐNG. Và chi_tiet trên 12 tệp thật: 110 s, điểm 0,0</t>
+        </is>
+      </c>
+      <c r="G40" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (tham số mới, mặc định giữ hành vi cũ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="59" t="inlineStr">
+        <is>
+          <t>Việc còn MỞ (ngoài 85 việc chưa làm)</t>
+        </is>
+      </c>
+      <c r="B42" s="59" t="inlineStr">
+        <is>
+          <t>Vì sao còn mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="63" t="inlineStr">
+        <is>
+          <t>Bảy cờ mới đều còn TẮT</t>
+        </is>
+      </c>
+      <c r="B43" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU · TRUY_VET · REQ_PHU · REQ_CHAT_LUONG · KE_HOACH_CONG_KIEM · ERC_TU_DONG · SIM_RUNNER_GIOI_HAN. Cả bảy đổi thứ Agent nhìn thấy, đọc, hoặc LÀM ĐƯỢC mỗi lượt, nên chỉ bộ 76 ca chạy hai chế độ mới nói được chúng làm Agent khá hơn hay tệ hơn. Bộ ấy tốn tiền mô hình nên §3.0 bắt hỏi người dùng trước.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="63" t="inlineStr">
+        <is>
+          <t>kiem_cap_goi_tra() chưa thành hàng rào</t>
+        </is>
+      </c>
+      <c r="B44" s="63" t="inlineStr">
+        <is>
+          <t>Soát được mọi phiên đã lưu, nhưng chưa hook nào gọi nó tự động — bắt được chuyện cũ, chưa chặn được chuyện mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="63" t="inlineStr">
+        <is>
+          <t>Luật ERC quá áp chưa nổ trên dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="B45" s="63" t="inlineStr">
+        <is>
+          <t>Đường dẫn đã thông ở M3-07, nhưng ba kho có Fact điện áp thì không có mô hình mạch, và ngược lại. Phải chờ một dự án có cả hai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="63" t="inlineStr">
+        <is>
+          <t>Cột “Mã nguồn” của ma trận truy vết trống ở mọi dự án</t>
+        </is>
+      </c>
+      <c r="B46" s="63" t="inlineStr">
+        <is>
+          <t>Nó đọc hien_thuc_req — trường vừa mới tồn tại, chưa tệp nào trên đĩa từng khai. Nên “chưa hiện thực” ở đó nghĩa là “chưa ai KHAI”, không phải “chưa ai viết”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="63" t="inlineStr">
+        <is>
+          <t>Lỗi _go_dau trong src/eide/tools/design.py</t>
+        </is>
+      </c>
+      <c r="B47" s="63" t="inlineStr">
+        <is>
+          <t>Viết .replace('d','d') nên 'ổn định' và 'ON DINH' không khớp nhau. Hàm ấy đang dùng cho một phép kiểm an toàn (người có thật sự chọn không). Tìm thấy ở M2-03, CHƯA sửa vì ngoài phạm vi — cần bộ ca kiểm riêng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="63" t="inlineStr">
+        <is>
+          <t>subagent req-critic (bước 4 của M2-03)</t>
+        </is>
+      </c>
+      <c r="B48" s="63" t="inlineStr">
+        <is>
+          <t>Kế hoạch ghi “tuỳ chọn, gộp M2-13”. Chưa làm, đúng theo kế hoạch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="63" t="inlineStr">
+        <is>
+          <t>Hai luật kiểm chân FPGA chưa có dữ liệu để nổ</t>
+        </is>
+      </c>
+      <c r="B49" s="63" t="inlineStr">
+        <is>
+          <t>chan_lech_kit và io_type_lech_bank cần Fact chân kit. Không kho nào trong repo có Fact pin:tangnano20k.* hay khoá vccio — nên hôm nay chỉ 3 trong 5 luật của M3-18 kết luận được gì trên dữ liệu thật. Cùng hình dạng với luật ERC quá áp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="63" t="inlineStr">
+        <is>
+          <t>Một bitstream cũ đã dựng với chân đồng hồ tự chọn</t>
+        </is>
+      </c>
+      <c r="B50" s="63" t="inlineStr">
+        <is>
+          <t>blinky của du-lieu/riscv-tn20k-b — xem DEV-345 và README §8. Không sửa hiện vật cũ: đó là dữ liệu của những lượt đo đã chốt. Từ nay phép kiểm chặn trước nextpnr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="63" t="inlineStr">
+        <is>
+          <t>Ba công cụ mới nhất chưa lượt Agent nào GỌI</t>
+        </is>
+      </c>
+      <c r="B51" s="63" t="inlineStr">
+        <is>
+          <t>hdl.sensitivity · hdl.constraints_check · test.criteria. Mã của cả ba đã chạy trên hiện vật thật, nhưng đó là tôi gọi hàm, không phải tác tử gọi công cụ. README §8 đếm cả ba vào phần chưa dùng thật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="63" t="inlineStr">
+        <is>
+          <t>Bộ kiểm C của ba dự án firmware thật đều KHÔNG đo được độ nhạy</t>
+        </is>
+      </c>
+      <c r="B52" s="63" t="inlineStr">
+        <is>
+          <t>rtos-sinhvien: 0/12 tệp đo được (4 font khong_thay, control_rtos.c trùng ký hiệu, main.c không dịch trên máy chủ, logo_ptit.c mọi mutant hỏng biên dịch). stm32f469-freertos và thu-nghiem-g6: bộ kiểm ĐỎ SẴN. Đây là trạng thái của dữ liệu đo, không phải lỗi sản phẩm — nhưng nó nghĩa là chưa dự án firmware nào trong repo có một con số độ nhạy đáng tin. Xem DEV-348.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="63" t="inlineStr">
+        <is>
+          <t>POL-N6-sua-test chưa nổ trên một phiên thật nào</t>
+        </is>
+      </c>
+      <c r="B53" s="63" t="inlineStr">
+        <is>
+          <t>Hook sua_test_sau_do cấp dữ kiện cho lời gọi SẮP xảy ra, nên không soát lại được phiên đã lưu — khác mọi phép đo trước của đợt này. Nó đã có 25 ca kiểm và phá lại 27/27, nhưng chưa lượt tác tử thật nào chạm vào nó. Cùng hình dạng với ba luật kiểm thiếu dữ liệu ở trên, chỉ khác lý do.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="59" t="inlineStr">
+        <is>
+          <t>Lỗi tìm thấy trong CHÍNH PHÉP ĐO của tôi</t>
+        </is>
+      </c>
+      <c r="B55" s="59" t="inlineStr">
+        <is>
+          <t>Lộ ra ở đâu</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="63" t="inlineStr">
+        <is>
+          <t>Kịch bản đo bị hàng rào của sản phẩm chặn (ghi tệp chưa đọc, E4020) và trả về một con số hợp lý thay vì nổ — 6→2 trông đẹp y như 9→3 đúng</t>
+        </is>
+      </c>
+      <c r="B56" s="63" t="inlineStr">
+        <is>
+          <t>M2-01 · DEV-333</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm dựng trên điều tôi tự nhớ sai: “thiết” bỏ dấu KHÔNG chứa “it”; chỗ va thật là bit/unit/init/exit</t>
+        </is>
+      </c>
+      <c r="B57" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá dài ĐÚNG BẰNG mã gốc (0.6 → 0.0) nên __pycache__ cũ còn hiệu lực — phép đo chạy mã khác với mã trong tệp</t>
+        </is>
+      </c>
+      <c r="B58" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="63" t="inlineStr">
+        <is>
+          <t>Phép đo trả lời ĐÚNG một câu hỏi KHÁC: đếm ở mức dự án ra 0 chỗ cần chặn; câu phải hỏi là “lần ghi NÀY đã được kiểm chưa” → 19/26</t>
+        </is>
+      </c>
+      <c r="B59" s="63" t="inlineStr">
+        <is>
+          <t>M2-06 · DEV-336</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm RỖNG: dàn dựng không có net đất nào, nên nó xanh cả khi tôi bỏ hẳn phép bỏ qua net đất</t>
+        </is>
+      </c>
+      <c r="B60" s="63" t="inlineStr">
+        <is>
+          <t>M3-01 · DEV-338</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="63" t="inlineStr">
+        <is>
+          <t>Hai phép phá chỉ ra THIẾT KẾ sai, không chỉ ca kiểm yếu (miễn net đất quá rộng; nhánh iout_max chưa ca nào chạm tới)</t>
+        </is>
+      </c>
+      <c r="B61" s="63" t="inlineStr">
+        <is>
+          <t>M3-03 · DEV-339</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá của tôi cũng SAI, và ca âm xanh vì lý do khác — hai cái sai che nhau</t>
+        </is>
+      </c>
+      <c r="B62" s="63" t="inlineStr">
+        <is>
+          <t>M3-07 · DEV-341</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm đo chính câu lệnh của mình (đặt bộ đếm = 3 rồi khẳng định nó khác rỗng, trong khi thực tế nó rỗng)</t>
+        </is>
+      </c>
+      <c r="B63" s="63" t="inlineStr">
+        <is>
+          <t>M3-10 · DEV-342</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="63" t="inlineStr">
+        <is>
+          <t>Regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 bản ghi thật; và ba ca kiểm xanh vì lý do sai (tệp giả dùng $4 thay $3; “FAILED” chứa “FAIL”)</t>
+        </is>
+      </c>
+      <c r="B64" s="63" t="inlineStr">
+        <is>
+          <t>M3-12 · DEV-343</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="63" t="inlineStr">
+        <is>
+          <t>"Phá lại thì đỏ 6/6" sai về TẬP, không sai về số: sáu phép phá ấy chọn đúng sáu chỗ đã có ca canh. Phá bằng tập rộng hơn ra 7/9.</t>
+        </is>
+      </c>
+      <c r="B65" s="63" t="inlineStr">
+        <is>
+          <t>M3-13 · DEV-344</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="63" t="inlineStr">
+        <is>
+          <t>409 'blocker' gần như toàn bộ từ một cặp vô nghĩa (mạng cổng của lõi CPU tổng hợp riêng, không bao giờ đem đặt-đi dây). Con số thật là 1.</t>
+        </is>
+      </c>
+      <c r="B66" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="63" t="inlineStr">
+        <is>
+          <t>Phép quét tệp .cst thật chỉ thu 4 trong 7 tệp mà ca kiểm vẫn xanh — câu 'mọi tệp .cst thật đều đọc được' nói về phần phép quét chạm tới.</t>
+        </is>
+      </c>
+      <c r="B67" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="63" t="inlineStr">
+        <is>
+          <t>Một ca kiểm và một phép phá nhắm hai NHÁNH khác nhau, nên ca mới xanh mà phép phá vẫn LỌT. Mất một lượt mới thấy.</t>
+        </is>
+      </c>
+      <c r="B68" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm xanh nhờ một DÒNG KHÁC: kiểm `"TỰ KHAI" in str(kh)` cả khối nên vẫn xanh khi phá chữ ấy ở dòng Kết luận — summary cũng chứa nó. Phép phá bắt được, ca kiểm thì không.</t>
+        </is>
+      </c>
+      <c r="B69" s="63" t="inlineStr">
+        <is>
+          <t>M4-01 · DEV-346</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="63" t="inlineStr">
+        <is>
+          <t>Một phép phá VÔ HIỆU: `them = [] or [[…]]` không đổi hành vi, nên nó báo LỌT oan và suýt làm tôi viết ca kiểm cho một chỗ vốn đã được canh.</t>
+        </is>
+      </c>
+      <c r="B70" s="63" t="inlineStr">
+        <is>
+          <t>M4-01 · DEV-346</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="63" t="inlineStr">
+        <is>
+          <t>HAI phép phá liền nhau VÔ HIỆU ở cùng một dòng: `cu = cu or ""` không đổi hành vi, rồi bỏ is_file() cũng không vì except OSError bắt FileNotFoundError. Phải bỏ cả hai lớp phòng mới phá được.</t>
+        </is>
+      </c>
+      <c r="B71" s="63" t="inlineStr">
+        <is>
+          <t>M4-02 · DEV-347</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="63" t="inlineStr">
+        <is>
+          <t>Một luật mới trỏ tới nhóm dữ kiện chưa khai thì DỪNG CẢ LƯỢT bằng ValueError, không phải 'không nổ' — và nhóm `criteria` của hàng rào N6 cũ cũng chưa bao giờ được khai.</t>
+        </is>
+      </c>
+      <c r="B72" s="63" t="inlineStr">
+        <is>
+          <t>M4-02 · DEV-347</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="63" t="inlineStr">
+        <is>
+          <t>Phép đo ĐỔ ngay lượt đầu trên dữ liệu thật (IndexError), và lỗi ấy nghĩa là test.sensitivity chưa bao giờ chạy nổi trên một tệp firmware thật — mọi con số cũ đều từ tệp nhỏ do ca kiểm tự dựng.</t>
+        </is>
+      </c>
+      <c r="B73" s="63" t="inlineStr">
+        <is>
+          <t>M4-05 · DEV-348</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="63" t="inlineStr">
+        <is>
+          <t>Bốn chỗ LỌT cùng một hình dạng: luật ĐÚNG, nằm ở chỗ ca kiểm không với tới — hai closure, một bảng phép không dựng nổi ca, và một tầng báo lại mà mọi ca cũ đều đi qua với stillborn == 0.</t>
+        </is>
+      </c>
+      <c r="B74" s="63" t="inlineStr">
+        <is>
+          <t>M4-05 · DEV-348</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="26" t="inlineStr">
+        <is>
+          <t>Tôi thêm MỘT cờ biên dịch để tránh một cáo buộc sai, và nó sinh ra MƯỜI MỘT cáo buộc sai khác: -I che header hệ thống, nên 11/12 tệp bị xếp là 'không dịch được trên máy chủ'. Phải là -iquote.</t>
+        </is>
+      </c>
+      <c r="B75" s="26" t="inlineStr">
+        <is>
+          <t>M4-19 · DEV-349</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="26" t="inlineStr">
+        <is>
+          <t>Gắn cờ biên dịch cho cả LƯỢT MỐC là đổi chính cái mốc mà mọi so sánh dựa vào — mốc của cả ba dự án thật từ XANH thành ĐỎ.</t>
+        </is>
+      </c>
+      <c r="B76" s="26" t="inlineStr">
+        <is>
+          <t>M4-19 · DEV-349</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="26" t="inlineStr">
+        <is>
+          <t>Phép đo mới TREO 10 phút trên tệp thật đầu tiên — không đổ, không báo gì, nên nó trông như một lượt chạy lâu. liet_ke dựng CẢ TỆP cho MỖI chỗ khớp: 57 600 chỗ × 720 KB ≈ 41 GB việc chuỗi.</t>
+        </is>
+      </c>
+      <c r="B77" s="26" t="inlineStr">
+        <is>
+          <t>M4-04 · DEV-350</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="26" t="inlineStr">
+        <is>
+          <t>Ca kiểm chi phí của tôi KHÔNG bắt được bản chậm, vì tệp dựng dùng hằng hex TRẦN — _bo_che trả về ngay khi không có chỗ giữ. Chính CHÚ THÍCH mỗi dòng của tệp thật mới làm mỗi lượt bỏ che thành một lượt regex thật.</t>
+        </is>
+      </c>
+      <c r="B78" s="26" t="inlineStr">
+        <is>
+          <t>M4-04 · DEV-350</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17012,13 +19331,47 @@
       <c r="P71" s="47" t="n"/>
       <c r="Q71" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R71" s="47" t="n"/>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="R71" s="47" t="inlineStr">
+        <is>
+          <t>Agent (Claude Opus 5)</t>
+        </is>
+      </c>
       <c r="S71" s="47" t="inlineStr">
         <is>
           <t>Kéo lên giai đoạn sớm hơn vì là tiền đề (xem §5 kế hoạch)</t>
+        </is>
+      </c>
+      <c r="T71" s="26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="U71" s="26" t="inlineStr">
+        <is>
+          <t>DEV-350</t>
+        </is>
+      </c>
+      <c r="V71" s="26" t="inlineStr">
+        <is>
+          <t>1846 → 1862 (+16)</t>
+        </is>
+      </c>
+      <c r="W71" s="26" t="inlineStr">
+        <is>
+          <t>TÁI HIỆN ĐƯỢC ca DANH-GIA §2.2 bằng máy, trên hiện vật thật control_rtos.c: bảng phép CŨ có 0 đột biến cho hằng hex (phép đo cũ về mặt cấu trúc KHÔNG THỂ thấy chỗ ấy); bảng MỚI tìm đúng dòng 147, *(--sp) = 0xFFFFFFFDU → 0x0U; áp vào rồi chạy bộ kiểm thật thì vẫn XANH ⇒ mutant SỐNG. Điểm mù hôm ấy chỉ tồn tại vì Agent tự khai và một người sửa tay, nay đo được bằng máy. · Chạy chi_tiet trên 12 tệp thật: 110 s, điểm 0,0 — ĐÚNG (sáu tệp bitmap, không bộ kiểm nào đọc chúng) mà vô dụng, và nó chỉ ra chỗ thật: control_rtos.c là khong_nap_duoc vì tệp test #include chính tệp .c đó. · font8.c từ 'không có chỗ nào để đột biến' thành 30 đột biến — bảng mới thấy những tệp bảng cũ không chạm tới.</t>
+        </is>
+      </c>
+      <c r="X71" s="26" t="inlineStr">
+        <is>
+          <t>không có cờ (tham số mới, mặc định giữ hành vi cũ)</t>
+        </is>
+      </c>
+      <c r="Y71" s="26" t="inlineStr">
+        <is>
+          <t>PHÉP ĐO MỚI TREO 10 phút trên tệp thật đầu tiên — không đổ, không báo gì. logo_ptit.c là 720 KB với 57 600 chỗ khớp phép hex, và liet_ke dựng CẢ TỆP cho MỖI chỗ: ≈41 GB việc chuỗi. Nay liệt kê rẻ, lấy mẫu TRƯỚC, số dòng tra qua bản đồ đoạn — 0,04 s so với ≈21 s. · Ca kiểm chi phí của tôi cũng sai một lần: dùng hằng hex TRẦN thì không bắt được bản chậm, vì _bo_che trả về ngay khi không có chỗ giữ; chính CHÚ THÍCH mỗi dòng mới làm mỗi lượt bỏ che thành một lượt regex thật. · HAI luật của dự án bắt được chuyện tôi làm sai: N8 không có ngoại lệ (ghi hiện vật thì phải đòi explain), và plan mode khoá công cụ ghi lấy từ HỢP ĐỒNG chứ không từ danh sách tên (giải bằng KHONG_KHOA, cùng lý do memory.note). · Phá lại 22/22, lượt đầu 15/22. · Hiện vật mới: sim_result:test-sensitivity.</t>
         </is>
       </c>
     </row>
@@ -18359,32 +20712,32 @@
           <t>Kéo lên giai đoạn sớm hơn vì là tiền đề (xem §5 kế hoạch)</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="T86" s="26" t="inlineStr">
         <is>
           <t>08/10/2026</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="U86" s="26" t="inlineStr">
         <is>
           <t>DEV-349</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
+      <c r="V86" s="26" t="inlineStr">
         <is>
           <t>1835 → 1846 (+11)</t>
         </is>
       </c>
-      <c r="W86" t="inlineStr">
+      <c r="W86" s="26" t="inlineStr">
         <is>
           <t>Chạy test.sensitivity TẠI CHỖ trên ba dự án firmware thật — không sao ra đâu cả, đó chính là điều cần chứng minh. Kết luận GIỐNG HỆT lượt đột biến tại chỗ của M4-05 (rtos-sinhvien: thay 0 · khong_thay 4 · khong_nap 3 · chua_do 5 · stillborn 1), và 50/50 tệp firmware của ba dự án giữ nguyên CẢ sha256 LẪN st_mtime_ns. mtime đáng kể riêng: nó là thứ make đọc, nên một phép đo ghi lại y nguyên nội dung vẫn làm cả cây dựng lại.</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="X86" s="26" t="inlineStr">
         <is>
           <t>không có cờ — sửa lỗi thuần</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Y86" s="26" t="inlineStr">
         <is>
           <t>HAI lần tôi tự tay làm phép đo cáo buộc sai, cả hai chỉ lộ ra trên dữ liệu thật: (1) gắn -I cho CẢ lượt mốc → mốc của rtos-sinhvien từ XANH thành ĐỎ, cả ba dự án thành 'không đo được'; (2) -I thay vì -iquote → firmware/ của rtos-sinhvien có stdio.h RIÊNG, nên #include &lt;stdio.h&gt; của tệp test khớp vào bản giả của bo (FILE thành undeclared) và 11 TRONG 12 tệp bị xếp là khong_nap_duoc. Tôi thêm một cờ để tránh một cáo buộc sai, và nó sinh ra mười một cáo buộc sai khác. · Sau khi đổi sang -iquote thì guard của lần 1 không còn đổi hành vi — đã BỎ nhánh ấy, không viết ca cho nó. · hdl.sensitivity KHÔNG dùng được thu_muc_tam vì chay của nó bỏ qua đối số và dịch lại cả thư mục nguồn. · Phá lại 13/13, lượt đầu 7/13; năm chỗ LỌT là năm chỗ tôi đã nghĩ 'cái này hiển nhiên'.</t>
         </is>
@@ -20481,845 +22834,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="24" customWidth="1" style="26" min="2" max="2"/>
-    <col width="16" customWidth="1" style="26" min="3" max="3"/>
-    <col width="55" customWidth="1" style="26" min="4" max="4"/>
-    <col width="65" customWidth="1" style="26" min="5" max="5"/>
-    <col width="13" customWidth="1" style="26" min="6" max="7"/>
-    <col width="11" customWidth="1" style="26" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="19.5" customHeight="1" s="27">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>ĐỐI CHIẾU EIDE v3 VỚI 18 MẪU KIẾN TRÚC AGENT (+ HITL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="27">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Hiện trạng đánh giá từ mã; cột 'Số đề xuất liên quan' đếm tự động các dòng ở sheet Danh mục có nhắc tên mẫu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="23.25" customHeight="1" s="27">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>Nhóm</t>
-        </is>
-      </c>
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>Mẫu</t>
-        </is>
-      </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>Hiện trạng trong EIDE</t>
-        </is>
-      </c>
-      <c r="D4" s="31" t="inlineStr">
-        <is>
-          <t>Bằng chứng trong mã</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t>Hướng áp dụng cho EIDE</t>
-        </is>
-      </c>
-      <c r="F4" s="31" t="inlineStr">
-        <is>
-          <t>Mức phù hợp</t>
-        </is>
-      </c>
-      <c r="G4" s="31" t="inlineStr">
-        <is>
-          <t>Số đề xuất liên quan</t>
-        </is>
-      </c>
-      <c r="H4" s="31" t="inlineStr">
-        <is>
-          <t>P0 liên quan</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="23.25" customHeight="1" s="27">
-      <c r="A5" s="47" t="inlineStr">
-        <is>
-          <t>A. Workflow</t>
-        </is>
-      </c>
-      <c r="B5" s="53" t="inlineStr">
-        <is>
-          <t>Prompt Chaining</t>
-        </is>
-      </c>
-      <c r="C5" s="54" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="D5" s="47" t="inlineStr">
-        <is>
-          <t>Hook S0 (0 token), kiem_ke_hoach, constant_guard, cổng G-* là các cổng kiểm bằng mã.</t>
-        </is>
-      </c>
-      <c r="E5" s="47" t="inlineStr">
-        <is>
-          <t>Chưa có chuỗi chặng có cổng cho HDL (lint→sim→độ nhạy→ràng buộc→synth→pnr) và cho sinh mã từng bước (mỗi bước phải build/test).</t>
-        </is>
-      </c>
-      <c r="F5" s="48" t="inlineStr">
-        <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="G5" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Prompt Chaining*")</f>
-        <v/>
-      </c>
-      <c r="H5" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Prompt Chaining*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="23.25" customHeight="1" s="27">
-      <c r="A6" s="47" t="inlineStr">
-        <is>
-          <t>A. Workflow</t>
-        </is>
-      </c>
-      <c r="B6" s="53" t="inlineStr">
-        <is>
-          <t>Routing</t>
-        </is>
-      </c>
-      <c r="C6" s="54" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="D6" s="47" t="inlineStr">
-        <is>
-          <t>S0 phân loại câu người dùng; công cụ core/ẩn + mở khoá theo ngữ cảnh (_mo_khoa_theo_ngu_canh).</t>
-        </is>
-      </c>
-      <c r="E6" s="47" t="inlineStr">
-        <is>
-          <t>Định tuyến bộ công cụ theo loại việc (giảm 73→~20 công cụ hiện), định tuyến mức suy nghĩ (thinking) theo bước vì chỉ được dùng một model.</t>
-        </is>
-      </c>
-      <c r="F6" s="48" t="inlineStr">
-        <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="G6" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Routing*")</f>
-        <v/>
-      </c>
-      <c r="H6" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Routing*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="23.25" customHeight="1" s="27">
-      <c r="A7" s="47" t="inlineStr">
-        <is>
-          <t>A. Workflow</t>
-        </is>
-      </c>
-      <c r="B7" s="53" t="inlineStr">
-        <is>
-          <t>Parallelization</t>
-        </is>
-      </c>
-      <c r="C7" s="55" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
-        </is>
-      </c>
-      <c r="D7" s="47" t="inlineStr">
-        <is>
-          <t>Mọi lời gọi công cụ chạy tuần tự; không có bỏ phiếu.</t>
-        </is>
-      </c>
-      <c r="E7" s="47" t="inlineStr">
-        <is>
-          <t>Song song các lời gọi chỉ-đọc trong một phản hồi; task.run_many cho nhiều worker chỉ-đọc; 2 verifier độc lập cho khẳng định R3/R4.</t>
-        </is>
-      </c>
-      <c r="F7" s="48" t="inlineStr">
-        <is>
-          <t>Trung bình</t>
-        </is>
-      </c>
-      <c r="G7" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Parallelization*")</f>
-        <v/>
-      </c>
-      <c r="H7" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Parallelization*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="23.25" customHeight="1" s="27">
-      <c r="A8" s="47" t="inlineStr">
-        <is>
-          <t>A. Workflow</t>
-        </is>
-      </c>
-      <c r="B8" s="53" t="inlineStr">
-        <is>
-          <t>Evaluator–Optimizer</t>
-        </is>
-      </c>
-      <c r="C8" s="54" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="D8" s="47" t="inlineStr">
-        <is>
-          <t>sim.criteria + xet_ket_qua (EIDE phán), subagent verifier, hook đòi tự kiểm.</t>
-        </is>
-      </c>
-      <c r="E8" s="47" t="inlineStr">
-        <is>
-          <t>Thêm vòng sửa có trần: ERC delta sau mỗi ckm.*, test.harden khi đột biến sống, sửa sau khi verifier bác, phiếu kiểm nén C2 thật.</t>
-        </is>
-      </c>
-      <c r="F8" s="48" t="inlineStr">
-        <is>
-          <t>Rất cao</t>
-        </is>
-      </c>
-      <c r="G8" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Evaluator*")</f>
-        <v/>
-      </c>
-      <c r="H8" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Evaluator*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="23.25" customHeight="1" s="27">
-      <c r="A9" s="47" t="inlineStr">
-        <is>
-          <t>B. Single-agent</t>
-        </is>
-      </c>
-      <c r="B9" s="53" t="inlineStr">
-        <is>
-          <t>ReAct</t>
-        </is>
-      </c>
-      <c r="C9" s="56" t="inlineStr">
-        <is>
-          <t>Đã có (lõi)</t>
-        </is>
-      </c>
-      <c r="D9" s="47" t="inlineStr">
-        <is>
-          <t>loop.py: vòng native tool-calling, ngân sách 40 lời gọi/300 s, phát hiện quay vòng, câu thay cho im lặng.</t>
-        </is>
-      </c>
-      <c r="E9" s="47" t="inlineStr">
-        <is>
-          <t>Sửa toàn vẹn cặp gọi–trả, xử lý finish_reason, chống lời gọi trùng y hệt, thử temperature theo khuyến nghị Gemini 3.</t>
-        </is>
-      </c>
-      <c r="F9" s="48" t="inlineStr">
-        <is>
-          <t>Rất cao</t>
-        </is>
-      </c>
-      <c r="G9" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*ReAct*")</f>
-        <v/>
-      </c>
-      <c r="H9" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*ReAct*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="23.25" customHeight="1" s="27">
-      <c r="A10" s="47" t="inlineStr">
-        <is>
-          <t>B. Single-agent</t>
-        </is>
-      </c>
-      <c r="B10" s="53" t="inlineStr">
-        <is>
-          <t>Plan-and-Execute</t>
-        </is>
-      </c>
-      <c r="C10" s="54" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="D10" s="47" t="inlineStr">
-        <is>
-          <t>Plan mode khoá công cụ ghi, kiểm kế hoạch bằng mã, G-SCOPE duyệt, plan.step_done đòi hiện vật.</t>
-        </is>
-      </c>
-      <c r="E10" s="47" t="inlineStr">
-        <is>
-          <t>Thêm plan.revise (Replanner), phụ thuộc giữa bước, tiêu chí xong kiểm được bằng máy, ngân sách con theo bước.</t>
-        </is>
-      </c>
-      <c r="F10" s="48" t="inlineStr">
-        <is>
-          <t>Rất cao</t>
-        </is>
-      </c>
-      <c r="G10" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Plan-and-Execute*")</f>
-        <v/>
-      </c>
-      <c r="H10" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Plan-and-Execute*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="23.25" customHeight="1" s="27">
-      <c r="A11" s="47" t="inlineStr">
-        <is>
-          <t>B. Single-agent</t>
-        </is>
-      </c>
-      <c r="B11" s="53" t="inlineStr">
-        <is>
-          <t>ReWOO</t>
-        </is>
-      </c>
-      <c r="C11" s="55" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
-        </is>
-      </c>
-      <c r="D11" s="47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="47" t="inlineStr">
-        <is>
-          <t>Phù hợp cho chuỗi tra cứu biết trước (nạp datasheet → trích khoá ERC → so sánh). Có thể gộp vào kb.ask / part.select thay vì làm riêng.</t>
-        </is>
-      </c>
-      <c r="F11" s="48" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="G11" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*ReWOO*")</f>
-        <v/>
-      </c>
-      <c r="H11" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*ReWOO*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="23.25" customHeight="1" s="27">
-      <c r="A12" s="47" t="inlineStr">
-        <is>
-          <t>B. Single-agent</t>
-        </is>
-      </c>
-      <c r="B12" s="53" t="inlineStr">
-        <is>
-          <t>LLMCompiler</t>
-        </is>
-      </c>
-      <c r="C12" s="55" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
-        </is>
-      </c>
-      <c r="D12" s="47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="47" t="inlineStr">
-        <is>
-          <t>Bản nhẹ: DAG chỉ cho lời gọi đọc độc lập trong cùng phản hồi (pha kiểm quyền tuần tự, pha chạy song song).</t>
-        </is>
-      </c>
-      <c r="F12" s="48" t="inlineStr">
-        <is>
-          <t>Trung bình</t>
-        </is>
-      </c>
-      <c r="G12" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*LLMCompiler*")</f>
-        <v/>
-      </c>
-      <c r="H12" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*LLMCompiler*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="23.25" customHeight="1" s="27">
-      <c r="A13" s="47" t="inlineStr">
-        <is>
-          <t>B. Single-agent</t>
-        </is>
-      </c>
-      <c r="B13" s="53" t="inlineStr">
-        <is>
-          <t>Reflexion</t>
-        </is>
-      </c>
-      <c r="C13" s="55" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
-        </is>
-      </c>
-      <c r="D13" s="47" t="inlineStr">
-        <is>
-          <t>Thất bại được ghi sổ cái nhưng không chưng cất thành bài học; bài học chỉ nằm trong chú thích mã.</t>
-        </is>
-      </c>
-      <c r="E13" s="47" t="inlineStr">
-        <is>
-          <t>Hiện vật 'lesson' theo chữ ký lỗi (công cụ + mã lỗi + chip), sinh sau chuỗi lỗi→sửa thành công, tra lại khi gặp lỗi tương tự; mục Bài học trong EIDE.md.</t>
-        </is>
-      </c>
-      <c r="F13" s="48" t="inlineStr">
-        <is>
-          <t>Rất cao</t>
-        </is>
-      </c>
-      <c r="G13" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Reflexion*")</f>
-        <v/>
-      </c>
-      <c r="H13" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Reflexion*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="23.25" customHeight="1" s="27">
-      <c r="A14" s="47" t="inlineStr">
-        <is>
-          <t>B. Single-agent</t>
-        </is>
-      </c>
-      <c r="B14" s="53" t="inlineStr">
-        <is>
-          <t>Tree of Thoughts / LATS</t>
-        </is>
-      </c>
-      <c r="C14" s="55" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
-        </is>
-      </c>
-      <c r="D14" s="47" t="inlineStr">
-        <is>
-          <t>Có option_create/option_choose nhưng do một mạch suy nghĩ sinh ra, không chấm điểm.</t>
-        </is>
-      </c>
-      <c r="E14" s="47" t="inlineStr">
-        <is>
-          <t>Chỉ dùng cho quyết định kiến trúc: design.explore sinh ≤3 phương án độc lập + chấm theo rubric REQ. Không áp ToT cho vòng thường (quá đắt).</t>
-        </is>
-      </c>
-      <c r="F14" s="48" t="inlineStr">
-        <is>
-          <t>Trung bình</t>
-        </is>
-      </c>
-      <c r="G14" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Tree of Thoughts*")</f>
-        <v/>
-      </c>
-      <c r="H14" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Tree of Thoughts*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="23.25" customHeight="1" s="27">
-      <c r="A15" s="47" t="inlineStr">
-        <is>
-          <t>B. Single-agent</t>
-        </is>
-      </c>
-      <c r="B15" s="53" t="inlineStr">
-        <is>
-          <t>CodeAct</t>
-        </is>
-      </c>
-      <c r="C15" s="54" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="D15" s="47" t="inlineStr">
-        <is>
-          <t>tool.propose cho tác tử tự viết công cụ lâu dài (có test, có duyệt); 3 công thức đóng trong khoi_thu_vien.</t>
-        </is>
-      </c>
-      <c r="E15" s="47" t="inlineStr">
-        <is>
-          <t>Thêm calc.eval (biểu thức có đơn vị, không eval tự do) và py.phan_tich chỉ-đọc trong sandbox cho phân tích dùng một lần.</t>
-        </is>
-      </c>
-      <c r="F15" s="48" t="inlineStr">
-        <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="G15" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*CodeAct*")</f>
-        <v/>
-      </c>
-      <c r="H15" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*CodeAct*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="34.5" customHeight="1" s="27">
-      <c r="A16" s="47" t="inlineStr">
-        <is>
-          <t>B. Single-agent</t>
-        </is>
-      </c>
-      <c r="B16" s="53" t="inlineStr">
-        <is>
-          <t>Agentic RAG</t>
-        </is>
-      </c>
-      <c r="C16" s="55" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
-        </is>
-      </c>
-      <c r="D16" s="47" t="inlineStr">
-        <is>
-          <t>doc.read khớp chuỗi con trong MỘT tài liệu, không xếp hạng; SVD được phân loại 'đầy đủ' nhưng không có bộ đọc; PDF không có cấu trúc bảng.</t>
-        </is>
-      </c>
-      <c r="E16" s="47" t="inlineStr">
-        <is>
-          <t>doc.search lai (FTS5/BM25 + embedding + RRF), kb.ask có định tuyến nguồn – chấm liên quan – viết lại truy vấn – kiểm bám nguồn từng con số.</t>
-        </is>
-      </c>
-      <c r="F16" s="48" t="inlineStr">
-        <is>
-          <t>Rất cao</t>
-        </is>
-      </c>
-      <c r="G16" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Agentic RAG*")</f>
-        <v/>
-      </c>
-      <c r="H16" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Agentic RAG*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="23.25" customHeight="1" s="27">
-      <c r="A17" s="47" t="inlineStr">
-        <is>
-          <t>B. Single-agent</t>
-        </is>
-      </c>
-      <c r="B17" s="53" t="inlineStr">
-        <is>
-          <t>Memory-augmented (MemGPT)</t>
-        </is>
-      </c>
-      <c r="C17" s="54" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="D17" s="47" t="inlineStr">
-        <is>
-          <t>EIDE.md theo dự án, bộ nhớ người dùng có duyệt, nén C1–C4 có blob, tombstone chống hồi sinh, khối resume.</t>
-        </is>
-      </c>
-      <c r="E17" s="47" t="inlineStr">
-        <is>
-          <t>Sửa resume không nạp bản tóm tắt, render EIDE.md cắt mất §Đừng, supersede Fact, hết hạn/mâu thuẫn, phiếu kiểm nén thật.</t>
-        </is>
-      </c>
-      <c r="F17" s="48" t="inlineStr">
-        <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="G17" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Memory*")</f>
-        <v/>
-      </c>
-      <c r="H17" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Memory*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="23.25" customHeight="1" s="27">
-      <c r="A18" s="47" t="inlineStr">
-        <is>
-          <t>C. Multi-agent</t>
-        </is>
-      </c>
-      <c r="B18" s="53" t="inlineStr">
-        <is>
-          <t>Supervisor–Workers</t>
-        </is>
-      </c>
-      <c r="C18" s="54" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="D18" s="47" t="inlineStr">
-        <is>
-          <t>task.run với 6+ loại tác tử con, ngữ cảnh sạch, công cụ lọc, báo cáo 6 trường.</t>
-        </is>
-      </c>
-      <c r="E18" s="47" t="inlineStr">
-        <is>
-          <t>Đưa tác tử con qua cùng hook/policy, ngân sách theo lời gọi + giây, cắt kết quả, nộp báo cáo bằng function call, chạy song song worker chỉ-đọc.</t>
-        </is>
-      </c>
-      <c r="F18" s="48" t="inlineStr">
-        <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="G18" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Supervisor*")</f>
-        <v/>
-      </c>
-      <c r="H18" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Supervisor*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="23.25" customHeight="1" s="27">
-      <c r="A19" s="47" t="inlineStr">
-        <is>
-          <t>C. Multi-agent</t>
-        </is>
-      </c>
-      <c r="B19" s="53" t="inlineStr">
-        <is>
-          <t>Hierarchical</t>
-        </is>
-      </c>
-      <c r="C19" s="55" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
-        </is>
-      </c>
-      <c r="D19" s="47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" s="47" t="inlineStr">
-        <is>
-          <t>Chưa cần: một supervisor một tầng chưa được chứng minh là thiếu. Chỉ xét khi có dự án nhiều miền (mạch + FPGA + firmware) chạy dài nhiều ngày.</t>
-        </is>
-      </c>
-      <c r="F19" s="48" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="G19" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Hierarchical*")</f>
-        <v/>
-      </c>
-      <c r="H19" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Hierarchical*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="23.25" customHeight="1" s="27">
-      <c r="A20" s="47" t="inlineStr">
-        <is>
-          <t>C. Multi-agent</t>
-        </is>
-      </c>
-      <c r="B20" s="53" t="inlineStr">
-        <is>
-          <t>Swarm / Handoff</t>
-        </is>
-      </c>
-      <c r="C20" s="55" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
-        </is>
-      </c>
-      <c r="D20" s="47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="47" t="inlineStr">
-        <is>
-          <t>Không khuyến nghị: EIDE có một người dùng, một giao diện; chuyển giao ngang hàng làm mất bức tranh toàn cục.</t>
-        </is>
-      </c>
-      <c r="F20" s="48" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="G20" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Swarm*")</f>
-        <v/>
-      </c>
-      <c r="H20" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Swarm*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="34.5" customHeight="1" s="27">
-      <c r="A21" s="47" t="inlineStr">
-        <is>
-          <t>C. Multi-agent</t>
-        </is>
-      </c>
-      <c r="B21" s="53" t="inlineStr">
-        <is>
-          <t>Debate</t>
-        </is>
-      </c>
-      <c r="C21" s="55" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
-        </is>
-      </c>
-      <c r="D21" s="47" t="inlineStr">
-        <is>
-          <t>design-review chỉ soi mạch và chỉ chạy khi tác tử chính tự giao.</t>
-        </is>
-      </c>
-      <c r="E21" s="47" t="inlineStr">
-        <is>
-          <t>Phản biện tự động khi chốt ADR (phan-bien / sw-design-review), criteria-critic trước khi người duyệt tiêu chí, req-critic cho đặc tả. Trần 1 vòng phản biện + 1 vòng sửa.</t>
-        </is>
-      </c>
-      <c r="F21" s="48" t="inlineStr">
-        <is>
-          <t>Trung bình</t>
-        </is>
-      </c>
-      <c r="G21" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Debate*")</f>
-        <v/>
-      </c>
-      <c r="H21" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Debate*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="23.25" customHeight="1" s="27">
-      <c r="A22" s="47" t="inlineStr">
-        <is>
-          <t>C. Multi-agent</t>
-        </is>
-      </c>
-      <c r="B22" s="53" t="inlineStr">
-        <is>
-          <t>Blackboard</t>
-        </is>
-      </c>
-      <c r="C22" s="54" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="D22" s="47" t="inlineStr">
-        <is>
-          <t>Kho hiện vật + sổ cái + lan STALE (deps.py) đóng vai bảng trạng thái chung.</t>
-        </is>
-      </c>
-      <c r="E22" s="47" t="inlineStr">
-        <is>
-          <t>Ghi deps.upstream thật (hiện luôn rỗng) để STALE đúng chỗ và có ma trận truy vết REQ→thiết kế→mã→test; address_map dùng chung RTL↔firmware.</t>
-        </is>
-      </c>
-      <c r="F22" s="48" t="inlineStr">
-        <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="G22" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Blackboard*")</f>
-        <v/>
-      </c>
-      <c r="H22" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Blackboard*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="23.25" customHeight="1" s="27">
-      <c r="A23" s="47" t="inlineStr">
-        <is>
-          <t>D. Cắt ngang</t>
-        </is>
-      </c>
-      <c r="B23" s="53" t="inlineStr">
-        <is>
-          <t>Human-in-the-loop</t>
-        </is>
-      </c>
-      <c r="C23" s="56" t="inlineStr">
-        <is>
-          <t>Đã có (mạnh)</t>
-        </is>
-      </c>
-      <c r="D23" s="47" t="inlineStr">
-        <is>
-          <t>Policy R0–R4, thẻ cổng G-*, nhớ duyệt trong lượt (trừ không hoàn tác/never_auto/≥R4), soft-lock tệp, kiểm xuất xứ quyết định người.</t>
-        </is>
-      </c>
-      <c r="E23" s="47" t="inlineStr">
-        <is>
-          <t>Thất bại an toàn khi luật policy lỗi; cổng G-QUAL cho việc sửa test sau khi đỏ; HITL cho đo mạch thật; tác tử con hiện đi vòng qua HITL.</t>
-        </is>
-      </c>
-      <c r="F23" s="48" t="inlineStr">
-        <is>
-          <t>Rất cao</t>
-        </is>
-      </c>
-      <c r="G23" s="48">
-        <f>COUNTIF('Danh mục tối ưu'!$H$5:$H$110,"*Human-in-the-loop*")</f>
-        <v/>
-      </c>
-      <c r="H23" s="48">
-        <f>COUNTIFS('Danh mục tối ưu'!$H$5:$H$110,"*Human-in-the-loop*",'Danh mục tối ưu'!$K$5:$K$110,"P0")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
 </file>
--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -16,13 +16,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 09-10-2026" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 09-10-2026 (chiều)" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 09-10-2026 (toi)" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục tối ưu" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đối chiếu 18 mẫu" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 09-10-2026 (khuya)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh mục tối ưu" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đối chiếu 18 mẫu" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -2126,6 +2127,1702 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G88"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" customWidth="1" style="27" min="1" max="1"/>
+    <col width="66" customWidth="1" style="27" min="2" max="2"/>
+    <col width="24" customWidth="1" style="27" min="3" max="3"/>
+    <col width="8" customWidth="1" style="27" min="4" max="4"/>
+    <col width="11" customWidth="1" style="27" min="5" max="5"/>
+    <col width="16" customWidth="1" style="27" min="6" max="6"/>
+    <col width="34" customWidth="1" style="27" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="57" t="inlineStr">
+        <is>
+          <t>TIẾN ĐỘ ĐỢT TỐI ƯU TÁC TỬ — chốt khuya 09/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="58" t="inlineStr">
+        <is>
+          <t>Mỗi dòng 'Xong' đều có: mục DEV-LOG tra lại được · số ca kiểm trước→sau · một con số đo trên dữ liệu thật · phần còn nợ. Cột chi tiết nằm ở sheet “Danh mục tối ưu”, cột T–Y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="59" t="inlineStr">
+        <is>
+          <t>Tổng quan</t>
+        </is>
+      </c>
+      <c r="B4" s="59" t="inlineStr">
+        <is>
+          <t>Số việc</t>
+        </is>
+      </c>
+      <c r="C4" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>Xong (đã gộp vào main, đã đẩy)</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="n">
+        <v>23</v>
+      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>23 việc đầu của Giai đoạn 1 — việc #22 và #23 mỗi cái còn MỘT tiêu chí chưa đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="60" t="inlineStr">
+        <is>
+          <t>Đang làm (chưa commit)</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="61" t="inlineStr">
+        <is>
+          <t>không việc nào đang dở</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="60" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="n">
+        <v>83</v>
+      </c>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>83 việc còn lại trong 106</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="62" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B8" s="62" t="n">
+        <v>106</v>
+      </c>
+      <c r="C8" s="61" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>Phép đo của cả đợt</t>
+        </is>
+      </c>
+      <c r="B10" s="59" t="inlineStr">
+        <is>
+          <t>Trước (06/10)</t>
+        </is>
+      </c>
+      <c r="C10" s="59" t="inlineStr">
+        <is>
+          <t>Sau (09/10 khuya)</t>
+        </is>
+      </c>
+      <c r="D10" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị Python (pytest -q)</t>
+        </is>
+      </c>
+      <c r="B11" s="63" t="inlineStr">
+        <is>
+          <t>1 610</t>
+        </is>
+      </c>
+      <c r="C11" s="63" t="inlineStr">
+        <is>
+          <t>1 896</t>
+        </is>
+      </c>
+      <c r="D11" s="63" t="inlineStr">
+        <is>
+          <t>+286 ca so với 06/10; không ca cũ nào đỏ ở bất kỳ bước nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị giao diện (swift test)</t>
+        </is>
+      </c>
+      <c r="B12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="inlineStr">
+        <is>
+          <t>không nhiệm vụ nào đụng ui/ — kiểu khối A2.2 dùng “table”, Swift đã dựng được</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>kiem_tai_lieu.py</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="C13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ LỆCH CHẮC CHẮN mọi lượt. M4-07 không thêm công cụ nào, nên số công cụ giữ 131 — nhưng nó SỬA chỗ đếm: kiem_tai_lieu bật mọi cờ theo Features.ten_co(), và danh sách ấy gõ tay nên cờ thứ 10 vô hình với nó</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>thu_sch.py (cờ schematic bật)</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="C14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="D14" s="63" t="inlineStr">
+        <is>
+          <t>chạy ở M3-03 và M3-04, không tụt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t>Mục DEV-LOG mới</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330 → DEV-352</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="inlineStr">
+        <is>
+          <t>23 mục, mỗi việc một mục</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="63" t="inlineStr">
+        <is>
+          <t>Cờ tính năng mới</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>1 (schematic)</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="63" t="inlineStr">
+        <is>
+          <t>9 cờ mới, TẤT CẢ mặc định TẮT. Cờ thứ 10 là VERIFIER_GOI_BANG_CHUNG (M4-07) — verifier nhận gói bằng chứng do MÃ dựng từ sổ cái thay cho đề bài tác tử chính tự viết. Phần sửa Features.ten_co() lấy tên cờ từ dataclass thì KHÔNG sau cờ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="63" t="inlineStr">
+        <is>
+          <t>Mã lỗi mới</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>E4031 · E4032 · E6012 · E4033 · E4024</t>
+        </is>
+      </c>
+      <c r="D17" s="63" t="inlineStr">
+        <is>
+          <t>M4-04, M4-05 và M4-19 không thêm mã nào; M4-02 dùng lại E5006. E4033 (M3-18), E4024 (M4-01). M4-01 còn DÙNG LẠI E4008/E4009/E4023 của sim.run — cùng một chuyện thì cùng một mã. M4-07 không thêm mã lỗi nào — nó không dựng thêm cổng chặn, nó đổi ĐẦU VÀO của một tác tử con</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="59" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="C19" s="59" t="inlineStr">
+        <is>
+          <t>Mảng</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="E19" s="59" t="inlineStr">
+        <is>
+          <t>DEV-LOG</t>
+        </is>
+      </c>
+      <c r="F19" s="59" t="inlineStr">
+        <is>
+          <t>Ca kiểm</t>
+        </is>
+      </c>
+      <c r="G19" s="59" t="inlineStr">
+        <is>
+          <t>Cờ mặc định</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="63" t="inlineStr">
+        <is>
+          <t>M1-01</t>
+        </is>
+      </c>
+      <c r="C20" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D20" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E20" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330</t>
+        </is>
+      </c>
+      <c r="F20" s="63" t="inlineStr">
+        <is>
+          <t>105/309 phiên thật có lịch sử tự mâu thuẫn — 255 chỗ (156 kết quả thứ hai cùng id, 74 message chen giữa, 24 kết quả lạc lượt, 1 lời gọi không kết quả)</t>
+        </is>
+      </c>
+      <c r="G20" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="63" t="inlineStr">
+        <is>
+          <t>M1-02</t>
+        </is>
+      </c>
+      <c r="C21" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D21" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E21" s="63" t="inlineStr">
+        <is>
+          <t>DEV-331</t>
+        </is>
+      </c>
+      <c r="F21" s="63" t="inlineStr">
+        <is>
+          <t>lược đồ công cụ thật: 25 869 token/lời gọi (trần tool_schema=4000 chưa dòng mã nào đọc). Cờ bật: 4 475 token, giảm 82,7 %; 73 → 18 công cụ</t>
+        </is>
+      </c>
+      <c r="G21" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="63" t="inlineStr">
+        <is>
+          <t>M1-03</t>
+        </is>
+      </c>
+      <c r="C22" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D22" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E22" s="63" t="inlineStr">
+        <is>
+          <t>DEV-332</t>
+        </is>
+      </c>
+      <c r="F22" s="63" t="inlineStr">
+        <is>
+          <t>1 822 lời gọi của tác tử con trong 26 phiên thật, 0 lần qua lớp luật. Toàn công cụ đọc trừ một build.compile — lỗ hổng chưa bị bước vào, không phải được canh</t>
+        </is>
+      </c>
+      <c r="G22" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="63" t="inlineStr">
+        <is>
+          <t>M2-01</t>
+        </is>
+      </c>
+      <c r="C23" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D23" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E23" s="63" t="inlineStr">
+        <is>
+          <t>DEV-333</t>
+        </is>
+      </c>
+      <c r="F23" s="63" t="inlineStr">
+        <is>
+          <t>kịch bản 3 REQ + 3 phương án + 3 tiêu chí + 3 tệp: sửa MỘT REQ làm 9 hiện vật STALE → còn 3. Phép đo đầu ra 6→2 vì bị hàng rào E4020 chặn, đã sửa kịch bản đo</t>
+        </is>
+      </c>
+      <c r="G23" s="63" t="inlineStr">
+        <is>
+          <t>TRUY_VET — TẮT (phần nền chạy cả khi tắt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>M2-02</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D24" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E24" s="63" t="inlineStr">
+        <is>
+          <t>DEV-334</t>
+        </is>
+      </c>
+      <c r="F24" s="63" t="inlineStr">
+        <is>
+          <t>63 kho thật: 5/37 REQ có ít nhất một phép đo; 27 chưa có phương án nào nhận; 0 REQ đi hết chuỗi. Cột 'Mã nguồn' trống ở MỌI dự án vì hien_thuc_req vừa mới tồn tại</t>
+        </is>
+      </c>
+      <c r="G24" s="63" t="inlineStr">
+        <is>
+          <t>REQ_PHU — TẮT (khối A2.2 trên tab không phụ thuộc cờ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="63" t="inlineStr">
+        <is>
+          <t>M2-03</t>
+        </is>
+      </c>
+      <c r="C25" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D25" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E25" s="63" t="inlineStr">
+        <is>
+          <t>DEV-335</t>
+        </is>
+      </c>
+      <c r="F25" s="63" t="inlineStr">
+        <is>
+          <t>37 REQ thật: 25 sạch (67 %), 11 thiếu tiêu chí đo được, 2 có từ mơ hồ. Lần đo đầu ra 3 từ mơ hồ, một là kêu oan ('ít nhất 2 lần' là mức đo được) — đã vá</t>
+        </is>
+      </c>
+      <c r="G25" s="63" t="inlineStr">
+        <is>
+          <t>REQ_CHAT_LUONG — TẮT (module yeu_cau.py luôn có)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="63" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="63" t="inlineStr">
+        <is>
+          <t>M2-06</t>
+        </is>
+      </c>
+      <c r="C26" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D26" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E26" s="63" t="inlineStr">
+        <is>
+          <t>DEV-336</t>
+        </is>
+      </c>
+      <c r="F26" s="63" t="inlineStr">
+        <is>
+          <t>sổ cái thật: 26 lần đánh dấu 'xong' ngay sau một lần ghi mã, 19 lần (73 %) không có phép kiểm nào đạt ở giữa. Phép đo đầu ở mức dự án ra 0 — đúng nhưng đo sai câu hỏi</t>
+        </is>
+      </c>
+      <c r="G26" s="63" t="inlineStr">
+        <is>
+          <t>KE_HOACH_CONG_KIEM — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="63" t="inlineStr">
+        <is>
+          <t>M2-08</t>
+        </is>
+      </c>
+      <c r="C27" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D27" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E27" s="63" t="inlineStr">
+        <is>
+          <t>DEV-337</t>
+        </is>
+      </c>
+      <c r="F27" s="63" t="inlineStr">
+        <is>
+          <t>185 tệp .c thật: 1 758 → 1 786 hàm thấy được (+28 hàm trước đây VÔ HÌNH: 8 ngắt + 20 bị regex tham lam nuốt). 78 hàm nay gắn nhãn 'isr', 70 trong đó vốn đã có trong danh sách</t>
+        </is>
+      </c>
+      <c r="G27" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="63" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="63" t="inlineStr">
+        <is>
+          <t>M3-01</t>
+        </is>
+      </c>
+      <c r="C28" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D28" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E28" s="63" t="inlineStr">
+        <is>
+          <t>DEV-338</t>
+        </is>
+      </c>
+      <c r="F28" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mô hình mạch thật — và lý do đáng hơn con số: 3 kho CÓ Fact v_max thì KHÔNG có mô hình mạch, 5 kho có mạch thì không có Fact ấy; thêm nữa Fact dùng chủ thể chip:X mà ERC không tra tiền tố đó</t>
+        </is>
+      </c>
+      <c r="G28" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="63" t="inlineStr">
+        <is>
+          <t>M3-03</t>
+        </is>
+      </c>
+      <c r="C29" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D29" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E29" s="63" t="inlineStr">
+        <is>
+          <t>DEV-339</t>
+        </is>
+      </c>
+      <c r="F29" s="63" t="inlineStr">
+        <is>
+          <t>8 phát hiện trên 5 mạch thật (6 nguon_khong_cap + 2 net_mot_chan), trong đó net clock I2C nối đúng một chân. SÁU trong tám là 'mô hình chưa khai' chứ không phải 'mạch sai'. robot-canbang: 107 Port lá, KHÔNG Port nào là power_out</t>
+        </is>
+      </c>
+      <c r="G29" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="63" t="n">
+        <v>11</v>
+      </c>
+      <c r="B30" s="63" t="inlineStr">
+        <is>
+          <t>M3-04</t>
+        </is>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D30" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E30" s="63" t="inlineStr">
+        <is>
+          <t>DEV-340</t>
+        </is>
+      </c>
+      <c r="F30" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mạch thật — và đây là con số ĐÚNG (hai lỗi này catastrophic, không bo nào sống tới lúc lưu kho). Đã CẤY hai bộ cấp vào bản sao kho robot-canbang để chứng minh luật sống: nổ đúng 1 blocker trên net +5V thật</t>
+        </is>
+      </c>
+      <c r="G30" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="B31" s="63" t="inlineStr">
+        <is>
+          <t>M3-07</t>
+        </is>
+      </c>
+      <c r="C31" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D31" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E31" s="63" t="inlineStr">
+        <is>
+          <t>DEV-341</t>
+        </is>
+      </c>
+      <c r="F31" s="63" t="inlineStr">
+        <is>
+          <t>Fact tới được ERC: 5 → 17 (+12). Ba kho có Fact datasheet thì TOÀN BỘ mang chủ thể chip:, tức trước đó không một Fact nào tới được ERC. Độ phủ 5 mạch thật nay đọc được</t>
+        </is>
+      </c>
+      <c r="G31" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="63" t="n">
+        <v>13</v>
+      </c>
+      <c r="B32" s="63" t="inlineStr">
+        <is>
+          <t>M3-10</t>
+        </is>
+      </c>
+      <c r="C32" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D32" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E32" s="63" t="inlineStr">
+        <is>
+          <t>DEV-342</t>
+        </is>
+      </c>
+      <c r="F32" s="63" t="inlineStr">
+        <is>
+          <t>chi phí đo thật: mạch lớn nhất trong kho 187 nút → ERC 7,6 ms mỗi lần ghi. Trần 2000 nút, vượt thì NÓI RA chứ không im lặng bỏ qua</t>
+        </is>
+      </c>
+      <c r="G32" s="63" t="inlineStr">
+        <is>
+          <t>ERC_TU_DONG — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="B33" s="63" t="inlineStr">
+        <is>
+          <t>M3-12</t>
+        </is>
+      </c>
+      <c r="C33" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D33" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E33" s="63" t="inlineStr">
+        <is>
+          <t>DEV-343</t>
+        </is>
+      </c>
+      <c r="F33" s="63" t="inlineStr">
+        <is>
+          <t>846 bản ghi mô phỏng thật: regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 (testbench dự án in 'KET QUA: PASS' — nhãn đứng TRƯỚC từ khoá). Nới đúng một chỗ → 846/846 khớp, vẫn bắt đủ bốn ca PASS giả</t>
+        </is>
+      </c>
+      <c r="G33" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="64" t="n">
+        <v>15</v>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>M3-13</t>
+        </is>
+      </c>
+      <c r="C34" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D34" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E34" s="64" t="inlineStr">
+        <is>
+          <t>DEV-344</t>
+        </is>
+      </c>
+      <c r="F34" s="64" t="inlineStr">
+        <is>
+          <t>testbench Verilog THẬT của bài 3: tb_pcpi_dot4 1/1, tb_pcpi_mac 1/1, tb_pcpi_vmini không đo được (tb gọi bản bram HAI CỔNG đã bị bỏ 02/10) — mẫu số là TỆP, không phải phép phá</t>
+        </is>
+      </c>
+      <c r="G34" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="64" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B35" s="64" t="inlineStr">
+        <is>
+          <t>M3-18</t>
+        </is>
+      </c>
+      <c r="C35" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D35" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E35" s="64" t="inlineStr">
+        <is>
+          <t>DEV-345</t>
+        </is>
+      </c>
+      <c r="F35" s="64" t="inlineStr">
+        <is>
+          <t>6 cặp (mạng cổng, .cst) thật → 1 chỗ CHẶN: blinky của riscv-tn20k-b dựng bitstream 4,6 MB với chân đồng hồ do nextpnr tự chọn (rơi đúng chân 4 — bằng may). Cả 7 tệp .cst thật đọc hết, 0 lỗi cú pháp</t>
+        </is>
+      </c>
+      <c r="G35" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="64" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B36" s="64" t="inlineStr">
+        <is>
+          <t>M4-01</t>
+        </is>
+      </c>
+      <c r="C36" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D36" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E36" s="64" t="inlineStr">
+        <is>
+          <t>DEV-346</t>
+        </is>
+      </c>
+      <c r="F36" s="64" t="inlineStr">
+        <is>
+          <t>18 ca chạy trình biên dịch C thật: tệp test in số đo {"T1":300} với ngưỡng &lt;=255 → EIDE phán 1 ca HỎNG. Chưa kho cũ nào có tiêu chí unit test để đo lại trên dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="G36" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="64" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B37" s="64" t="inlineStr">
+        <is>
+          <t>M4-02</t>
+        </is>
+      </c>
+      <c r="C37" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D37" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E37" s="64" t="inlineStr">
+        <is>
+          <t>DEV-347</t>
+        </is>
+      </c>
+      <c r="F37" s="64" t="inlineStr">
+        <is>
+          <t>25 ca dựng đúng trạng thái thật (tệp test 3 ca, 1 ca đỏ, hiện vật dat=False) → fs.write còn 1 ca thì test.weakened=True. Và hàng rào cũ criteria.has_result chưa bao giờ nổ ngoài sim-01</t>
+        </is>
+      </c>
+      <c r="G37" s="64" t="inlineStr">
+        <is>
+          <t>SIM_RUNNER_GIOI_HAN — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="64" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B38" s="64" t="inlineStr">
+        <is>
+          <t>M4-05</t>
+        </is>
+      </c>
+      <c r="C38" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D38" s="64" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E38" s="64" t="inlineStr">
+        <is>
+          <t>DEV-348</t>
+        </is>
+      </c>
+      <c r="F38" s="64" t="inlineStr">
+        <is>
+          <t>du-lieu/rtos-sinhvien, chạy CẢ HAI hành vi: cũ so_thay=1, mới so_thay=0 — logo_ptit.c từ 'bộ kiểm ĐỎ' thành 'mọi đột biến đều làm hỏng biên dịch'. Một ô xanh giả, đã sửa</t>
+        </is>
+      </c>
+      <c r="G38" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B39" s="64" t="inlineStr">
+        <is>
+          <t>M4-19</t>
+        </is>
+      </c>
+      <c r="C39" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D39" s="64" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E39" s="64" t="inlineStr">
+        <is>
+          <t>DEV-349</t>
+        </is>
+      </c>
+      <c r="F39" s="64" t="inlineStr">
+        <is>
+          <t>chạy TẠI CHỖ trên ba dự án firmware thật: kết luận giống hệt lượt đột biến tại chỗ của M4-05, và 50/50 tệp giữ nguyên cả sha256 lẫn mtime</t>
+        </is>
+      </c>
+      <c r="G39" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="64" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B40" s="64" t="inlineStr">
+        <is>
+          <t>M4-04</t>
+        </is>
+      </c>
+      <c r="C40" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D40" s="64" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E40" s="64" t="inlineStr">
+        <is>
+          <t>DEV-350</t>
+        </is>
+      </c>
+      <c r="F40" s="64" t="inlineStr">
+        <is>
+          <t>TÁI HIỆN được ca DANH-GIA §2.2 bằng máy trên control_rtos.c thật: bảng cũ 0 đột biến cho hằng hex, bảng mới dòng 147 → mutant SỐNG. Và chi_tiet trên 12 tệp thật: 110 s, điểm 0,0</t>
+        </is>
+      </c>
+      <c r="G40" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (tham số mới, mặc định giữ hành vi cũ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="64" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B41" s="64" t="inlineStr">
+        <is>
+          <t>M4-06</t>
+        </is>
+      </c>
+      <c r="C41" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D41" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E41" s="64" t="inlineStr">
+        <is>
+          <t>DEV-351</t>
+        </is>
+      </c>
+      <c r="F41" s="64" t="inlineStr">
+        <is>
+          <t>đo TRƯỚC trên logo_ptit.c thật: điểm 0,0 · 30 mutant · 20 sống. Phần SAU chưa đo — cần lời gọi mô hình (§3.0 bắt hỏi trước), và dự án mẫu không có chỗ để đo</t>
+        </is>
+      </c>
+      <c r="G41" s="64" t="inlineStr">
+        <is>
+          <t>TEST_HARDEN — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="64" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B42" s="64" t="inlineStr">
+        <is>
+          <t>M4-07</t>
+        </is>
+      </c>
+      <c r="C42" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D42" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E42" s="64" t="inlineStr">
+        <is>
+          <t>DEV-352</t>
+        </is>
+      </c>
+      <c r="F42" s="64" t="inlineStr">
+        <is>
+          <t>sổ cái 42 dự án: 327 lời gọi task.run có việc, 323 là verifier · 209/323 đề bài dài hơn trần 300 ký tự · gói bằng chứng dựng được CÓ NỘI DUNG trên 29/42 dự án, 0 lần đổ · loc_claim bỏ 95/1 706 câu (năm dấu hiệu kế hoạch chỉ bỏ được 11)</t>
+        </is>
+      </c>
+      <c r="G42" s="64" t="inlineStr">
+        <is>
+          <t>VERIFIER_GOI_BANG_CHUNG — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="59" t="inlineStr">
+        <is>
+          <t>Việc còn MỞ (ngoài 84 việc chưa làm)</t>
+        </is>
+      </c>
+      <c r="B43" s="59" t="inlineStr">
+        <is>
+          <t>Vì sao còn mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="63" t="inlineStr">
+        <is>
+          <t>Bảy cờ mới đều còn TẮT</t>
+        </is>
+      </c>
+      <c r="B44" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU · TRUY_VET · REQ_PHU · REQ_CHAT_LUONG · KE_HOACH_CONG_KIEM · ERC_TU_DONG · SIM_RUNNER_GIOI_HAN. Cả bảy đổi thứ Agent nhìn thấy, đọc, hoặc LÀM ĐƯỢC mỗi lượt, nên chỉ bộ 76 ca chạy hai chế độ mới nói được chúng làm Agent khá hơn hay tệ hơn. Bộ ấy tốn tiền mô hình nên §3.0 bắt hỏi người dùng trước.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="63" t="inlineStr">
+        <is>
+          <t>kiem_cap_goi_tra() chưa thành hàng rào</t>
+        </is>
+      </c>
+      <c r="B45" s="63" t="inlineStr">
+        <is>
+          <t>Soát được mọi phiên đã lưu, nhưng chưa hook nào gọi nó tự động — bắt được chuyện cũ, chưa chặn được chuyện mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="63" t="inlineStr">
+        <is>
+          <t>Luật ERC quá áp chưa nổ trên dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="B46" s="63" t="inlineStr">
+        <is>
+          <t>Đường dẫn đã thông ở M3-07, nhưng ba kho có Fact điện áp thì không có mô hình mạch, và ngược lại. Phải chờ một dự án có cả hai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="63" t="inlineStr">
+        <is>
+          <t>Cột “Mã nguồn” của ma trận truy vết trống ở mọi dự án</t>
+        </is>
+      </c>
+      <c r="B47" s="63" t="inlineStr">
+        <is>
+          <t>Nó đọc hien_thuc_req — trường vừa mới tồn tại, chưa tệp nào trên đĩa từng khai. Nên “chưa hiện thực” ở đó nghĩa là “chưa ai KHAI”, không phải “chưa ai viết”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="63" t="inlineStr">
+        <is>
+          <t>Lỗi _go_dau trong src/eide/tools/design.py</t>
+        </is>
+      </c>
+      <c r="B48" s="63" t="inlineStr">
+        <is>
+          <t>Viết .replace('d','d') nên 'ổn định' và 'ON DINH' không khớp nhau. Hàm ấy đang dùng cho một phép kiểm an toàn (người có thật sự chọn không). Tìm thấy ở M2-03, CHƯA sửa vì ngoài phạm vi — cần bộ ca kiểm riêng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="63" t="inlineStr">
+        <is>
+          <t>subagent req-critic (bước 4 của M2-03)</t>
+        </is>
+      </c>
+      <c r="B49" s="63" t="inlineStr">
+        <is>
+          <t>Kế hoạch ghi “tuỳ chọn, gộp M2-13”. Chưa làm, đúng theo kế hoạch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="63" t="inlineStr">
+        <is>
+          <t>Hai luật kiểm chân FPGA chưa có dữ liệu để nổ</t>
+        </is>
+      </c>
+      <c r="B50" s="63" t="inlineStr">
+        <is>
+          <t>chan_lech_kit và io_type_lech_bank cần Fact chân kit. Không kho nào trong repo có Fact pin:tangnano20k.* hay khoá vccio — nên hôm nay chỉ 3 trong 5 luật của M3-18 kết luận được gì trên dữ liệu thật. Cùng hình dạng với luật ERC quá áp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="63" t="inlineStr">
+        <is>
+          <t>Một bitstream cũ đã dựng với chân đồng hồ tự chọn</t>
+        </is>
+      </c>
+      <c r="B51" s="63" t="inlineStr">
+        <is>
+          <t>blinky của du-lieu/riscv-tn20k-b — xem DEV-345 và README §8. Không sửa hiện vật cũ: đó là dữ liệu của những lượt đo đã chốt. Từ nay phép kiểm chặn trước nextpnr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="63" t="inlineStr">
+        <is>
+          <t>Ba công cụ mới nhất chưa lượt Agent nào GỌI</t>
+        </is>
+      </c>
+      <c r="B52" s="63" t="inlineStr">
+        <is>
+          <t>hdl.sensitivity · hdl.constraints_check · test.criteria. Mã của cả ba đã chạy trên hiện vật thật, nhưng đó là tôi gọi hàm, không phải tác tử gọi công cụ. README §8 đếm cả ba vào phần chưa dùng thật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="63" t="inlineStr">
+        <is>
+          <t>Bộ kiểm C của ba dự án firmware thật đều KHÔNG đo được độ nhạy</t>
+        </is>
+      </c>
+      <c r="B53" s="63" t="inlineStr">
+        <is>
+          <t>rtos-sinhvien: 0/12 tệp đo được (4 font khong_thay, control_rtos.c trùng ký hiệu, main.c không dịch trên máy chủ, logo_ptit.c mọi mutant hỏng biên dịch). stm32f469-freertos và thu-nghiem-g6: bộ kiểm ĐỎ SẴN. Đây là trạng thái của dữ liệu đo, không phải lỗi sản phẩm — nhưng nó nghĩa là chưa dự án firmware nào trong repo có một con số độ nhạy đáng tin. Xem DEV-348.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="63" t="inlineStr">
+        <is>
+          <t>POL-N6-sua-test chưa nổ trên một phiên thật nào</t>
+        </is>
+      </c>
+      <c r="B54" s="63" t="inlineStr">
+        <is>
+          <t>Hook sua_test_sau_do cấp dữ kiện cho lời gọi SẮP xảy ra, nên không soát lại được phiên đã lưu — khác mọi phép đo trước của đợt này. Nó đã có 25 ca kiểm và phá lại 27/27, nhưng chưa lượt tác tử thật nào chạm vào nó. Cùng hình dạng với ba luật kiểm thiếu dữ liệu ở trên, chỉ khác lý do.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="63" t="inlineStr">
+        <is>
+          <t>Tiêu chí 'mutation score tăng sau harden' của M4-06 chưa đo</t>
+        </is>
+      </c>
+      <c r="B55" s="63" t="inlineStr">
+        <is>
+          <t>Cần LỜI GỌI MÔ HÌNH, và §3.0 bắt hỏi anh Công trước. Đo 'trước' đã có (điểm 0,0 trên logo_ptit.c). Và dự án mẫu không có chỗ để đo: control_rtos.c là khong_nap_duoc, sáu tệp còn lại là bitmap. Cờ TEST_HARDEN giữ TẮT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="63" t="inlineStr">
+        <is>
+          <t>Một dự án chỉ dùng được MỘT tệp test</t>
+        </is>
+      </c>
+      <c r="B56" s="63" t="inlineStr">
+        <is>
+          <t>chay_test dịch MỌI tệp trong test/ cùng nhau, nên tệp thứ hai có main() là trùng ký hiệu. Kiểm trên dữ liệu thật: cả bốn dự án có test/ đều đúng một tệp. M4-06 lách bằng cách thêm ca vào tệp đang có — nhưng ràng buộc ấy vẫn còn, và nó giới hạn cách tổ chức bộ kiểm của mọi dự án.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="63" t="inlineStr">
+        <is>
+          <t>Gói bằng chứng chưa lần nào tới một MÔ HÌNH thật</t>
+        </is>
+      </c>
+      <c r="B57" s="63" t="inlineStr">
+        <is>
+          <t>Nó dựng được trên 29/42 dự án và đọc rất rõ với người, nhưng 'verifier đọc gói này có bác đúng hơn không' là câu hỏi về HÀNH VI MÔ HÌNH, và nó chưa được đo. Tiêu chí xong của M4-07 đòi bộ ca gài lỗi M4-22 — mà M4-22 nằm ở nhiệm vụ SAU trong kế hoạch. Cờ VERIFIER_GOI_BANG_CHUNG giữ TẮT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="63" t="inlineStr">
+        <is>
+          <t>loc_claim là một phép lọc văn xuôi, và nó leaky CÓ SỐ ĐO</t>
+        </is>
+      </c>
+      <c r="B58" s="63" t="inlineStr">
+        <is>
+          <t>95 trong 1 706 câu của 323 đề bài thật. Một câu lập luận không mang chữ nào trong sáu dấu hiệu vẫn đi qua. Đừng nhầm nó với hàng rào — hàng rào là gói bằng chứng do MÃ dựng, thứ tác tử chính không soạn được.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="59" t="inlineStr">
+        <is>
+          <t>Lỗi tìm thấy trong CHÍNH PHÉP ĐO của tôi</t>
+        </is>
+      </c>
+      <c r="B59" s="59" t="inlineStr">
+        <is>
+          <t>Lộ ra ở đâu</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="63" t="inlineStr">
+        <is>
+          <t>Kịch bản đo bị hàng rào của sản phẩm chặn (ghi tệp chưa đọc, E4020) và trả về một con số hợp lý thay vì nổ — 6→2 trông đẹp y như 9→3 đúng</t>
+        </is>
+      </c>
+      <c r="B60" s="63" t="inlineStr">
+        <is>
+          <t>M2-01 · DEV-333</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm dựng trên điều tôi tự nhớ sai: “thiết” bỏ dấu KHÔNG chứa “it”; chỗ va thật là bit/unit/init/exit</t>
+        </is>
+      </c>
+      <c r="B61" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá dài ĐÚNG BẰNG mã gốc (0.6 → 0.0) nên __pycache__ cũ còn hiệu lực — phép đo chạy mã khác với mã trong tệp</t>
+        </is>
+      </c>
+      <c r="B62" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="63" t="inlineStr">
+        <is>
+          <t>Phép đo trả lời ĐÚNG một câu hỏi KHÁC: đếm ở mức dự án ra 0 chỗ cần chặn; câu phải hỏi là “lần ghi NÀY đã được kiểm chưa” → 19/26</t>
+        </is>
+      </c>
+      <c r="B63" s="63" t="inlineStr">
+        <is>
+          <t>M2-06 · DEV-336</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm RỖNG: dàn dựng không có net đất nào, nên nó xanh cả khi tôi bỏ hẳn phép bỏ qua net đất</t>
+        </is>
+      </c>
+      <c r="B64" s="63" t="inlineStr">
+        <is>
+          <t>M3-01 · DEV-338</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="63" t="inlineStr">
+        <is>
+          <t>Hai phép phá chỉ ra THIẾT KẾ sai, không chỉ ca kiểm yếu (miễn net đất quá rộng; nhánh iout_max chưa ca nào chạm tới)</t>
+        </is>
+      </c>
+      <c r="B65" s="63" t="inlineStr">
+        <is>
+          <t>M3-03 · DEV-339</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá của tôi cũng SAI, và ca âm xanh vì lý do khác — hai cái sai che nhau</t>
+        </is>
+      </c>
+      <c r="B66" s="63" t="inlineStr">
+        <is>
+          <t>M3-07 · DEV-341</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm đo chính câu lệnh của mình (đặt bộ đếm = 3 rồi khẳng định nó khác rỗng, trong khi thực tế nó rỗng)</t>
+        </is>
+      </c>
+      <c r="B67" s="63" t="inlineStr">
+        <is>
+          <t>M3-10 · DEV-342</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="63" t="inlineStr">
+        <is>
+          <t>Regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 bản ghi thật; và ba ca kiểm xanh vì lý do sai (tệp giả dùng $4 thay $3; “FAILED” chứa “FAIL”)</t>
+        </is>
+      </c>
+      <c r="B68" s="63" t="inlineStr">
+        <is>
+          <t>M3-12 · DEV-343</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="63" t="inlineStr">
+        <is>
+          <t>"Phá lại thì đỏ 6/6" sai về TẬP, không sai về số: sáu phép phá ấy chọn đúng sáu chỗ đã có ca canh. Phá bằng tập rộng hơn ra 7/9.</t>
+        </is>
+      </c>
+      <c r="B69" s="63" t="inlineStr">
+        <is>
+          <t>M3-13 · DEV-344</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="63" t="inlineStr">
+        <is>
+          <t>409 'blocker' gần như toàn bộ từ một cặp vô nghĩa (mạng cổng của lõi CPU tổng hợp riêng, không bao giờ đem đặt-đi dây). Con số thật là 1.</t>
+        </is>
+      </c>
+      <c r="B70" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="63" t="inlineStr">
+        <is>
+          <t>Phép quét tệp .cst thật chỉ thu 4 trong 7 tệp mà ca kiểm vẫn xanh — câu 'mọi tệp .cst thật đều đọc được' nói về phần phép quét chạm tới.</t>
+        </is>
+      </c>
+      <c r="B71" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="63" t="inlineStr">
+        <is>
+          <t>Một ca kiểm và một phép phá nhắm hai NHÁNH khác nhau, nên ca mới xanh mà phép phá vẫn LỌT. Mất một lượt mới thấy.</t>
+        </is>
+      </c>
+      <c r="B72" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm xanh nhờ một DÒNG KHÁC: kiểm `"TỰ KHAI" in str(kh)` cả khối nên vẫn xanh khi phá chữ ấy ở dòng Kết luận — summary cũng chứa nó. Phép phá bắt được, ca kiểm thì không.</t>
+        </is>
+      </c>
+      <c r="B73" s="63" t="inlineStr">
+        <is>
+          <t>M4-01 · DEV-346</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="63" t="inlineStr">
+        <is>
+          <t>Một phép phá VÔ HIỆU: `them = [] or [[…]]` không đổi hành vi, nên nó báo LỌT oan và suýt làm tôi viết ca kiểm cho một chỗ vốn đã được canh.</t>
+        </is>
+      </c>
+      <c r="B74" s="63" t="inlineStr">
+        <is>
+          <t>M4-01 · DEV-346</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="63" t="inlineStr">
+        <is>
+          <t>HAI phép phá liền nhau VÔ HIỆU ở cùng một dòng: `cu = cu or ""` không đổi hành vi, rồi bỏ is_file() cũng không vì except OSError bắt FileNotFoundError. Phải bỏ cả hai lớp phòng mới phá được.</t>
+        </is>
+      </c>
+      <c r="B75" s="63" t="inlineStr">
+        <is>
+          <t>M4-02 · DEV-347</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="63" t="inlineStr">
+        <is>
+          <t>Một luật mới trỏ tới nhóm dữ kiện chưa khai thì DỪNG CẢ LƯỢT bằng ValueError, không phải 'không nổ' — và nhóm `criteria` của hàng rào N6 cũ cũng chưa bao giờ được khai.</t>
+        </is>
+      </c>
+      <c r="B76" s="63" t="inlineStr">
+        <is>
+          <t>M4-02 · DEV-347</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="63" t="inlineStr">
+        <is>
+          <t>Phép đo ĐỔ ngay lượt đầu trên dữ liệu thật (IndexError), và lỗi ấy nghĩa là test.sensitivity chưa bao giờ chạy nổi trên một tệp firmware thật — mọi con số cũ đều từ tệp nhỏ do ca kiểm tự dựng.</t>
+        </is>
+      </c>
+      <c r="B77" s="63" t="inlineStr">
+        <is>
+          <t>M4-05 · DEV-348</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="63" t="inlineStr">
+        <is>
+          <t>Bốn chỗ LỌT cùng một hình dạng: luật ĐÚNG, nằm ở chỗ ca kiểm không với tới — hai closure, một bảng phép không dựng nổi ca, và một tầng báo lại mà mọi ca cũ đều đi qua với stillborn == 0.</t>
+        </is>
+      </c>
+      <c r="B78" s="63" t="inlineStr">
+        <is>
+          <t>M4-05 · DEV-348</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="26" t="inlineStr">
+        <is>
+          <t>Tôi thêm MỘT cờ biên dịch để tránh một cáo buộc sai, và nó sinh ra MƯỜI MỘT cáo buộc sai khác: -I che header hệ thống, nên 11/12 tệp bị xếp là 'không dịch được trên máy chủ'. Phải là -iquote.</t>
+        </is>
+      </c>
+      <c r="B79" s="26" t="inlineStr">
+        <is>
+          <t>M4-19 · DEV-349</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="26" t="inlineStr">
+        <is>
+          <t>Gắn cờ biên dịch cho cả LƯỢT MỐC là đổi chính cái mốc mà mọi so sánh dựa vào — mốc của cả ba dự án thật từ XANH thành ĐỎ.</t>
+        </is>
+      </c>
+      <c r="B80" s="26" t="inlineStr">
+        <is>
+          <t>M4-19 · DEV-349</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="26" t="inlineStr">
+        <is>
+          <t>Phép đo mới TREO 10 phút trên tệp thật đầu tiên — không đổ, không báo gì, nên nó trông như một lượt chạy lâu. liet_ke dựng CẢ TỆP cho MỖI chỗ khớp: 57 600 chỗ × 720 KB ≈ 41 GB việc chuỗi.</t>
+        </is>
+      </c>
+      <c r="B81" s="26" t="inlineStr">
+        <is>
+          <t>M4-04 · DEV-350</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="26" t="inlineStr">
+        <is>
+          <t>Ca kiểm chi phí của tôi KHÔNG bắt được bản chậm, vì tệp dựng dùng hằng hex TRẦN — _bo_che trả về ngay khi không có chỗ giữ. Chính CHÚ THÍCH mỗi dòng của tệp thật mới làm mỗi lượt bỏ che thành một lượt regex thật.</t>
+        </is>
+      </c>
+      <c r="B82" s="26" t="inlineStr">
+        <is>
+          <t>M4-04 · DEV-350</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="26" t="inlineStr">
+        <is>
+          <t>Hook so MỐC THỜI GIAN thay vì số phiên bản: updated_at có độ phân giải thô nên hai lần ghi trong cùng một giây BẰNG NHAU, và phép so 'mới hơn' im lặng sai. Ca kiểm đầu tiên của chính hook ấy đỏ ngay.</t>
+        </is>
+      </c>
+      <c r="B83" s="26" t="inlineStr">
+        <is>
+          <t>M4-06 · DEV-351</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="26" t="inlineStr">
+        <is>
+          <t>Tôi quên mở nhánh và commit thẳng lên main. Nội dung đúng, quy trình §3.1 thì không — đã dựng lại con trỏ toi-uu/M4-06 tại đúng commit.</t>
+        </is>
+      </c>
+      <c r="B84" s="26" t="inlineStr">
+        <is>
+          <t>M4-06 · DEV-351</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="26" t="inlineStr">
+        <is>
+          <t>Năm dấu hiệu mà KẾ HOẠCH nêu cho loc_claim chỉ bỏ được 11 trong 1 706 câu của 323 đề bài THẬT — phép lọc đúng đề mà gần như không chạm gì. Chỗ rò thật là PHÁN QUYẾT TRÍCH SẴN ("kết quả 'dat: false'"), và phải thêm một dấu hiệu thứ sáu mới lên 95/1 706.</t>
+        </is>
+      </c>
+      <c r="B85" s="26" t="inlineStr">
+        <is>
+          <t>M4-07 · DEV-352</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="26" t="inlineStr">
+        <is>
+          <t>Hai phép phá LỌT vì ca kiểm xanh nhờ MỘT DÒNG KHÁC: xoá hẳn khối B khỏi gói bằng chứng mà bộ kiểm vẫn xanh, do ca của khối A đã thấy đúng tên tệp ấy qua dòng changeset. Cùng hình dạng DEV-344.</t>
+        </is>
+      </c>
+      <c r="B86" s="26" t="inlineStr">
+        <is>
+          <t>M4-07 · DEV-352</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="26" t="inlineStr">
+        <is>
+          <t>Ca kiểm CŨ nêu đúng bất biến "mọi cờ phải có trong ten_co()" mà kiểm nó trên MỘT TÊN GÕ SẴN, nên nó xanh suốt trong khi cờ thứ 10 vô hình: Features.load() trả False cả khi biến môi trường đã đặt. Phép so đúng là so hai TẬP HỢP.</t>
+        </is>
+      </c>
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>M4-07 · DEV-352</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="26" t="inlineStr">
+        <is>
+          <t>Tôi ghi con số ca kiểm (1 895) vào BỐN tệp tài liệu TRƯỚC khi bộ kiểm đầy đủ chạy xong — số thật là 1 896. Một con số suy ra bằng phép cộng trong đầu trông giống hệt một con số đo được.</t>
+        </is>
+      </c>
+      <c r="B88" s="26" t="inlineStr">
+        <is>
+          <t>M4-07 · DEV-352</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -2171,6 +3868,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="27">
       <c r="A4" s="31" t="inlineStr">
         <is>
@@ -8929,32 +10627,32 @@
         </is>
       </c>
       <c r="S73" s="47" t="n"/>
-      <c r="T73" t="inlineStr">
+      <c r="T73" s="26" t="inlineStr">
         <is>
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="U73" s="26" t="inlineStr">
         <is>
           <t>DEV-351</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="V73" s="26" t="inlineStr">
         <is>
           <t>1862 → 1878 (+16)</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="W73" s="26" t="inlineStr">
         <is>
           <t>Đo 'TRƯỚC' trên dự án thật du-lieu/rtos-sinhvien, tệp logo_ptit.c: điểm 0,0 · 30 mutant · 20 sống · 18 s. Phần 'SAU' CHƯA ĐO: chạy test.harden thật cần LỜI GỌI MÔ HÌNH và §3.0 bắt hỏi anh Công trước — tôi chưa hỏi. Và kể cả có hỏi, dự án ấy KHÔNG CÓ CHỖ để đo: tệp duy nhất đáng nâng là control_rtos.c, mà nó là khong_nap_duoc vì tệp test #include chính tệp .c đó (DEV-350); sáu tệp còn lại là bitmap — không ca kiểm nào giết được một đột biến một byte trong logo. · Kiểm trên dữ liệu thật một ràng buộc khác: cả BỐN dự án có test/ đều đúng MỘT tệp test, nên ca mới phải thêm vào tệp đang có.</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="X73" s="26" t="inlineStr">
         <is>
           <t>TEST_HARDEN — TẮT (phần ghi deps.upstream thì KHÔNG sau cờ)</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Y73" s="26" t="inlineStr">
         <is>
           <t>TIÊU CHÍ 'mutation score tăng sau harden' CHƯA ĐẠT — xem cột bên. Cờ giữ TẮT; bật mặc định còn cần bộ 76 ca chạy hai chế độ, cũng phải hỏi trước. · So PHIÊN BẢN, không so updated_at: độ phân giải thô nên hai lần ghi cùng giây BẰNG NHAU và phép so 'mới hơn' im lặng sai — ca kiểm đầu tiên của chính hook ấy đỏ ngay. · Phần Evaluator do MÃ làm: EIDE chạy bộ kiểm HAI lần (xanh trên mã thật, đỏ trên mutant), thiếu một chiều là loại, ca bị loại được TRẢ LẠI. Chỉ đòi chiều 'đỏ trên mutant' là nhận cả ca đỏ sẵn → vòng tự nâng tự khoá chính nó. · Hai hàng rào có sẵn chỉ ra hai ràng buộc thật: một dự án chỉ có MỘT tệp test, và fs.write không ghi đè tệp chưa đọc (E4020). · Bộ dò tài liệu tự khai 'kể cả công cụ sau cờ' mà chỉ bật MỘT cờ theo tên — đã sửa để lấy từ Features.ten_co(). · Phá lại 22/22, lượt đầu 18/22. · QUY TRÌNH: tôi quên mở nhánh và commit thẳng lên main; đã dựng lại con trỏ toi-uu/M4-06 tại đúng commit f829ddb.</t>
         </is>
@@ -9042,11 +10740,45 @@
       </c>
       <c r="Q74" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R74" s="47" t="n"/>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="R74" s="47" t="inlineStr">
+        <is>
+          <t>Claude (Opus 5)</t>
+        </is>
+      </c>
       <c r="S74" s="47" t="n"/>
+      <c r="T74" s="26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="U74" s="26" t="inlineStr">
+        <is>
+          <t>DEV-352</t>
+        </is>
+      </c>
+      <c r="V74" s="26" t="inlineStr">
+        <is>
+          <t>18 ca mới trong tests/test_subagent.py (TC-M4-07-01…18). Phá lại thì đỏ: 34/36 lượt đầu → 36/36 sau khi thêm hai ca đọc riêng khối A rỗng và khối B</t>
+        </is>
+      </c>
+      <c r="W74" s="26" t="inlineStr">
+        <is>
+          <t>sổ cái 42 dự án: 327 lời gọi task.run có việc, 323 là verifier · 209/323 đề bài dài hơn trần 300 ký tự · gói bằng chứng dựng được CÓ NỘI DUNG trên 29/42 dự án, 0 lần đổ · robot-canbang đụng ĐÚNG trần 6 000 ký tự · loc_claim bỏ 95/1 706 câu (năm dấu hiệu kế hoạch chỉ bỏ 11) · history làm gói rtos-sinhvien dài 2 142 → 2 322 ký tự, thêm (update→v24)</t>
+        </is>
+      </c>
+      <c r="X74" s="26" t="inlineStr">
+        <is>
+          <t>VERIFIER_GOI_BANG_CHUNG — mặc định TẮT</t>
+        </is>
+      </c>
+      <c r="Y74" s="26" t="inlineStr">
+        <is>
+          <t>Tiêu chí 'tỉ lệ verifier bác đúng không giảm khi bật cờ' CHƯA ĐẠT: nó cần bộ ca gài lỗi M4-22, mà M4-22 nằm ở nhiệm vụ SAU trong kế hoạch, và phép đo ấy cần lời gọi mô hình thật (§3.0 bắt hỏi anh Công trước). Gói bằng chứng chưa lần nào tới một mô hình thật.</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="79.5" customHeight="1" s="27">
       <c r="A75" s="46" t="inlineStr">
@@ -12215,7 +13947,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13056,7 +14788,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13511,7 +15243,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21375,7 +23107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" style="27" min="1" max="1"/>
@@ -21401,7 +23133,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="59" t="inlineStr">
         <is>
@@ -21475,7 +23206,6 @@
       </c>
       <c r="C8" s="61" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="59" t="inlineStr">
         <is>
@@ -21652,7 +23382,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="59" t="inlineStr">
         <is>
@@ -22437,7 +24166,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="A42" s="59" t="inlineStr">
         <is>
@@ -22582,7 +24310,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="59" t="inlineStr">
         <is>
@@ -22871,7 +24598,6 @@
         </is>
       </c>
     </row>
-    <row r="81"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22883,7 +24609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" style="27" min="1" max="1"/>
@@ -22909,7 +24635,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="59" t="inlineStr">
         <is>
@@ -22983,7 +24708,6 @@
       </c>
       <c r="C8" s="61" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="59" t="inlineStr">
         <is>
@@ -23160,7 +24884,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="59" t="inlineStr">
         <is>
@@ -23982,7 +25705,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="59" t="inlineStr">
         <is>
@@ -24151,7 +25873,6 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="59" t="inlineStr">
         <is>
@@ -24441,45 +26162,29 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="26" t="inlineStr">
         <is>
           <t>Hook so MỐC THỜI GIAN thay vì số phiên bản: updated_at có độ phân giải thô nên hai lần ghi trong cùng một giây BẰNG NHAU, và phép so 'mới hơn' im lặng sai. Ca kiểm đầu tiên của chính hook ấy đỏ ngay.</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="26" t="inlineStr">
         <is>
           <t>M4-06 · DEV-351</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="26" t="inlineStr">
         <is>
           <t>Tôi quên mở nhánh và commit thẳng lên main. Nội dung đúng, quy trình §3.1 thì không — đã dựng lại con trỏ toi-uu/M4-06 tại đúng commit.</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="26" t="inlineStr">
         <is>
           <t>M4-06 · DEV-351</t>
         </is>
       </c>
     </row>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -2105,17 +2105,17 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
-    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
     <mergeCell ref="A41:G41"/>
-    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -3868,7 +3868,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="27">
       <c r="A4" s="31" t="inlineStr">
         <is>
@@ -10946,11 +10945,45 @@
       <c r="P76" s="47" t="n"/>
       <c r="Q76" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R76" s="47" t="n"/>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="R76" s="47" t="inlineStr">
+        <is>
+          <t>Claude (Opus 5)</t>
+        </is>
+      </c>
       <c r="S76" s="47" t="n"/>
+      <c r="T76" s="26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="U76" s="26" t="inlineStr">
+        <is>
+          <t>DEV-353</t>
+        </is>
+      </c>
+      <c r="V76" s="26" t="inlineStr">
+        <is>
+          <t>1 896 → 1 901 (5 ca mới trong tests/test_tu_phat_hien_sai.py: TC-M4-09-01, TC-M4-09-02 cả hai mặt firmware/verifier, TC-M4-09-03, và ca mặc định của getattr). Ca CŨ test_da_goi_verifier_roi_thi_thoi đã sửa vì nó khoá đúng hành vi SAI (§3.2). Phá lại thì đỏ: 10/12 — hai chỗ LỌT đã kiểm lại là KHÔNG đổi hành vi (bỏ res.ok là guard chết vì _one_tool return sớm; so lỏng 'verifier' in ten vô hiệu vì trong tám tên SUBAGENT chỉ verifier chứa chuỗi ấy)</t>
+        </is>
+      </c>
+      <c r="W76" s="26" t="inlineStr">
+        <is>
+          <t>68 sổ cái dự án (26 sổ có task.run, 257 lời gọi: verifier 253 · code-analyst 2 · firmware 1 · sim-runner 1). Hook Stop ghi lại chính checks của nó, nên đếm được: 41 lượt hook khai tu_kiem_da_chay (đã IM), và 1 trong 41 lượt ấy KHÔNG có task.run(verifier) nào — robot-sinhvien2 run-007, nơi lời gọi task.run(code-analyst) nằm TRƯỚC fs.edit vào ISR(TIMER2_COMPA_vect), build.compile và fs.write sim/dump_isr.c. Quét theo hình dạng ra 2 lượt: thêm rtos-sinhvien run-026, lượt có cả target.flash.</t>
+        </is>
+      </c>
+      <c r="X76" s="26" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+      <c r="Y76" s="26" t="inlineStr">
+        <is>
+          <t>Không còn nợ tiêu chí nào. Ghi chú thiết kế: câu 'còn việc chưa ai kiểm chưa' vẫn đọc SỔ CÁI (xuyên phiên, co_viec_chua_kiem không đổi); chỉ câu 'verifier có chạy trong LƯỢT này không' mới dùng cờ trên ctx — ctx sinh ra và chết cùng lượt nên nó là vật đúng để hỏi.</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="57" customHeight="1" s="27">
       <c r="A77" s="46" t="inlineStr">

--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -2105,17 +2105,17 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
-    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -11155,11 +11155,45 @@
       </c>
       <c r="Q78" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R78" s="47" t="n"/>
+          <t>Xong (một tiêu chí CHƯA đạt)</t>
+        </is>
+      </c>
+      <c r="R78" s="47" t="inlineStr">
+        <is>
+          <t>Claude (Opus 5)</t>
+        </is>
+      </c>
       <c r="S78" s="47" t="n"/>
+      <c r="T78" s="26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="U78" s="26" t="inlineStr">
+        <is>
+          <t>DEV-354</t>
+        </is>
+      </c>
+      <c r="V78" s="26" t="inlineStr">
+        <is>
+          <t>1 901 → 1 929 (28 ca mới trong tests/test_hoi_quy.py). Phá lại thì đỏ: 24/32 lượt đầu → 31/34 sau khi thêm bảy ca kiểm và hai phép phá GỘP. Ba chỗ LỌT còn lại đã kiểm lại là KHÔNG đổi hành vi: bỏ ung.is_file() (p.is_file() vẫn lọc), trần quay lại đếm len(xong) (dedupe vẫn làm hàng đợi cạn), bỏ res.ok (guard chết vì _one_tool return sớm). Hai lớp phòng độc lập thì CHỈ phép phá gộp nói được có ca canh hay không — gộp dedupe + trần-đếm-lượt thì vòng lặp không dừng, và ca luồng-có-đồng-hồ biến nó thành chữ ĐỎ trong 8 giây thay vì một lượt treo 120 giây.</t>
+        </is>
+      </c>
+      <c r="W78" s="26" t="inlineStr">
+        <is>
+          <t>9 kho THẬT: bán kính STALE của kết quả test/sim khi sửa một tệp mã 107 lần → 49 lần, tức 58/107 (54 %) là cáo buộc OAN. Chi tiết: robot-canbang 6→3 · robot-sinhvien 14→10 · robot-sinhvien2 14→5 · robot-tu-can-bang 24→13 · rtos-sinhvien 30→8 · stm32f469-freertos 12→6 · usecase/uc03 3→1 · usecase/uc11 4→3. Và chính dữ liệu thật bác bước 1 của kế hoạch: robot-sinhvien2 lưu tep_nguon = ['sim/test_balance.c'] MỘT tệp, mà tệp ấy #include '../firmware/pid.c', motor.c, filter.c — nên upstream phải là bao đóng #include, không phải danh sách tệp đưa cho trình biên dịch. Bao đóng ra đúng 5 mắt.</t>
+        </is>
+      </c>
+      <c r="X78" s="26" t="inlineStr">
+        <is>
+          <t>HOI_QUY_NEN — mặc định TẮT (phần deps.upstream + hook ket_qua_stale KHÔNG sau cờ)</t>
+        </is>
+      </c>
+      <c r="Y78" s="26" t="inlineStr">
+        <is>
+          <t>Tiêu chí 'số lần tuyên xong với kết quả STALE = 0' CHƯA ĐẠT: sổ cái ghi lời gọi công cụ và checks của hook, nhưng KHÔNG ghi trạng thái kho tại thời điểm ấy — nên khác mọi phép đo khác của đợt, nó không soát lại được phiên đã lưu. Đóng nó cần PHÁT LẠI phiên mẫu với hook mới, tức lời gọi mô hình thật (§3.0 bắt hỏi anh Công trước). Và kế hoạch SAI chỗ: nó bảo sửa deps.ha_nguon_cua, nhưng ba ca kiểm đầu XANH SẴN — lớp đọc đã đúng từ M2-01; chỗ đứt là lớp GHI (test.run/sim.run gọi store.apply không có deps). Lỗi tìm thấy trong chính mã vừa viết: trần của _khep_include đếm len(xong) nên không chặn được vòng #include vô hạn — phép phá treo 900 giây thay vì đỏ; nay trần đếm LƯỢT.</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="68.25" customHeight="1" s="27">
       <c r="A79" s="46" t="inlineStr">

--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -2108,13 +2108,13 @@
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
+    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B48:G48"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
@@ -3868,6 +3868,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="27">
       <c r="A4" s="31" t="inlineStr">
         <is>
@@ -12431,11 +12432,45 @@
       <c r="P92" s="47" t="n"/>
       <c r="Q92" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R92" s="47" t="n"/>
+          <t>Xong (một tiêu chí CHƯA đạt)</t>
+        </is>
+      </c>
+      <c r="R92" s="47" t="inlineStr">
+        <is>
+          <t>Claude (Opus 5)</t>
+        </is>
+      </c>
       <c r="S92" s="47" t="n"/>
+      <c r="T92" s="26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="U92" s="26" t="inlineStr">
+        <is>
+          <t>DEV-355</t>
+        </is>
+      </c>
+      <c r="V92" s="26" t="inlineStr">
+        <is>
+          <t>1 942 → 1 950 (21 ca mới + 1 ca nha_that) trong tests/test_svd.py. Phá lại thì đỏ: 28/34 lượt đầu → 34/34. Sáu chỗ LỌT đều là lỗ THẬT, không chỗ nào vô hiệu: _so trả 0 thay vì None; bỏ lối khai bit thứ ba lsb/msb; thanh ghi thiếu addressOffset vẫn nạp; dem() trả (r,r) vẫn xanh vì ca kiểm chính ra 4 thanh ghi và 4 trường — HAI VẾ TÌNH CỜ BẰNG NHAU; reg.lookup không gom theo chủ thể vẫn xanh vì 25 thanh ghi của ca trần chỉ có MỘT Fact mỗi cái; trần 20 nâng được lên 500 qua tham số. Hai chỗ giữa cùng một hình dạng: phép đo xanh vì DÀN DỰNG làm hai vế trùng nhau, không vì mã đúng.</t>
+        </is>
+      </c>
+      <c r="W92" s="26" t="inlineStr">
+        <is>
+          <t>grep -rni svd src/ TRƯỚC khi sửa ra đúng HAI chỗ: phép phân loại, và một câu comment nói 'bốn loại đó có công cụ riêng' — không có bộ đọc nào. Tức phan_loai khai ĐẦY ĐỦ còn doc.load trả E1001 'chưa có bộ đọc': hai câu trả lời trái nhau cho cùng một tệp. CHƯA đo được trên SVD thật: quét cả máy 09/10/2026 không có tệp .svd nào ngoài tệp do chính bộ kiểm sinh trong tmp.</t>
+        </is>
+      </c>
+      <c r="X92" s="26" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần + công cụ mới core=False</t>
+        </is>
+      </c>
+      <c r="Y92" s="26" t="inlineStr">
+        <is>
+          <t>Tiêu chí 'nạp được SVD thật STM32F469, ghi số thanh ghi' CHƯA ĐẠT: máy không có tệp .svd thật nào. Ca test_nap_duoc_SVD_THAT đã viết, đánh nha_that + skipif, dò ~/STM32Cube · ~/.platformio · STM32CubeIDE.app · tai-lieu-tham-khao/ và SKIP. Không tự viết một SVD lớn rồi gọi nó là 'thật' — một bộ đọc chạy đúng trên tệp tự viết chưa nói gì về một tệp có derivedFrom khắp nơi và cluster lồng nhau. reg.lookup là công cụ thứ 132 và CHƯA lượt Agent nào gọi (README §8 đếm nó vào phần chưa dùng thật). Lỗi tìm thấy trong chính mã vừa viết: trần TRAN_DON_VI cắt IM LẶNG — nay doc.load trả da_cat_o_tran và nói ra, vì 'chip không có' và 'chưa nạp tới' dẫn tới hai việc ngược nhau.</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="79.5" customHeight="1" s="27">
       <c r="A93" s="46" t="inlineStr">

--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -2105,17 +2105,17 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
-    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
     <mergeCell ref="A41:G41"/>
-    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -12642,11 +12642,45 @@
       </c>
       <c r="Q94" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R94" s="47" t="n"/>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="R94" s="47" t="inlineStr">
+        <is>
+          <t>Claude (Opus 5)</t>
+        </is>
+      </c>
       <c r="S94" s="47" t="n"/>
+      <c r="T94" s="26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="U94" s="26" t="inlineStr">
+        <is>
+          <t>DEV-356</t>
+        </is>
+      </c>
+      <c r="V94" s="26" t="inlineStr">
+        <is>
+          <t>1 976 → 1 980 (30 ca mới trong tests/test_don_vi_fact.py). Phá lại thì đỏ: 17/21 lượt đầu → 23/24. Hai chỗ LỌT là LỖ THẬT, thành hai phần sửa thêm: hop_ly NỔ TypeError với giá trị chuỗi (i2c.addr sống sót chỉ vì nó không có khoảng), và hàng bảng tra bằng khoa_goc nên mất phép kiểm KHOẢNG. Hai chỗ còn lại vô hiệu: 'tra tiền tố ngắn nhất trước' không đổi gì vì bảng không có khoá 'i2c' — tức ca kiểm i2c của tôi KHÔNG đo được tính chất nó nói nó đo; và break thay continue thoát một vòng lặp MỘT phần tử.</t>
+        </is>
+      </c>
+      <c r="W94" s="26" t="inlineStr">
+        <is>
+          <t>hop_ly('vdd.max', 25, '°C') trả True trên mã cũ — 25 lọt khoảng điện áp 0,5–60 V. Và TC-M5-05-04 của kế hoạch XANH SẴN vì một lý do khác: 'VDD' trơn không khớp mẫu nào trong _MAU_THONG_SO, nên hàng rỗng vì tên chứ không vì phép kiểm đơn vị. Lỗ thứ hai đo được bằng tập phá: đường BẢNG và đường DÒNG CHỮ sinh HAI khoá khác nhau cho cùng một thông số — flash.size/flash.max, fmax/fmax.max, i2c.addr/i2c.max — và xay_dung._han_muc KHÔNG đọc flash.max, nên một dung lượng Flash đọc từ BẢNG chưa bao giờ thành hạn mức.</t>
+        </is>
+      </c>
+      <c r="X94" s="26" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+      <c r="Y94" s="26" t="inlineStr">
+        <is>
+          <t>Không còn nợ tiêu chí nào. Ba khoá bị đổi (flash.max, fmax.max, i2c.max) là ba khoá KHÔNG chỗ nào đọc, nên đổi chúng không làm lệch Fact cũ nào đang khớp với ai — đúng tinh thần dòng 'Không đổi tên khoá mà bộ trích sinh ra' của kế hoạch.</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="68.25" customHeight="1" s="27">
       <c r="A95" s="46" t="inlineStr">

--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -2105,17 +2105,17 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
-    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -12848,11 +12848,45 @@
       <c r="P96" s="47" t="n"/>
       <c r="Q96" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R96" s="47" t="n"/>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="R96" s="47" t="inlineStr">
+        <is>
+          <t>Claude (Opus 5)</t>
+        </is>
+      </c>
       <c r="S96" s="47" t="n"/>
+      <c r="T96" s="26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="U96" s="26" t="inlineStr">
+        <is>
+          <t>DEV-357</t>
+        </is>
+      </c>
+      <c r="V96" s="26" t="inlineStr">
+        <is>
+          <t>1 993 → 2 000 (20 ca mới trong tests/test_fact_from_doc.py). Phá lại thì đỏ: 15/22 lượt đầu → 22/22. CẢ BẢY chỗ LỌT là ca kiểm của tôi CHƯA CHẠM TỚI, không chỗ nào vô hiệu — và năm trong bảy chỉ lộ ra khi dàn dựng có đúng hình dạng cần đo: bốn dòng văn bản thêm vào bộ dàn dựng (0.39 phần trăm · 0x27 một mình · '39,' · 100 mA) là thứ biến bảy chữ LỌT thành bảy chữ ĐỎ. Một ca CŨ phải sửa theo §3.2 (nêu `trich` cho giá trị '39').</t>
+        </is>
+      </c>
+      <c r="W96" s="26" t="inlineStr">
+        <is>
+          <t>Phép kiểm cũ: re.sub(r'[\s.,]', '', x) rồi `in`. Nó nhận bừa ở hai chỗ, đo được bằng ca kiểm trên tài liệu thật nạp qua doc.load: '2.7 V' thành '27v' nên gia_tri='27' đi qua; và phép CHỨA không ranh giới nên '3' khớp 'Table 3', '180' khớp '1800', '39' khớp '0.39'. source.quote lưu 200 ký tự ĐẦU đoạn, không phải chỗ có con số — người mở Fact ra xem thấy một đoạn không chứa con số.</t>
+        </is>
+      </c>
+      <c r="X96" s="26" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+      <c r="Y96" s="26" t="inlineStr">
+        <is>
+          <t>Không còn nợ tiêu chí nào. HAI chỗ không theo chữ kế hoạch: (1) giữ E2006 cho 'giá trị không có trong đoạn' và dùng E2008 chỉ cho ba lý do MỚI — gộp cả bốn vào một mã là bắt tác tử học một mã cho bốn việc khác nhau, và một ca kiểm cũ đang khoá đúng nghĩa cũ; (2) TC-M5-07-01 viết đúng chữ thì XANH VÌ LÝ DO KHÁC — '27' dài hai ký tự nên luật số-ngắn chặn trước và phép so dấu chấm không bao giờ chạy tới. `trich` KHÔNG thành tham số bắt buộc: giá trị từ 3 ký tự trở lên vẫn gọi được như cũ.</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="79.5" customHeight="1" s="27">
       <c r="A97" s="46" t="inlineStr">

--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -2108,13 +2108,13 @@
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
+    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B48:G48"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
@@ -13390,11 +13390,45 @@
       </c>
       <c r="Q102" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R102" s="47" t="n"/>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="R102" s="47" t="inlineStr">
+        <is>
+          <t>Claude (Opus 5)</t>
+        </is>
+      </c>
       <c r="S102" s="47" t="n"/>
+      <c r="T102" s="26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="U102" s="26" t="inlineStr">
+        <is>
+          <t>DEV-358</t>
+        </is>
+      </c>
+      <c r="V102" s="26" t="inlineStr">
+        <is>
+          <t>2 012 → 2 015 (tổng 15 ca mới trong tests/test_mem_a.py). Phá lại thì đỏ: 20/23 lượt đầu → 23/23. Cả BA chỗ LỌT là DÀN DỰNG làm phép phá vô hiệu, không phải mã đúng: không ca nào có hàng bảng nhiều ô; ca âm dựng `source` ĐÃ ĐÚNG hình dạng _gon trả về nên hạ trần kích hoạt cũng không đổi gì; và ca {'ds': [...]} có MỘT khoá nên chia ngân sách cho một là phép đồng nhất. Lần thứ ba liền (M5-03 · M5-07 · M5-13) chỗ LỌT nằm ở bộ dàn dựng.</t>
+        </is>
+      </c>
+      <c r="W102" s="26" t="inlineStr">
+        <is>
+          <t>23 kho THẬT: một lời gọi fact.query không tham số đưa 67 635 token vào ngữ cảnh trước → 32 560 sau (giảm 35 075, tức 51 %). Đo bằng cách bọc hai lần — một lần với chính sách mới, một lần với bảng CHINH_SACH đã bỏ fact.query ra. robot-sinhvien một mình: 30 Fact → 12 076 token cho MỘT lời gọi, nay 4 579 (bốn lời gọi như thế là hết một cửa sổ 48k). Bốn kho nhỏ (1–2 Fact) ra con số y nguyên, đúng như ca âm đòi.</t>
+        </is>
+      </c>
+      <c r="X102" s="26" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+      <c r="Y102" s="26" t="inlineStr">
+        <is>
+          <t>Không còn nợ tiêu chí nào. Lỗi tìm thấy trong chính mã vừa viết: _cat_chung tiêu ĐÚNG ngân sách nó được giao, nên giao cả trần thì shown_tokens nhảy lên 4 024 vì vỏ JSON — một cái trần bị vượt bởi chính phép cắt dựng ra để giữ nó; nay chỗ gọi chừa một phần tư. Bài học gom lại: khi dựng ca kiểm cho một phép CHIA hay một phép CẮT, dàn dựng phải có ít nhất HAI phần tử và chúng phải KHÁC NHAU.</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="102" customHeight="1" s="27">
       <c r="A103" s="46" t="inlineStr">

--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -2105,17 +2105,17 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
-    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
     <mergeCell ref="A41:G41"/>
-    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -13764,11 +13764,45 @@
       <c r="P106" s="47" t="n"/>
       <c r="Q106" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R106" s="47" t="n"/>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="R106" s="47" t="inlineStr">
+        <is>
+          <t>Claude (Opus 5)</t>
+        </is>
+      </c>
       <c r="S106" s="47" t="n"/>
+      <c r="T106" s="26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="U106" s="26" t="inlineStr">
+        <is>
+          <t>DEV-359</t>
+        </is>
+      </c>
+      <c r="V106" s="26" t="inlineStr">
+        <is>
+          <t>2 015 → 2 030 (18 ca mới trong tests/test_mem_c.py). Phá lại thì đỏ: 20/23 lượt đầu → 23/23. Cả BA chỗ LỌT là ca kiểm CHƯA chạm tới dòng mã nó nói nó canh: chuỗi '`target.flash` → E4040' cũng có ở dòng 'Lỗi cuối cùng' nên assertion xanh qua dòng khác; transcript dàn dựng ngắn hơn trần 1 500 nên bỏ trần không đổi gì; và ca 'transcript hỏng' chạy trên dự án CHỈ CÓ MỘT PHIÊN nên hàm trả rỗng ngay ở bước 'không có phiên trước'. Bốn nhiệm vụ liền (M5-03 · M5-07 · M5-13 · M5-17) đều có chỗ LỌT ở bộ DÀN DỰNG.</t>
+        </is>
+      </c>
+      <c r="W106" s="26" t="inlineStr">
+        <is>
+          <t>4 lần nén C2 ĐẠT trên sổ cái thật, 0 lần huỷ, ở 2 dự án (robot-tu-can-bang, thu-nghiem-mem-c) — và bản tóm tắt cuối nạp lại được qua tu_dict, KHÔNG rỗng, ở 2/2. 313 phiên có transcript, 303 (96 %) thuộc dự án CHƯA TỪNG NÉN: câu 'chưa có bản tóm tắt nào' là câu khối resume nói ở gần như mọi lần mở lại, trong khi một transcript đầy đủ đang nằm sẵn trên đĩa. LỖI TRONG CHÍNH PHÉP ĐO: phép đếm đầu tiên lọc bằng '"buoc": "ok"' in line, mà sổ cái thật ghi JSON KHÔNG có khoảng trắng sau dấu hai chấm — nên nó trả 100 % thay vì trả rỗng. Cứu được vì grep -c '"compact"' ra 146 dòng, chỏi với kết luận 'chưa nén lần nào'.</t>
+        </is>
+      </c>
+      <c r="X106" s="26" t="inlineStr">
+        <is>
+          <t>RESUME_TUONG_THUAT — mặc định TẮT (phần nạp lại tóm tắt C2 KHÔNG sau cờ)</t>
+        </is>
+      </c>
+      <c r="Y106" s="26" t="inlineStr">
+        <is>
+          <t>Không còn nợ tiêu chí nào. Cờ thứ 12, giữ TẮT. Phần A (nạp lại tóm tắt từ sổ cái) là sửa lỗi thuần nên chạy cả khi cờ tắt. Bỏ phần 'trạng thái kế hoạch vào resume' theo đúng ghi chú của kế hoạch — plan:current đã hiện ở &lt;pending&gt; mỗi lượt.</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="102" customHeight="1" s="27">
       <c r="A107" s="46" t="inlineStr">

--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -21,6 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đối chiếu 18 mẫu" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 09-10-2026 (sau #32)" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
@@ -2105,17 +2106,17 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
-    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -3868,7 +3869,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="27">
       <c r="A4" s="31" t="inlineStr">
         <is>
@@ -15748,6 +15748,1962 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G95"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" customWidth="1" style="27" min="1" max="1"/>
+    <col width="66" customWidth="1" style="27" min="2" max="2"/>
+    <col width="24" customWidth="1" style="27" min="3" max="3"/>
+    <col width="8" customWidth="1" style="27" min="4" max="4"/>
+    <col width="11" customWidth="1" style="27" min="5" max="5"/>
+    <col width="16" customWidth="1" style="27" min="6" max="6"/>
+    <col width="34" customWidth="1" style="27" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="57" t="inlineStr">
+        <is>
+          <t>TIẾN ĐỘ ĐỢT TỐI ƯU TÁC TỬ — chốt sau việc #32, 09/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="58" t="inlineStr">
+        <is>
+          <t>Mỗi dòng 'Xong' đều có: mục DEV-LOG tra lại được · số ca kiểm trước→sau · một con số đo trên dữ liệu thật · phần còn nợ. Cột chi tiết nằm ở sheet “Danh mục tối ưu”, cột T–Y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="59" t="inlineStr">
+        <is>
+          <t>Tổng quan</t>
+        </is>
+      </c>
+      <c r="B4" s="59" t="inlineStr">
+        <is>
+          <t>Số việc</t>
+        </is>
+      </c>
+      <c r="C4" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>Xong (đã gộp vào main, đã đẩy)</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="n">
+        <v>30</v>
+      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>30/106 — và HẾT P0 KHÔNG BỊ CHẶN của Giai đoạn 1. GĐ1 có 32 việc; còn #26 M2-09 (P1 · L, tiền đề cứng) và #27 M4-13 (P0 · M, bị #26 chặn).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="60" t="inlineStr">
+        <is>
+          <t>Đang làm (chưa commit)</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="61" t="inlineStr">
+        <is>
+          <t>không việc nào đang dở; main đã đẩy và khớp origin/main</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="60" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="n">
+        <v>76</v>
+      </c>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>76 việc còn lại trong 106</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="62" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B8" s="62" t="n">
+        <v>106</v>
+      </c>
+      <c r="C8" s="61" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>Phép đo của cả đợt</t>
+        </is>
+      </c>
+      <c r="B10" s="59" t="inlineStr">
+        <is>
+          <t>Trước (06/10)</t>
+        </is>
+      </c>
+      <c r="C10" s="59" t="inlineStr">
+        <is>
+          <t>Sau (09/10 sau #32)</t>
+        </is>
+      </c>
+      <c r="D10" s="59" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị Python (pytest -q)</t>
+        </is>
+      </c>
+      <c r="B11" s="63" t="inlineStr">
+        <is>
+          <t>1 610</t>
+        </is>
+      </c>
+      <c r="C11" s="63" t="inlineStr">
+        <is>
+          <t>2 030</t>
+        </is>
+      </c>
+      <c r="D11" s="63" t="inlineStr">
+        <is>
+          <t>+420 ca so với 06/10; 1 skip (cần tệp .svd thật, máy không có); không ca cũ nào đỏ ở bất kỳ bước nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="63" t="inlineStr">
+        <is>
+          <t>Ca đơn vị giao diện (swift test)</t>
+        </is>
+      </c>
+      <c r="B12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C12" s="63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="inlineStr">
+        <is>
+          <t>không nhiệm vụ nào đụng ui/ — kiểu khối A2.2 dùng “table”, Swift đã dựng được</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>kiem_tai_lieu.py</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="C13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ lệch</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="inlineStr">
+        <is>
+          <t>0 chỗ LỆCH CHẮC CHẮN mọi lượt. M4-07 không thêm công cụ nào, nên số công cụ giữ 131 — nhưng nó SỬA chỗ đếm: kiem_tai_lieu bật mọi cờ theo Features.ten_co(), và danh sách ấy gõ tay nên cờ thứ 10 vô hình với nó</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>thu_sch.py (cờ schematic bật)</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="C14" s="63" t="inlineStr">
+        <is>
+          <t>63/63</t>
+        </is>
+      </c>
+      <c r="D14" s="63" t="inlineStr">
+        <is>
+          <t>chạy ở M3-03 và M3-04, không tụt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t>Mục DEV-LOG mới</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330 → DEV-359</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="inlineStr">
+        <is>
+          <t>30 mục, mỗi việc một mục</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="63" t="inlineStr">
+        <is>
+          <t>Cờ tính năng mới</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>1 (schematic)</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="63" t="inlineStr">
+        <is>
+          <t>11 cờ mới, TẤT CẢ mặc định TẮT. Hai cờ mới nhất: HOI_QUY_NEN (M4-11) và RESUME_TUONG_THUAT (M5-17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="63" t="inlineStr">
+        <is>
+          <t>Mã lỗi mới</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>E4031 · E4032 · E6012 · E4033 · E4024 · E2007 · E2008</t>
+        </is>
+      </c>
+      <c r="D17" s="63" t="inlineStr">
+        <is>
+          <t>M5-03 dùng E2007 (SVD không đọc được); M5-07 dùng E2008 cho BA lý do mới và GIỮ E2006 cho 'giá trị không có trong đoạn' — bốn lý do dẫn tới bốn việc khác nhau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="59" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="C19" s="59" t="inlineStr">
+        <is>
+          <t>Mảng</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="E19" s="59" t="inlineStr">
+        <is>
+          <t>DEV-LOG</t>
+        </is>
+      </c>
+      <c r="F19" s="59" t="inlineStr">
+        <is>
+          <t>Ca kiểm</t>
+        </is>
+      </c>
+      <c r="G19" s="59" t="inlineStr">
+        <is>
+          <t>Cờ mặc định</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="63" t="inlineStr">
+        <is>
+          <t>M1-01</t>
+        </is>
+      </c>
+      <c r="C20" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D20" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E20" s="63" t="inlineStr">
+        <is>
+          <t>DEV-330</t>
+        </is>
+      </c>
+      <c r="F20" s="63" t="inlineStr">
+        <is>
+          <t>105/309 phiên thật có lịch sử tự mâu thuẫn — 255 chỗ (156 kết quả thứ hai cùng id, 74 message chen giữa, 24 kết quả lạc lượt, 1 lời gọi không kết quả)</t>
+        </is>
+      </c>
+      <c r="G20" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="63" t="inlineStr">
+        <is>
+          <t>M1-02</t>
+        </is>
+      </c>
+      <c r="C21" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D21" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E21" s="63" t="inlineStr">
+        <is>
+          <t>DEV-331</t>
+        </is>
+      </c>
+      <c r="F21" s="63" t="inlineStr">
+        <is>
+          <t>lược đồ công cụ thật: 25 869 token/lời gọi (trần tool_schema=4000 chưa dòng mã nào đọc). Cờ bật: 4 475 token, giảm 82,7 %; 73 → 18 công cụ</t>
+        </is>
+      </c>
+      <c r="G21" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="63" t="inlineStr">
+        <is>
+          <t>M1-03</t>
+        </is>
+      </c>
+      <c r="C22" s="63" t="inlineStr">
+        <is>
+          <t>1. Lõi tác tử</t>
+        </is>
+      </c>
+      <c r="D22" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E22" s="63" t="inlineStr">
+        <is>
+          <t>DEV-332</t>
+        </is>
+      </c>
+      <c r="F22" s="63" t="inlineStr">
+        <is>
+          <t>1 822 lời gọi của tác tử con trong 26 phiên thật, 0 lần qua lớp luật. Toàn công cụ đọc trừ một build.compile — lỗ hổng chưa bị bước vào, không phải được canh</t>
+        </is>
+      </c>
+      <c r="G22" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="63" t="inlineStr">
+        <is>
+          <t>M2-01</t>
+        </is>
+      </c>
+      <c r="C23" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D23" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E23" s="63" t="inlineStr">
+        <is>
+          <t>DEV-333</t>
+        </is>
+      </c>
+      <c r="F23" s="63" t="inlineStr">
+        <is>
+          <t>kịch bản 3 REQ + 3 phương án + 3 tiêu chí + 3 tệp: sửa MỘT REQ làm 9 hiện vật STALE → còn 3. Phép đo đầu ra 6→2 vì bị hàng rào E4020 chặn, đã sửa kịch bản đo</t>
+        </is>
+      </c>
+      <c r="G23" s="63" t="inlineStr">
+        <is>
+          <t>TRUY_VET — TẮT (phần nền chạy cả khi tắt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>M2-02</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D24" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E24" s="63" t="inlineStr">
+        <is>
+          <t>DEV-334</t>
+        </is>
+      </c>
+      <c r="F24" s="63" t="inlineStr">
+        <is>
+          <t>63 kho thật: 5/37 REQ có ít nhất một phép đo; 27 chưa có phương án nào nhận; 0 REQ đi hết chuỗi. Cột 'Mã nguồn' trống ở MỌI dự án vì hien_thuc_req vừa mới tồn tại</t>
+        </is>
+      </c>
+      <c r="G24" s="63" t="inlineStr">
+        <is>
+          <t>REQ_PHU — TẮT (khối A2.2 trên tab không phụ thuộc cờ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="63" t="inlineStr">
+        <is>
+          <t>M2-03</t>
+        </is>
+      </c>
+      <c r="C25" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D25" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E25" s="63" t="inlineStr">
+        <is>
+          <t>DEV-335</t>
+        </is>
+      </c>
+      <c r="F25" s="63" t="inlineStr">
+        <is>
+          <t>37 REQ thật: 25 sạch (67 %), 11 thiếu tiêu chí đo được, 2 có từ mơ hồ. Lần đo đầu ra 3 từ mơ hồ, một là kêu oan ('ít nhất 2 lần' là mức đo được) — đã vá</t>
+        </is>
+      </c>
+      <c r="G25" s="63" t="inlineStr">
+        <is>
+          <t>REQ_CHAT_LUONG — TẮT (module yeu_cau.py luôn có)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="63" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="63" t="inlineStr">
+        <is>
+          <t>M2-06</t>
+        </is>
+      </c>
+      <c r="C26" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D26" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E26" s="63" t="inlineStr">
+        <is>
+          <t>DEV-336</t>
+        </is>
+      </c>
+      <c r="F26" s="63" t="inlineStr">
+        <is>
+          <t>sổ cái thật: 26 lần đánh dấu 'xong' ngay sau một lần ghi mã, 19 lần (73 %) không có phép kiểm nào đạt ở giữa. Phép đo đầu ở mức dự án ra 0 — đúng nhưng đo sai câu hỏi</t>
+        </is>
+      </c>
+      <c r="G26" s="63" t="inlineStr">
+        <is>
+          <t>KE_HOACH_CONG_KIEM — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="63" t="inlineStr">
+        <is>
+          <t>M2-08</t>
+        </is>
+      </c>
+      <c r="C27" s="63" t="inlineStr">
+        <is>
+          <t>2. Phân tích &amp; thiết kế phần mềm</t>
+        </is>
+      </c>
+      <c r="D27" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E27" s="63" t="inlineStr">
+        <is>
+          <t>DEV-337</t>
+        </is>
+      </c>
+      <c r="F27" s="63" t="inlineStr">
+        <is>
+          <t>185 tệp .c thật: 1 758 → 1 786 hàm thấy được (+28 hàm trước đây VÔ HÌNH: 8 ngắt + 20 bị regex tham lam nuốt). 78 hàm nay gắn nhãn 'isr', 70 trong đó vốn đã có trong danh sách</t>
+        </is>
+      </c>
+      <c r="G27" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="63" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="63" t="inlineStr">
+        <is>
+          <t>M3-01</t>
+        </is>
+      </c>
+      <c r="C28" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D28" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E28" s="63" t="inlineStr">
+        <is>
+          <t>DEV-338</t>
+        </is>
+      </c>
+      <c r="F28" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mô hình mạch thật — và lý do đáng hơn con số: 3 kho CÓ Fact v_max thì KHÔNG có mô hình mạch, 5 kho có mạch thì không có Fact ấy; thêm nữa Fact dùng chủ thể chip:X mà ERC không tra tiền tố đó</t>
+        </is>
+      </c>
+      <c r="G28" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="63" t="inlineStr">
+        <is>
+          <t>M3-03</t>
+        </is>
+      </c>
+      <c r="C29" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D29" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E29" s="63" t="inlineStr">
+        <is>
+          <t>DEV-339</t>
+        </is>
+      </c>
+      <c r="F29" s="63" t="inlineStr">
+        <is>
+          <t>8 phát hiện trên 5 mạch thật (6 nguon_khong_cap + 2 net_mot_chan), trong đó net clock I2C nối đúng một chân. SÁU trong tám là 'mô hình chưa khai' chứ không phải 'mạch sai'. robot-canbang: 107 Port lá, KHÔNG Port nào là power_out</t>
+        </is>
+      </c>
+      <c r="G29" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="63" t="n">
+        <v>11</v>
+      </c>
+      <c r="B30" s="63" t="inlineStr">
+        <is>
+          <t>M3-04</t>
+        </is>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D30" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E30" s="63" t="inlineStr">
+        <is>
+          <t>DEV-340</t>
+        </is>
+      </c>
+      <c r="F30" s="63" t="inlineStr">
+        <is>
+          <t>0 phát hiện trên 5 mạch thật — và đây là con số ĐÚNG (hai lỗi này catastrophic, không bo nào sống tới lúc lưu kho). Đã CẤY hai bộ cấp vào bản sao kho robot-canbang để chứng minh luật sống: nổ đúng 1 blocker trên net +5V thật</t>
+        </is>
+      </c>
+      <c r="G30" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="B31" s="63" t="inlineStr">
+        <is>
+          <t>M3-07</t>
+        </is>
+      </c>
+      <c r="C31" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D31" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E31" s="63" t="inlineStr">
+        <is>
+          <t>DEV-341</t>
+        </is>
+      </c>
+      <c r="F31" s="63" t="inlineStr">
+        <is>
+          <t>Fact tới được ERC: 5 → 17 (+12). Ba kho có Fact datasheet thì TOÀN BỘ mang chủ thể chip:, tức trước đó không một Fact nào tới được ERC. Độ phủ 5 mạch thật nay đọc được</t>
+        </is>
+      </c>
+      <c r="G31" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="63" t="n">
+        <v>13</v>
+      </c>
+      <c r="B32" s="63" t="inlineStr">
+        <is>
+          <t>M3-10</t>
+        </is>
+      </c>
+      <c r="C32" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D32" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E32" s="63" t="inlineStr">
+        <is>
+          <t>DEV-342</t>
+        </is>
+      </c>
+      <c r="F32" s="63" t="inlineStr">
+        <is>
+          <t>chi phí đo thật: mạch lớn nhất trong kho 187 nút → ERC 7,6 ms mỗi lần ghi. Trần 2000 nút, vượt thì NÓI RA chứ không im lặng bỏ qua</t>
+        </is>
+      </c>
+      <c r="G32" s="63" t="inlineStr">
+        <is>
+          <t>ERC_TU_DONG — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="B33" s="63" t="inlineStr">
+        <is>
+          <t>M3-12</t>
+        </is>
+      </c>
+      <c r="C33" s="63" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D33" s="63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E33" s="63" t="inlineStr">
+        <is>
+          <t>DEV-343</t>
+        </is>
+      </c>
+      <c r="F33" s="63" t="inlineStr">
+        <is>
+          <t>846 bản ghi mô phỏng thật: regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 (testbench dự án in 'KET QUA: PASS' — nhãn đứng TRƯỚC từ khoá). Nới đúng một chỗ → 846/846 khớp, vẫn bắt đủ bốn ca PASS giả</t>
+        </is>
+      </c>
+      <c r="G33" s="63" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="64" t="n">
+        <v>15</v>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>M3-13</t>
+        </is>
+      </c>
+      <c r="C34" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D34" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E34" s="64" t="inlineStr">
+        <is>
+          <t>DEV-344</t>
+        </is>
+      </c>
+      <c r="F34" s="64" t="inlineStr">
+        <is>
+          <t>testbench Verilog THẬT của bài 3: tb_pcpi_dot4 1/1, tb_pcpi_mac 1/1, tb_pcpi_vmini không đo được (tb gọi bản bram HAI CỔNG đã bị bỏ 02/10) — mẫu số là TỆP, không phải phép phá</t>
+        </is>
+      </c>
+      <c r="G34" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="64" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B35" s="64" t="inlineStr">
+        <is>
+          <t>M3-18</t>
+        </is>
+      </c>
+      <c r="C35" s="64" t="inlineStr">
+        <is>
+          <t>3. Mạch, ERC, HDL/FPGA</t>
+        </is>
+      </c>
+      <c r="D35" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E35" s="64" t="inlineStr">
+        <is>
+          <t>DEV-345</t>
+        </is>
+      </c>
+      <c r="F35" s="64" t="inlineStr">
+        <is>
+          <t>6 cặp (mạng cổng, .cst) thật → 1 chỗ CHẶN: blinky của riscv-tn20k-b dựng bitstream 4,6 MB với chân đồng hồ do nextpnr tự chọn (rơi đúng chân 4 — bằng may). Cả 7 tệp .cst thật đọc hết, 0 lỗi cú pháp</t>
+        </is>
+      </c>
+      <c r="G35" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="64" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B36" s="64" t="inlineStr">
+        <is>
+          <t>M4-01</t>
+        </is>
+      </c>
+      <c r="C36" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D36" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E36" s="64" t="inlineStr">
+        <is>
+          <t>DEV-346</t>
+        </is>
+      </c>
+      <c r="F36" s="64" t="inlineStr">
+        <is>
+          <t>18 ca chạy trình biên dịch C thật: tệp test in số đo {"T1":300} với ngưỡng &lt;=255 → EIDE phán 1 ca HỎNG. Chưa kho cũ nào có tiêu chí unit test để đo lại trên dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="G36" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (công cụ mới core=False)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="64" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B37" s="64" t="inlineStr">
+        <is>
+          <t>M4-02</t>
+        </is>
+      </c>
+      <c r="C37" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D37" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E37" s="64" t="inlineStr">
+        <is>
+          <t>DEV-347</t>
+        </is>
+      </c>
+      <c r="F37" s="64" t="inlineStr">
+        <is>
+          <t>25 ca dựng đúng trạng thái thật (tệp test 3 ca, 1 ca đỏ, hiện vật dat=False) → fs.write còn 1 ca thì test.weakened=True. Và hàng rào cũ criteria.has_result chưa bao giờ nổ ngoài sim-01</t>
+        </is>
+      </c>
+      <c r="G37" s="64" t="inlineStr">
+        <is>
+          <t>SIM_RUNNER_GIOI_HAN — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="64" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B38" s="64" t="inlineStr">
+        <is>
+          <t>M4-05</t>
+        </is>
+      </c>
+      <c r="C38" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D38" s="64" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E38" s="64" t="inlineStr">
+        <is>
+          <t>DEV-348</t>
+        </is>
+      </c>
+      <c r="F38" s="64" t="inlineStr">
+        <is>
+          <t>du-lieu/rtos-sinhvien, chạy CẢ HAI hành vi: cũ so_thay=1, mới so_thay=0 — logo_ptit.c từ 'bộ kiểm ĐỎ' thành 'mọi đột biến đều làm hỏng biên dịch'. Một ô xanh giả, đã sửa</t>
+        </is>
+      </c>
+      <c r="G38" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B39" s="64" t="inlineStr">
+        <is>
+          <t>M4-19</t>
+        </is>
+      </c>
+      <c r="C39" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D39" s="64" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E39" s="64" t="inlineStr">
+        <is>
+          <t>DEV-349</t>
+        </is>
+      </c>
+      <c r="F39" s="64" t="inlineStr">
+        <is>
+          <t>chạy TẠI CHỖ trên ba dự án firmware thật: kết luận giống hệt lượt đột biến tại chỗ của M4-05, và 50/50 tệp giữ nguyên cả sha256 lẫn mtime</t>
+        </is>
+      </c>
+      <c r="G39" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="64" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B40" s="64" t="inlineStr">
+        <is>
+          <t>M4-04</t>
+        </is>
+      </c>
+      <c r="C40" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D40" s="64" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E40" s="64" t="inlineStr">
+        <is>
+          <t>DEV-350</t>
+        </is>
+      </c>
+      <c r="F40" s="64" t="inlineStr">
+        <is>
+          <t>TÁI HIỆN được ca DANH-GIA §2.2 bằng máy trên control_rtos.c thật: bảng cũ 0 đột biến cho hằng hex, bảng mới dòng 147 → mutant SỐNG. Và chi_tiet trên 12 tệp thật: 110 s, điểm 0,0</t>
+        </is>
+      </c>
+      <c r="G40" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ (tham số mới, mặc định giữ hành vi cũ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="64" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B41" s="64" t="inlineStr">
+        <is>
+          <t>M4-06</t>
+        </is>
+      </c>
+      <c r="C41" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D41" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E41" s="64" t="inlineStr">
+        <is>
+          <t>DEV-351</t>
+        </is>
+      </c>
+      <c r="F41" s="64" t="inlineStr">
+        <is>
+          <t>đo TRƯỚC trên logo_ptit.c thật: điểm 0,0 · 30 mutant · 20 sống. Phần SAU chưa đo — cần lời gọi mô hình (§3.0 bắt hỏi trước), và dự án mẫu không có chỗ để đo</t>
+        </is>
+      </c>
+      <c r="G41" s="64" t="inlineStr">
+        <is>
+          <t>TEST_HARDEN — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="64" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B42" s="64" t="inlineStr">
+        <is>
+          <t>M4-07</t>
+        </is>
+      </c>
+      <c r="C42" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D42" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E42" s="64" t="inlineStr">
+        <is>
+          <t>DEV-352</t>
+        </is>
+      </c>
+      <c r="F42" s="64" t="inlineStr">
+        <is>
+          <t>sổ cái 42 dự án: 327 lời gọi task.run có việc, 323 là verifier · 209/323 đề bài dài hơn trần 300 ký tự · gói bằng chứng dựng được CÓ NỘI DUNG trên 29/42 dự án, 0 lần đổ · loc_claim bỏ 95/1 706 câu (năm dấu hiệu kế hoạch chỉ bỏ được 11)</t>
+        </is>
+      </c>
+      <c r="G42" s="64" t="inlineStr">
+        <is>
+          <t>VERIFIER_GOI_BANG_CHUNG — TẮT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="64" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B43" s="64" t="inlineStr">
+        <is>
+          <t>M4-09</t>
+        </is>
+      </c>
+      <c r="C43" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D43" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E43" s="64" t="inlineStr">
+        <is>
+          <t>DEV-353</t>
+        </is>
+      </c>
+      <c r="F43" s="64" t="inlineStr">
+        <is>
+          <t>68 sổ cái: hook Stop khai tu_kiem_da_chay ở 41 lượt, và 1 trong 41 lượt ấy KHÔNG có task.run(verifier) nào — robot-sinhvien2 run-007, nơi lời gọi làm hook im nằm TRƯỚC fs.edit vào ISR(TIMER2_COMPA_vect). Phá lại thì đỏ 10/12.</t>
+        </is>
+      </c>
+      <c r="G43" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="64" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B44" s="64" t="inlineStr">
+        <is>
+          <t>M4-11</t>
+        </is>
+      </c>
+      <c r="C44" s="64" t="inlineStr">
+        <is>
+          <t>4. Kiểm thử &amp; chất lượng</t>
+        </is>
+      </c>
+      <c r="D44" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E44" s="64" t="inlineStr">
+        <is>
+          <t>DEV-354</t>
+        </is>
+      </c>
+      <c r="F44" s="64" t="inlineStr">
+        <is>
+          <t>9 kho thật: bán kính STALE của kết quả test/sim khi sửa một tệp mã 107 → 49 lần (58/107 là cáo buộc OAN). Dữ liệu thật bác bước 1 của kế hoạch: robot-sinhvien2 lưu MỘT tệp nguồn, mà tệp ấy #include ba tệp firmware. Phá lại thì đỏ 24/32 → 31/34.</t>
+        </is>
+      </c>
+      <c r="G44" s="64" t="inlineStr">
+        <is>
+          <t>HOI_QUY_NEN — TẮT (deps.upstream + hook ket_qua_stale KHÔNG sau cờ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="64" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B45" s="64" t="inlineStr">
+        <is>
+          <t>M5-03</t>
+        </is>
+      </c>
+      <c r="C45" s="64" t="inlineStr">
+        <is>
+          <t>5. Tri thức &amp; tài liệu</t>
+        </is>
+      </c>
+      <c r="D45" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E45" s="64" t="inlineStr">
+        <is>
+          <t>DEV-355</t>
+        </is>
+      </c>
+      <c r="F45" s="64" t="inlineStr">
+        <is>
+          <t>grep -rni svd src/ TRƯỚC khi sửa ra đúng HAI chỗ: phép phân loại, và một comment nói 'bốn loại đó có công cụ riêng' — không có bộ đọc nào. Tức phan_loai khai ĐẦY ĐỦ còn doc.load trả E1001. Phá lại thì đỏ 28/34 → 34/34.</t>
+        </is>
+      </c>
+      <c r="G45" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần + công cụ mới core=False</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="64" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B46" s="64" t="inlineStr">
+        <is>
+          <t>M5-05</t>
+        </is>
+      </c>
+      <c r="C46" s="64" t="inlineStr">
+        <is>
+          <t>5. Tri thức &amp; tài liệu</t>
+        </is>
+      </c>
+      <c r="D46" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E46" s="64" t="inlineStr">
+        <is>
+          <t>DEV-356</t>
+        </is>
+      </c>
+      <c r="F46" s="64" t="inlineStr">
+        <is>
+          <t>hop_ly('vdd.max', 25, '°C') trả True trên mã cũ — 25 lọt khoảng điện áp 0,5–60 V. Và đường BẢNG sinh khoá khác đường DÒNG CHỮ (flash.size → flash.max), nên một dung lượng Flash đọc từ bảng chưa bao giờ thành hạn mức. Phá lại thì đỏ 17/21 → 23/24.</t>
+        </is>
+      </c>
+      <c r="G46" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="64" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B47" s="64" t="inlineStr">
+        <is>
+          <t>M5-07</t>
+        </is>
+      </c>
+      <c r="C47" s="64" t="inlineStr">
+        <is>
+          <t>5. Tri thức &amp; tài liệu</t>
+        </is>
+      </c>
+      <c r="D47" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E47" s="64" t="inlineStr">
+        <is>
+          <t>DEV-357</t>
+        </is>
+      </c>
+      <c r="F47" s="64" t="inlineStr">
+        <is>
+          <t>Phép kiểm cũ xoá hết dấu chấm rồi so chuỗi chứa: '2.7 V' thành '27v' nên giá trị '27' đi qua, và '3' khớp 'Table 3', '180' khớp '1800', '39' khớp '0.39'. Phá lại thì đỏ 15/22 → 22/22; cả bảy chỗ LỌT là ca kiểm chưa chạm tới.</t>
+        </is>
+      </c>
+      <c r="G47" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="64" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B48" s="64" t="inlineStr">
+        <is>
+          <t>M5-13</t>
+        </is>
+      </c>
+      <c r="C48" s="64" t="inlineStr">
+        <is>
+          <t>5. Tri thức &amp; tài liệu</t>
+        </is>
+      </c>
+      <c r="D48" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E48" s="64" t="inlineStr">
+        <is>
+          <t>DEV-358</t>
+        </is>
+      </c>
+      <c r="F48" s="64" t="inlineStr">
+        <is>
+          <t>23 kho thật: một lời gọi fact.query không tham số đưa 67 635 → 32 560 token vào ngữ cảnh (−51 %); robot-sinhvien một mình 12 076 → 4 579. Trần chung bị LÁCH vì _cat_chung cắt số phần tử mà không cắt phần tử. Phá lại thì đỏ 20/23 → 23/23.</t>
+        </is>
+      </c>
+      <c r="G48" s="64" t="inlineStr">
+        <is>
+          <t>không có cờ — sửa lỗi thuần</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="64" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B49" s="64" t="inlineStr">
+        <is>
+          <t>M5-17</t>
+        </is>
+      </c>
+      <c r="C49" s="64" t="inlineStr">
+        <is>
+          <t>5. Tri thức &amp; tài liệu</t>
+        </is>
+      </c>
+      <c r="D49" s="64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E49" s="64" t="inlineStr">
+        <is>
+          <t>DEV-359</t>
+        </is>
+      </c>
+      <c r="F49" s="64" t="inlineStr">
+        <is>
+          <t>4 lần nén C2 đạt trên sổ cái thật (2 dự án), bản tóm tắt nạp lại được và KHÔNG rỗng ở 2/2. Và 303/313 phiên (96 %) thuộc dự án CHƯA TỪNG NÉN — nên câu 'chưa có bản tóm tắt' là câu nói ở gần như mọi lần mở lại. Phá lại thì đỏ 20/23 → 23/23.</t>
+        </is>
+      </c>
+      <c r="G49" s="64" t="inlineStr">
+        <is>
+          <t>RESUME_TUONG_THUAT — TẮT (phần nạp lại tóm tắt C2 KHÔNG sau cờ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="59" t="inlineStr">
+        <is>
+          <t>Việc còn MỞ (ngoài 84 việc chưa làm)</t>
+        </is>
+      </c>
+      <c r="B50" s="59" t="inlineStr">
+        <is>
+          <t>Vì sao còn mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="63" t="inlineStr">
+        <is>
+          <t>Bảy cờ mới đều còn TẮT</t>
+        </is>
+      </c>
+      <c r="B51" s="63" t="inlineStr">
+        <is>
+          <t>GON_CONG_CU · TRUY_VET · REQ_PHU · REQ_CHAT_LUONG · KE_HOACH_CONG_KIEM · ERC_TU_DONG · SIM_RUNNER_GIOI_HAN. Cả bảy đổi thứ Agent nhìn thấy, đọc, hoặc LÀM ĐƯỢC mỗi lượt, nên chỉ bộ 76 ca chạy hai chế độ mới nói được chúng làm Agent khá hơn hay tệ hơn. Bộ ấy tốn tiền mô hình nên §3.0 bắt hỏi người dùng trước.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="63" t="inlineStr">
+        <is>
+          <t>kiem_cap_goi_tra() chưa thành hàng rào</t>
+        </is>
+      </c>
+      <c r="B52" s="63" t="inlineStr">
+        <is>
+          <t>Soát được mọi phiên đã lưu, nhưng chưa hook nào gọi nó tự động — bắt được chuyện cũ, chưa chặn được chuyện mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="63" t="inlineStr">
+        <is>
+          <t>Luật ERC quá áp chưa nổ trên dữ liệu thật</t>
+        </is>
+      </c>
+      <c r="B53" s="63" t="inlineStr">
+        <is>
+          <t>Đường dẫn đã thông ở M3-07, nhưng ba kho có Fact điện áp thì không có mô hình mạch, và ngược lại. Phải chờ một dự án có cả hai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="63" t="inlineStr">
+        <is>
+          <t>Cột “Mã nguồn” của ma trận truy vết trống ở mọi dự án</t>
+        </is>
+      </c>
+      <c r="B54" s="63" t="inlineStr">
+        <is>
+          <t>Nó đọc hien_thuc_req — trường vừa mới tồn tại, chưa tệp nào trên đĩa từng khai. Nên “chưa hiện thực” ở đó nghĩa là “chưa ai KHAI”, không phải “chưa ai viết”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="63" t="inlineStr">
+        <is>
+          <t>Lỗi _go_dau trong src/eide/tools/design.py</t>
+        </is>
+      </c>
+      <c r="B55" s="63" t="inlineStr">
+        <is>
+          <t>Viết .replace('d','d') nên 'ổn định' và 'ON DINH' không khớp nhau. Hàm ấy đang dùng cho một phép kiểm an toàn (người có thật sự chọn không). Tìm thấy ở M2-03, CHƯA sửa vì ngoài phạm vi — cần bộ ca kiểm riêng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="63" t="inlineStr">
+        <is>
+          <t>subagent req-critic (bước 4 của M2-03)</t>
+        </is>
+      </c>
+      <c r="B56" s="63" t="inlineStr">
+        <is>
+          <t>Kế hoạch ghi “tuỳ chọn, gộp M2-13”. Chưa làm, đúng theo kế hoạch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="63" t="inlineStr">
+        <is>
+          <t>Hai luật kiểm chân FPGA chưa có dữ liệu để nổ</t>
+        </is>
+      </c>
+      <c r="B57" s="63" t="inlineStr">
+        <is>
+          <t>chan_lech_kit và io_type_lech_bank cần Fact chân kit. Không kho nào trong repo có Fact pin:tangnano20k.* hay khoá vccio — nên hôm nay chỉ 3 trong 5 luật của M3-18 kết luận được gì trên dữ liệu thật. Cùng hình dạng với luật ERC quá áp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="63" t="inlineStr">
+        <is>
+          <t>Một bitstream cũ đã dựng với chân đồng hồ tự chọn</t>
+        </is>
+      </c>
+      <c r="B58" s="63" t="inlineStr">
+        <is>
+          <t>blinky của du-lieu/riscv-tn20k-b — xem DEV-345 và README §8. Không sửa hiện vật cũ: đó là dữ liệu của những lượt đo đã chốt. Từ nay phép kiểm chặn trước nextpnr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="63" t="inlineStr">
+        <is>
+          <t>Ba công cụ mới nhất chưa lượt Agent nào GỌI</t>
+        </is>
+      </c>
+      <c r="B59" s="63" t="inlineStr">
+        <is>
+          <t>hdl.sensitivity · hdl.constraints_check · test.criteria. Mã của cả ba đã chạy trên hiện vật thật, nhưng đó là tôi gọi hàm, không phải tác tử gọi công cụ. README §8 đếm cả ba vào phần chưa dùng thật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="63" t="inlineStr">
+        <is>
+          <t>Bộ kiểm C của ba dự án firmware thật đều KHÔNG đo được độ nhạy</t>
+        </is>
+      </c>
+      <c r="B60" s="63" t="inlineStr">
+        <is>
+          <t>rtos-sinhvien: 0/12 tệp đo được (4 font khong_thay, control_rtos.c trùng ký hiệu, main.c không dịch trên máy chủ, logo_ptit.c mọi mutant hỏng biên dịch). stm32f469-freertos và thu-nghiem-g6: bộ kiểm ĐỎ SẴN. Đây là trạng thái của dữ liệu đo, không phải lỗi sản phẩm — nhưng nó nghĩa là chưa dự án firmware nào trong repo có một con số độ nhạy đáng tin. Xem DEV-348.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="63" t="inlineStr">
+        <is>
+          <t>POL-N6-sua-test chưa nổ trên một phiên thật nào</t>
+        </is>
+      </c>
+      <c r="B61" s="63" t="inlineStr">
+        <is>
+          <t>Hook sua_test_sau_do cấp dữ kiện cho lời gọi SẮP xảy ra, nên không soát lại được phiên đã lưu — khác mọi phép đo trước của đợt này. Nó đã có 25 ca kiểm và phá lại 27/27, nhưng chưa lượt tác tử thật nào chạm vào nó. Cùng hình dạng với ba luật kiểm thiếu dữ liệu ở trên, chỉ khác lý do.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="63" t="inlineStr">
+        <is>
+          <t>Tiêu chí 'mutation score tăng sau harden' của M4-06 chưa đo</t>
+        </is>
+      </c>
+      <c r="B62" s="63" t="inlineStr">
+        <is>
+          <t>Cần LỜI GỌI MÔ HÌNH, và §3.0 bắt hỏi anh Công trước. Đo 'trước' đã có (điểm 0,0 trên logo_ptit.c). Và dự án mẫu không có chỗ để đo: control_rtos.c là khong_nap_duoc, sáu tệp còn lại là bitmap. Cờ TEST_HARDEN giữ TẮT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="63" t="inlineStr">
+        <is>
+          <t>Một dự án chỉ dùng được MỘT tệp test</t>
+        </is>
+      </c>
+      <c r="B63" s="63" t="inlineStr">
+        <is>
+          <t>chay_test dịch MỌI tệp trong test/ cùng nhau, nên tệp thứ hai có main() là trùng ký hiệu. Kiểm trên dữ liệu thật: cả bốn dự án có test/ đều đúng một tệp. M4-06 lách bằng cách thêm ca vào tệp đang có — nhưng ràng buộc ấy vẫn còn, và nó giới hạn cách tổ chức bộ kiểm của mọi dự án.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="63" t="inlineStr">
+        <is>
+          <t>Gói bằng chứng chưa lần nào tới một MÔ HÌNH thật</t>
+        </is>
+      </c>
+      <c r="B64" s="63" t="inlineStr">
+        <is>
+          <t>Nó dựng được trên 29/42 dự án và đọc rất rõ với người, nhưng 'verifier đọc gói này có bác đúng hơn không' là câu hỏi về HÀNH VI MÔ HÌNH, và nó chưa được đo. Tiêu chí xong của M4-07 đòi bộ ca gài lỗi M4-22 — mà M4-22 nằm ở nhiệm vụ SAU trong kế hoạch. Cờ VERIFIER_GOI_BANG_CHUNG giữ TẮT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="63" t="inlineStr">
+        <is>
+          <t>loc_claim là một phép lọc văn xuôi, và nó leaky CÓ SỐ ĐO</t>
+        </is>
+      </c>
+      <c r="B65" s="63" t="inlineStr">
+        <is>
+          <t>95 trong 1 706 câu của 323 đề bài thật. Một câu lập luận không mang chữ nào trong sáu dấu hiệu vẫn đi qua. Đừng nhầm nó với hàng rào — hàng rào là gói bằng chứng do MÃ dựng, thứ tác tử chính không soạn được.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="59" t="inlineStr">
+        <is>
+          <t>Lỗi tìm thấy trong CHÍNH PHÉP ĐO của tôi</t>
+        </is>
+      </c>
+      <c r="B66" s="59" t="inlineStr">
+        <is>
+          <t>Lộ ra ở đâu</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="63" t="inlineStr">
+        <is>
+          <t>Kịch bản đo bị hàng rào của sản phẩm chặn (ghi tệp chưa đọc, E4020) và trả về một con số hợp lý thay vì nổ — 6→2 trông đẹp y như 9→3 đúng</t>
+        </is>
+      </c>
+      <c r="B67" s="63" t="inlineStr">
+        <is>
+          <t>M2-01 · DEV-333</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm dựng trên điều tôi tự nhớ sai: “thiết” bỏ dấu KHÔNG chứa “it”; chỗ va thật là bit/unit/init/exit</t>
+        </is>
+      </c>
+      <c r="B68" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá dài ĐÚNG BẰNG mã gốc (0.6 → 0.0) nên __pycache__ cũ còn hiệu lực — phép đo chạy mã khác với mã trong tệp</t>
+        </is>
+      </c>
+      <c r="B69" s="63" t="inlineStr">
+        <is>
+          <t>M2-03 · DEV-335</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="63" t="inlineStr">
+        <is>
+          <t>Phép đo trả lời ĐÚNG một câu hỏi KHÁC: đếm ở mức dự án ra 0 chỗ cần chặn; câu phải hỏi là “lần ghi NÀY đã được kiểm chưa” → 19/26</t>
+        </is>
+      </c>
+      <c r="B70" s="63" t="inlineStr">
+        <is>
+          <t>M2-06 · DEV-336</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm RỖNG: dàn dựng không có net đất nào, nên nó xanh cả khi tôi bỏ hẳn phép bỏ qua net đất</t>
+        </is>
+      </c>
+      <c r="B71" s="63" t="inlineStr">
+        <is>
+          <t>M3-01 · DEV-338</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="63" t="inlineStr">
+        <is>
+          <t>Hai phép phá chỉ ra THIẾT KẾ sai, không chỉ ca kiểm yếu (miễn net đất quá rộng; nhánh iout_max chưa ca nào chạm tới)</t>
+        </is>
+      </c>
+      <c r="B72" s="63" t="inlineStr">
+        <is>
+          <t>M3-03 · DEV-339</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="63" t="inlineStr">
+        <is>
+          <t>Phép phá của tôi cũng SAI, và ca âm xanh vì lý do khác — hai cái sai che nhau</t>
+        </is>
+      </c>
+      <c r="B73" s="63" t="inlineStr">
+        <is>
+          <t>M3-07 · DEV-341</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm đo chính câu lệnh của mình (đặt bộ đếm = 3 rồi khẳng định nó khác rỗng, trong khi thực tế nó rỗng)</t>
+        </is>
+      </c>
+      <c r="B74" s="63" t="inlineStr">
+        <is>
+          <t>M3-10 · DEV-342</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="63" t="inlineStr">
+        <is>
+          <t>Regex mà KẾ HOẠCH ghi sẵn từ chối oan 588/846 bản ghi thật; và ba ca kiểm xanh vì lý do sai (tệp giả dùng $4 thay $3; “FAILED” chứa “FAIL”)</t>
+        </is>
+      </c>
+      <c r="B75" s="63" t="inlineStr">
+        <is>
+          <t>M3-12 · DEV-343</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="63" t="inlineStr">
+        <is>
+          <t>"Phá lại thì đỏ 6/6" sai về TẬP, không sai về số: sáu phép phá ấy chọn đúng sáu chỗ đã có ca canh. Phá bằng tập rộng hơn ra 7/9.</t>
+        </is>
+      </c>
+      <c r="B76" s="63" t="inlineStr">
+        <is>
+          <t>M3-13 · DEV-344</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="63" t="inlineStr">
+        <is>
+          <t>409 'blocker' gần như toàn bộ từ một cặp vô nghĩa (mạng cổng của lõi CPU tổng hợp riêng, không bao giờ đem đặt-đi dây). Con số thật là 1.</t>
+        </is>
+      </c>
+      <c r="B77" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="63" t="inlineStr">
+        <is>
+          <t>Phép quét tệp .cst thật chỉ thu 4 trong 7 tệp mà ca kiểm vẫn xanh — câu 'mọi tệp .cst thật đều đọc được' nói về phần phép quét chạm tới.</t>
+        </is>
+      </c>
+      <c r="B78" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="63" t="inlineStr">
+        <is>
+          <t>Một ca kiểm và một phép phá nhắm hai NHÁNH khác nhau, nên ca mới xanh mà phép phá vẫn LỌT. Mất một lượt mới thấy.</t>
+        </is>
+      </c>
+      <c r="B79" s="63" t="inlineStr">
+        <is>
+          <t>M3-18 · DEV-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="63" t="inlineStr">
+        <is>
+          <t>Ca kiểm xanh nhờ một DÒNG KHÁC: kiểm `"TỰ KHAI" in str(kh)` cả khối nên vẫn xanh khi phá chữ ấy ở dòng Kết luận — summary cũng chứa nó. Phép phá bắt được, ca kiểm thì không.</t>
+        </is>
+      </c>
+      <c r="B80" s="63" t="inlineStr">
+        <is>
+          <t>M4-01 · DEV-346</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="63" t="inlineStr">
+        <is>
+          <t>Một phép phá VÔ HIỆU: `them = [] or [[…]]` không đổi hành vi, nên nó báo LỌT oan và suýt làm tôi viết ca kiểm cho một chỗ vốn đã được canh.</t>
+        </is>
+      </c>
+      <c r="B81" s="63" t="inlineStr">
+        <is>
+          <t>M4-01 · DEV-346</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="63" t="inlineStr">
+        <is>
+          <t>HAI phép phá liền nhau VÔ HIỆU ở cùng một dòng: `cu = cu or ""` không đổi hành vi, rồi bỏ is_file() cũng không vì except OSError bắt FileNotFoundError. Phải bỏ cả hai lớp phòng mới phá được.</t>
+        </is>
+      </c>
+      <c r="B82" s="63" t="inlineStr">
+        <is>
+          <t>M4-02 · DEV-347</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="63" t="inlineStr">
+        <is>
+          <t>Một luật mới trỏ tới nhóm dữ kiện chưa khai thì DỪNG CẢ LƯỢT bằng ValueError, không phải 'không nổ' — và nhóm `criteria` của hàng rào N6 cũ cũng chưa bao giờ được khai.</t>
+        </is>
+      </c>
+      <c r="B83" s="63" t="inlineStr">
+        <is>
+          <t>M4-02 · DEV-347</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="63" t="inlineStr">
+        <is>
+          <t>Phép đo ĐỔ ngay lượt đầu trên dữ liệu thật (IndexError), và lỗi ấy nghĩa là test.sensitivity chưa bao giờ chạy nổi trên một tệp firmware thật — mọi con số cũ đều từ tệp nhỏ do ca kiểm tự dựng.</t>
+        </is>
+      </c>
+      <c r="B84" s="63" t="inlineStr">
+        <is>
+          <t>M4-05 · DEV-348</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="63" t="inlineStr">
+        <is>
+          <t>Bốn chỗ LỌT cùng một hình dạng: luật ĐÚNG, nằm ở chỗ ca kiểm không với tới — hai closure, một bảng phép không dựng nổi ca, và một tầng báo lại mà mọi ca cũ đều đi qua với stillborn == 0.</t>
+        </is>
+      </c>
+      <c r="B85" s="63" t="inlineStr">
+        <is>
+          <t>M4-05 · DEV-348</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="26" t="inlineStr">
+        <is>
+          <t>Tôi thêm MỘT cờ biên dịch để tránh một cáo buộc sai, và nó sinh ra MƯỜI MỘT cáo buộc sai khác: -I che header hệ thống, nên 11/12 tệp bị xếp là 'không dịch được trên máy chủ'. Phải là -iquote.</t>
+        </is>
+      </c>
+      <c r="B86" s="26" t="inlineStr">
+        <is>
+          <t>M4-19 · DEV-349</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="26" t="inlineStr">
+        <is>
+          <t>Gắn cờ biên dịch cho cả LƯỢT MỐC là đổi chính cái mốc mà mọi so sánh dựa vào — mốc của cả ba dự án thật từ XANH thành ĐỎ.</t>
+        </is>
+      </c>
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>M4-19 · DEV-349</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="26" t="inlineStr">
+        <is>
+          <t>Phép đo mới TREO 10 phút trên tệp thật đầu tiên — không đổ, không báo gì, nên nó trông như một lượt chạy lâu. liet_ke dựng CẢ TỆP cho MỖI chỗ khớp: 57 600 chỗ × 720 KB ≈ 41 GB việc chuỗi.</t>
+        </is>
+      </c>
+      <c r="B88" s="26" t="inlineStr">
+        <is>
+          <t>M4-04 · DEV-350</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="26" t="inlineStr">
+        <is>
+          <t>Ca kiểm chi phí của tôi KHÔNG bắt được bản chậm, vì tệp dựng dùng hằng hex TRẦN — _bo_che trả về ngay khi không có chỗ giữ. Chính CHÚ THÍCH mỗi dòng của tệp thật mới làm mỗi lượt bỏ che thành một lượt regex thật.</t>
+        </is>
+      </c>
+      <c r="B89" s="26" t="inlineStr">
+        <is>
+          <t>M4-04 · DEV-350</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="26" t="inlineStr">
+        <is>
+          <t>Hook so MỐC THỜI GIAN thay vì số phiên bản: updated_at có độ phân giải thô nên hai lần ghi trong cùng một giây BẰNG NHAU, và phép so 'mới hơn' im lặng sai. Ca kiểm đầu tiên của chính hook ấy đỏ ngay.</t>
+        </is>
+      </c>
+      <c r="B90" s="26" t="inlineStr">
+        <is>
+          <t>M4-06 · DEV-351</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="26" t="inlineStr">
+        <is>
+          <t>Tôi quên mở nhánh và commit thẳng lên main. Nội dung đúng, quy trình §3.1 thì không — đã dựng lại con trỏ toi-uu/M4-06 tại đúng commit.</t>
+        </is>
+      </c>
+      <c r="B91" s="26" t="inlineStr">
+        <is>
+          <t>M4-06 · DEV-351</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="26" t="inlineStr">
+        <is>
+          <t>Năm dấu hiệu mà KẾ HOẠCH nêu cho loc_claim chỉ bỏ được 11 trong 1 706 câu của 323 đề bài THẬT — phép lọc đúng đề mà gần như không chạm gì. Chỗ rò thật là PHÁN QUYẾT TRÍCH SẴN ("kết quả 'dat: false'"), và phải thêm một dấu hiệu thứ sáu mới lên 95/1 706.</t>
+        </is>
+      </c>
+      <c r="B92" s="26" t="inlineStr">
+        <is>
+          <t>M4-07 · DEV-352</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="26" t="inlineStr">
+        <is>
+          <t>Hai phép phá LỌT vì ca kiểm xanh nhờ MỘT DÒNG KHÁC: xoá hẳn khối B khỏi gói bằng chứng mà bộ kiểm vẫn xanh, do ca của khối A đã thấy đúng tên tệp ấy qua dòng changeset. Cùng hình dạng DEV-344.</t>
+        </is>
+      </c>
+      <c r="B93" s="26" t="inlineStr">
+        <is>
+          <t>M4-07 · DEV-352</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="26" t="inlineStr">
+        <is>
+          <t>Ca kiểm CŨ nêu đúng bất biến "mọi cờ phải có trong ten_co()" mà kiểm nó trên MỘT TÊN GÕ SẴN, nên nó xanh suốt trong khi cờ thứ 10 vô hình: Features.load() trả False cả khi biến môi trường đã đặt. Phép so đúng là so hai TẬP HỢP.</t>
+        </is>
+      </c>
+      <c r="B94" s="26" t="inlineStr">
+        <is>
+          <t>M4-07 · DEV-352</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="26" t="inlineStr">
+        <is>
+          <t>Tôi ghi con số ca kiểm (1 895) vào BỐN tệp tài liệu TRƯỚC khi bộ kiểm đầy đủ chạy xong — số thật là 1 896. Một con số suy ra bằng phép cộng trong đầu trông giống hệt một con số đo được.</t>
+        </is>
+      </c>
+      <c r="B95" s="26" t="inlineStr">
+        <is>
+          <t>M4-07 · DEV-352</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -2109,13 +2109,13 @@
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
+    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B48:G48"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
@@ -3869,6 +3869,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="27">
       <c r="A4" s="31" t="inlineStr">
         <is>
@@ -12264,11 +12265,45 @@
       <c r="P90" s="47" t="n"/>
       <c r="Q90" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R90" s="47" t="n"/>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="R90" s="47" t="inlineStr">
+        <is>
+          <t>Claude (Opus 5)</t>
+        </is>
+      </c>
       <c r="S90" s="47" t="n"/>
+      <c r="T90" s="26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="U90" s="26" t="inlineStr">
+        <is>
+          <t>DEV-360</t>
+        </is>
+      </c>
+      <c r="V90" s="26" t="inlineStr">
+        <is>
+          <t>2 046 → 2 060 (30 ca mới trong tests/test_chi_muc.py). Phá lại thì đỏ: 21/30 lượt đầu → 30/30. MỘT chỗ LỌT là lỗ THẬT: `pull-up` chưa bọc nháy kép làm FTS5 nổ 'no such column: up', mã rơi im lặng xuống đường thô mà note_vi vẫn khai là BM25 — nay doc.search trả `duong_xep_hang`. TÁM chỗ còn lại là DÀN DỰNG không phân biệt được, lần thứ NĂM liền: ca cũ chỉ kiểm điểm đơn điệu giảm nên đảo chiều bm25 (số âm) vẫn xanh; kho 7 trang nên bỏ trần k=20 không đổi gì; hai điểm bằng nhau thì sắp xếp phụ đưa trang ngắn lên đầu; và ca skipif(not co_fts) TỰ VÔ HIỆU HOÁ CHÍNH NÓ khi phép phá làm co_fts thành False. Một ca CŨ sửa theo §3.2: ha_cap(1) == [4,3,2] gõ tay → lấy từ MIGRATIONS.</t>
+        </is>
+      </c>
+      <c r="W90" s="26" t="inlineStr">
+        <is>
+          <t>recall@5 trên 7 PDF THẬT trên máy (92 trang trong một kho: DS40002061B, TMP-5V0, tài liệu kiến trúc C4, một bài báo, ba bài arXiv). Bộ vàng dựng CƠ HỌC — đáp án do mã chọn (cụm từ chỉ có ở đúng một trang), không do tôi chọn. Phép đo A: 34/34 = 100 % ở cả @1 và @5. Phép đo B (truy vấn dùng TÊN KHÁC): 3/5 @1, 5/5 @5 — và phép `in` của doc.read cũ trên cùng bộ B là 0/5, mà nó còn phải biết trước tìm ở tài liệu nào. Mức độ: A DỄ (từ khoá lấy từ chính trang đáp án); B khó nhưng chỉ có 5 ca vì điều kiện dựng rất chặt — năm ca không phải một bộ eval, nó là mốc để so khi bật embedding. grep -i 'fts5|bm25|embedd|rerank' trong src/ TRƯỚC khi sửa: 0 kết quả.</t>
+        </is>
+      </c>
+      <c r="X90" s="26" t="inlineStr">
+        <is>
+          <t>không có cờ (DOC_EMBED để giai đoạn sau) — công cụ mới core=False</t>
+        </is>
+      </c>
+      <c r="Y90" s="26" t="inlineStr">
+        <is>
+          <t>Không còn nợ tiêu chí nào, nhưng tiêu chí recall KHÔNG đo trên bộ vàng M5-21 (chưa làm) — đã nói rõ thay vì chờ. Lược đồ kho v4 → v5, có đường lùi (ha_cap(4) gỡ hai bảng, không chạm dữ liệu cũ). FTS5 là module biên dịch TUỲ CHỌN của SQLite: thiếu thì tạo bảng nội dung thôi và xếp hạng bằng đếm từ khoá (N-10), không lỗi cứng. `doc.search` là công cụ thứ 133 và CHƯA lượt Agent nào gọi.</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="113.25" customHeight="1" s="27">
       <c r="A91" s="46" t="inlineStr">
@@ -16029,7 +16064,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="59" t="inlineStr">
         <is>

--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -2106,17 +2106,17 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
-    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
     <mergeCell ref="A41:G41"/>
-    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -6947,13 +6947,47 @@
       </c>
       <c r="Q35" s="48" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R35" s="47" t="n"/>
+          <t>Xong (một tiêu chí CHƯA đạt)</t>
+        </is>
+      </c>
+      <c r="R35" s="47" t="inlineStr">
+        <is>
+          <t>Claude (Opus 5)</t>
+        </is>
+      </c>
       <c r="S35" s="47" t="inlineStr">
         <is>
           <t>Kéo lên giai đoạn sớm hơn vì là tiền đề (xem §5 kế hoạch)</t>
+        </is>
+      </c>
+      <c r="T35" s="26" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="U35" s="26" t="inlineStr">
+        <is>
+          <t>DEV-361</t>
+        </is>
+      </c>
+      <c r="V35" s="26" t="inlineStr">
+        <is>
+          <t>2 060 → 2 096 (36 ca mới trong tests/test_phan_tich_tinh.py). Phá lại thì đỏ: 29/35 lượt đầu → 35/35. HAI chỗ LỌT là lỗ THẬT: luật ISR bị chặn sau cửa `chay_duoc` (nó đọc MÃ NGUỒN, không cần trình biên dịch — nên trên máy chủ mọi firmware AVR không bao giờ đưa được vi phạm nào tới tác tử), và chú thích khối nhiều dòng chưa được xử lý. BỐN chỗ còn lại là dàn dựng không phân biệt được (lần thứ SÁU liền): nhánh sâu tên `a` đứng trước theo thứ tự chữ nên 'lấy nhánh đầu' cũng đúng; dàn dựng chỉ sinh 0–1 vi phạm nên trần 20 không bind; ca 'chưa chạy được' không qua công cụ; và ca bước 4 gọi _tom_tat_tinh TRỰC TIẾP nên bỏ hẳn chỗ nối trong code.analyze mà bộ kiểm vẫn xanh. Một phép phá hoá ra là MÃ CHẾT (hai tên .su trùng nhau) → bỏ nhánh thay vì dựng ca contrived.</t>
+        </is>
+      </c>
+      <c r="W35" s="26" t="inlineStr">
+        <is>
+          <t>BỐN chỗ trình biên dịch thật khác kế hoạch, đo 09/10/2026: (1) .su có HAI dạng — arm-none-eabi-gcc ghi tep.c:DÒNG:CỘT:ham, Apple clang ghi tep.c:DÒNG:ham (thiếu cột); (2) clang KHÔNG có -fcallgraph-info (unknown argument); (3) tên nút VCG không nhất quán (static → 'm2.c:loc', extern → 'tinh'); (4) -O1 INLINE MẤT hàm static và mọi mức ≥ -O1 báo hàm lá 0 byte — nên dùng -O0 và tự khai bi_quan=True. Firmware THẬT: rtos-tu-viet (ARM) 13 hàm + có đồ thị + 3 ISR + 0 vi phạm (main.c/startup.c không dịch được: thiếu stm32f469xx.h, header CMSIS không nằm trong repo); robot-sinhvien2 (AVR) ngăn xếp chưa đo được + 3 ISR + 0 vi phạm. Con số 0 ấy ĐÃ KIỂM CHÉO: 8 hàm dùng float/double trong cả firmware, KHÔNG hàm nào ISR gọi tới được (tập ISR tới được đúng 4 hàm) — khớp luật thiết kế PA-A 'ISR không được dùng phép chia hay số thực'.</t>
+        </is>
+      </c>
+      <c r="X35" s="26" t="inlineStr">
+        <is>
+          <t>không có cờ — công cụ mới core=False, chỉ đọc</t>
+        </is>
+      </c>
+      <c r="Y35" s="26" t="inlineStr">
+        <is>
+          <t>Tiêu chí 'đối chiếu với đo stack-painting' CHƯA ĐẠT, và lý do nằm trong repo: grep -rn '0xA5A5A5A5' ra 0 KẾT QUẢ — phép sơn ngăn xếp chưa bao giờ được chạy ở dự án này, chính DANH-GIA-NGUOI-VS-AGENT-2-VIEC.md §3.2 đã ghi thế. Con số painting duy nhất ('Đo thật: 65 word', §3.3) nằm trong VĂN XUÔI, không hiện vật nào đứng sau, không nói rõ tác vụ nào trên bản mã nào. Ghép con số tĩnh với một con số không truy nguồn được là đúng cái bài học 'hằng số phần cứng phải tra, không được dựng lại' cấm. `code.static` là công cụ thứ 134 và CHƯA lượt Agent nào gọi. M2-09 xong thì #27 M4-13 (P0 · M) hết bị chặn.</t>
         </is>
       </c>
     </row>

--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -22,6 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm mạnh cần giữ" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 09-10-2026 (sau #32)" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 09-10-2026 (sau #27)" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
@@ -244,7 +245,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -430,6 +431,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2106,17 +2113,17 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
-    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B48:G48"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -3869,7 +3876,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="27">
       <c r="A4" s="31" t="inlineStr">
         <is>
@@ -11395,13 +11401,51 @@
           <t>M2-09</t>
         </is>
       </c>
-      <c r="Q80" s="48" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R80" s="47" t="n"/>
-      <c r="S80" s="47" t="n"/>
+      <c r="Q80" s="65" t="inlineStr">
+        <is>
+          <t>Xong</t>
+        </is>
+      </c>
+      <c r="R80" s="65" t="inlineStr">
+        <is>
+          <t>Claude (Opus 5)</t>
+        </is>
+      </c>
+      <c r="S80" s="65" t="inlineStr">
+        <is>
+          <t>Luật dò của kế hoạch VIẾT LẠI: 'có ký hiệu mạnh ở địa chỉ khác' bắt được 0 ca (GNU ld tự ưu tiên định nghĩa mạnh trước alias yếu). Cơ chế thật là SAI CHÍNH TẢ tên và khai static → luật thành 'ô trỏ Default_Handler VÀ mã nguồn có tên gần giống, kể cả giống hệt'. doc_vector trả (chỉ_số, địa_chỉ), không trả tên: objdump -s chỉ in byte.</t>
+        </is>
+      </c>
+      <c r="T80" s="66" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="U80" s="66" t="inlineStr">
+        <is>
+          <t>DEV-362</t>
+        </is>
+      </c>
+      <c r="V80" s="66" t="inlineStr">
+        <is>
+          <t>2 096 → 2 125 xanh, 1 skip (29 ca mới trong tests/test_kiem_noi.py). Phá lại thì đỏ 26/26 — tập dựng từ git diff; vòng đầu 20/29, chín chỗ LỌT chia ba loại: sáu lỗ trong tập CA KIỂM, hai phép phá VÔ HIỆU (bit Thumb ở ô 0 vì SP luôn căn 8 byte; mốc 0 trùng mốc bỏ ô trống), một cửa mã CHẾT đã xoá.</t>
+        </is>
+      </c>
+      <c r="W80" s="66" t="inlineStr">
+        <is>
+          <t>Đo trên ELF dựng bằng arm-none-eabi-gcc trên máy 09/10/2026, KHÔNG trên vector viết tay. Tái hiện 3/7 ca DANH-GIA §3.1: #3 hàm không ai gọi (--print-gc-sections loại .text.tong_kiem_chuan), #5 SysTick_handler chữ h nhỏ → ô 15 giữ alias yếu, #7 hàm static (-Wunused-function có từ trước). Bốn hằng số công cụ TRA chứ không nhớ: bit Thumb, objdump -s little-endian 4 từ/dòng, nm T vs W, một hàm bị loại ở hai đơn vị dịch ra hai dòng cho một chỗ.</t>
+        </is>
+      </c>
+      <c r="X80" s="66" t="inlineStr">
+        <is>
+          <t>kiem_noi — TẮT (N-4: nó đổi note_vi của MỌI lần biên dịch). build.wiring luôn đăng ký, core=False.</t>
+        </is>
+      </c>
+      <c r="Y80" s="66" t="inlineStr">
+        <is>
+          <t>Ca #6 'không ai tạo tác vụ rỗi' và 'không ai đặt PENDSVSET' NGOÀI phạm vi — cần hiểu ngữ nghĩa RTOS, không đọc ra từ bảng vector. note_vi TỰ KHAI điều đó mỗi lần kết quả rỗng, để 'không thấy gì' không bị đọc thành 'nối đúng hết' (N6).</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="68.25" customHeight="1" s="27">
       <c r="A81" s="46" t="inlineStr">
@@ -17772,6 +17816,461 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" style="27" min="1" max="1"/>
+    <col width="34" customWidth="1" style="27" min="2" max="2"/>
+    <col width="38" customWidth="1" style="27" min="3" max="3"/>
+    <col width="44" customWidth="1" style="27" min="4" max="4"/>
+    <col width="52" customWidth="1" style="27" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="66" t="inlineStr">
+        <is>
+          <t>TIẾN ĐỘ CHIẾN DỊCH TỐI ƯU TÁC TỬ — chốt sau việc #27 (M4-13)</t>
+        </is>
+      </c>
+      <c r="B1" s="66" t="inlineStr"/>
+      <c r="C1" s="66" t="inlineStr"/>
+      <c r="D1" s="66" t="inlineStr"/>
+      <c r="E1" s="66" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="66" t="inlineStr">
+        <is>
+          <t>Mốc: 09/10/2026 · nhánh main · Giai đoạn 1 ĐÓNG</t>
+        </is>
+      </c>
+      <c r="B2" s="66" t="inlineStr"/>
+      <c r="C2" s="66" t="inlineStr"/>
+      <c r="D2" s="66" t="inlineStr"/>
+      <c r="E2" s="66" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="66" t="inlineStr"/>
+      <c r="B3" s="66" t="n"/>
+      <c r="C3" s="66" t="n"/>
+      <c r="D3" s="66" t="n"/>
+      <c r="E3" s="66" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="66" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="B4" s="66" t="inlineStr">
+        <is>
+          <t>Trước #27</t>
+        </is>
+      </c>
+      <c r="C4" s="66" t="inlineStr">
+        <is>
+          <t>Sau #27</t>
+        </is>
+      </c>
+      <c r="D4" s="66" t="inlineStr">
+        <is>
+          <t>Nguồn số</t>
+        </is>
+      </c>
+      <c r="E4" s="66" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="66" t="inlineStr">
+        <is>
+          <t>Việc đã xong / 106</t>
+        </is>
+      </c>
+      <c r="B5" s="66" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" s="66" t="n">
+        <v>33</v>
+      </c>
+      <c r="D5" s="66" t="inlineStr">
+        <is>
+          <t>đếm ☑ trong KE-HOACH-SUA-VA-KIEM-THU.md</t>
+        </is>
+      </c>
+      <c r="E5" s="66" t="inlineStr">
+        <is>
+          <t>#33 thuộc GĐ2 (M5-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="66" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1 (#1–#32)</t>
+        </is>
+      </c>
+      <c r="B6" s="66" t="inlineStr">
+        <is>
+          <t>31/32</t>
+        </is>
+      </c>
+      <c r="C6" s="66" t="inlineStr">
+        <is>
+          <t>32/32</t>
+        </is>
+      </c>
+      <c r="D6" s="66" t="inlineStr">
+        <is>
+          <t>cột Giai đoạn của kế hoạch</t>
+        </is>
+      </c>
+      <c r="E6" s="66" t="inlineStr">
+        <is>
+          <t>ĐÓNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="66" t="inlineStr">
+        <is>
+          <t>P0 xong / 30</t>
+        </is>
+      </c>
+      <c r="B7" s="66" t="inlineStr">
+        <is>
+          <t>28/30</t>
+        </is>
+      </c>
+      <c r="C7" s="66" t="inlineStr">
+        <is>
+          <t>29/30</t>
+        </is>
+      </c>
+      <c r="D7" s="66" t="inlineStr">
+        <is>
+          <t>cột Ưu tiên của kế hoạch</t>
+        </is>
+      </c>
+      <c r="E7" s="66" t="inlineStr">
+        <is>
+          <t>còn đúng #34 M5-04 (cần pdfplumber, N-10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="66" t="inlineStr">
+        <is>
+          <t>P1 xong / 54</t>
+        </is>
+      </c>
+      <c r="B8" s="66" t="inlineStr">
+        <is>
+          <t>2/54</t>
+        </is>
+      </c>
+      <c r="C8" s="66" t="inlineStr">
+        <is>
+          <t>2/54</t>
+        </is>
+      </c>
+      <c r="D8" s="66" t="inlineStr">
+        <is>
+          <t>cột Ưu tiên</t>
+        </is>
+      </c>
+      <c r="E8" s="66" t="inlineStr">
+        <is>
+          <t>chưa mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="66" t="inlineStr">
+        <is>
+          <t>P2 xong / 20</t>
+        </is>
+      </c>
+      <c r="B9" s="66" t="inlineStr">
+        <is>
+          <t>1/20</t>
+        </is>
+      </c>
+      <c r="C9" s="66" t="inlineStr">
+        <is>
+          <t>1/20</t>
+        </is>
+      </c>
+      <c r="D9" s="66" t="inlineStr">
+        <is>
+          <t>cột Ưu tiên</t>
+        </is>
+      </c>
+      <c r="E9" s="66" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="66" t="inlineStr">
+        <is>
+          <t>P3 xong / 2</t>
+        </is>
+      </c>
+      <c r="B10" s="66" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="C10" s="66" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="D10" s="66" t="inlineStr">
+        <is>
+          <t>cột Ưu tiên</t>
+        </is>
+      </c>
+      <c r="E10" s="66" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="66" t="inlineStr">
+        <is>
+          <t>Ca kiểm xanh</t>
+        </is>
+      </c>
+      <c r="B11" s="66" t="n">
+        <v>2096</v>
+      </c>
+      <c r="C11" s="66" t="n">
+        <v>2125</v>
+      </c>
+      <c r="D11" s="66" t="inlineStr">
+        <is>
+          <t>pytest -q</t>
+        </is>
+      </c>
+      <c r="E11" s="66" t="inlineStr">
+        <is>
+          <t>1 skip, 0 đỏ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="66" t="inlineStr">
+        <is>
+          <t>Công cụ</t>
+        </is>
+      </c>
+      <c r="B12" s="66" t="n">
+        <v>134</v>
+      </c>
+      <c r="C12" s="66" t="n">
+        <v>135</v>
+      </c>
+      <c r="D12" s="66" t="inlineStr">
+        <is>
+          <t>build_registry() với mọi cờ BẬT</t>
+        </is>
+      </c>
+      <c r="E12" s="66" t="inlineStr">
+        <is>
+          <t>125 thấy mặc định · 73 core · 10 sau cờ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="66" t="inlineStr">
+        <is>
+          <t>Cờ tính năng</t>
+        </is>
+      </c>
+      <c r="B13" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="D13" s="66" t="inlineStr">
+        <is>
+          <t>dataclasses.fields(Features)</t>
+        </is>
+      </c>
+      <c r="E13" s="66" t="inlineStr">
+        <is>
+          <t>cả 13 mặc định TẮT (N-4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="66" t="inlineStr">
+        <is>
+          <t>Mục DEV-LOG</t>
+        </is>
+      </c>
+      <c r="B14" s="66" t="inlineStr">
+        <is>
+          <t>DEV-361</t>
+        </is>
+      </c>
+      <c r="C14" s="66" t="inlineStr">
+        <is>
+          <t>DEV-362</t>
+        </is>
+      </c>
+      <c r="D14" s="66" t="inlineStr">
+        <is>
+          <t>docs/md/EIDE-DEV-LOG.md</t>
+        </is>
+      </c>
+      <c r="E14" s="66" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="66" t="inlineStr">
+        <is>
+          <t>kiem_tai_lieu — chỗ lệch chắc chắn</t>
+        </is>
+      </c>
+      <c r="B15" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="66" t="inlineStr">
+        <is>
+          <t>tools/kiem_tai_lieu.py</t>
+        </is>
+      </c>
+      <c r="E15" s="66" t="inlineStr">
+        <is>
+          <t>17 con số cần đọc lại (không tính là lệch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="66" t="inlineStr"/>
+      <c r="B16" s="66" t="n"/>
+      <c r="C16" s="66" t="n"/>
+      <c r="D16" s="66" t="n"/>
+      <c r="E16" s="66" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="66" t="inlineStr">
+        <is>
+          <t>BA CA của DANH-GIA §3.1 mà #27 bắt được, đo trên ELF thật</t>
+        </is>
+      </c>
+      <c r="B17" s="66" t="inlineStr"/>
+      <c r="C17" s="66" t="inlineStr"/>
+      <c r="D17" s="66" t="inlineStr"/>
+      <c r="E17" s="66" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="66" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="B18" s="66" t="inlineStr">
+        <is>
+          <t>Cơ chế</t>
+        </is>
+      </c>
+      <c r="C18" s="66" t="inlineStr">
+        <is>
+          <t>Phát hiện bằng</t>
+        </is>
+      </c>
+      <c r="D18" s="66" t="inlineStr"/>
+      <c r="E18" s="66" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="66" t="inlineStr">
+        <is>
+          <t>#3 hàm không ai gọi</t>
+        </is>
+      </c>
+      <c r="B19" s="66" t="inlineStr">
+        <is>
+          <t>ld loại .text.tong_kiem_chuan</t>
+        </is>
+      </c>
+      <c r="C19" s="66" t="inlineStr">
+        <is>
+          <t>ham_bi_loai đọc log --print-gc-sections</t>
+        </is>
+      </c>
+      <c r="D19" s="66" t="inlineStr"/>
+      <c r="E19" s="66" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="66" t="inlineStr">
+        <is>
+          <t>#5 ngắt không nối</t>
+        </is>
+      </c>
+      <c r="B20" s="66" t="inlineStr">
+        <is>
+          <t>mã viết SysTick_handler (h nhỏ)</t>
+        </is>
+      </c>
+      <c r="C20" s="66" t="inlineStr">
+        <is>
+          <t>isr_bi_bo_quen (so sau khi chuẩn hoá)</t>
+        </is>
+      </c>
+      <c r="D20" s="66" t="inlineStr"/>
+      <c r="E20" s="66" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="66" t="inlineStr">
+        <is>
+          <t>#7 hàm static</t>
+        </is>
+      </c>
+      <c r="B21" s="66" t="inlineStr">
+        <is>
+          <t>vector cần, linker không thấy ký hiệu</t>
+        </is>
+      </c>
+      <c r="C21" s="66" t="inlineStr">
+        <is>
+          <t>-Wunused-function (có từ trước)</t>
+        </is>
+      </c>
+      <c r="D21" s="66" t="inlineStr"/>
+      <c r="E21" s="66" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="66" t="inlineStr">
+        <is>
+          <t>#6 tác vụ rỗi + PENDSVSET</t>
+        </is>
+      </c>
+      <c r="B22" s="66" t="inlineStr">
+        <is>
+          <t>cần hiểu ngữ nghĩa RTOS</t>
+        </is>
+      </c>
+      <c r="C22" s="66" t="inlineStr">
+        <is>
+          <t>NGOÀI phạm vi — note_vi tự khai</t>
+        </is>
+      </c>
+      <c r="D22" s="66" t="inlineStr"/>
+      <c r="E22" s="66" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
+++ b/toi-uu/EIDE_Toi_uu_Agent_2026-10-06.xlsx
@@ -23,6 +23,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phương pháp &amp; nguồn" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 09-10-2026 (sau #32)" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 09-10-2026 (sau #27)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ 10-10-2026 (HẾT P0)" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Danh mục tối ưu'!$A$4:$S$110</definedName>
@@ -2116,13 +2117,13 @@
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B49:G49"/>
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="A43:G43"/>
+    <mergeCell ref="B53:G53"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B48:G48"/>
     <mergeCell ref="A45:G45"/>
   </mergeCells>
@@ -3876,6 +3877,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="31.5" customHeight="1" s="27">
       <c r="A4" s="31" t="inlineStr">
         <is>
@@ -12665,13 +12667,51 @@
           <t>M3-09</t>
         </is>
       </c>
-      <c r="Q93" s="48" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="R93" s="47" t="n"/>
-      <c r="S93" s="47" t="n"/>
+      <c r="Q93" s="65" t="inlineStr">
+        <is>
+          <t>Xong (một tiêu chí CHƯA đạt)</t>
+        </is>
+      </c>
+      <c r="R93" s="65" t="inlineStr">
+        <is>
+          <t>Claude (Opus 5)</t>
+        </is>
+      </c>
+      <c r="S93" s="65" t="inlineStr">
+        <is>
+          <t>Kế hoạch nói SAI hai chỗ. (1) Bước 4 coi _tu_hang_bang đã chạy được trên bảng datasheet — đo ra là KHÔNG: _MAU_THONG_SO đòi tên đã kèm hậu tố (V DD (max)) vì nó sinh cho đường theo DÒNG CHỮ, còn ô Parameter của bảng ghi VDD trần, nên nó không khớp nổi một hàng datasheet nào. Thêm _MAU_THONG_SO_BANG (tên trần, neo ^, hậu tố do cột cấp). (2) Bước 4 chỉ nói abs_max; bảng Absolute maximum cũng có cột Min (VDD = −0,5 V), đọc thành vdd.min là nói 'chip chạy được từ −0,5 V' → cả hai biên mang tiền tố abs_. NGOÀI phạm vi, làm vì là hệ quả trực tiếp: PHAM_VI_GOC + pham_vi_cua() — tám gốc khoá có thứ nguyên mà KHÔNG có khoảng nào, nên vddio = 6 000 V đi qua.</t>
+        </is>
+      </c>
+      <c r="T93" s="66" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="U93" s="66" t="inlineStr">
+        <is>
+          <t>DEV-363</t>
+        </is>
+      </c>
+      <c r="V93" s="66" t="inlineStr">
+        <is>
+          <t>2 125 → 2 160 xanh, 1 skip (35 ca mới trong tests/test_bang_pdf.py). Phá lại thì đỏ: lượt đầu 17/29 → 37/37. Mười hai chỗ LỌT ở lượt đầu: 11 lỗ thật trong tập CA KIỂM, 1 VÔ HIỆU (bảng một hàng: hang[1:] rỗng nên vòng lặp không chạy lần nào). Ba chỗ LỌT ở lượt hai cùng một hình dạng: chúng thăm dò ba luật thứ tự của pham_vi_cua, mà hai bảng số thật TRÙNG NHAU ở mọi khoá — ba luật đang được một sự tình cờ bảo vệ. Chữa bằng ca dựng bảng RIÊNG. Và một chỗ LỌT vì bản mẫu của tôi đặt điều kiện ở cột Conditions, trong khi ô tên lấy từ cột Parameter.</t>
+        </is>
+      </c>
+      <c r="W93" s="66" t="inlineStr">
+        <is>
+          <t>Đo 10/10/2026 trên 21 PDF THẬT của repo (293 trang), ba lượt: hàng bảng 0 → 109; Fact 18 → 18 (KHÔNG tăng, vì không tệp nào là datasheet — 21 tệp đều là bài báo và báo cáo); 0 trong 109 hàng bị nhận là bảng thông số (vế PRECISION, và là con số đúng); thời gian nạp ×4,3–4,7 (5,0 s → 23,8 s). Phép đo chỉ ra hai lỗi thật trong bản đầu: 41/150 hàng là rác (cid:NN) — mã glyph thô khi phông không có ToUnicode, để vào kho thì thành ĐƠN VỊ TRÍCH DẪN không ai đọc được; và một khung trình bày có viền thành 'bảng' (tiêu đề ['','','','Green)','Sáng, 1: Tắt)']). Vá cả hai: 150 → 109. Giấy phép CẢ CHUỖI phụ thuộc đã tra, không nhớ lại: pdfplumber MIT · pdfminer.six MIT · pillow MIT-CMU · pypdfium2 BSD-3/Apache-2.0 · cryptography Apache-2.0 OR BSD-3 · charset-normalizer MIT — không gói nào AGPL.</t>
+        </is>
+      </c>
+      <c r="X93" s="66" t="inlineStr">
+        <is>
+          <t>pdf_bang — TẮT (N-4: nó đổi TẬP FACT tác tử nhìn thấy). pdfplumber là phụ thuộc TUỲ CHỌN, nhóm [pdf]; thiếu nó thì xuống đường dòng chữ VÀ NÓI RA.</t>
+        </is>
+      </c>
+      <c r="Y93" s="66" t="inlineStr">
+        <is>
+          <t>Tiêu chí 'precision/recall trên bộ vàng M5-21' CHƯA ĐẠT: bộ vàng M5-21 chưa tồn tại (việc #85, P1), và repo không có một datasheet PDF nào để con số recall nói được điều gì. Bảng đo trên 21 PDF thật nói được vế precision và chi phí, KHÔNG nói được recall — không lấy nó làm tiêu chí đã đạt. Và một con số tôi TỰ ĐẶT đã bị ca kiểm cũ bác: biên dưới i2c.pullup đặt 10 Ω theo thói quen 'pull-up I2C thường 1–10 kΩ', mà ô bảng ghi 4R7 = 4,7 Ω — một giá trị điện trở có thật. Phanh độ lớn chỉ được chặn thứ KHÔNG THỂ, không chặn thứ hiếm.</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="79.5" customHeight="1" s="27">
       <c r="A94" s="46" t="inlineStr">
@@ -18271,6 +18311,485 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" style="27" min="1" max="1"/>
+    <col width="22" customWidth="1" style="27" min="2" max="2"/>
+    <col width="24" customWidth="1" style="27" min="3" max="3"/>
+    <col width="46" customWidth="1" style="27" min="4" max="4"/>
+    <col width="40" customWidth="1" style="27" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="66" t="inlineStr">
+        <is>
+          <t>TIẾN ĐỘ CHIẾN DỊCH TỐI ƯU TÁC TỬ — HẾT ƯU TIÊN CAO NHẤT (P0)</t>
+        </is>
+      </c>
+      <c r="B1" s="66" t="inlineStr"/>
+      <c r="C1" s="66" t="inlineStr"/>
+      <c r="D1" s="66" t="inlineStr"/>
+      <c r="E1" s="66" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="66" t="inlineStr">
+        <is>
+          <t>Mốc: 10/10/2026 · nhánh main · 30/30 việc P0 đã xong</t>
+        </is>
+      </c>
+      <c r="B2" s="66" t="inlineStr"/>
+      <c r="C2" s="66" t="inlineStr"/>
+      <c r="D2" s="66" t="inlineStr"/>
+      <c r="E2" s="66" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="66" t="inlineStr"/>
+      <c r="B3" s="66" t="n"/>
+      <c r="C3" s="66" t="n"/>
+      <c r="D3" s="66" t="n"/>
+      <c r="E3" s="66" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="66" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="B4" s="66" t="inlineStr">
+        <is>
+          <t>Trước #34</t>
+        </is>
+      </c>
+      <c r="C4" s="66" t="inlineStr">
+        <is>
+          <t>Sau #34</t>
+        </is>
+      </c>
+      <c r="D4" s="66" t="inlineStr">
+        <is>
+          <t>Nguồn số</t>
+        </is>
+      </c>
+      <c r="E4" s="66" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="66" t="inlineStr">
+        <is>
+          <t>Việc đã xong / 106</t>
+        </is>
+      </c>
+      <c r="B5" s="66" t="n">
+        <v>33</v>
+      </c>
+      <c r="C5" s="66" t="n">
+        <v>34</v>
+      </c>
+      <c r="D5" s="66" t="inlineStr">
+        <is>
+          <t>đếm ☑ trong KE-HOACH-SUA-VA-KIEM-THU.md</t>
+        </is>
+      </c>
+      <c r="E5" s="66" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="66" t="inlineStr">
+        <is>
+          <t>P0 xong / 30</t>
+        </is>
+      </c>
+      <c r="B6" s="66" t="inlineStr">
+        <is>
+          <t>29/30</t>
+        </is>
+      </c>
+      <c r="C6" s="66" t="inlineStr">
+        <is>
+          <t>30/30</t>
+        </is>
+      </c>
+      <c r="D6" s="66" t="inlineStr">
+        <is>
+          <t>cột Ưu tiên của kế hoạch</t>
+        </is>
+      </c>
+      <c r="E6" s="66" t="inlineStr">
+        <is>
+          <t>HẾT P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="66" t="inlineStr">
+        <is>
+          <t>P1 xong / 54</t>
+        </is>
+      </c>
+      <c r="B7" s="66" t="inlineStr">
+        <is>
+          <t>3/54</t>
+        </is>
+      </c>
+      <c r="C7" s="66" t="inlineStr">
+        <is>
+          <t>3/54</t>
+        </is>
+      </c>
+      <c r="D7" s="66" t="inlineStr">
+        <is>
+          <t>cột Ưu tiên</t>
+        </is>
+      </c>
+      <c r="E7" s="66" t="inlineStr">
+        <is>
+          <t>chưa mở — cần anh Công quyết</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="66" t="inlineStr">
+        <is>
+          <t>P2 xong / 20</t>
+        </is>
+      </c>
+      <c r="B8" s="66" t="inlineStr">
+        <is>
+          <t>1/20</t>
+        </is>
+      </c>
+      <c r="C8" s="66" t="inlineStr">
+        <is>
+          <t>1/20</t>
+        </is>
+      </c>
+      <c r="D8" s="66" t="inlineStr">
+        <is>
+          <t>cột Ưu tiên</t>
+        </is>
+      </c>
+      <c r="E8" s="66" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="66" t="inlineStr">
+        <is>
+          <t>P3 xong / 2</t>
+        </is>
+      </c>
+      <c r="B9" s="66" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="C9" s="66" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="D9" s="66" t="inlineStr">
+        <is>
+          <t>cột Ưu tiên</t>
+        </is>
+      </c>
+      <c r="E9" s="66" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="66" t="inlineStr">
+        <is>
+          <t>Ca kiểm xanh</t>
+        </is>
+      </c>
+      <c r="B10" s="66" t="n">
+        <v>2125</v>
+      </c>
+      <c r="C10" s="66" t="n">
+        <v>2160</v>
+      </c>
+      <c r="D10" s="66" t="inlineStr">
+        <is>
+          <t>pytest -q</t>
+        </is>
+      </c>
+      <c r="E10" s="66" t="inlineStr">
+        <is>
+          <t>1 skip, 0 đỏ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="66" t="inlineStr">
+        <is>
+          <t>Công cụ</t>
+        </is>
+      </c>
+      <c r="B11" s="66" t="n">
+        <v>135</v>
+      </c>
+      <c r="C11" s="66" t="n">
+        <v>135</v>
+      </c>
+      <c r="D11" s="66" t="inlineStr">
+        <is>
+          <t>build_registry() với mọi cờ BẬT</t>
+        </is>
+      </c>
+      <c r="E11" s="66" t="inlineStr">
+        <is>
+          <t>việc này mở rộng doc.load, không thêm công cụ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="66" t="inlineStr">
+        <is>
+          <t>Cờ tính năng</t>
+        </is>
+      </c>
+      <c r="B12" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" s="66" t="inlineStr">
+        <is>
+          <t>dataclasses.fields(Features)</t>
+        </is>
+      </c>
+      <c r="E12" s="66" t="inlineStr">
+        <is>
+          <t>cả 14 mặc định TẮT (N-4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="66" t="inlineStr">
+        <is>
+          <t>Phụ thuộc tuỳ chọn</t>
+        </is>
+      </c>
+      <c r="B13" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="66" t="inlineStr">
+        <is>
+          <t>pdfplumber&gt;=0.11</t>
+        </is>
+      </c>
+      <c r="D13" s="66" t="inlineStr">
+        <is>
+          <t>pyproject.toml [pdf]</t>
+        </is>
+      </c>
+      <c r="E13" s="66" t="inlineStr">
+        <is>
+          <t>anh Công duyệt cài 10/10/2026 (N-10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="66" t="inlineStr">
+        <is>
+          <t>Mục DEV-LOG</t>
+        </is>
+      </c>
+      <c r="B14" s="66" t="inlineStr">
+        <is>
+          <t>DEV-362</t>
+        </is>
+      </c>
+      <c r="C14" s="66" t="inlineStr">
+        <is>
+          <t>DEV-363</t>
+        </is>
+      </c>
+      <c r="D14" s="66" t="inlineStr">
+        <is>
+          <t>docs/md/EIDE-DEV-LOG.md</t>
+        </is>
+      </c>
+      <c r="E14" s="66" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="66" t="inlineStr"/>
+      <c r="B15" s="66" t="n"/>
+      <c r="C15" s="66" t="n"/>
+      <c r="D15" s="66" t="n"/>
+      <c r="E15" s="66" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="66" t="inlineStr">
+        <is>
+          <t>ĐO CỜ pdf_bang TRÊN 21 PDF THẬT CỦA REPO (293 trang) — 10/10/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="66" t="inlineStr"/>
+      <c r="C16" s="66" t="inlineStr"/>
+      <c r="D16" s="66" t="inlineStr"/>
+      <c r="E16" s="66" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="66" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="B17" s="66" t="inlineStr">
+        <is>
+          <t>cờ TẮT</t>
+        </is>
+      </c>
+      <c r="C17" s="66" t="inlineStr">
+        <is>
+          <t>cờ BẬT</t>
+        </is>
+      </c>
+      <c r="D17" s="66" t="inlineStr">
+        <is>
+          <t>Nói lên điều gì</t>
+        </is>
+      </c>
+      <c r="E17" s="66" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="66" t="inlineStr">
+        <is>
+          <t>Hàng bảng (đơn vị trích dẫn)</t>
+        </is>
+      </c>
+      <c r="B18" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="66" t="n">
+        <v>109</v>
+      </c>
+      <c r="D18" s="66" t="inlineStr">
+        <is>
+          <t>đường bảng đã chạy trên PDF</t>
+        </is>
+      </c>
+      <c r="E18" s="66" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="66" t="inlineStr">
+        <is>
+          <t>Fact trích được</t>
+        </is>
+      </c>
+      <c r="B19" s="66" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" s="66" t="n">
+        <v>18</v>
+      </c>
+      <c r="D19" s="66" t="inlineStr">
+        <is>
+          <t>KHÔNG tăng — không tệp nào là datasheet</t>
+        </is>
+      </c>
+      <c r="E19" s="66" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="66" t="inlineStr">
+        <is>
+          <t>Hàng bị nhận là bảng thông số</t>
+        </is>
+      </c>
+      <c r="B20" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="66" t="inlineStr">
+        <is>
+          <t>vế PRECISION, và là con số ĐÚNG</t>
+        </is>
+      </c>
+      <c r="E20" s="66" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="66" t="inlineStr">
+        <is>
+          <t>Thời gian nạp (3 lượt)</t>
+        </is>
+      </c>
+      <c r="B21" s="66" t="inlineStr">
+        <is>
+          <t>5,0 · 5,5 · 5,4 s</t>
+        </is>
+      </c>
+      <c r="C21" s="66" t="inlineStr">
+        <is>
+          <t>23,8 · 23,6 · 23,9 s</t>
+        </is>
+      </c>
+      <c r="D21" s="66" t="inlineStr">
+        <is>
+          <t>×4,3–4,7 — chi phí thật, nói ra</t>
+        </is>
+      </c>
+      <c r="E21" s="66" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="66" t="inlineStr">
+        <is>
+          <t>Hàng rác (cid:NN) đã lọc</t>
+        </is>
+      </c>
+      <c r="B22" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" s="66" t="inlineStr">
+        <is>
+          <t>41 / 150</t>
+        </is>
+      </c>
+      <c r="D22" s="66" t="inlineStr">
+        <is>
+          <t>mã glyph thô khi phông không có ToUnicode</t>
+        </is>
+      </c>
+      <c r="E22" s="66" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="66" t="inlineStr"/>
+      <c r="B23" s="66" t="n"/>
+      <c r="C23" s="66" t="n"/>
+      <c r="D23" s="66" t="n"/>
+      <c r="E23" s="66" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="66" t="inlineStr">
+        <is>
+          <t>CÒN LẠI: 72 việc, tất cả P1 trở xuống — 51 P1 · 19 P2 · 2 P3. Chưa ai yêu cầu mở.</t>
+        </is>
+      </c>
+      <c r="B24" s="66" t="inlineStr"/>
+      <c r="C24" s="66" t="inlineStr"/>
+      <c r="D24" s="66" t="inlineStr"/>
+      <c r="E24" s="66" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
